--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A009742C-F46A-458A-9CA2-1E6692EC7991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DFDFE0-CB00-4FA5-9296-0C1571CFBE03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
     <definedName name="簽退時間">'[1]條碼_簽到表 (v2)'!$L$2:$L$452</definedName>
     <definedName name="簽退條碼">'[1]條碼_簽到表 (v2)'!$I$2:$I$452</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="185">
   <si>
     <t>序號</t>
   </si>
@@ -404,10 +404,6 @@
   </si>
   <si>
     <t>114年3月25日校教師評審委員會議通過</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>(請款額度依學雜費繳費單申請,上限60000元/學期)</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -1007,6 +1003,26 @@
   </si>
   <si>
     <t>跨領域教育中心</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>參加國際研討會並發表(國內)_研習差旅費</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>參加國際研討會並發表(國內)_研習報名(註冊)費</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>創新教學115-1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>115年2月23日教學發展委員會會議通過</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>115年9月1日教學發展委員會會議通過</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -10244,7 +10260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BAC909-8D45-4443-AECB-1592B366F0B1}">
-  <dimension ref="A1:H235"/>
+  <dimension ref="A1:H257"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="4.75" bestFit="1" customWidth="1"/>
@@ -10289,19 +10305,19 @@
         <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F2" s="11">
         <v>3500</v>
       </c>
       <c r="G2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -10312,19 +10328,19 @@
         <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F3" s="11">
         <v>3500</v>
       </c>
       <c r="G3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -10335,19 +10351,19 @@
         <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>86</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F4" s="11">
         <v>5100</v>
       </c>
       <c r="G4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -10358,19 +10374,19 @@
         <v>115</v>
       </c>
       <c r="C5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D5" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F5" s="11">
         <v>3500</v>
       </c>
       <c r="G5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -10381,22 +10397,22 @@
         <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F6" s="2">
         <v>29000</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -10407,22 +10423,22 @@
         <v>115</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F7" s="2">
         <v>2000</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -10433,19 +10449,19 @@
         <v>115</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F8" s="11">
         <v>5000</v>
       </c>
       <c r="G8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -10485,13 +10501,13 @@
         <v>23</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F10" s="11">
         <v>3500</v>
       </c>
       <c r="G10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -10554,13 +10570,13 @@
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F13" s="11">
         <v>3700</v>
       </c>
       <c r="G13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -10623,13 +10639,13 @@
         <v>13</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F16" s="11">
         <v>500</v>
       </c>
       <c r="G16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -10640,22 +10656,22 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
         <v>23</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F17" s="2">
         <v>29636</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
@@ -10666,22 +10682,22 @@
         <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
         <v>23</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F18" s="2">
         <v>11068</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
@@ -10692,19 +10708,19 @@
         <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
         <v>23</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F19" s="11">
         <v>3900</v>
       </c>
       <c r="G19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
@@ -10767,16 +10783,16 @@
         <v>23</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F22" s="2">
         <v>30850</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H22" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
@@ -10793,16 +10809,16 @@
         <v>23</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F23" s="2">
         <v>12726</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
@@ -10819,13 +10835,13 @@
         <v>23</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F24" s="11">
         <v>7600</v>
       </c>
       <c r="G24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
@@ -10836,19 +10852,19 @@
         <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D25" t="s">
         <v>23</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F25" s="11">
         <v>3500</v>
       </c>
       <c r="G25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
@@ -10859,19 +10875,19 @@
         <v>115</v>
       </c>
       <c r="C26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D26" t="s">
         <v>23</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F26" s="11">
         <v>3500</v>
       </c>
       <c r="G26" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
@@ -10957,13 +10973,13 @@
         <v>16</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F30" s="11">
         <v>10000</v>
       </c>
       <c r="G30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
@@ -11026,13 +11042,13 @@
         <v>13</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F33" s="11">
         <v>10000</v>
       </c>
       <c r="G33" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
@@ -11095,13 +11111,13 @@
         <v>16</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F36" s="11">
         <v>10000</v>
       </c>
       <c r="G36" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
@@ -11112,19 +11128,19 @@
         <v>115</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
-      </c>
-      <c r="D37" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>78</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F37" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G37" t="s">
-        <v>168</v>
+        <v>182</v>
+      </c>
+      <c r="F37">
+        <v>45000</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
@@ -11135,19 +11151,19 @@
         <v>115</v>
       </c>
       <c r="C38" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D38" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F38" s="11">
-        <v>3900</v>
+        <v>10000</v>
       </c>
       <c r="G38" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
@@ -11157,20 +11173,20 @@
       <c r="B39" s="1">
         <v>115</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>16</v>
+      <c r="C39" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39" t="s">
+        <v>23</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F39" s="2">
-        <v>16571</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>84</v>
+        <v>169</v>
+      </c>
+      <c r="F39" s="11">
+        <v>3900</v>
+      </c>
+      <c r="G39" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
@@ -11180,23 +11196,26 @@
       <c r="B40" s="1">
         <v>115</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="F40" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G40" t="s">
-        <v>168</v>
+        <v>83</v>
+      </c>
+      <c r="F40" s="2">
+        <v>16571</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>40</v>
+      </c>
       <c r="B41" s="1">
         <v>115</v>
       </c>
@@ -11206,20 +11225,20 @@
       <c r="D41" t="s">
         <v>16</v>
       </c>
-      <c r="E41" t="s">
-        <v>179</v>
+      <c r="E41" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="F41" s="11">
         <v>10000</v>
       </c>
-      <c r="G41" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H41" t="s">
-        <v>174</v>
+      <c r="G41" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>41</v>
+      </c>
       <c r="B42" s="1">
         <v>115</v>
       </c>
@@ -11230,19 +11249,22 @@
         <v>16</v>
       </c>
       <c r="E42" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F42" s="11">
         <v>10000</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H42" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>42</v>
+      </c>
       <c r="B43" s="1">
         <v>115</v>
       </c>
@@ -11253,19 +11275,22 @@
         <v>16</v>
       </c>
       <c r="E43" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F43" s="11">
         <v>10000</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H43" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>43</v>
+      </c>
       <c r="B44" s="1">
         <v>115</v>
       </c>
@@ -11276,19 +11301,22 @@
         <v>16</v>
       </c>
       <c r="E44" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F44" s="11">
         <v>10000</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H44" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>44</v>
+      </c>
       <c r="B45" s="1">
         <v>115</v>
       </c>
@@ -11299,358 +11327,361 @@
         <v>16</v>
       </c>
       <c r="E45" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F45" s="11">
         <v>10000</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H45" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B46" s="1">
         <v>115</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F46" s="2">
-        <v>31500</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>8</v>
+      <c r="C46" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" t="s">
+        <v>178</v>
+      </c>
+      <c r="F46" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H46" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B47" s="1">
         <v>115</v>
       </c>
-      <c r="C47" t="s">
-        <v>118</v>
-      </c>
-      <c r="D47" t="s">
-        <v>29</v>
+      <c r="C47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F47" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G47" t="s">
-        <v>168</v>
+        <v>21</v>
+      </c>
+      <c r="F47" s="2">
+        <v>31500</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B48" s="1">
         <v>115</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>23</v>
+      <c r="C48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>8</v>
+        <v>182</v>
+      </c>
+      <c r="F48">
+        <v>25500</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B49" s="1">
         <v>115</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>23</v>
+      <c r="C49" t="s">
+        <v>117</v>
+      </c>
+      <c r="D49" t="s">
+        <v>29</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F49" s="2">
-        <v>20564</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F49" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G49" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B50" s="1">
         <v>115</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E50" s="8" t="s">
-        <v>87</v>
+      <c r="E50" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F50" s="2">
-        <v>45000</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>88</v>
+        <v>59500</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B51" s="1">
         <v>115</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F51" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G51" t="s">
-        <v>168</v>
+        <v>21</v>
+      </c>
+      <c r="F51" s="2">
+        <v>20564</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B52" s="1">
         <v>115</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>7</v>
+      <c r="C52" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" t="s">
+        <v>23</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="F52" s="2">
-        <v>51750</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>8</v>
+        <v>45000</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B53" s="1">
         <v>115</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>13</v>
+      <c r="C53" t="s">
+        <v>22</v>
+      </c>
+      <c r="D53" t="s">
+        <v>23</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F53" s="2">
-        <v>47687</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>84</v>
+        <v>169</v>
+      </c>
+      <c r="F53" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G53" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B54" s="1">
         <v>115</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
-      </c>
-      <c r="D54" t="s">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F54" s="11">
-        <v>7200</v>
-      </c>
-      <c r="G54" t="s">
-        <v>168</v>
+        <v>182</v>
+      </c>
+      <c r="F54">
+        <v>17479</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B55" s="1">
         <v>115</v>
       </c>
-      <c r="C55" t="s">
-        <v>134</v>
-      </c>
-      <c r="D55" t="s">
-        <v>23</v>
+      <c r="C55" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F55" s="11">
-        <v>1500</v>
-      </c>
-      <c r="G55" t="s">
-        <v>168</v>
+        <v>7</v>
+      </c>
+      <c r="F55" s="2">
+        <v>51750</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B56" s="1">
         <v>115</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="F56" s="2">
-        <v>42500</v>
+        <v>47687</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B57" s="1">
         <v>115</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>16</v>
+      <c r="C57" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" t="s">
+        <v>13</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F57" s="11">
+        <v>7200</v>
+      </c>
+      <c r="G57" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B58" s="1">
         <v>115</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F58" s="11">
-        <v>5600</v>
+        <v>1500</v>
       </c>
       <c r="G58" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B59" s="1">
         <v>115</v>
       </c>
-      <c r="C59" t="s">
-        <v>135</v>
-      </c>
-      <c r="D59" t="s">
-        <v>23</v>
+      <c r="C59" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F59" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G59" t="s">
-        <v>168</v>
+        <v>21</v>
+      </c>
+      <c r="F59" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B60" s="1">
         <v>115</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F60" s="2">
-        <v>17000</v>
+        <v>63000</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>8</v>
@@ -11658,373 +11689,358 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B61" s="1">
         <v>115</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>20</v>
+      <c r="C61" t="s">
+        <v>25</v>
+      </c>
+      <c r="D61" t="s">
+        <v>16</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61" s="2">
-        <v>60000</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F61" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G61" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B62" s="1">
         <v>115</v>
       </c>
       <c r="C62" t="s">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="D62" t="s">
-        <v>86</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F62" s="2">
-        <v>47500</v>
-      </c>
-      <c r="G62" s="9" t="s">
-        <v>88</v>
+        <v>23</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F62" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G62" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B63" s="1">
         <v>115</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F63" s="11">
-        <v>8400</v>
-      </c>
-      <c r="G63" t="s">
-        <v>168</v>
+        <v>21</v>
+      </c>
+      <c r="F63" s="2">
+        <v>17000</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B64" s="1">
         <v>115</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>87</v>
+        <v>20</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="F64" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G64" s="9" t="s">
-        <v>88</v>
+        <v>60000</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B65" s="1">
         <v>115</v>
       </c>
       <c r="C65" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="D65" t="s">
-        <v>23</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>171</v>
+        <v>86</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="F65" s="2">
-        <v>30850</v>
-      </c>
-      <c r="G65" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H65" t="s">
-        <v>108</v>
+        <v>47500</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B66" s="1">
         <v>115</v>
       </c>
       <c r="C66" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="D66" t="s">
-        <v>23</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F66" s="2">
-        <v>9696</v>
-      </c>
-      <c r="G66" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H66" t="s">
-        <v>108</v>
+        <v>20</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F66" s="11">
+        <v>8400</v>
+      </c>
+      <c r="G66" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B67" s="1">
         <v>115</v>
       </c>
       <c r="C67" t="s">
-        <v>85</v>
-      </c>
-      <c r="D67" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F67" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G67" t="s">
-        <v>168</v>
+        <v>182</v>
+      </c>
+      <c r="F67">
+        <v>43200</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B68" s="1">
         <v>115</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>7</v>
+      <c r="E68" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="F68" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>8</v>
+        <v>50000</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B69" s="1">
         <v>115</v>
       </c>
-      <c r="C69" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>94</v>
+      <c r="C69" t="s">
+        <v>85</v>
+      </c>
+      <c r="D69" t="s">
+        <v>23</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>170</v>
       </c>
       <c r="F69" s="2">
-        <v>32320</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>92</v>
+        <v>30850</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>116</v>
       </c>
       <c r="H69" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B70" s="1">
         <v>115</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D70" s="1" t="s">
+      <c r="C70" t="s">
+        <v>85</v>
+      </c>
+      <c r="D70" t="s">
         <v>23</v>
       </c>
-      <c r="E70" s="3" t="s">
-        <v>81</v>
+      <c r="E70" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="F70" s="2">
-        <v>140000</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>82</v>
+        <v>9696</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H70" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B71" s="1">
         <v>115</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D71" s="1" t="s">
+      <c r="C71" t="s">
+        <v>85</v>
+      </c>
+      <c r="D71" t="s">
         <v>23</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F71" s="2">
-        <v>28884</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>84</v>
+        <v>169</v>
+      </c>
+      <c r="F71" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G71" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B72" s="1">
         <v>115</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E72" s="10" t="s">
-        <v>171</v>
+      <c r="E72" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F72" s="2">
-        <v>30850</v>
-      </c>
-      <c r="G72" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H72" t="s">
-        <v>101</v>
+        <v>59500</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B73" s="1">
         <v>115</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F73" s="2">
+        <v>32320</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" s="1">
+        <v>115</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D74" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E73" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F73" s="2">
-        <v>19150</v>
-      </c>
-      <c r="G73" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H73" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A74">
-        <v>68</v>
-      </c>
-      <c r="B74" s="1">
-        <v>115</v>
-      </c>
-      <c r="C74" t="s">
-        <v>27</v>
-      </c>
-      <c r="D74" t="s">
-        <v>23</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>172</v>
+      <c r="E74" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F74" s="2">
-        <v>12936</v>
-      </c>
-      <c r="G74" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H74" t="s">
-        <v>101</v>
+        <v>140000</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B75" s="1">
         <v>115</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E75" s="10" t="s">
-        <v>172</v>
+      <c r="E75" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F75" s="2">
-        <v>31462</v>
-      </c>
-      <c r="G75" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H75" t="s">
-        <v>106</v>
+        <v>28884</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B76" s="1">
         <v>115</v>
@@ -12035,1107 +12051,1119 @@
       <c r="D76" t="s">
         <v>23</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E76" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="F76" s="11">
-        <v>3700</v>
-      </c>
-      <c r="G76" t="s">
-        <v>168</v>
+      <c r="F76" s="2">
+        <v>30850</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H76" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B77" s="1">
         <v>115</v>
       </c>
       <c r="C77" t="s">
-        <v>136</v>
+        <v>27</v>
       </c>
       <c r="D77" t="s">
         <v>23</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E77" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="F77" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G77" t="s">
-        <v>168</v>
+      <c r="F77" s="2">
+        <v>19150</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H77" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B78" s="1">
         <v>115</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>7</v>
+      <c r="C78" t="s">
+        <v>27</v>
+      </c>
+      <c r="D78" t="s">
+        <v>23</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="F78" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>12936</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H78" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B79" s="1">
         <v>115</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>81</v>
+      <c r="C79" t="s">
+        <v>27</v>
+      </c>
+      <c r="D79" t="s">
+        <v>23</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="F79" s="2">
-        <v>150000</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>82</v>
+        <v>31462</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H79" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B80" s="1">
         <v>115</v>
       </c>
       <c r="C80" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D80" t="s">
-        <v>29</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F80" s="2">
-        <v>17789</v>
-      </c>
-      <c r="G80" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H80" t="s">
-        <v>107</v>
+        <v>23</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F80" s="11">
+        <v>3700</v>
+      </c>
+      <c r="G80" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B81" s="1">
         <v>115</v>
       </c>
       <c r="C81" t="s">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="D81" t="s">
-        <v>29</v>
-      </c>
-      <c r="E81" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F81" s="2">
-        <v>8085</v>
-      </c>
-      <c r="G81" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H81" t="s">
-        <v>107</v>
+        <v>23</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F81" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G81" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" s="1">
+        <v>115</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F82" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" s="1">
+        <v>115</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B82" s="1">
-        <v>115</v>
-      </c>
-      <c r="C82" t="s">
-        <v>28</v>
-      </c>
-      <c r="D82" t="s">
-        <v>29</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F82" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G82" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A83">
-        <v>77</v>
-      </c>
-      <c r="B83" s="1">
-        <v>115</v>
-      </c>
-      <c r="C83" t="s">
-        <v>132</v>
-      </c>
-      <c r="D83" t="s">
-        <v>23</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F83" s="11">
-        <v>8700</v>
-      </c>
-      <c r="G83" t="s">
-        <v>168</v>
+      <c r="E83" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F83" s="2">
+        <v>150000</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B84" s="1">
         <v>115</v>
       </c>
       <c r="C84" t="s">
-        <v>141</v>
+        <v>28</v>
       </c>
       <c r="D84" t="s">
-        <v>23</v>
-      </c>
-      <c r="E84" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="F84" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G84" t="s">
-        <v>168</v>
+      <c r="F84" s="2">
+        <v>17789</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H84" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B85" s="1">
         <v>115</v>
       </c>
       <c r="C85" t="s">
-        <v>137</v>
+        <v>28</v>
       </c>
       <c r="D85" t="s">
-        <v>23</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F85" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G85" t="s">
-        <v>168</v>
+        <v>29</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F85" s="2">
+        <v>8085</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H85" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B86" s="1">
         <v>115</v>
       </c>
       <c r="C86" t="s">
-        <v>125</v>
+        <v>28</v>
       </c>
       <c r="D86" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F86" s="11">
-        <v>9600</v>
+        <v>10000</v>
       </c>
       <c r="G86" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B87" s="1">
         <v>115</v>
       </c>
       <c r="C87" t="s">
-        <v>138</v>
-      </c>
-      <c r="D87" t="s">
-        <v>23</v>
+        <v>28</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F87" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G87" t="s">
-        <v>168</v>
+        <v>182</v>
+      </c>
+      <c r="F87">
+        <v>42500</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B88" s="1">
         <v>115</v>
       </c>
       <c r="C88" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D88" t="s">
         <v>23</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F88" s="11">
-        <v>10000</v>
+        <v>8700</v>
       </c>
       <c r="G88" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B89" s="1">
         <v>115</v>
       </c>
       <c r="C89" t="s">
-        <v>162</v>
-      </c>
-      <c r="D89" s="10" t="s">
-        <v>180</v>
+        <v>140</v>
+      </c>
+      <c r="D89" t="s">
+        <v>23</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F89" s="11">
-        <v>400</v>
+        <v>3500</v>
       </c>
       <c r="G89" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B90" s="1">
         <v>115</v>
       </c>
       <c r="C90" t="s">
-        <v>161</v>
-      </c>
-      <c r="D90" s="10" t="s">
-        <v>180</v>
+        <v>136</v>
+      </c>
+      <c r="D90" t="s">
+        <v>23</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F90" s="11">
-        <v>500</v>
+        <v>3500</v>
       </c>
       <c r="G90" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B91" s="1">
         <v>115</v>
       </c>
       <c r="C91" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="D91" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F91" s="11">
-        <v>8700</v>
+        <v>9600</v>
       </c>
       <c r="G91" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B92" s="1">
         <v>115</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>60</v>
+      <c r="C92" t="s">
+        <v>124</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F92" s="2">
-        <v>11185</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>84</v>
+        <v>182</v>
+      </c>
+      <c r="F92">
+        <v>30000</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B93" s="1">
         <v>115</v>
       </c>
       <c r="C93" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="D93" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F93" s="11">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="G93" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B94" s="1">
         <v>115</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D94" s="1" t="s">
+      <c r="C94" t="s">
+        <v>138</v>
+      </c>
+      <c r="D94" t="s">
         <v>23</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F94" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F94" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G94" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B95" s="1">
         <v>115</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>23</v>
+      <c r="C95" t="s">
+        <v>161</v>
+      </c>
+      <c r="D95" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F95" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F95" s="11">
+        <v>400</v>
+      </c>
+      <c r="G95" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B96" s="1">
         <v>115</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>23</v>
+      <c r="C96" t="s">
+        <v>161</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F96" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>8</v>
+        <v>182</v>
+      </c>
+      <c r="F96">
+        <v>39613</v>
+      </c>
+      <c r="G96" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B97" s="1">
         <v>115</v>
       </c>
       <c r="C97" t="s">
-        <v>30</v>
-      </c>
-      <c r="D97" t="s">
-        <v>23</v>
+        <v>160</v>
+      </c>
+      <c r="D97" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F97" s="11">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="G97" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B98" s="1">
         <v>115</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D98" s="1" t="s">
+      <c r="C98" t="s">
+        <v>139</v>
+      </c>
+      <c r="D98" t="s">
         <v>23</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F98" s="2">
-        <v>70000</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F98" s="11">
+        <v>8700</v>
+      </c>
+      <c r="G98" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B99" s="1">
         <v>115</v>
       </c>
-      <c r="C99" t="s">
-        <v>31</v>
-      </c>
-      <c r="D99" t="s">
-        <v>23</v>
-      </c>
-      <c r="E99" s="8" t="s">
-        <v>87</v>
+      <c r="C99" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F99" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G99" s="9" t="s">
-        <v>88</v>
+        <v>11185</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B100" s="1">
         <v>115</v>
       </c>
       <c r="C100" t="s">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="D100" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F100" s="11">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="G100" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B101" s="1">
         <v>115</v>
       </c>
-      <c r="C101" t="s">
-        <v>97</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="C101" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E101" s="10" t="s">
-        <v>171</v>
+      <c r="E101" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F101" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G101" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H101" t="s">
-        <v>111</v>
+        <v>59500</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B102" s="1">
         <v>115</v>
       </c>
-      <c r="C102" t="s">
-        <v>97</v>
-      </c>
-      <c r="D102" t="s">
+      <c r="C102" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E102" s="10" t="s">
-        <v>172</v>
+      <c r="E102" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="F102" s="2">
-        <v>38015</v>
-      </c>
-      <c r="G102" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H102" t="s">
-        <v>111</v>
+        <v>63000</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B103" s="1">
         <v>115</v>
       </c>
-      <c r="C103" t="s">
-        <v>97</v>
-      </c>
-      <c r="D103" s="10" t="s">
-        <v>64</v>
+      <c r="C103" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F103" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G103" t="s">
-        <v>168</v>
+        <v>21</v>
+      </c>
+      <c r="F103" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B104" s="1">
         <v>115</v>
       </c>
       <c r="C104" t="s">
-        <v>128</v>
+        <v>30</v>
       </c>
       <c r="D104" t="s">
         <v>23</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F104" s="11">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="G104" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B105" s="1">
         <v>115</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>13</v>
+      <c r="C105" t="s">
+        <v>30</v>
+      </c>
+      <c r="D105" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F105" s="2">
-        <v>56000</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>8</v>
+        <v>182</v>
+      </c>
+      <c r="F105">
+        <v>12000</v>
+      </c>
+      <c r="G105" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B106" s="1">
         <v>115</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F106" s="2">
-        <v>39355</v>
+        <v>70000</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>84</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B107" s="1">
         <v>115</v>
       </c>
       <c r="C107" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D107" t="s">
-        <v>13</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F107" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G107" t="s">
-        <v>168</v>
+        <v>23</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F107" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G107" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B108" s="1">
         <v>115</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>10</v>
+      <c r="C108" t="s">
+        <v>31</v>
+      </c>
+      <c r="D108" t="s">
+        <v>23</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F108" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F108" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G108" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B109" s="1">
         <v>115</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>7</v>
+      <c r="C109" t="s">
+        <v>96</v>
+      </c>
+      <c r="D109" t="s">
+        <v>23</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>170</v>
       </c>
       <c r="F109" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>50000</v>
+      </c>
+      <c r="G109" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H109" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B110" s="1">
         <v>115</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D110" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>81</v>
+      <c r="C110" t="s">
+        <v>96</v>
+      </c>
+      <c r="D110" t="s">
+        <v>23</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="F110" s="2">
-        <v>106530</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>82</v>
+        <v>38015</v>
+      </c>
+      <c r="G110" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H110" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B111" s="1">
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>33</v>
-      </c>
-      <c r="D111" t="s">
-        <v>10</v>
-      </c>
-      <c r="E111" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F111" s="2">
-        <v>19942</v>
-      </c>
-      <c r="G111" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H111" t="s">
-        <v>109</v>
+        <v>96</v>
+      </c>
+      <c r="D111" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F111" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G111" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B112" s="1">
         <v>115</v>
       </c>
       <c r="C112" t="s">
+        <v>127</v>
+      </c>
+      <c r="D112" t="s">
+        <v>23</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F112" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G112" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" s="1">
+        <v>115</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F113" s="2">
+        <v>56000</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" s="1">
+        <v>115</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F114" s="2">
+        <v>39355</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" s="1">
+        <v>115</v>
+      </c>
+      <c r="C115" t="s">
+        <v>32</v>
+      </c>
+      <c r="D115" t="s">
+        <v>13</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F115" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G115" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" s="1">
+        <v>115</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D116" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E112" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F112" s="2">
+      <c r="E116" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F116" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" s="1">
+        <v>115</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F117" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" s="1">
+        <v>115</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F118" s="2">
+        <v>106530</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" s="1">
+        <v>115</v>
+      </c>
+      <c r="C119" t="s">
+        <v>33</v>
+      </c>
+      <c r="D119" t="s">
+        <v>10</v>
+      </c>
+      <c r="E119" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F119" s="2">
+        <v>19942</v>
+      </c>
+      <c r="G119" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H119" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" s="1">
+        <v>115</v>
+      </c>
+      <c r="C120" t="s">
+        <v>33</v>
+      </c>
+      <c r="D120" t="s">
+        <v>10</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F120" s="2">
         <v>16447</v>
       </c>
-      <c r="G112" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H112" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="A113">
-        <v>107</v>
-      </c>
-      <c r="B113" s="1">
-        <v>115</v>
-      </c>
-      <c r="C113" s="1" t="s">
+      <c r="G120" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H120" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" s="1">
+        <v>115</v>
+      </c>
+      <c r="C121" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D113" s="4" t="s">
+      <c r="D121" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F113" s="2">
-        <v>117750</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A114">
-        <v>108</v>
-      </c>
-      <c r="B114" s="1">
-        <v>115</v>
-      </c>
-      <c r="C114" t="s">
-        <v>74</v>
-      </c>
-      <c r="D114" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F114" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G114" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A115">
-        <v>109</v>
-      </c>
-      <c r="B115" s="1">
-        <v>115</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F115" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A116">
-        <v>110</v>
-      </c>
-      <c r="B116" s="1">
-        <v>115</v>
-      </c>
-      <c r="C116" t="s">
-        <v>34</v>
-      </c>
-      <c r="D116" t="s">
-        <v>29</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F116" s="11">
-        <v>6000</v>
-      </c>
-      <c r="G116" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A117">
-        <v>111</v>
-      </c>
-      <c r="B117" s="1">
-        <v>115</v>
-      </c>
-      <c r="C117" t="s">
-        <v>147</v>
-      </c>
-      <c r="D117" t="s">
-        <v>23</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F117" s="11">
-        <v>6400</v>
-      </c>
-      <c r="G117" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A118">
-        <v>112</v>
-      </c>
-      <c r="B118" s="1">
-        <v>115</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F118" s="2">
-        <v>23014</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A119">
-        <v>113</v>
-      </c>
-      <c r="B119" s="1">
-        <v>115</v>
-      </c>
-      <c r="C119" t="s">
-        <v>69</v>
-      </c>
-      <c r="D119" t="s">
-        <v>23</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F119" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G119" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A120">
-        <v>114</v>
-      </c>
-      <c r="B120" s="1">
-        <v>115</v>
-      </c>
-      <c r="C120" t="s">
-        <v>133</v>
-      </c>
-      <c r="D120" t="s">
-        <v>23</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F120" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G120" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="A121">
-        <v>115</v>
-      </c>
-      <c r="B121" s="1">
-        <v>115</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>81</v>
       </c>
       <c r="F121" s="2">
-        <v>300000</v>
+        <v>117750</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B122" s="1">
         <v>115</v>
       </c>
       <c r="C122" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F122" s="11">
-        <v>3800</v>
+        <v>10000</v>
       </c>
       <c r="G122" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B123" s="1">
         <v>115</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F123" s="2">
         <v>59500</v>
@@ -13144,2324 +13172,3133 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B124" s="1">
         <v>115</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F124" s="2">
-        <v>255000</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C124" t="s">
+        <v>34</v>
+      </c>
+      <c r="D124" t="s">
+        <v>29</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F124" s="11">
+        <v>6000</v>
+      </c>
+      <c r="G124" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B125" s="1">
         <v>115</v>
       </c>
-      <c r="C125" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>16</v>
+      <c r="C125" t="s">
+        <v>34</v>
+      </c>
+      <c r="D125" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F125" s="2">
-        <v>8285</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+        <v>182</v>
+      </c>
+      <c r="F125">
+        <v>37500</v>
+      </c>
+      <c r="G125" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B126" s="1">
         <v>115</v>
       </c>
       <c r="C126" t="s">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="D126" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F126" s="11">
-        <v>9400</v>
+        <v>6400</v>
       </c>
       <c r="G126" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B127" s="1">
         <v>115</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F127" s="2">
-        <v>51000</v>
+        <v>23014</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B128" s="1">
         <v>115</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D128" s="1" t="s">
+      <c r="C128" t="s">
+        <v>69</v>
+      </c>
+      <c r="D128" t="s">
         <v>23</v>
       </c>
-      <c r="E128" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F128" s="2">
-        <v>250000</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E128" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F128" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G128" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B129" s="1">
         <v>115</v>
       </c>
       <c r="C129" t="s">
-        <v>36</v>
-      </c>
-      <c r="D129" s="10" t="s">
-        <v>64</v>
+        <v>132</v>
+      </c>
+      <c r="D129" t="s">
+        <v>23</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F129" s="11">
         <v>3500</v>
       </c>
       <c r="G129" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A130">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B130" s="1">
         <v>115</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E130" s="1" t="s">
+      <c r="E130" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F130" s="2">
+        <v>300000</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" s="1">
+        <v>115</v>
+      </c>
+      <c r="C131" t="s">
+        <v>71</v>
+      </c>
+      <c r="D131" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F131" s="11">
+        <v>3800</v>
+      </c>
+      <c r="G131" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" s="1">
+        <v>115</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F132" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" s="1">
+        <v>115</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F133" s="2">
+        <v>255000</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" s="1">
+        <v>115</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F134" s="2">
+        <v>8285</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" s="1">
+        <v>115</v>
+      </c>
+      <c r="C135" t="s">
+        <v>35</v>
+      </c>
+      <c r="D135" t="s">
+        <v>16</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F135" s="11">
+        <v>9400</v>
+      </c>
+      <c r="G135" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" s="1">
+        <v>115</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F136" s="2">
+        <v>51000</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" s="1">
+        <v>115</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F137" s="2">
+        <v>250000</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" s="1">
+        <v>115</v>
+      </c>
+      <c r="C138" t="s">
+        <v>36</v>
+      </c>
+      <c r="D138" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F138" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G138" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" s="1">
+        <v>115</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E139" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F130" s="2">
+      <c r="F139" s="2">
         <v>20368</v>
       </c>
-      <c r="G130" s="1" t="s">
+      <c r="G139" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A131">
-        <v>125</v>
-      </c>
-      <c r="B131" s="1">
-        <v>115</v>
-      </c>
-      <c r="C131" t="s">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" s="1">
+        <v>115</v>
+      </c>
+      <c r="C140" t="s">
         <v>37</v>
       </c>
-      <c r="D131" t="s">
+      <c r="D140" t="s">
         <v>23</v>
       </c>
-      <c r="E131" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F131" s="11">
+      <c r="E140" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F140" s="11">
         <v>3500</v>
       </c>
-      <c r="G131" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A132">
-        <v>126</v>
-      </c>
-      <c r="B132" s="1">
-        <v>115</v>
-      </c>
-      <c r="C132" t="s">
-        <v>163</v>
-      </c>
-      <c r="D132" s="10" t="s">
+      <c r="G140" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" s="1">
+        <v>115</v>
+      </c>
+      <c r="C141" t="s">
+        <v>37</v>
+      </c>
+      <c r="D141" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F141">
+        <v>29750</v>
+      </c>
+      <c r="G141" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" s="1">
+        <v>115</v>
+      </c>
+      <c r="C142" t="s">
+        <v>162</v>
+      </c>
+      <c r="D142" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F142" s="11">
+        <v>7200</v>
+      </c>
+      <c r="G142" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" s="1">
+        <v>115</v>
+      </c>
+      <c r="C143" t="s">
+        <v>149</v>
+      </c>
+      <c r="D143" t="s">
+        <v>23</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F143" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G143" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" s="1">
+        <v>115</v>
+      </c>
+      <c r="C144" t="s">
+        <v>122</v>
+      </c>
+      <c r="D144" t="s">
+        <v>20</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F144" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G144" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" s="1">
+        <v>115</v>
+      </c>
+      <c r="C145" t="s">
+        <v>122</v>
+      </c>
+      <c r="D145" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F145">
+        <v>45000</v>
+      </c>
+      <c r="G145" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" s="1">
+        <v>115</v>
+      </c>
+      <c r="C146" t="s">
+        <v>155</v>
+      </c>
+      <c r="D146" t="s">
+        <v>23</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F146" s="11">
+        <v>5700</v>
+      </c>
+      <c r="G146" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" s="1">
+        <v>115</v>
+      </c>
+      <c r="C147" t="s">
+        <v>166</v>
+      </c>
+      <c r="D147" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F147" s="11">
+        <v>1400</v>
+      </c>
+      <c r="G147" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" s="1">
+        <v>115</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F148" s="2">
+        <v>45000</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" s="1">
+        <v>115</v>
+      </c>
+      <c r="C149" t="s">
+        <v>38</v>
+      </c>
+      <c r="D149" t="s">
+        <v>20</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F149" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G149" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" s="1">
+        <v>115</v>
+      </c>
+      <c r="C150" t="s">
+        <v>38</v>
+      </c>
+      <c r="D150" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F150">
+        <v>13500</v>
+      </c>
+      <c r="G150" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" s="1">
+        <v>115</v>
+      </c>
+      <c r="C151" t="s">
+        <v>99</v>
+      </c>
+      <c r="D151" t="s">
+        <v>60</v>
+      </c>
+      <c r="E151" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="E132" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F132" s="11">
-        <v>7200</v>
-      </c>
-      <c r="G132" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A133">
-        <v>127</v>
-      </c>
-      <c r="B133" s="1">
-        <v>115</v>
-      </c>
-      <c r="C133" t="s">
-        <v>150</v>
-      </c>
-      <c r="D133" t="s">
+      <c r="F151" s="2">
+        <v>3400</v>
+      </c>
+      <c r="G151" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H151" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" s="1">
+        <v>115</v>
+      </c>
+      <c r="C152" t="s">
+        <v>99</v>
+      </c>
+      <c r="D152" t="s">
+        <v>60</v>
+      </c>
+      <c r="E152" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F152" s="2">
+        <v>13120</v>
+      </c>
+      <c r="G152" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H152" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" s="1">
+        <v>115</v>
+      </c>
+      <c r="C153" t="s">
+        <v>99</v>
+      </c>
+      <c r="D153" t="s">
+        <v>60</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F153" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G153" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" s="1">
+        <v>115</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F154" s="2">
+        <v>2682</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" s="1">
+        <v>115</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F155" s="2">
+        <v>51000</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" s="1">
+        <v>115</v>
+      </c>
+      <c r="C156" t="s">
+        <v>39</v>
+      </c>
+      <c r="D156" t="s">
+        <v>40</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F156" s="11">
+        <v>900</v>
+      </c>
+      <c r="G156" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" s="1">
+        <v>115</v>
+      </c>
+      <c r="C157" t="s">
+        <v>39</v>
+      </c>
+      <c r="D157" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F157">
+        <v>17850</v>
+      </c>
+      <c r="G157" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" s="1">
+        <v>115</v>
+      </c>
+      <c r="C158" t="s">
+        <v>156</v>
+      </c>
+      <c r="D158" t="s">
         <v>23</v>
       </c>
-      <c r="E133" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F133" s="11">
+      <c r="E158" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F158" s="11">
         <v>3500</v>
       </c>
-      <c r="G133" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B134" s="1">
-        <v>115</v>
-      </c>
-      <c r="C134" t="s">
-        <v>123</v>
-      </c>
-      <c r="D134" t="s">
-        <v>20</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F134" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G134" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B135" s="1">
-        <v>115</v>
-      </c>
-      <c r="C135" t="s">
-        <v>156</v>
-      </c>
-      <c r="D135" t="s">
-        <v>23</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F135" s="11">
-        <v>5700</v>
-      </c>
-      <c r="G135" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B136" s="1">
-        <v>115</v>
-      </c>
-      <c r="C136" t="s">
+      <c r="G158" t="s">
         <v>167</v>
       </c>
-      <c r="D136" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F136" s="11">
-        <v>1400</v>
-      </c>
-      <c r="G136" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B137" s="1">
-        <v>115</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F137" s="2">
-        <v>45000</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B138" s="1">
-        <v>115</v>
-      </c>
-      <c r="C138" t="s">
-        <v>38</v>
-      </c>
-      <c r="D138" t="s">
-        <v>20</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F138" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G138" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B139" s="1">
-        <v>115</v>
-      </c>
-      <c r="C139" t="s">
-        <v>100</v>
-      </c>
-      <c r="D139" t="s">
-        <v>60</v>
-      </c>
-      <c r="E139" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F139" s="2">
-        <v>3400</v>
-      </c>
-      <c r="G139" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H139" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B140" s="1">
-        <v>115</v>
-      </c>
-      <c r="C140" t="s">
-        <v>100</v>
-      </c>
-      <c r="D140" t="s">
-        <v>60</v>
-      </c>
-      <c r="E140" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F140" s="2">
-        <v>13120</v>
-      </c>
-      <c r="G140" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H140" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B141" s="1">
-        <v>115</v>
-      </c>
-      <c r="C141" t="s">
-        <v>100</v>
-      </c>
-      <c r="D141" t="s">
-        <v>60</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F141" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G141" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B142" s="1">
-        <v>115</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D142" s="1" t="s">
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" s="1">
+        <v>115</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F142" s="2">
-        <v>2682</v>
-      </c>
-      <c r="G142" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B143" s="1">
-        <v>115</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F143" s="2">
-        <v>51000</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B144" s="1">
-        <v>115</v>
-      </c>
-      <c r="C144" t="s">
-        <v>39</v>
-      </c>
-      <c r="D144" t="s">
-        <v>40</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F144" s="11">
-        <v>900</v>
-      </c>
-      <c r="G144" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="145" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B145" s="1">
-        <v>115</v>
-      </c>
-      <c r="C145" t="s">
-        <v>157</v>
-      </c>
-      <c r="D145" t="s">
-        <v>23</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F145" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G145" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="146" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B146" s="1">
-        <v>115</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F146" s="2">
-        <v>16788</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="147" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B147" s="1">
-        <v>115</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F147" s="2">
-        <v>12800</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="148" spans="2:7" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="B148" s="1">
-        <v>115</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D148" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E148" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F148" s="2">
-        <v>143300</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="149" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B149" s="1">
-        <v>115</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F149" s="2">
-        <v>34568</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="150" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B150" s="1">
-        <v>115</v>
-      </c>
-      <c r="C150" t="s">
-        <v>66</v>
-      </c>
-      <c r="D150" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F150" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G150" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="151" spans="2:7" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="B151" s="1">
-        <v>115</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E151" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F151" s="2">
-        <v>300000</v>
-      </c>
-      <c r="G151" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="152" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B152" s="1">
-        <v>115</v>
-      </c>
-      <c r="C152" t="s">
-        <v>73</v>
-      </c>
-      <c r="D152" t="s">
-        <v>23</v>
-      </c>
-      <c r="E152" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F152" s="2">
-        <v>47500</v>
-      </c>
-      <c r="G152" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="153" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B153" s="1">
-        <v>115</v>
-      </c>
-      <c r="C153" t="s">
-        <v>73</v>
-      </c>
-      <c r="D153" t="s">
-        <v>23</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F153" s="11">
-        <v>3700</v>
-      </c>
-      <c r="G153" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="154" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B154" s="1">
-        <v>115</v>
-      </c>
-      <c r="C154" t="s">
-        <v>155</v>
-      </c>
-      <c r="D154" t="s">
-        <v>23</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F154" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G154" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="155" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B155" s="1">
-        <v>115</v>
-      </c>
-      <c r="C155" t="s">
-        <v>158</v>
-      </c>
-      <c r="D155" t="s">
-        <v>23</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F155" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G155" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="156" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B156" s="1">
-        <v>115</v>
-      </c>
-      <c r="C156" t="s">
-        <v>154</v>
-      </c>
-      <c r="D156" t="s">
-        <v>23</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F156" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G156" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="157" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B157" s="1">
-        <v>115</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F157" s="2">
-        <v>52000</v>
-      </c>
-      <c r="G157" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="158" spans="2:7" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="B158" s="1">
-        <v>115</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D158" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E158" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F158" s="2">
-        <v>210000</v>
-      </c>
-      <c r="G158" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="159" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B159" s="1">
-        <v>115</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F159" s="2">
-        <v>42500</v>
+        <v>16788</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A160">
+        <v>159</v>
+      </c>
       <c r="B160" s="1">
         <v>115</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F160" s="2">
-        <v>70000</v>
+        <v>12800</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="161" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A161">
+        <v>160</v>
+      </c>
       <c r="B161" s="1">
         <v>115</v>
       </c>
       <c r="C161" t="s">
-        <v>43</v>
-      </c>
-      <c r="D161" t="s">
-        <v>20</v>
+        <v>41</v>
+      </c>
+      <c r="D161" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F161" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G161" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="162" spans="2:8" x14ac:dyDescent="0.35">
+        <v>182</v>
+      </c>
+      <c r="F161">
+        <v>15800</v>
+      </c>
+      <c r="G161" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A162">
+        <v>161</v>
+      </c>
       <c r="B162" s="1">
         <v>115</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>11</v>
+        <v>66</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F162" s="2">
-        <v>59500</v>
+        <v>143300</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="163" spans="2:8" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A163">
+        <v>162</v>
+      </c>
       <c r="B163" s="1">
         <v>115</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F163" s="2">
-        <v>59500</v>
+        <v>34568</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="164" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A164">
+        <v>163</v>
+      </c>
       <c r="B164" s="1">
         <v>115</v>
       </c>
-      <c r="C164" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D164" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E164" s="3" t="s">
+      <c r="C164" t="s">
+        <v>66</v>
+      </c>
+      <c r="D164" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F164" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G164" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165" s="1">
+        <v>115</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E165" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F164" s="2">
-        <v>200000</v>
-      </c>
-      <c r="G164" s="1" t="s">
+      <c r="F165" s="2">
+        <v>300000</v>
+      </c>
+      <c r="G165" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="165" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B165" s="1">
-        <v>115</v>
-      </c>
-      <c r="C165" t="s">
-        <v>95</v>
-      </c>
-      <c r="D165" t="s">
-        <v>23</v>
-      </c>
-      <c r="E165" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F165" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G165" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H165" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="166" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A166">
+        <v>165</v>
+      </c>
       <c r="B166" s="1">
         <v>115</v>
       </c>
       <c r="C166" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D166" t="s">
         <v>23</v>
       </c>
-      <c r="E166" s="10" t="s">
-        <v>172</v>
+      <c r="E166" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="F166" s="2">
-        <v>42393</v>
-      </c>
-      <c r="G166" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H166" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="167" spans="2:8" x14ac:dyDescent="0.35">
+        <v>47500</v>
+      </c>
+      <c r="G166" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A167">
+        <v>166</v>
+      </c>
       <c r="B167" s="1">
         <v>115</v>
       </c>
       <c r="C167" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D167" t="s">
         <v>23</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F167" s="11">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="G167" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="168" spans="2:8" x14ac:dyDescent="0.35">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A168">
+        <v>167</v>
+      </c>
       <c r="B168" s="1">
         <v>115</v>
       </c>
       <c r="C168" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D168" t="s">
         <v>23</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F168" s="11">
         <v>3500</v>
       </c>
       <c r="G168" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A169">
         <v>168</v>
       </c>
-    </row>
-    <row r="169" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B169" s="1">
         <v>115</v>
       </c>
       <c r="C169" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="D169" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E169" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F169" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G169" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170" s="1">
+        <v>115</v>
+      </c>
+      <c r="C170" t="s">
+        <v>153</v>
+      </c>
+      <c r="D170" t="s">
+        <v>23</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F170" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G170" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A171">
         <v>170</v>
       </c>
-      <c r="F169" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G169" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="170" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B170" s="1">
-        <v>115</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E170" s="1" t="s">
+      <c r="B171" s="1">
+        <v>115</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F171" s="2">
+        <v>52000</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172" s="1">
+        <v>115</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F172" s="2">
+        <v>210000</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173" s="1">
+        <v>115</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E173" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F170" s="2">
-        <v>44118</v>
-      </c>
-      <c r="G170" s="1" t="s">
+      <c r="F173" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G173" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="171" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="B171" s="1">
-        <v>115</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D171" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E171" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F171" s="2">
-        <v>217500</v>
-      </c>
-      <c r="G171" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="172" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B172" s="1">
-        <v>115</v>
-      </c>
-      <c r="C172" t="s">
-        <v>45</v>
-      </c>
-      <c r="D172" t="s">
-        <v>46</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F172" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G172" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="173" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B173" s="1">
-        <v>115</v>
-      </c>
-      <c r="C173" t="s">
-        <v>166</v>
-      </c>
-      <c r="D173" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F173" s="11">
-        <v>6000</v>
-      </c>
-      <c r="G173" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="174" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A174">
+        <v>173</v>
+      </c>
       <c r="B174" s="1">
         <v>115</v>
       </c>
-      <c r="C174" t="s">
-        <v>120</v>
-      </c>
-      <c r="D174" t="s">
-        <v>10</v>
+      <c r="C174" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F174" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G174" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="175" spans="2:8" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="F174" s="2">
+        <v>70000</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A175">
+        <v>174</v>
+      </c>
       <c r="B175" s="1">
         <v>115</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>46</v>
+      <c r="C175" t="s">
+        <v>43</v>
+      </c>
+      <c r="D175" t="s">
+        <v>20</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F175" s="2">
+        <v>169</v>
+      </c>
+      <c r="F175" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G175" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176" s="1">
+        <v>115</v>
+      </c>
+      <c r="C176" t="s">
+        <v>43</v>
+      </c>
+      <c r="D176" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F176">
+        <v>20250</v>
+      </c>
+      <c r="G176" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177" s="1">
+        <v>115</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F177" s="2">
         <v>59500</v>
       </c>
-      <c r="G175" s="1" t="s">
+      <c r="G177" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="176" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B176" s="1">
-        <v>115</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E176" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F176" s="2">
-        <v>60000</v>
-      </c>
-      <c r="G176" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H176" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="177" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B177" s="1">
-        <v>115</v>
-      </c>
-      <c r="C177" t="s">
-        <v>47</v>
-      </c>
-      <c r="D177" t="s">
-        <v>46</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F177" s="11">
-        <v>1400</v>
-      </c>
-      <c r="G177" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="178" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A178">
+        <v>177</v>
+      </c>
       <c r="B178" s="1">
         <v>115</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F178" s="2">
-        <v>52500</v>
+        <v>59500</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A179">
+        <v>178</v>
+      </c>
       <c r="B179" s="1">
         <v>115</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E179" s="1" t="s">
-        <v>83</v>
+        <v>44</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F179" s="2">
-        <v>52776</v>
+        <v>200000</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="180" spans="2:8" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A180">
+        <v>179</v>
+      </c>
       <c r="B180" s="1">
         <v>115</v>
       </c>
       <c r="C180" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="D180" t="s">
-        <v>13</v>
-      </c>
-      <c r="E180" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E180" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="F180" s="11">
-        <v>900</v>
-      </c>
-      <c r="G180" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="181" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="F180" s="2">
+        <v>50000</v>
+      </c>
+      <c r="G180" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H180" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A181">
+        <v>180</v>
+      </c>
       <c r="B181" s="1">
         <v>115</v>
       </c>
-      <c r="C181" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D181" s="1" t="s">
+      <c r="C181" t="s">
+        <v>94</v>
+      </c>
+      <c r="D181" t="s">
         <v>23</v>
       </c>
-      <c r="E181" s="1" t="s">
-        <v>7</v>
+      <c r="E181" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="F181" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G181" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="182" spans="2:8" x14ac:dyDescent="0.35">
+        <v>42393</v>
+      </c>
+      <c r="G181" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H181" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A182">
+        <v>181</v>
+      </c>
       <c r="B182" s="1">
         <v>115</v>
       </c>
       <c r="C182" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="D182" t="s">
         <v>23</v>
       </c>
-      <c r="E182" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F182" s="2">
-        <v>41616</v>
-      </c>
-      <c r="G182" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="183" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="E182" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F182" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G182" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A183">
+        <v>182</v>
+      </c>
       <c r="B183" s="1">
         <v>115</v>
       </c>
       <c r="C183" t="s">
-        <v>49</v>
+        <v>158</v>
       </c>
       <c r="D183" t="s">
         <v>23</v>
       </c>
-      <c r="E183" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F183" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G183" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H183" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="184" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="E183" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F183" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G183" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A184">
+        <v>183</v>
+      </c>
       <c r="B184" s="1">
         <v>115</v>
       </c>
       <c r="C184" t="s">
+        <v>118</v>
+      </c>
+      <c r="D184" t="s">
+        <v>29</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F184" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G184" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185" s="1">
+        <v>115</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F185" s="2">
+        <v>44118</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186" s="1">
+        <v>115</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F186" s="2">
+        <v>217500</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187" s="1">
+        <v>115</v>
+      </c>
+      <c r="C187" t="s">
+        <v>45</v>
+      </c>
+      <c r="D187" t="s">
+        <v>46</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F187" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G187" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188" s="1">
+        <v>115</v>
+      </c>
+      <c r="C188" t="s">
+        <v>165</v>
+      </c>
+      <c r="D188" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F188" s="11">
+        <v>6000</v>
+      </c>
+      <c r="G188" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189" s="1">
+        <v>115</v>
+      </c>
+      <c r="C189" t="s">
+        <v>119</v>
+      </c>
+      <c r="D189" t="s">
+        <v>10</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F189" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G189" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190" s="1">
+        <v>115</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F190" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191" s="1">
+        <v>115</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E191" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F191" s="2">
+        <v>60000</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192" s="1">
+        <v>115</v>
+      </c>
+      <c r="C192" t="s">
+        <v>47</v>
+      </c>
+      <c r="D192" t="s">
+        <v>46</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F192" s="11">
+        <v>1400</v>
+      </c>
+      <c r="G192" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193" s="1">
+        <v>115</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F193" s="2">
+        <v>52500</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194" s="1">
+        <v>115</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F194" s="2">
+        <v>52776</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195" s="1">
+        <v>115</v>
+      </c>
+      <c r="C195" t="s">
+        <v>48</v>
+      </c>
+      <c r="D195" t="s">
+        <v>13</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F195" s="11">
+        <v>900</v>
+      </c>
+      <c r="G195" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196" s="1">
+        <v>115</v>
+      </c>
+      <c r="C196" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D184" t="s">
+      <c r="D196" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E184" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F184" s="2">
-        <v>38569</v>
-      </c>
-      <c r="G184" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H184" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="185" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B185" s="1">
-        <v>115</v>
-      </c>
-      <c r="C185" t="s">
+      <c r="E196" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F196" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197" s="1">
+        <v>115</v>
+      </c>
+      <c r="C197" t="s">
         <v>49</v>
-      </c>
-      <c r="D185" t="s">
-        <v>23</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F185" s="11">
-        <v>5000</v>
-      </c>
-      <c r="G185" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="186" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B186" s="1">
-        <v>115</v>
-      </c>
-      <c r="C186" t="s">
-        <v>142</v>
-      </c>
-      <c r="D186" t="s">
-        <v>23</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F186" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G186" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="187" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B187" s="1">
-        <v>115</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F187" s="2">
-        <v>31500</v>
-      </c>
-      <c r="G187" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="188" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B188" s="1">
-        <v>115</v>
-      </c>
-      <c r="C188" t="s">
-        <v>50</v>
-      </c>
-      <c r="D188" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F188" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G188" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="189" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B189" s="1">
-        <v>115</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F189" s="2">
-        <v>42500</v>
-      </c>
-      <c r="G189" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="190" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B190" s="1">
-        <v>115</v>
-      </c>
-      <c r="C190" t="s">
-        <v>51</v>
-      </c>
-      <c r="D190" t="s">
-        <v>20</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F190" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G190" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="191" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="B191" s="1">
-        <v>115</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E191" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F191" s="2">
-        <v>95912</v>
-      </c>
-      <c r="G191" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="192" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B192" s="1">
-        <v>115</v>
-      </c>
-      <c r="C192" t="s">
-        <v>72</v>
-      </c>
-      <c r="D192" t="s">
-        <v>23</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F192" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G192" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="193" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B193" s="1">
-        <v>115</v>
-      </c>
-      <c r="C193" t="s">
-        <v>130</v>
-      </c>
-      <c r="D193" t="s">
-        <v>23</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F193" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G193" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="194" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="B194" s="1">
-        <v>115</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E194" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F194" s="2">
-        <v>28500</v>
-      </c>
-      <c r="G194" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="195" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B195" s="1">
-        <v>115</v>
-      </c>
-      <c r="C195" t="s">
-        <v>129</v>
-      </c>
-      <c r="D195" t="s">
-        <v>23</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F195" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G195" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="196" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B196" s="1">
-        <v>115</v>
-      </c>
-      <c r="C196" t="s">
-        <v>143</v>
-      </c>
-      <c r="D196" t="s">
-        <v>23</v>
-      </c>
-      <c r="E196" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F196" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G196" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="197" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B197" s="1">
-        <v>115</v>
-      </c>
-      <c r="C197" t="s">
-        <v>148</v>
       </c>
       <c r="D197" t="s">
         <v>23</v>
       </c>
-      <c r="E197" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F197" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G197" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="198" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="E197" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F197" s="2">
+        <v>41616</v>
+      </c>
+      <c r="G197" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A198">
+        <v>197</v>
+      </c>
       <c r="B198" s="1">
         <v>115</v>
       </c>
       <c r="C198" t="s">
-        <v>149</v>
+        <v>49</v>
       </c>
       <c r="D198" t="s">
         <v>23</v>
       </c>
-      <c r="E198" s="1" t="s">
+      <c r="E198" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="F198" s="11">
+      <c r="F198" s="2">
+        <v>50000</v>
+      </c>
+      <c r="G198" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H198" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199" s="1">
+        <v>115</v>
+      </c>
+      <c r="C199" t="s">
+        <v>49</v>
+      </c>
+      <c r="D199" t="s">
+        <v>23</v>
+      </c>
+      <c r="E199" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F199" s="2">
+        <v>38569</v>
+      </c>
+      <c r="G199" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H199" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200" s="1">
+        <v>115</v>
+      </c>
+      <c r="C200" t="s">
+        <v>49</v>
+      </c>
+      <c r="D200" t="s">
+        <v>23</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F200" s="11">
+        <v>5000</v>
+      </c>
+      <c r="G200" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201" s="1">
+        <v>115</v>
+      </c>
+      <c r="C201" t="s">
+        <v>49</v>
+      </c>
+      <c r="D201" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F201">
+        <v>50000</v>
+      </c>
+      <c r="G201" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202" s="1">
+        <v>115</v>
+      </c>
+      <c r="C202" t="s">
+        <v>141</v>
+      </c>
+      <c r="D202" t="s">
+        <v>23</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F202" s="11">
         <v>3500</v>
       </c>
-      <c r="G198" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="199" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B199" s="1">
-        <v>115</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E199" s="1" t="s">
+      <c r="G202" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203" s="1">
+        <v>115</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E203" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F199" s="2">
-        <v>29250</v>
-      </c>
-      <c r="G199" s="1" t="s">
+      <c r="F203" s="2">
+        <v>31500</v>
+      </c>
+      <c r="G203" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="200" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B200" s="1">
-        <v>115</v>
-      </c>
-      <c r="C200" t="s">
-        <v>52</v>
-      </c>
-      <c r="D200" t="s">
-        <v>29</v>
-      </c>
-      <c r="E200" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F200" s="2">
-        <v>8900</v>
-      </c>
-      <c r="G200" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H200" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="201" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B201" s="1">
-        <v>115</v>
-      </c>
-      <c r="C201" t="s">
-        <v>52</v>
-      </c>
-      <c r="D201" t="s">
-        <v>29</v>
-      </c>
-      <c r="E201" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F201" s="2">
-        <v>0</v>
-      </c>
-      <c r="G201" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H201" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="202" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B202" s="1">
-        <v>115</v>
-      </c>
-      <c r="C202" t="s">
-        <v>52</v>
-      </c>
-      <c r="D202" t="s">
-        <v>29</v>
-      </c>
-      <c r="E202" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F202" s="2">
-        <v>19190</v>
-      </c>
-      <c r="G202" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H202" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="203" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B203" s="1">
-        <v>115</v>
-      </c>
-      <c r="C203" t="s">
-        <v>52</v>
-      </c>
-      <c r="D203" t="s">
-        <v>29</v>
-      </c>
-      <c r="E203" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F203" s="2">
-        <v>17728</v>
-      </c>
-      <c r="G203" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H203" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="204" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A204">
+        <v>203</v>
+      </c>
       <c r="B204" s="1">
         <v>115</v>
       </c>
       <c r="C204" t="s">
-        <v>52</v>
-      </c>
-      <c r="D204" t="s">
-        <v>29</v>
+        <v>50</v>
+      </c>
+      <c r="D204" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F204" s="11">
-        <v>2200</v>
+        <v>3500</v>
       </c>
       <c r="G204" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="205" spans="2:8" x14ac:dyDescent="0.35">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A205">
+        <v>204</v>
+      </c>
       <c r="B205" s="1">
         <v>115</v>
       </c>
       <c r="C205" t="s">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="D205" s="10" t="s">
         <v>64</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F205" s="11">
+        <v>182</v>
+      </c>
+      <c r="F205">
+        <v>30150</v>
+      </c>
+      <c r="G205" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206" s="1">
+        <v>115</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F206" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207" s="1">
+        <v>115</v>
+      </c>
+      <c r="C207" t="s">
+        <v>51</v>
+      </c>
+      <c r="D207" t="s">
+        <v>20</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F207" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G207" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208" s="1">
+        <v>115</v>
+      </c>
+      <c r="C208" t="s">
+        <v>51</v>
+      </c>
+      <c r="D208" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F208">
+        <v>12750</v>
+      </c>
+      <c r="G208" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209" s="1">
+        <v>115</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F209" s="2">
+        <v>95912</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210" s="1">
+        <v>115</v>
+      </c>
+      <c r="C210" t="s">
+        <v>72</v>
+      </c>
+      <c r="D210" t="s">
+        <v>23</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F210" s="11">
         <v>3500</v>
       </c>
-      <c r="G205" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="206" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B206" s="1">
-        <v>115</v>
-      </c>
-      <c r="C206" t="s">
-        <v>99</v>
-      </c>
-      <c r="D206" t="s">
-        <v>23</v>
-      </c>
-      <c r="E206" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F206" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G206" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H206" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="207" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B207" s="1">
-        <v>115</v>
-      </c>
-      <c r="C207" t="s">
-        <v>99</v>
-      </c>
-      <c r="D207" t="s">
-        <v>23</v>
-      </c>
-      <c r="E207" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F207" s="2">
-        <v>17600</v>
-      </c>
-      <c r="G207" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H207" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="208" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B208" s="1">
-        <v>115</v>
-      </c>
-      <c r="C208" t="s">
-        <v>99</v>
-      </c>
-      <c r="D208" t="s">
-        <v>23</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F208" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G208" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="209" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B209" s="1">
-        <v>115</v>
-      </c>
-      <c r="C209" t="s">
-        <v>151</v>
-      </c>
-      <c r="D209" t="s">
-        <v>23</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F209" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G209" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="210" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B210" s="1">
-        <v>115</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E210" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F210" s="2">
-        <v>41384</v>
-      </c>
-      <c r="G210" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="211" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="G210" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A211">
+        <v>210</v>
+      </c>
       <c r="B211" s="1">
         <v>115</v>
       </c>
       <c r="C211" t="s">
-        <v>53</v>
+        <v>129</v>
       </c>
       <c r="D211" t="s">
         <v>23</v>
       </c>
-      <c r="E211" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F211" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G211" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H211" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="212" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="E211" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F211" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G211" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A212">
+        <v>211</v>
+      </c>
       <c r="B212" s="1">
         <v>115</v>
       </c>
-      <c r="C212" t="s">
-        <v>53</v>
-      </c>
-      <c r="D212" t="s">
-        <v>23</v>
-      </c>
-      <c r="E212" s="10" t="s">
-        <v>172</v>
+      <c r="C212" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F212" s="2">
-        <v>19200</v>
-      </c>
-      <c r="G212" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H212" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="213" spans="2:8" x14ac:dyDescent="0.35">
+        <v>28500</v>
+      </c>
+      <c r="G212" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A213">
+        <v>212</v>
+      </c>
       <c r="B213" s="1">
         <v>115</v>
       </c>
       <c r="C213" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="D213" t="s">
         <v>23</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F213" s="11">
         <v>3500</v>
       </c>
       <c r="G213" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="214" spans="2:8" x14ac:dyDescent="0.35">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A214">
+        <v>213</v>
+      </c>
       <c r="B214" s="1">
         <v>115</v>
       </c>
-      <c r="C214" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D214" s="1" t="s">
-        <v>13</v>
+      <c r="C214" t="s">
+        <v>142</v>
+      </c>
+      <c r="D214" t="s">
+        <v>23</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F214" s="2">
-        <v>56000</v>
-      </c>
-      <c r="G214" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="215" spans="2:8" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+      <c r="F214" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G214" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A215">
+        <v>214</v>
+      </c>
       <c r="B215" s="1">
         <v>115</v>
       </c>
-      <c r="C215" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>13</v>
+      <c r="C215" t="s">
+        <v>147</v>
+      </c>
+      <c r="D215" t="s">
+        <v>23</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F215" s="2">
-        <v>48284</v>
-      </c>
-      <c r="G215" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="216" spans="2:8" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+      <c r="F215" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G215" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A216">
+        <v>215</v>
+      </c>
       <c r="B216" s="1">
         <v>115</v>
       </c>
       <c r="C216" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="D216" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F216" s="11">
-        <v>6300</v>
+        <v>3500</v>
       </c>
       <c r="G216" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="217" spans="2:8" x14ac:dyDescent="0.35">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A217">
+        <v>216</v>
+      </c>
       <c r="B217" s="1">
         <v>115</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F217" s="2">
-        <v>42500</v>
+        <v>29250</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="218" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A218">
+        <v>217</v>
+      </c>
       <c r="B218" s="1">
         <v>115</v>
       </c>
       <c r="C218" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D218" t="s">
-        <v>20</v>
-      </c>
-      <c r="E218" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E218" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="F218" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G218" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="219" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="F218" s="2">
+        <v>8900</v>
+      </c>
+      <c r="G218" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H218" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A219">
+        <v>218</v>
+      </c>
       <c r="B219" s="1">
         <v>115</v>
       </c>
-      <c r="C219" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E219" s="1" t="s">
-        <v>21</v>
+      <c r="C219" t="s">
+        <v>52</v>
+      </c>
+      <c r="D219" t="s">
+        <v>29</v>
+      </c>
+      <c r="E219" s="10" t="s">
+        <v>170</v>
       </c>
       <c r="F219" s="2">
-        <v>41770</v>
-      </c>
-      <c r="G219" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="220" spans="2:8" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="G219" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H219" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A220">
+        <v>219</v>
+      </c>
       <c r="B220" s="1">
         <v>115</v>
       </c>
       <c r="C220" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D220" t="s">
-        <v>23</v>
-      </c>
-      <c r="E220" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F220" s="11">
-        <v>4100</v>
-      </c>
-      <c r="G220" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="221" spans="2:8" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="E220" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F220" s="2">
+        <v>19190</v>
+      </c>
+      <c r="G220" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H220" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A221">
+        <v>220</v>
+      </c>
       <c r="B221" s="1">
         <v>115</v>
       </c>
-      <c r="C221" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E221" s="1" t="s">
-        <v>7</v>
+      <c r="C221" t="s">
+        <v>52</v>
+      </c>
+      <c r="D221" t="s">
+        <v>29</v>
+      </c>
+      <c r="E221" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="F221" s="2">
-        <v>45000</v>
-      </c>
-      <c r="G221" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="222" spans="2:8" x14ac:dyDescent="0.35">
+        <v>17728</v>
+      </c>
+      <c r="G221" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H221" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A222">
+        <v>221</v>
+      </c>
       <c r="B222" s="1">
         <v>115</v>
       </c>
       <c r="C222" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D222" t="s">
-        <v>86</v>
-      </c>
-      <c r="E222" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F222" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G222" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="223" spans="2:8" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F222" s="11">
+        <v>2200</v>
+      </c>
+      <c r="G222" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A223">
+        <v>222</v>
+      </c>
       <c r="B223" s="1">
         <v>115</v>
       </c>
       <c r="C223" t="s">
-        <v>57</v>
-      </c>
-      <c r="D223" t="s">
-        <v>20</v>
+        <v>52</v>
+      </c>
+      <c r="D223" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F223" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G223" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="224" spans="2:8" x14ac:dyDescent="0.35">
+        <v>182</v>
+      </c>
+      <c r="F223">
+        <v>32175</v>
+      </c>
+      <c r="G223" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A224">
+        <v>223</v>
+      </c>
       <c r="B224" s="1">
         <v>115</v>
       </c>
       <c r="C224" t="s">
-        <v>152</v>
-      </c>
-      <c r="D224" t="s">
-        <v>23</v>
+        <v>159</v>
+      </c>
+      <c r="D224" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F224" s="11">
         <v>3500</v>
       </c>
       <c r="G224" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="225" spans="2:7" x14ac:dyDescent="0.35">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A225">
+        <v>224</v>
+      </c>
       <c r="B225" s="1">
         <v>115</v>
       </c>
       <c r="C225" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="D225" t="s">
         <v>23</v>
       </c>
-      <c r="E225" s="1" t="s">
+      <c r="E225" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="F225" s="11">
-        <v>5000</v>
-      </c>
-      <c r="G225" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="226" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F225" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G225" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H225" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A226">
+        <v>225</v>
+      </c>
       <c r="B226" s="1">
         <v>115</v>
       </c>
-      <c r="C226" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D226" s="1" t="s">
+      <c r="C226" t="s">
+        <v>98</v>
+      </c>
+      <c r="D226" t="s">
         <v>23</v>
       </c>
-      <c r="E226" s="1" t="s">
-        <v>83</v>
+      <c r="E226" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="F226" s="2">
-        <v>39125</v>
-      </c>
-      <c r="G226" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="227" spans="2:7" x14ac:dyDescent="0.35">
+        <v>17600</v>
+      </c>
+      <c r="G226" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H226" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A227">
+        <v>226</v>
+      </c>
       <c r="B227" s="1">
         <v>115</v>
       </c>
       <c r="C227" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="D227" t="s">
         <v>23</v>
       </c>
       <c r="E227" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F227" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G227" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228" s="1">
+        <v>115</v>
+      </c>
+      <c r="C228" t="s">
+        <v>150</v>
+      </c>
+      <c r="D228" t="s">
+        <v>23</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F228" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G228" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229" s="1">
+        <v>115</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F229" s="2">
+        <v>41384</v>
+      </c>
+      <c r="G229" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230" s="1">
+        <v>115</v>
+      </c>
+      <c r="C230" t="s">
+        <v>53</v>
+      </c>
+      <c r="D230" t="s">
+        <v>23</v>
+      </c>
+      <c r="E230" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="F227" s="11">
+      <c r="F230" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G230" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H230" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231" s="1">
+        <v>115</v>
+      </c>
+      <c r="C231" t="s">
+        <v>53</v>
+      </c>
+      <c r="D231" t="s">
+        <v>23</v>
+      </c>
+      <c r="E231" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F231" s="2">
+        <v>19200</v>
+      </c>
+      <c r="G231" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H231" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232" s="1">
+        <v>115</v>
+      </c>
+      <c r="C232" t="s">
+        <v>53</v>
+      </c>
+      <c r="D232" t="s">
+        <v>23</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F232" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G232" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A233">
+        <v>232</v>
+      </c>
+      <c r="B233" s="1">
+        <v>115</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F233" s="2">
+        <v>56000</v>
+      </c>
+      <c r="G233" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234" s="1">
+        <v>115</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F234" s="2">
+        <v>48284</v>
+      </c>
+      <c r="G234" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A235">
+        <v>234</v>
+      </c>
+      <c r="B235" s="1">
+        <v>115</v>
+      </c>
+      <c r="C235" t="s">
+        <v>54</v>
+      </c>
+      <c r="D235" t="s">
+        <v>13</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F235" s="11">
+        <v>6300</v>
+      </c>
+      <c r="G235" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A236">
+        <v>235</v>
+      </c>
+      <c r="B236" s="1">
+        <v>115</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F236" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G236" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A237">
+        <v>236</v>
+      </c>
+      <c r="B237" s="1">
+        <v>115</v>
+      </c>
+      <c r="C237" t="s">
+        <v>55</v>
+      </c>
+      <c r="D237" t="s">
+        <v>20</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F237" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G237" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A238">
+        <v>237</v>
+      </c>
+      <c r="B238" s="1">
+        <v>115</v>
+      </c>
+      <c r="C238" t="s">
+        <v>55</v>
+      </c>
+      <c r="D238" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F238">
+        <v>19125</v>
+      </c>
+      <c r="G238" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A239">
+        <v>238</v>
+      </c>
+      <c r="B239" s="1">
+        <v>115</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F239" s="2">
+        <v>41770</v>
+      </c>
+      <c r="G239" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A240">
+        <v>239</v>
+      </c>
+      <c r="B240" s="1">
+        <v>115</v>
+      </c>
+      <c r="C240" t="s">
+        <v>56</v>
+      </c>
+      <c r="D240" t="s">
+        <v>23</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F240" s="11">
+        <v>4100</v>
+      </c>
+      <c r="G240" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A241">
+        <v>240</v>
+      </c>
+      <c r="B241" s="1">
+        <v>115</v>
+      </c>
+      <c r="C241" t="s">
+        <v>56</v>
+      </c>
+      <c r="D241" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F241">
+        <v>18584</v>
+      </c>
+      <c r="G241" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A242">
+        <v>241</v>
+      </c>
+      <c r="B242" s="1">
+        <v>115</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F242" s="2">
+        <v>45000</v>
+      </c>
+      <c r="G242" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A243">
+        <v>242</v>
+      </c>
+      <c r="B243" s="1">
+        <v>115</v>
+      </c>
+      <c r="C243" t="s">
+        <v>57</v>
+      </c>
+      <c r="D243" t="s">
+        <v>86</v>
+      </c>
+      <c r="E243" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F243" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G243" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A244">
+        <v>243</v>
+      </c>
+      <c r="B244" s="1">
+        <v>115</v>
+      </c>
+      <c r="C244" t="s">
+        <v>57</v>
+      </c>
+      <c r="D244" t="s">
+        <v>20</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F244" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G244" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A245">
+        <v>244</v>
+      </c>
+      <c r="B245" s="1">
+        <v>115</v>
+      </c>
+      <c r="C245" t="s">
+        <v>151</v>
+      </c>
+      <c r="D245" t="s">
+        <v>23</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F245" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G245" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A246">
+        <v>245</v>
+      </c>
+      <c r="B246" s="1">
+        <v>115</v>
+      </c>
+      <c r="C246" t="s">
+        <v>152</v>
+      </c>
+      <c r="D246" t="s">
+        <v>23</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F246" s="11">
+        <v>5000</v>
+      </c>
+      <c r="G246" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A247">
+        <v>246</v>
+      </c>
+      <c r="B247" s="1">
+        <v>115</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F247" s="2">
+        <v>39125</v>
+      </c>
+      <c r="G247" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A248">
+        <v>247</v>
+      </c>
+      <c r="B248" s="1">
+        <v>115</v>
+      </c>
+      <c r="C248" t="s">
+        <v>65</v>
+      </c>
+      <c r="D248" t="s">
+        <v>23</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F248" s="11">
         <v>7500</v>
       </c>
-      <c r="G227" t="s">
+      <c r="G248" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A249">
+        <v>248</v>
+      </c>
+      <c r="B249" s="1">
+        <v>115</v>
+      </c>
+      <c r="C249" t="s">
+        <v>163</v>
+      </c>
+      <c r="D249" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F249" s="11">
+        <v>5200</v>
+      </c>
+      <c r="G249" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A250">
+        <v>249</v>
+      </c>
+      <c r="B250" s="1">
+        <v>115</v>
+      </c>
+      <c r="C250" t="s">
+        <v>164</v>
+      </c>
+      <c r="D250" t="s">
+        <v>40</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F250" s="11">
+        <v>5200</v>
+      </c>
+      <c r="G250" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A251">
+        <v>250</v>
+      </c>
+      <c r="B251" s="1">
+        <v>115</v>
+      </c>
+      <c r="C251" t="s">
+        <v>164</v>
+      </c>
+      <c r="D251" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F251">
+        <v>13515</v>
+      </c>
+      <c r="G251" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A252">
+        <v>251</v>
+      </c>
+      <c r="B252" s="1">
+        <v>115</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F252" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G252" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A253">
+        <v>252</v>
+      </c>
+      <c r="B253" s="1">
+        <v>115</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D253" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F253" s="2">
+        <v>221000</v>
+      </c>
+      <c r="G253" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A254">
+        <v>253</v>
+      </c>
+      <c r="B254" s="1">
+        <v>115</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F254" s="2">
+        <v>26283</v>
+      </c>
+      <c r="G254" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A255">
+        <v>254</v>
+      </c>
+      <c r="B255" s="1">
+        <v>115</v>
+      </c>
+      <c r="C255" t="s">
+        <v>58</v>
+      </c>
+      <c r="D255" t="s">
+        <v>60</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F255" s="11">
+        <v>1100</v>
+      </c>
+      <c r="G255" s="12" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="228" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B228" s="1">
-        <v>115</v>
-      </c>
-      <c r="C228" t="s">
-        <v>164</v>
-      </c>
-      <c r="D228" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E228" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F228" s="11">
-        <v>5200</v>
-      </c>
-      <c r="G228" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="229" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B229" s="1">
-        <v>115</v>
-      </c>
-      <c r="C229" t="s">
-        <v>165</v>
-      </c>
-      <c r="D229" t="s">
-        <v>40</v>
-      </c>
-      <c r="E229" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F229" s="11">
-        <v>5200</v>
-      </c>
-      <c r="G229" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="230" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B230" s="1">
-        <v>115</v>
-      </c>
-      <c r="C230" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D230" s="1" t="s">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A256">
+        <v>255</v>
+      </c>
+      <c r="B256" s="1">
+        <v>115</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D256" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E230" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F230" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G230" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="231" spans="2:7" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="B231" s="1">
-        <v>115</v>
-      </c>
-      <c r="C231" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D231" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E231" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F231" s="2">
-        <v>221000</v>
-      </c>
-      <c r="G231" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="232" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B232" s="1">
-        <v>115</v>
-      </c>
-      <c r="C232" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D232" s="1" t="s">
+      <c r="E256" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F256" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G256" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A257">
+        <v>256</v>
+      </c>
+      <c r="B257" s="1">
+        <v>115</v>
+      </c>
+      <c r="C257" t="s">
+        <v>59</v>
+      </c>
+      <c r="D257" t="s">
         <v>60</v>
       </c>
-      <c r="E232" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F232" s="2">
-        <v>26283</v>
-      </c>
-      <c r="G232" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="233" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B233" s="1">
-        <v>115</v>
-      </c>
-      <c r="C233" t="s">
-        <v>58</v>
-      </c>
-      <c r="D233" t="s">
-        <v>60</v>
-      </c>
-      <c r="E233" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F233" s="11">
-        <v>1100</v>
-      </c>
-      <c r="G233" s="12" t="s">
+      <c r="E257" s="1" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="234" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B234" s="1">
-        <v>115</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E234" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F234" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G234" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="235" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B235" s="1">
-        <v>115</v>
-      </c>
-      <c r="C235" t="s">
-        <v>59</v>
-      </c>
-      <c r="D235" t="s">
-        <v>60</v>
-      </c>
-      <c r="E235" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F235" s="11">
+      <c r="F257" s="11">
         <v>2700</v>
       </c>
-      <c r="G235" t="s">
-        <v>168</v>
+      <c r="G257" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:H235">
-    <sortCondition ref="C2:C235"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H257">
+    <sortCondition ref="C2:C257"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DFDFE0-CB00-4FA5-9296-0C1571CFBE03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C92ACFB3-42BE-478A-9F41-898547ADC62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="資料表" sheetId="2" r:id="rId1"/>
+    <sheet name="工作表1" sheetId="3" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料表!$A$1:$H$235</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料表!$A$1:$H$306</definedName>
     <definedName name="Barcode">OFFSET(#REF!,MATCH(#REF!,#REF!,0)-1,0)</definedName>
     <definedName name="重大活動行事曆">[1]重要活動行事曆!$C$2:$I$467</definedName>
     <definedName name="資料">#REF!</definedName>
@@ -29,7 +30,7 @@
     <definedName name="簽退時間">'[1]條碼_簽到表 (v2)'!$L$2:$L$452</definedName>
     <definedName name="簽退條碼">'[1]條碼_簽到表 (v2)'!$I$2:$I$452</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="224">
   <si>
     <t>序號</t>
   </si>
@@ -1025,6 +1026,124 @@
     <t>115年9月1日教學發展委員會會議通過</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
+  <si>
+    <t>人體試驗研究倫理講習班GCP課程研習</t>
+  </si>
+  <si>
+    <t>與AI共行文獻耙梳從搜尋拆解到審稿的完整研究流程研習</t>
+  </si>
+  <si>
+    <t>AI教學工具應用與管理研習</t>
+  </si>
+  <si>
+    <t>寒假教師AI賦能研習</t>
+  </si>
+  <si>
+    <t>AI教學工具應用與管理專業研習</t>
+  </si>
+  <si>
+    <t>測量工具設計與開發信度效度困難度工作坊研習</t>
+  </si>
+  <si>
+    <t>神經重症繼續教育課程研習</t>
+  </si>
+  <si>
+    <t>志為護理國際研討會</t>
+  </si>
+  <si>
+    <t>泌乳支持實務工作坊動機式晤談泌乳諮詢研習</t>
+  </si>
+  <si>
+    <t>Suno x Sora2 x oiioii x Seedance2.0動畫創作AI Agent全實戰線上研習</t>
+  </si>
+  <si>
+    <t>Winning+英文線上課程研習</t>
+  </si>
+  <si>
+    <t>Tzu Chi Nursing International Conference慈濟國際護理研討會</t>
+  </si>
+  <si>
+    <t>Nudge巧推xZ世代家長溝通教學策略研習</t>
+  </si>
+  <si>
+    <t>AI＋Skill研發協作實戰從學術研究到專案開發的效率工程研習</t>
+  </si>
+  <si>
+    <t>感控法規性別倫理(四合一)研習</t>
+  </si>
+  <si>
+    <t>人體試驗研究倫理講習班研習</t>
+  </si>
+  <si>
+    <t>回歸本能實證滋養台灣母乳哺育聯合學會20週年學術年會研習</t>
+  </si>
+  <si>
+    <t>Moonland AI視覺創作與教學實戰工作坊研習</t>
+  </si>
+  <si>
+    <t>人體試驗研究講習班研習</t>
+  </si>
+  <si>
+    <t>5大熱門AI神器一次學會研習</t>
+  </si>
+  <si>
+    <t>Linux達人系列基礎能力快速養成研習</t>
+  </si>
+  <si>
+    <t>終極學習系統6週實踐計畫快速精通的學習方法研習</t>
+  </si>
+  <si>
+    <t>一次搞定Google NotebookLM入門到進階情境整合實戰把功能變成可交付成果研習</t>
+  </si>
+  <si>
+    <t>熟齡族健康促進與體適能研習</t>
+  </si>
+  <si>
+    <t>日本HANDCARE手部按摩課程研習</t>
+  </si>
+  <si>
+    <t>法式餐點研習</t>
+  </si>
+  <si>
+    <t>西方舞蹈小品工作坊研習</t>
+  </si>
+  <si>
+    <t>生命的禮讚心靈粉彩錄影課程線上研習</t>
+  </si>
+  <si>
+    <t>國際行為發展研究學會第28屆雙年會並發表論文研習</t>
+  </si>
+  <si>
+    <t>基礎腫瘤護理訓練課程研習</t>
+  </si>
+  <si>
+    <t>Make Ideas Visible生成式AI在教材製作的實務應用研習</t>
+  </si>
+  <si>
+    <t>許祖維</t>
+  </si>
+  <si>
+    <t>社區長照機構小規模多機能籌設課程研習</t>
+  </si>
+  <si>
+    <t>第二季禮儀師教育訓練研習</t>
+  </si>
+  <si>
+    <t>AIx各行各業短影音行銷與數位教材製作教師增能</t>
+  </si>
+  <si>
+    <t>青春思播客社區性健康與性教育人才培育計畫研習</t>
+  </si>
+  <si>
+    <t>手機入班招生&amp;新生體驗無料Vibe   Coding急救包(線上課程)研習</t>
+  </si>
+  <si>
+    <t>ChatGPT5.5xCodex自動化的終極組合研習</t>
+  </si>
+  <si>
+    <t>教師參加國內研習(討)會</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1034,7 +1153,7 @@
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
     <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="37">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -1285,6 +1404,18 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="MingLiU_HKSCS"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1721,7 +1852,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1760,6 +1891,15 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="45">
@@ -10260,8 +10400,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BAC909-8D45-4443-AECB-1592B366F0B1}">
-  <dimension ref="A1:H257"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H306"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="4.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.125" customWidth="1"/>
@@ -10271,7 +10411,7 @@
     <col min="7" max="7" width="33.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10297,7 +10437,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
@@ -10320,7 +10460,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
@@ -10343,7 +10483,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
@@ -10366,7 +10506,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
@@ -10389,7 +10529,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
@@ -10415,7 +10555,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>6</v>
       </c>
@@ -10441,7 +10581,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -10464,7 +10604,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>8</v>
       </c>
@@ -10487,7 +10627,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>9</v>
       </c>
@@ -10510,7 +10650,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>10</v>
       </c>
@@ -10533,7 +10673,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>11</v>
       </c>
@@ -10556,7 +10696,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>12</v>
       </c>
@@ -10579,7 +10719,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>13</v>
       </c>
@@ -10602,7 +10742,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>14</v>
       </c>
@@ -10625,7 +10765,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>15</v>
       </c>
@@ -10648,7 +10788,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>16</v>
       </c>
@@ -10674,7 +10814,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>17</v>
       </c>
@@ -10700,7 +10840,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>18</v>
       </c>
@@ -10723,7 +10863,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>19</v>
       </c>
@@ -10746,7 +10886,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="17.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -10769,7 +10909,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>21</v>
       </c>
@@ -10795,7 +10935,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>22</v>
       </c>
@@ -10821,7 +10961,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>23</v>
       </c>
@@ -10844,7 +10984,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>24</v>
       </c>
@@ -10867,7 +11007,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>25</v>
       </c>
@@ -10890,7 +11030,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>26</v>
       </c>
@@ -10913,7 +11053,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="17.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -10936,7 +11076,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>28</v>
       </c>
@@ -10959,7 +11099,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>29</v>
       </c>
@@ -10982,7 +11122,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8">
       <c r="A31">
         <v>30</v>
       </c>
@@ -11005,7 +11145,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8">
       <c r="A32">
         <v>31</v>
       </c>
@@ -11028,7 +11168,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8">
       <c r="A33">
         <v>32</v>
       </c>
@@ -11051,7 +11191,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8">
       <c r="A34">
         <v>33</v>
       </c>
@@ -11074,7 +11214,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8">
       <c r="A35">
         <v>34</v>
       </c>
@@ -11097,7 +11237,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8">
       <c r="A36">
         <v>35</v>
       </c>
@@ -11120,7 +11260,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8">
       <c r="A37">
         <v>36</v>
       </c>
@@ -11143,7 +11283,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8">
       <c r="A38">
         <v>37</v>
       </c>
@@ -11166,7 +11306,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8">
       <c r="A39">
         <v>38</v>
       </c>
@@ -11189,7 +11329,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8">
       <c r="A40">
         <v>39</v>
       </c>
@@ -11212,7 +11352,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8">
       <c r="A41">
         <v>40</v>
       </c>
@@ -11235,7 +11375,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8">
       <c r="A42">
         <v>41</v>
       </c>
@@ -11261,7 +11401,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8">
       <c r="A43">
         <v>42</v>
       </c>
@@ -11287,7 +11427,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8">
       <c r="A44">
         <v>43</v>
       </c>
@@ -11313,7 +11453,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8">
       <c r="A45">
         <v>44</v>
       </c>
@@ -11339,7 +11479,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8">
       <c r="A46">
         <v>45</v>
       </c>
@@ -11365,7 +11505,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8">
       <c r="A47">
         <v>46</v>
       </c>
@@ -11388,7 +11528,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8">
       <c r="A48">
         <v>47</v>
       </c>
@@ -11411,7 +11551,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>48</v>
       </c>
@@ -11434,7 +11574,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7">
       <c r="A50">
         <v>49</v>
       </c>
@@ -11457,7 +11597,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7">
       <c r="A51">
         <v>50</v>
       </c>
@@ -11480,7 +11620,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7">
       <c r="A52">
         <v>51</v>
       </c>
@@ -11503,7 +11643,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7">
       <c r="A53">
         <v>52</v>
       </c>
@@ -11526,7 +11666,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7">
       <c r="A54">
         <v>53</v>
       </c>
@@ -11549,7 +11689,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7">
       <c r="A55">
         <v>54</v>
       </c>
@@ -11572,7 +11712,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7">
       <c r="A56">
         <v>55</v>
       </c>
@@ -11595,7 +11735,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7">
       <c r="A57">
         <v>56</v>
       </c>
@@ -11618,7 +11758,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7">
       <c r="A58">
         <v>57</v>
       </c>
@@ -11641,7 +11781,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7">
       <c r="A59">
         <v>58</v>
       </c>
@@ -11664,7 +11804,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7">
       <c r="A60">
         <v>59</v>
       </c>
@@ -11687,7 +11827,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7">
       <c r="A61">
         <v>60</v>
       </c>
@@ -11710,7 +11850,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7">
       <c r="A62">
         <v>61</v>
       </c>
@@ -11733,7 +11873,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7">
       <c r="A63">
         <v>62</v>
       </c>
@@ -11756,7 +11896,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7">
       <c r="A64">
         <v>63</v>
       </c>
@@ -11779,7 +11919,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8">
       <c r="A65">
         <v>64</v>
       </c>
@@ -11802,7 +11942,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8">
       <c r="A66">
         <v>65</v>
       </c>
@@ -11825,7 +11965,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8">
       <c r="A67">
         <v>66</v>
       </c>
@@ -11848,7 +11988,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8">
       <c r="A68">
         <v>67</v>
       </c>
@@ -11871,7 +12011,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8">
       <c r="A69">
         <v>68</v>
       </c>
@@ -11897,7 +12037,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8">
       <c r="A70">
         <v>69</v>
       </c>
@@ -11923,7 +12063,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8">
       <c r="A71">
         <v>70</v>
       </c>
@@ -11946,7 +12086,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8">
       <c r="A72">
         <v>71</v>
       </c>
@@ -11969,7 +12109,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8">
       <c r="A73">
         <v>72</v>
       </c>
@@ -11992,7 +12132,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" ht="17.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -12015,7 +12155,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8">
       <c r="A75">
         <v>74</v>
       </c>
@@ -12038,7 +12178,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8">
       <c r="A76">
         <v>75</v>
       </c>
@@ -12064,7 +12204,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8">
       <c r="A77">
         <v>76</v>
       </c>
@@ -12090,7 +12230,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8">
       <c r="A78">
         <v>77</v>
       </c>
@@ -12116,7 +12256,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8">
       <c r="A79">
         <v>78</v>
       </c>
@@ -12142,7 +12282,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8">
       <c r="A80">
         <v>79</v>
       </c>
@@ -12165,7 +12305,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8">
       <c r="A81">
         <v>80</v>
       </c>
@@ -12188,7 +12328,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8">
       <c r="A82">
         <v>81</v>
       </c>
@@ -12211,7 +12351,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" ht="17.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -12234,7 +12374,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8">
       <c r="A84">
         <v>83</v>
       </c>
@@ -12260,7 +12400,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8">
       <c r="A85">
         <v>84</v>
       </c>
@@ -12286,7 +12426,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8">
       <c r="A86">
         <v>85</v>
       </c>
@@ -12309,7 +12449,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8">
       <c r="A87">
         <v>86</v>
       </c>
@@ -12332,7 +12472,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8">
       <c r="A88">
         <v>87</v>
       </c>
@@ -12355,7 +12495,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8">
       <c r="A89">
         <v>88</v>
       </c>
@@ -12378,7 +12518,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8">
       <c r="A90">
         <v>89</v>
       </c>
@@ -12401,7 +12541,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8">
       <c r="A91">
         <v>90</v>
       </c>
@@ -12424,7 +12564,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8">
       <c r="A92">
         <v>91</v>
       </c>
@@ -12447,7 +12587,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8">
       <c r="A93">
         <v>92</v>
       </c>
@@ -12470,7 +12610,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8">
       <c r="A94">
         <v>93</v>
       </c>
@@ -12493,7 +12633,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8">
       <c r="A95">
         <v>94</v>
       </c>
@@ -12516,7 +12656,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8">
       <c r="A96">
         <v>95</v>
       </c>
@@ -12539,7 +12679,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8">
       <c r="A97">
         <v>96</v>
       </c>
@@ -12562,7 +12702,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8">
       <c r="A98">
         <v>97</v>
       </c>
@@ -12585,7 +12725,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8">
       <c r="A99">
         <v>98</v>
       </c>
@@ -12608,7 +12748,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8">
       <c r="A100">
         <v>99</v>
       </c>
@@ -12631,7 +12771,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8">
       <c r="A101">
         <v>100</v>
       </c>
@@ -12654,7 +12794,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8">
       <c r="A102">
         <v>101</v>
       </c>
@@ -12677,7 +12817,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8">
       <c r="A103">
         <v>102</v>
       </c>
@@ -12700,7 +12840,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8">
       <c r="A104">
         <v>103</v>
       </c>
@@ -12723,7 +12863,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8">
       <c r="A105">
         <v>104</v>
       </c>
@@ -12746,7 +12886,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8">
       <c r="A106">
         <v>105</v>
       </c>
@@ -12769,7 +12909,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8">
       <c r="A107">
         <v>106</v>
       </c>
@@ -12792,7 +12932,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8">
       <c r="A108">
         <v>107</v>
       </c>
@@ -12815,7 +12955,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8">
       <c r="A109">
         <v>108</v>
       </c>
@@ -12841,7 +12981,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8">
       <c r="A110">
         <v>109</v>
       </c>
@@ -12867,7 +13007,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8">
       <c r="A111">
         <v>110</v>
       </c>
@@ -12890,7 +13030,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8">
       <c r="A112">
         <v>111</v>
       </c>
@@ -12913,7 +13053,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8">
       <c r="A113">
         <v>112</v>
       </c>
@@ -12936,7 +13076,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8">
       <c r="A114">
         <v>113</v>
       </c>
@@ -12959,7 +13099,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8">
       <c r="A115">
         <v>114</v>
       </c>
@@ -12982,7 +13122,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8">
       <c r="A116">
         <v>115</v>
       </c>
@@ -13005,7 +13145,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8">
       <c r="A117">
         <v>116</v>
       </c>
@@ -13028,7 +13168,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" ht="17.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -13051,7 +13191,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8">
       <c r="A119">
         <v>118</v>
       </c>
@@ -13077,7 +13217,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8">
       <c r="A120">
         <v>119</v>
       </c>
@@ -13103,7 +13243,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" ht="17.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -13126,7 +13266,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8">
       <c r="A122">
         <v>121</v>
       </c>
@@ -13149,7 +13289,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8">
       <c r="A123">
         <v>122</v>
       </c>
@@ -13172,7 +13312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8">
       <c r="A124">
         <v>123</v>
       </c>
@@ -13195,7 +13335,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8">
       <c r="A125">
         <v>124</v>
       </c>
@@ -13218,7 +13358,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8">
       <c r="A126">
         <v>125</v>
       </c>
@@ -13241,7 +13381,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8">
       <c r="A127">
         <v>126</v>
       </c>
@@ -13264,7 +13404,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8">
       <c r="A128">
         <v>127</v>
       </c>
@@ -13287,7 +13427,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7">
       <c r="A129">
         <v>128</v>
       </c>
@@ -13310,7 +13450,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" ht="17.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -13333,7 +13473,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7">
       <c r="A131">
         <v>130</v>
       </c>
@@ -13356,7 +13496,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7">
       <c r="A132">
         <v>131</v>
       </c>
@@ -13379,7 +13519,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" ht="17.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -13402,7 +13542,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7">
       <c r="A134">
         <v>133</v>
       </c>
@@ -13425,7 +13565,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7">
       <c r="A135">
         <v>134</v>
       </c>
@@ -13448,7 +13588,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7">
       <c r="A136">
         <v>135</v>
       </c>
@@ -13471,7 +13611,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" ht="17.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -13494,7 +13634,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7">
       <c r="A138">
         <v>137</v>
       </c>
@@ -13517,7 +13657,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7">
       <c r="A139">
         <v>138</v>
       </c>
@@ -13540,7 +13680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7">
       <c r="A140">
         <v>139</v>
       </c>
@@ -13563,7 +13703,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7">
       <c r="A141">
         <v>140</v>
       </c>
@@ -13586,7 +13726,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7">
       <c r="A142">
         <v>141</v>
       </c>
@@ -13609,7 +13749,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7">
       <c r="A143">
         <v>142</v>
       </c>
@@ -13632,7 +13772,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7">
       <c r="A144">
         <v>143</v>
       </c>
@@ -13655,7 +13795,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8">
       <c r="A145">
         <v>144</v>
       </c>
@@ -13678,7 +13818,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8">
       <c r="A146">
         <v>145</v>
       </c>
@@ -13701,7 +13841,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8">
       <c r="A147">
         <v>146</v>
       </c>
@@ -13724,7 +13864,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8">
       <c r="A148">
         <v>147</v>
       </c>
@@ -13747,7 +13887,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8">
       <c r="A149">
         <v>148</v>
       </c>
@@ -13770,7 +13910,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8">
       <c r="A150">
         <v>149</v>
       </c>
@@ -13793,7 +13933,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8">
       <c r="A151">
         <v>150</v>
       </c>
@@ -13819,7 +13959,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8">
       <c r="A152">
         <v>151</v>
       </c>
@@ -13845,7 +13985,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8">
       <c r="A153">
         <v>152</v>
       </c>
@@ -13868,7 +14008,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8">
       <c r="A154">
         <v>153</v>
       </c>
@@ -13891,7 +14031,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8">
       <c r="A155">
         <v>154</v>
       </c>
@@ -13914,7 +14054,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8">
       <c r="A156">
         <v>155</v>
       </c>
@@ -13937,7 +14077,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8">
       <c r="A157">
         <v>156</v>
       </c>
@@ -13960,7 +14100,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8">
       <c r="A158">
         <v>157</v>
       </c>
@@ -13983,7 +14123,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8">
       <c r="A159">
         <v>158</v>
       </c>
@@ -14006,7 +14146,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8">
       <c r="A160">
         <v>159</v>
       </c>
@@ -14029,7 +14169,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7">
       <c r="A161">
         <v>160</v>
       </c>
@@ -14052,7 +14192,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7" ht="17.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -14075,7 +14215,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7">
       <c r="A163">
         <v>162</v>
       </c>
@@ -14098,7 +14238,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7">
       <c r="A164">
         <v>163</v>
       </c>
@@ -14121,7 +14261,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" ht="17.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -14144,7 +14284,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7">
       <c r="A166">
         <v>165</v>
       </c>
@@ -14167,7 +14307,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7">
       <c r="A167">
         <v>166</v>
       </c>
@@ -14190,7 +14330,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7">
       <c r="A168">
         <v>167</v>
       </c>
@@ -14213,7 +14353,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7">
       <c r="A169">
         <v>168</v>
       </c>
@@ -14236,7 +14376,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7">
       <c r="A170">
         <v>169</v>
       </c>
@@ -14259,7 +14399,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7">
       <c r="A171">
         <v>170</v>
       </c>
@@ -14282,7 +14422,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" ht="17.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -14305,7 +14445,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7">
       <c r="A173">
         <v>172</v>
       </c>
@@ -14328,7 +14468,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7">
       <c r="A174">
         <v>173</v>
       </c>
@@ -14351,7 +14491,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7">
       <c r="A175">
         <v>174</v>
       </c>
@@ -14374,7 +14514,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:7">
       <c r="A176">
         <v>175</v>
       </c>
@@ -14397,7 +14537,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8">
       <c r="A177">
         <v>176</v>
       </c>
@@ -14420,7 +14560,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8">
       <c r="A178">
         <v>177</v>
       </c>
@@ -14443,7 +14583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" ht="17.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -14466,7 +14606,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8">
       <c r="A180">
         <v>179</v>
       </c>
@@ -14492,7 +14632,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8">
       <c r="A181">
         <v>180</v>
       </c>
@@ -14518,7 +14658,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8">
       <c r="A182">
         <v>181</v>
       </c>
@@ -14541,7 +14681,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8">
       <c r="A183">
         <v>182</v>
       </c>
@@ -14564,7 +14704,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8">
       <c r="A184">
         <v>183</v>
       </c>
@@ -14587,7 +14727,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8">
       <c r="A185">
         <v>184</v>
       </c>
@@ -14610,7 +14750,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" ht="17.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -14633,7 +14773,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8">
       <c r="A187">
         <v>186</v>
       </c>
@@ -14656,7 +14796,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8">
       <c r="A188">
         <v>187</v>
       </c>
@@ -14679,7 +14819,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:8">
       <c r="A189">
         <v>188</v>
       </c>
@@ -14702,7 +14842,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:8">
       <c r="A190">
         <v>189</v>
       </c>
@@ -14725,7 +14865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:8">
       <c r="A191">
         <v>190</v>
       </c>
@@ -14748,7 +14888,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:8">
       <c r="A192">
         <v>191</v>
       </c>
@@ -14771,7 +14911,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:8">
       <c r="A193">
         <v>192</v>
       </c>
@@ -14794,7 +14934,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8">
       <c r="A194">
         <v>193</v>
       </c>
@@ -14817,7 +14957,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8">
       <c r="A195">
         <v>194</v>
       </c>
@@ -14840,7 +14980,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:8">
       <c r="A196">
         <v>195</v>
       </c>
@@ -14863,7 +15003,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8">
       <c r="A197">
         <v>196</v>
       </c>
@@ -14886,7 +15026,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8">
       <c r="A198">
         <v>197</v>
       </c>
@@ -14912,7 +15052,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8">
       <c r="A199">
         <v>198</v>
       </c>
@@ -14938,7 +15078,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8">
       <c r="A200">
         <v>199</v>
       </c>
@@ -14961,7 +15101,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:8">
       <c r="A201">
         <v>200</v>
       </c>
@@ -14984,7 +15124,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:8">
       <c r="A202">
         <v>201</v>
       </c>
@@ -15007,7 +15147,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:8">
       <c r="A203">
         <v>202</v>
       </c>
@@ -15030,7 +15170,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:8">
       <c r="A204">
         <v>203</v>
       </c>
@@ -15053,7 +15193,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:8">
       <c r="A205">
         <v>204</v>
       </c>
@@ -15076,7 +15216,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:8">
       <c r="A206">
         <v>205</v>
       </c>
@@ -15099,7 +15239,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:8">
       <c r="A207">
         <v>206</v>
       </c>
@@ -15122,7 +15262,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:8">
       <c r="A208">
         <v>207</v>
       </c>
@@ -15145,7 +15285,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" ht="17.25">
       <c r="A209">
         <v>208</v>
       </c>
@@ -15168,7 +15308,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:8">
       <c r="A210">
         <v>209</v>
       </c>
@@ -15191,7 +15331,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:8">
       <c r="A211">
         <v>210</v>
       </c>
@@ -15214,7 +15354,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:8" ht="17.25">
       <c r="A212">
         <v>211</v>
       </c>
@@ -15237,7 +15377,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:8">
       <c r="A213">
         <v>212</v>
       </c>
@@ -15260,7 +15400,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:8">
       <c r="A214">
         <v>213</v>
       </c>
@@ -15283,7 +15423,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8">
       <c r="A215">
         <v>214</v>
       </c>
@@ -15306,7 +15446,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:8">
       <c r="A216">
         <v>215</v>
       </c>
@@ -15329,7 +15469,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:8">
       <c r="A217">
         <v>216</v>
       </c>
@@ -15352,7 +15492,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:8">
       <c r="A218">
         <v>217</v>
       </c>
@@ -15378,7 +15518,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:8">
       <c r="A219">
         <v>218</v>
       </c>
@@ -15404,7 +15544,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:8">
       <c r="A220">
         <v>219</v>
       </c>
@@ -15430,7 +15570,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:8">
       <c r="A221">
         <v>220</v>
       </c>
@@ -15456,7 +15596,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:8">
       <c r="A222">
         <v>221</v>
       </c>
@@ -15479,7 +15619,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:8">
       <c r="A223">
         <v>222</v>
       </c>
@@ -15502,7 +15642,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:8">
       <c r="A224">
         <v>223</v>
       </c>
@@ -15525,7 +15665,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:8">
       <c r="A225">
         <v>224</v>
       </c>
@@ -15551,7 +15691,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:8">
       <c r="A226">
         <v>225</v>
       </c>
@@ -15577,7 +15717,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:8">
       <c r="A227">
         <v>226</v>
       </c>
@@ -15600,7 +15740,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:8">
       <c r="A228">
         <v>227</v>
       </c>
@@ -15623,7 +15763,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:8">
       <c r="A229">
         <v>228</v>
       </c>
@@ -15646,7 +15786,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:8">
       <c r="A230">
         <v>229</v>
       </c>
@@ -15672,7 +15812,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:8">
       <c r="A231">
         <v>230</v>
       </c>
@@ -15698,7 +15838,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:8">
       <c r="A232">
         <v>231</v>
       </c>
@@ -15721,7 +15861,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:8">
       <c r="A233">
         <v>232</v>
       </c>
@@ -15744,7 +15884,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:8">
       <c r="A234">
         <v>233</v>
       </c>
@@ -15767,7 +15907,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:8">
       <c r="A235">
         <v>234</v>
       </c>
@@ -15790,7 +15930,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:8">
       <c r="A236">
         <v>235</v>
       </c>
@@ -15813,7 +15953,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:8">
       <c r="A237">
         <v>236</v>
       </c>
@@ -15836,7 +15976,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:8">
       <c r="A238">
         <v>237</v>
       </c>
@@ -15859,7 +15999,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:8">
       <c r="A239">
         <v>238</v>
       </c>
@@ -15882,7 +16022,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:8">
       <c r="A240">
         <v>239</v>
       </c>
@@ -15905,7 +16045,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:7">
       <c r="A241">
         <v>240</v>
       </c>
@@ -15928,7 +16068,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:7">
       <c r="A242">
         <v>241</v>
       </c>
@@ -15951,7 +16091,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:7">
       <c r="A243">
         <v>242</v>
       </c>
@@ -15974,7 +16114,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:7">
       <c r="A244">
         <v>243</v>
       </c>
@@ -15997,7 +16137,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:7">
       <c r="A245">
         <v>244</v>
       </c>
@@ -16020,7 +16160,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:7">
       <c r="A246">
         <v>245</v>
       </c>
@@ -16043,7 +16183,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:7">
       <c r="A247">
         <v>246</v>
       </c>
@@ -16066,7 +16206,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:7">
       <c r="A248">
         <v>247</v>
       </c>
@@ -16089,7 +16229,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:7">
       <c r="A249">
         <v>248</v>
       </c>
@@ -16112,7 +16252,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:7">
       <c r="A250">
         <v>249</v>
       </c>
@@ -16135,7 +16275,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:7">
       <c r="A251">
         <v>250</v>
       </c>
@@ -16158,7 +16298,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:7">
       <c r="A252">
         <v>251</v>
       </c>
@@ -16181,7 +16321,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="253" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:7" ht="17.25">
       <c r="A253">
         <v>252</v>
       </c>
@@ -16204,7 +16344,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:7">
       <c r="A254">
         <v>253</v>
       </c>
@@ -16227,7 +16367,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:7">
       <c r="A255">
         <v>254</v>
       </c>
@@ -16250,7 +16390,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:7">
       <c r="A256">
         <v>255</v>
       </c>
@@ -16273,7 +16413,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:8">
       <c r="A257">
         <v>256</v>
       </c>
@@ -16294,6 +16434,1133 @@
       </c>
       <c r="G257" t="s">
         <v>167</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8">
+      <c r="A258">
+        <v>257</v>
+      </c>
+      <c r="B258" s="1">
+        <v>115</v>
+      </c>
+      <c r="C258" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D258" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F258" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H258" s="13" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8">
+      <c r="A259">
+        <v>258</v>
+      </c>
+      <c r="B259" s="1">
+        <v>115</v>
+      </c>
+      <c r="C259" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D259" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F259" s="14">
+        <v>3600</v>
+      </c>
+      <c r="H259" s="13" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8">
+      <c r="A260">
+        <v>259</v>
+      </c>
+      <c r="B260" s="1">
+        <v>115</v>
+      </c>
+      <c r="C260" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D260" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F260" s="14">
+        <v>4800</v>
+      </c>
+      <c r="H260" s="13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8">
+      <c r="A261">
+        <v>260</v>
+      </c>
+      <c r="B261" s="1">
+        <v>115</v>
+      </c>
+      <c r="C261" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F261" s="14">
+        <v>6000</v>
+      </c>
+      <c r="H261" s="13" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8">
+      <c r="A262">
+        <v>261</v>
+      </c>
+      <c r="B262" s="1">
+        <v>115</v>
+      </c>
+      <c r="C262" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F262" s="14">
+        <v>4800</v>
+      </c>
+      <c r="H262" s="13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8">
+      <c r="A263">
+        <v>262</v>
+      </c>
+      <c r="B263" s="1">
+        <v>115</v>
+      </c>
+      <c r="C263" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F263" s="14">
+        <v>4800</v>
+      </c>
+      <c r="H263" s="13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8">
+      <c r="A264">
+        <v>263</v>
+      </c>
+      <c r="B264" s="1">
+        <v>115</v>
+      </c>
+      <c r="C264" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F264" s="14">
+        <v>3000</v>
+      </c>
+      <c r="H264" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8">
+      <c r="A265">
+        <v>264</v>
+      </c>
+      <c r="B265" s="1">
+        <v>115</v>
+      </c>
+      <c r="C265" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F265" s="15">
+        <v>500</v>
+      </c>
+      <c r="H265" s="13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8">
+      <c r="A266">
+        <v>265</v>
+      </c>
+      <c r="B266" s="1">
+        <v>115</v>
+      </c>
+      <c r="C266" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F266" s="14">
+        <v>3000</v>
+      </c>
+      <c r="H266" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8">
+      <c r="A267">
+        <v>266</v>
+      </c>
+      <c r="B267" s="1">
+        <v>115</v>
+      </c>
+      <c r="C267" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F267" s="14">
+        <v>3166</v>
+      </c>
+      <c r="H267" s="13" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8">
+      <c r="A268">
+        <v>267</v>
+      </c>
+      <c r="B268" s="1">
+        <v>115</v>
+      </c>
+      <c r="C268" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F268" s="14">
+        <v>4500</v>
+      </c>
+      <c r="H268" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8">
+      <c r="A269">
+        <v>268</v>
+      </c>
+      <c r="B269" s="1">
+        <v>115</v>
+      </c>
+      <c r="C269" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F269" s="14">
+        <v>2000</v>
+      </c>
+      <c r="H269" s="13" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8">
+      <c r="A270">
+        <v>269</v>
+      </c>
+      <c r="B270" s="1">
+        <v>115</v>
+      </c>
+      <c r="C270" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F270" s="14">
+        <v>20000</v>
+      </c>
+      <c r="H270" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8">
+      <c r="A271">
+        <v>270</v>
+      </c>
+      <c r="B271" s="1">
+        <v>115</v>
+      </c>
+      <c r="C271" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F271" s="14">
+        <v>3081</v>
+      </c>
+      <c r="H271" s="13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8">
+      <c r="A272">
+        <v>271</v>
+      </c>
+      <c r="B272" s="1">
+        <v>115</v>
+      </c>
+      <c r="C272" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="D272" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F272" s="14">
+        <v>2400</v>
+      </c>
+      <c r="H272" s="13" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8">
+      <c r="A273">
+        <v>272</v>
+      </c>
+      <c r="B273" s="1">
+        <v>115</v>
+      </c>
+      <c r="C273" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D273" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F273" s="14">
+        <v>2000</v>
+      </c>
+      <c r="H273" s="13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8">
+      <c r="A274">
+        <v>273</v>
+      </c>
+      <c r="B274" s="1">
+        <v>115</v>
+      </c>
+      <c r="C274" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F274" s="15">
+        <v>850</v>
+      </c>
+      <c r="H274" s="13" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8">
+      <c r="A275">
+        <v>274</v>
+      </c>
+      <c r="B275" s="1">
+        <v>115</v>
+      </c>
+      <c r="C275" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F275" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H275" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8">
+      <c r="A276">
+        <v>275</v>
+      </c>
+      <c r="B276" s="1">
+        <v>115</v>
+      </c>
+      <c r="C276" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F276" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H276" s="13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8">
+      <c r="A277">
+        <v>276</v>
+      </c>
+      <c r="B277" s="1">
+        <v>115</v>
+      </c>
+      <c r="C277" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F277" s="15">
+        <v>688</v>
+      </c>
+      <c r="H277" s="13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8">
+      <c r="A278">
+        <v>277</v>
+      </c>
+      <c r="B278" s="1">
+        <v>115</v>
+      </c>
+      <c r="C278" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D278" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F278" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H278" s="13" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8">
+      <c r="A279">
+        <v>278</v>
+      </c>
+      <c r="B279" s="1">
+        <v>115</v>
+      </c>
+      <c r="C279" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E279" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F279" s="14">
+        <v>4800</v>
+      </c>
+      <c r="H279" s="13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8">
+      <c r="A280">
+        <v>279</v>
+      </c>
+      <c r="B280" s="1">
+        <v>115</v>
+      </c>
+      <c r="C280" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F280" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H280" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8">
+      <c r="A281">
+        <v>280</v>
+      </c>
+      <c r="B281" s="1">
+        <v>115</v>
+      </c>
+      <c r="C281" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E281" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F281" s="15">
+        <v>999</v>
+      </c>
+      <c r="H281" s="13" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8">
+      <c r="A282">
+        <v>281</v>
+      </c>
+      <c r="B282" s="1">
+        <v>115</v>
+      </c>
+      <c r="C282" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E282" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F282" s="14">
+        <v>4090</v>
+      </c>
+      <c r="H282" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8">
+      <c r="A283">
+        <v>282</v>
+      </c>
+      <c r="B283" s="1">
+        <v>115</v>
+      </c>
+      <c r="C283" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E283" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F283" s="14">
+        <v>8900</v>
+      </c>
+      <c r="H283" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8">
+      <c r="A284">
+        <v>283</v>
+      </c>
+      <c r="B284" s="1">
+        <v>115</v>
+      </c>
+      <c r="C284" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E284" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F284" s="14">
+        <v>2490</v>
+      </c>
+      <c r="H284" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8">
+      <c r="A285">
+        <v>284</v>
+      </c>
+      <c r="B285" s="1">
+        <v>115</v>
+      </c>
+      <c r="C285" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E285" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F285" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H285" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8">
+      <c r="A286">
+        <v>285</v>
+      </c>
+      <c r="B286" s="1">
+        <v>115</v>
+      </c>
+      <c r="C286" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E286" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F286" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H286" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8">
+      <c r="A287">
+        <v>286</v>
+      </c>
+      <c r="B287" s="1">
+        <v>115</v>
+      </c>
+      <c r="C287" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F287" s="14">
+        <v>4600</v>
+      </c>
+      <c r="H287" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8">
+      <c r="A288">
+        <v>287</v>
+      </c>
+      <c r="B288" s="1">
+        <v>115</v>
+      </c>
+      <c r="C288" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F288" s="14">
+        <v>4600</v>
+      </c>
+      <c r="H288" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8">
+      <c r="A289">
+        <v>288</v>
+      </c>
+      <c r="B289" s="1">
+        <v>115</v>
+      </c>
+      <c r="C289" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F289" s="14">
+        <v>7000</v>
+      </c>
+      <c r="H289" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8">
+      <c r="A290">
+        <v>289</v>
+      </c>
+      <c r="B290" s="1">
+        <v>115</v>
+      </c>
+      <c r="C290" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E290" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F290" s="14">
+        <v>4600</v>
+      </c>
+      <c r="H290" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8">
+      <c r="A291">
+        <v>290</v>
+      </c>
+      <c r="B291" s="1">
+        <v>115</v>
+      </c>
+      <c r="C291" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="D291" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E291" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F291" s="14">
+        <v>7000</v>
+      </c>
+      <c r="H291" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8">
+      <c r="A292">
+        <v>291</v>
+      </c>
+      <c r="B292" s="1">
+        <v>115</v>
+      </c>
+      <c r="C292" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D292" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E292" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F292" s="14">
+        <v>3600</v>
+      </c>
+      <c r="H292" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8">
+      <c r="A293">
+        <v>292</v>
+      </c>
+      <c r="B293" s="1">
+        <v>115</v>
+      </c>
+      <c r="C293" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="D293" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E293" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F293" s="14">
+        <v>20000</v>
+      </c>
+      <c r="H293" s="13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8">
+      <c r="A294">
+        <v>293</v>
+      </c>
+      <c r="B294" s="1">
+        <v>115</v>
+      </c>
+      <c r="C294" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D294" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E294" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F294" s="14">
+        <v>3582</v>
+      </c>
+      <c r="H294" s="13" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8">
+      <c r="A295">
+        <v>294</v>
+      </c>
+      <c r="B295" s="1">
+        <v>115</v>
+      </c>
+      <c r="C295" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D295" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E295" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F295" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H295" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8">
+      <c r="A296">
+        <v>295</v>
+      </c>
+      <c r="B296" s="1">
+        <v>115</v>
+      </c>
+      <c r="C296" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D296" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E296" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F296" s="14">
+        <v>8900</v>
+      </c>
+      <c r="H296" s="13" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8">
+      <c r="A297">
+        <v>296</v>
+      </c>
+      <c r="B297" s="1">
+        <v>115</v>
+      </c>
+      <c r="C297" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E297" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F297" s="14">
+        <v>7200</v>
+      </c>
+      <c r="H297" s="13" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8">
+      <c r="A298">
+        <v>297</v>
+      </c>
+      <c r="B298" s="1">
+        <v>115</v>
+      </c>
+      <c r="C298" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E298" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F298" s="15">
+        <v>500</v>
+      </c>
+      <c r="H298" s="13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8">
+      <c r="A299">
+        <v>298</v>
+      </c>
+      <c r="B299" s="1">
+        <v>115</v>
+      </c>
+      <c r="C299" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="D299" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E299" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F299" s="14">
+        <v>7800</v>
+      </c>
+      <c r="H299" s="13" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8">
+      <c r="A300">
+        <v>299</v>
+      </c>
+      <c r="B300" s="1">
+        <v>115</v>
+      </c>
+      <c r="C300" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="D300" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E300" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F300" s="14">
+        <v>2400</v>
+      </c>
+      <c r="H300" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8">
+      <c r="A301">
+        <v>300</v>
+      </c>
+      <c r="B301" s="1">
+        <v>115</v>
+      </c>
+      <c r="C301" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D301" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E301" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F301" s="14">
+        <v>12000</v>
+      </c>
+      <c r="H301" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8">
+      <c r="A302">
+        <v>301</v>
+      </c>
+      <c r="B302" s="1">
+        <v>115</v>
+      </c>
+      <c r="C302" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D302" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E302" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F302" s="14">
+        <v>12000</v>
+      </c>
+      <c r="H302" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8">
+      <c r="A303">
+        <v>302</v>
+      </c>
+      <c r="B303" s="1">
+        <v>115</v>
+      </c>
+      <c r="C303" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D303" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E303" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F303" s="14">
+        <v>12000</v>
+      </c>
+      <c r="H303" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8">
+      <c r="A304">
+        <v>303</v>
+      </c>
+      <c r="B304" s="1">
+        <v>115</v>
+      </c>
+      <c r="C304" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E304" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F304" s="14">
+        <v>5960</v>
+      </c>
+      <c r="H304" s="13" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8">
+      <c r="A305">
+        <v>304</v>
+      </c>
+      <c r="B305" s="1">
+        <v>115</v>
+      </c>
+      <c r="C305" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E305" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F305" s="14">
+        <v>2000</v>
+      </c>
+      <c r="H305" s="13" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8">
+      <c r="A306">
+        <v>305</v>
+      </c>
+      <c r="B306" s="1">
+        <v>115</v>
+      </c>
+      <c r="C306" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E306" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F306" s="14">
+        <v>2000</v>
+      </c>
+      <c r="H306" s="13" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -16304,4 +17571,554 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4EDA9A-D572-46FD-8A89-9AA665A34A78}">
+  <dimension ref="A1:D49"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="14">
+        <v>1000</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="14">
+        <v>3600</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="14">
+        <v>4800</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="14">
+        <v>6000</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="14">
+        <v>4800</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="14">
+        <v>4800</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="14">
+        <v>3000</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="15">
+        <v>500</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="14">
+        <v>3000</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="14">
+        <v>3166</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="14">
+        <v>4500</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="14">
+        <v>20000</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="14">
+        <v>3081</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="14">
+        <v>2400</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="C17" s="15">
+        <v>850</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="14">
+        <v>1000</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" s="14">
+        <v>1000</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="15">
+        <v>688</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="14">
+        <v>1000</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="14">
+        <v>4800</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="14">
+        <v>1000</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="15">
+        <v>999</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="14">
+        <v>4090</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="14">
+        <v>8900</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="14">
+        <v>2490</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" s="14">
+        <v>1000</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="14">
+        <v>1000</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="14">
+        <v>4600</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="14">
+        <v>4600</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="14">
+        <v>7000</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C33" s="14">
+        <v>4600</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C34" s="14">
+        <v>7000</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="14">
+        <v>3600</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="C36" s="14">
+        <v>20000</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="14">
+        <v>3582</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="14">
+        <v>1000</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="14">
+        <v>8900</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="C40" s="14">
+        <v>7200</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" s="15">
+        <v>500</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="C42" s="14">
+        <v>7800</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C43" s="14">
+        <v>2400</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" s="14">
+        <v>12000</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="14">
+        <v>12000</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C46" s="14">
+        <v>12000</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C47" s="14">
+        <v>5960</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C48" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C49" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>222</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C92ACFB3-42BE-478A-9F41-898547ADC62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2294B3F-7E5F-4A72-995B-22913B073146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10490,20 +10490,20 @@
       <c r="B4" s="1">
         <v>115</v>
       </c>
-      <c r="C4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>86</v>
+      <c r="C4" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F4" s="11">
-        <v>5100</v>
-      </c>
-      <c r="G4" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F4" s="14">
+        <v>3000</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -10514,16 +10514,16 @@
         <v>115</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
+        <v>121</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F5" s="11">
-        <v>3500</v>
+        <v>5100</v>
       </c>
       <c r="G5" t="s">
         <v>167</v>
@@ -10537,22 +10537,19 @@
         <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F6" s="2">
-        <v>29000</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H6" t="s">
-        <v>112</v>
+      <c r="E6" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F6" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G6" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -10569,10 +10566,10 @@
         <v>23</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F7" s="2">
-        <v>2000</v>
+        <v>29000</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>116</v>
@@ -10594,14 +10591,17 @@
       <c r="D8" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F8" s="11">
-        <v>5000</v>
-      </c>
-      <c r="G8" t="s">
-        <v>167</v>
+      <c r="E8" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F8" s="2">
+        <v>2000</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H8" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -10611,20 +10611,20 @@
       <c r="B9" s="1">
         <v>115</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="C9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" t="s">
         <v>23</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F9" s="11">
+        <v>5000</v>
+      </c>
+      <c r="G9" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -10634,20 +10634,20 @@
       <c r="B10" s="1">
         <v>115</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F10" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G10" t="s">
-        <v>167</v>
+        <v>7</v>
+      </c>
+      <c r="F10" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -10657,20 +10657,20 @@
       <c r="B11" s="1">
         <v>115</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>10</v>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="2">
-        <v>52500</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F11" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G11" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -10687,10 +10687,10 @@
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F12" s="2">
-        <v>56000</v>
+        <v>52500</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>8</v>
@@ -10703,20 +10703,20 @@
       <c r="B13" s="1">
         <v>115</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F13" s="11">
-        <v>3700</v>
-      </c>
-      <c r="G13" t="s">
-        <v>167</v>
+        <v>7</v>
+      </c>
+      <c r="F13" s="2">
+        <v>56000</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -10726,20 +10726,20 @@
       <c r="B14" s="1">
         <v>115</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>13</v>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F14" s="11">
+        <v>3700</v>
+      </c>
+      <c r="G14" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -10756,13 +10756,13 @@
         <v>13</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F15" s="2">
-        <v>43084</v>
+        <v>40000</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>84</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -10772,20 +10772,20 @@
       <c r="B16" s="1">
         <v>115</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F16" s="11">
-        <v>500</v>
-      </c>
-      <c r="G16" t="s">
-        <v>167</v>
+        <v>83</v>
+      </c>
+      <c r="F16" s="2">
+        <v>43084</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -10796,22 +10796,19 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F17" s="2">
-        <v>29636</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H17" t="s">
-        <v>103</v>
+        <v>13</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F17" s="11">
+        <v>500</v>
+      </c>
+      <c r="G17" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -10828,10 +10825,10 @@
         <v>23</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F18" s="2">
-        <v>11068</v>
+        <v>29636</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>116</v>
@@ -10853,14 +10850,17 @@
       <c r="D19" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F19" s="11">
-        <v>3900</v>
-      </c>
-      <c r="G19" t="s">
-        <v>167</v>
+      <c r="E19" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F19" s="2">
+        <v>11068</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H19" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -10870,43 +10870,43 @@
       <c r="B20" s="1">
         <v>115</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="1" t="s">
+      <c r="C20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" t="s">
         <v>23</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" s="2">
-        <v>51931</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="17.25">
+        <v>169</v>
+      </c>
+      <c r="F20" s="11">
+        <v>3900</v>
+      </c>
+      <c r="G20" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="1">
         <v>115</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>14</v>
+      <c r="C21" s="13" t="s">
+        <v>95</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F21" s="2">
-        <v>128075</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>82</v>
+      <c r="E21" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F21" s="14">
+        <v>4800</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -10916,23 +10916,20 @@
       <c r="B22" s="1">
         <v>115</v>
       </c>
-      <c r="C22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="C22" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E22" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F22" s="2">
-        <v>30850</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H22" t="s">
-        <v>102</v>
+      <c r="E22" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F22" s="14">
+        <v>3166</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -10942,46 +10939,43 @@
       <c r="B23" s="1">
         <v>115</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E23" s="10" t="s">
-        <v>171</v>
+      <c r="E23" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F23" s="2">
-        <v>12726</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H23" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>51931</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="17.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" s="1">
         <v>115</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F24" s="11">
-        <v>7600</v>
-      </c>
-      <c r="G24" t="s">
-        <v>167</v>
+      <c r="E24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" s="2">
+        <v>128075</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -10992,19 +10986,22 @@
         <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>144</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
         <v>23</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F25" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G25" t="s">
-        <v>167</v>
+      <c r="E25" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F25" s="2">
+        <v>30850</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H25" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -11015,19 +11012,22 @@
         <v>115</v>
       </c>
       <c r="C26" t="s">
-        <v>145</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
         <v>23</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F26" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G26" t="s">
-        <v>167</v>
+      <c r="E26" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F26" s="2">
+        <v>12726</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H26" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -11037,43 +11037,43 @@
       <c r="B27" s="1">
         <v>115</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>16</v>
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" t="s">
+        <v>23</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="17.25">
+        <v>169</v>
+      </c>
+      <c r="F27" s="11">
+        <v>7600</v>
+      </c>
+      <c r="G27" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" s="1">
         <v>115</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F28" s="2">
-        <v>165000</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>82</v>
+      <c r="C28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F28" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G28" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -11083,20 +11083,20 @@
       <c r="B29" s="1">
         <v>115</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>15</v>
+      <c r="C29" s="13" t="s">
+        <v>144</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F29" s="2">
-        <v>8285</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>84</v>
+        <v>223</v>
+      </c>
+      <c r="F29" s="14">
+        <v>4600</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -11107,16 +11107,16 @@
         <v>115</v>
       </c>
       <c r="C30" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F30" s="11">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="G30" t="s">
         <v>167</v>
@@ -11129,20 +11129,20 @@
       <c r="B31" s="1">
         <v>115</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>17</v>
+      <c r="C31" s="13" t="s">
+        <v>145</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" s="2">
-        <v>48000</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>8</v>
+        <v>223</v>
+      </c>
+      <c r="F31" s="14">
+        <v>4600</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -11152,20 +11152,20 @@
       <c r="B32" s="1">
         <v>115</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>17</v>
+      <c r="C32" s="13" t="s">
+        <v>145</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F32" s="2">
-        <v>62600</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>84</v>
+        <v>223</v>
+      </c>
+      <c r="F32" s="14">
+        <v>7000</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -11175,23 +11175,23 @@
       <c r="B33" s="1">
         <v>115</v>
       </c>
-      <c r="C33" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" t="s">
-        <v>13</v>
+      <c r="C33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F33" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G33" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+        <v>11</v>
+      </c>
+      <c r="F33" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="17.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -11199,19 +11199,19 @@
         <v>115</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F34" s="2">
-        <v>56000</v>
+        <v>165000</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -11222,7 +11222,7 @@
         <v>115</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>16</v>
@@ -11231,7 +11231,7 @@
         <v>83</v>
       </c>
       <c r="F35" s="2">
-        <v>18412</v>
+        <v>8285</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>84</v>
@@ -11245,7 +11245,7 @@
         <v>115</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D36" t="s">
         <v>16</v>
@@ -11267,20 +11267,20 @@
       <c r="B37" s="1">
         <v>115</v>
       </c>
-      <c r="C37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D37" s="10" t="s">
+      <c r="C37" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>78</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F37">
-        <v>45000</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>184</v>
+        <v>223</v>
+      </c>
+      <c r="F37" s="14">
+        <v>12000</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -11290,20 +11290,20 @@
       <c r="B38" s="1">
         <v>115</v>
       </c>
-      <c r="C38" t="s">
-        <v>120</v>
-      </c>
-      <c r="D38" t="s">
-        <v>20</v>
+      <c r="C38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F38" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G38" t="s">
-        <v>167</v>
+        <v>7</v>
+      </c>
+      <c r="F38" s="2">
+        <v>48000</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -11313,20 +11313,20 @@
       <c r="B39" s="1">
         <v>115</v>
       </c>
-      <c r="C39" t="s">
-        <v>130</v>
-      </c>
-      <c r="D39" t="s">
-        <v>23</v>
+      <c r="C39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F39" s="11">
-        <v>3900</v>
-      </c>
-      <c r="G39" t="s">
-        <v>167</v>
+        <v>83</v>
+      </c>
+      <c r="F39" s="2">
+        <v>62600</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -11336,20 +11336,20 @@
       <c r="B40" s="1">
         <v>115</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>16</v>
+      <c r="C40" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" t="s">
+        <v>13</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F40" s="2">
-        <v>16571</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>84</v>
+        <v>169</v>
+      </c>
+      <c r="F40" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G40" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -11359,20 +11359,20 @@
       <c r="B41" s="1">
         <v>115</v>
       </c>
-      <c r="C41" t="s">
-        <v>68</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="C41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F41" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G41" t="s">
-        <v>167</v>
+        <v>11</v>
+      </c>
+      <c r="F41" s="2">
+        <v>56000</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -11382,23 +11382,20 @@
       <c r="B42" s="1">
         <v>115</v>
       </c>
-      <c r="C42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="C42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E42" t="s">
-        <v>178</v>
-      </c>
-      <c r="F42" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H42" t="s">
-        <v>173</v>
+      <c r="E42" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42" s="2">
+        <v>18412</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -11409,22 +11406,19 @@
         <v>115</v>
       </c>
       <c r="C43" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="D43" t="s">
         <v>16</v>
       </c>
-      <c r="E43" t="s">
-        <v>178</v>
+      <c r="E43" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="F43" s="11">
         <v>10000</v>
       </c>
-      <c r="G43" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H43" t="s">
-        <v>174</v>
+      <c r="G43" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -11435,22 +11429,19 @@
         <v>115</v>
       </c>
       <c r="C44" t="s">
-        <v>68</v>
-      </c>
-      <c r="D44" t="s">
-        <v>16</v>
-      </c>
-      <c r="E44" t="s">
-        <v>178</v>
-      </c>
-      <c r="F44" s="11">
-        <v>10000</v>
+        <v>18</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F44">
+        <v>45000</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H44" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -11461,22 +11452,19 @@
         <v>115</v>
       </c>
       <c r="C45" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
-      </c>
-      <c r="E45" t="s">
-        <v>178</v>
+        <v>20</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="F45" s="11">
         <v>10000</v>
       </c>
-      <c r="G45" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H45" t="s">
-        <v>176</v>
+      <c r="G45" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -11487,22 +11475,19 @@
         <v>115</v>
       </c>
       <c r="C46" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
-      </c>
-      <c r="E46" t="s">
-        <v>178</v>
+        <v>23</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="F46" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H46" t="s">
-        <v>177</v>
+        <v>3900</v>
+      </c>
+      <c r="G46" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -11513,19 +11498,19 @@
         <v>115</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="F47" s="2">
-        <v>31500</v>
+        <v>16571</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -11536,22 +11521,22 @@
         <v>115</v>
       </c>
       <c r="C48" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>86</v>
+        <v>68</v>
+      </c>
+      <c r="D48" t="s">
+        <v>16</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F48">
-        <v>25500</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>172</v>
+      </c>
+      <c r="F48" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G48" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49">
         <v>48</v>
       </c>
@@ -11559,68 +11544,77 @@
         <v>115</v>
       </c>
       <c r="C49" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="D49" t="s">
-        <v>29</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>169</v>
+        <v>16</v>
+      </c>
+      <c r="E49" t="s">
+        <v>178</v>
       </c>
       <c r="F49" s="11">
         <v>10000</v>
       </c>
-      <c r="G49" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+      <c r="G49" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H49" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" s="1">
         <v>115</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+      <c r="C50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" t="s">
+        <v>178</v>
+      </c>
+      <c r="F50" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H50" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" s="1">
         <v>115</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F51" s="2">
-        <v>20564</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+      <c r="C51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" t="s">
+        <v>178</v>
+      </c>
+      <c r="F51" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H51" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52">
         <v>51</v>
       </c>
@@ -11628,22 +11622,25 @@
         <v>115</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D52" t="s">
-        <v>23</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F52" s="2">
-        <v>45000</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>16</v>
+      </c>
+      <c r="E52" t="s">
+        <v>178</v>
+      </c>
+      <c r="F52" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H52" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53">
         <v>52</v>
       </c>
@@ -11651,183 +11648,186 @@
         <v>115</v>
       </c>
       <c r="C53" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>169</v>
+        <v>16</v>
+      </c>
+      <c r="E53" t="s">
+        <v>178</v>
       </c>
       <c r="F53" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G53" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>10000</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H53" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" s="1">
         <v>115</v>
       </c>
-      <c r="C54" t="s">
-        <v>22</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>64</v>
+      <c r="C54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F54">
-        <v>17479</v>
-      </c>
-      <c r="G54" s="10" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="F54" s="2">
+        <v>31500</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" s="1">
         <v>115</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>13</v>
+      <c r="C55" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55" s="2">
-        <v>51750</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>182</v>
+      </c>
+      <c r="F55">
+        <v>25500</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" s="1">
         <v>115</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>13</v>
+      <c r="C56" t="s">
+        <v>117</v>
+      </c>
+      <c r="D56" t="s">
+        <v>29</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F56" s="2">
-        <v>47687</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>169</v>
+      </c>
+      <c r="F56" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G56" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" s="1">
         <v>115</v>
       </c>
-      <c r="C57" t="s">
-        <v>24</v>
-      </c>
-      <c r="D57" t="s">
-        <v>13</v>
+      <c r="C57" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F57" s="11">
-        <v>7200</v>
-      </c>
-      <c r="G57" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>7</v>
+      </c>
+      <c r="F57" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" s="1">
         <v>115</v>
       </c>
-      <c r="C58" t="s">
-        <v>133</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="C58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F58" s="11">
-        <v>1500</v>
-      </c>
-      <c r="G58" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="F58" s="2">
+        <v>20564</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" s="1">
         <v>115</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>21</v>
+      <c r="C59" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="F59" s="2">
-        <v>42500</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>45000</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" s="1">
         <v>115</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>16</v>
+      <c r="C60" t="s">
+        <v>22</v>
+      </c>
+      <c r="D60" t="s">
+        <v>23</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F60" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>169</v>
+      </c>
+      <c r="F60" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G60" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61">
         <v>60</v>
       </c>
@@ -11835,45 +11835,45 @@
         <v>115</v>
       </c>
       <c r="C61" t="s">
-        <v>25</v>
-      </c>
-      <c r="D61" t="s">
-        <v>16</v>
+        <v>22</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F61" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G61" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>182</v>
+      </c>
+      <c r="F61">
+        <v>17479</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" s="1">
         <v>115</v>
       </c>
-      <c r="C62" t="s">
-        <v>134</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="C62" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F62" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G62" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>223</v>
+      </c>
+      <c r="F62" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H62" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63">
         <v>62</v>
       </c>
@@ -11881,22 +11881,22 @@
         <v>115</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F63" s="2">
-        <v>17000</v>
+        <v>51750</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:8">
       <c r="A64">
         <v>63</v>
       </c>
@@ -11904,19 +11904,19 @@
         <v>115</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="F64" s="2">
-        <v>60000</v>
+        <v>47687</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -11927,19 +11927,19 @@
         <v>115</v>
       </c>
       <c r="C65" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D65" t="s">
-        <v>86</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F65" s="2">
-        <v>47500</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>88</v>
+        <v>13</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F65" s="11">
+        <v>7200</v>
+      </c>
+      <c r="G65" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -11950,16 +11950,16 @@
         <v>115</v>
       </c>
       <c r="C66" t="s">
-        <v>26</v>
+        <v>133</v>
       </c>
       <c r="D66" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F66" s="11">
-        <v>8400</v>
+        <v>1500</v>
       </c>
       <c r="G66" t="s">
         <v>167</v>
@@ -11972,20 +11972,20 @@
       <c r="B67" s="1">
         <v>115</v>
       </c>
-      <c r="C67" t="s">
-        <v>26</v>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>86</v>
+      <c r="C67" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F67">
-        <v>43200</v>
-      </c>
-      <c r="G67" s="10" t="s">
-        <v>184</v>
+        <v>21</v>
+      </c>
+      <c r="F67" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -11996,19 +11996,19 @@
         <v>115</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>87</v>
+        <v>16</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="F68" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>88</v>
+        <v>63000</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -12019,22 +12019,19 @@
         <v>115</v>
       </c>
       <c r="C69" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="D69" t="s">
-        <v>23</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F69" s="2">
-        <v>30850</v>
-      </c>
-      <c r="G69" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H69" t="s">
-        <v>107</v>
+        <v>16</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F69" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G69" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -12044,23 +12041,20 @@
       <c r="B70" s="1">
         <v>115</v>
       </c>
-      <c r="C70" t="s">
-        <v>85</v>
-      </c>
-      <c r="D70" t="s">
-        <v>23</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F70" s="2">
-        <v>9696</v>
-      </c>
-      <c r="G70" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H70" t="s">
-        <v>107</v>
+      <c r="C70" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F70" s="14">
+        <v>4800</v>
+      </c>
+      <c r="H70" s="13" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -12070,20 +12064,20 @@
       <c r="B71" s="1">
         <v>115</v>
       </c>
-      <c r="C71" t="s">
-        <v>85</v>
-      </c>
-      <c r="D71" t="s">
-        <v>23</v>
+      <c r="C71" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F71" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G71" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F71" s="14">
+        <v>12000</v>
+      </c>
+      <c r="H71" s="13" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -12093,20 +12087,20 @@
       <c r="B72" s="1">
         <v>115</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D72" s="1" t="s">
+      <c r="C72" t="s">
+        <v>134</v>
+      </c>
+      <c r="D72" t="s">
         <v>23</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F72" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F72" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G72" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -12116,23 +12110,23 @@
       <c r="B73" s="1">
         <v>115</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>93</v>
+      <c r="C73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="F73" s="2">
-        <v>32320</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="17.25">
+        <v>17000</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74">
         <v>73</v>
       </c>
@@ -12140,19 +12134,19 @@
         <v>115</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>81</v>
+        <v>20</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="F74" s="2">
-        <v>140000</v>
+        <v>60000</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -12162,20 +12156,20 @@
       <c r="B75" s="1">
         <v>115</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>83</v>
+      <c r="C75" t="s">
+        <v>26</v>
+      </c>
+      <c r="D75" t="s">
+        <v>86</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="F75" s="2">
-        <v>28884</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>84</v>
+        <v>47500</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -12186,22 +12180,19 @@
         <v>115</v>
       </c>
       <c r="C76" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D76" t="s">
-        <v>23</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F76" s="2">
-        <v>30850</v>
-      </c>
-      <c r="G76" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H76" t="s">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F76" s="11">
+        <v>8400</v>
+      </c>
+      <c r="G76" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -12212,22 +12203,19 @@
         <v>115</v>
       </c>
       <c r="C77" t="s">
-        <v>27</v>
-      </c>
-      <c r="D77" t="s">
-        <v>23</v>
-      </c>
-      <c r="E77" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F77" s="2">
-        <v>19150</v>
+        <v>26</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F77">
+        <v>43200</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H77" t="s">
-        <v>105</v>
+        <v>184</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -12237,23 +12225,20 @@
       <c r="B78" s="1">
         <v>115</v>
       </c>
-      <c r="C78" t="s">
-        <v>27</v>
-      </c>
-      <c r="D78" t="s">
-        <v>23</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F78" s="2">
-        <v>12936</v>
-      </c>
-      <c r="G78" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H78" t="s">
-        <v>100</v>
+      <c r="C78" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F78" s="14">
+        <v>12000</v>
+      </c>
+      <c r="H78" s="13" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -12263,23 +12248,20 @@
       <c r="B79" s="1">
         <v>115</v>
       </c>
-      <c r="C79" t="s">
-        <v>27</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="C79" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E79" s="10" t="s">
-        <v>171</v>
+      <c r="E79" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="F79" s="2">
-        <v>31462</v>
-      </c>
-      <c r="G79" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H79" t="s">
-        <v>105</v>
+        <v>50000</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -12290,19 +12272,22 @@
         <v>115</v>
       </c>
       <c r="C80" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="D80" t="s">
         <v>23</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F80" s="11">
-        <v>3700</v>
-      </c>
-      <c r="G80" t="s">
-        <v>167</v>
+      <c r="E80" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F80" s="2">
+        <v>30850</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H80" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -12313,19 +12298,22 @@
         <v>115</v>
       </c>
       <c r="C81" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="D81" t="s">
         <v>23</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F81" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G81" t="s">
-        <v>167</v>
+      <c r="E81" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F81" s="2">
+        <v>9696</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H81" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -12335,43 +12323,43 @@
       <c r="B82" s="1">
         <v>115</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>29</v>
+      <c r="C82" t="s">
+        <v>85</v>
+      </c>
+      <c r="D82" t="s">
+        <v>23</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F82" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="17.25">
+        <v>169</v>
+      </c>
+      <c r="F82" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G82" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" s="1">
         <v>115</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>28</v>
+      <c r="C83" s="13" t="s">
+        <v>85</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F83" s="2">
-        <v>150000</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>82</v>
+        <v>23</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F83" s="14">
+        <v>5960</v>
+      </c>
+      <c r="H83" s="13" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -12381,23 +12369,20 @@
       <c r="B84" s="1">
         <v>115</v>
       </c>
-      <c r="C84" t="s">
-        <v>28</v>
-      </c>
-      <c r="D84" t="s">
-        <v>29</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>170</v>
+      <c r="C84" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F84" s="2">
-        <v>17789</v>
-      </c>
-      <c r="G84" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H84" t="s">
-        <v>106</v>
+        <v>59500</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -12407,46 +12392,43 @@
       <c r="B85" s="1">
         <v>115</v>
       </c>
-      <c r="C85" t="s">
-        <v>28</v>
-      </c>
-      <c r="D85" t="s">
-        <v>29</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>171</v>
+      <c r="C85" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="F85" s="2">
-        <v>8085</v>
-      </c>
-      <c r="G85" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H85" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
+        <v>32320</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="17.25">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" s="1">
         <v>115</v>
       </c>
-      <c r="C86" t="s">
-        <v>28</v>
-      </c>
-      <c r="D86" t="s">
-        <v>29</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F86" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G86" t="s">
-        <v>167</v>
+      <c r="C86" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F86" s="2">
+        <v>140000</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -12456,20 +12438,20 @@
       <c r="B87" s="1">
         <v>115</v>
       </c>
-      <c r="C87" t="s">
-        <v>28</v>
-      </c>
-      <c r="D87" s="10" t="s">
-        <v>76</v>
+      <c r="C87" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F87">
-        <v>42500</v>
-      </c>
-      <c r="G87" s="10" t="s">
-        <v>184</v>
+        <v>83</v>
+      </c>
+      <c r="F87" s="2">
+        <v>28884</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -12480,19 +12462,22 @@
         <v>115</v>
       </c>
       <c r="C88" t="s">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="D88" t="s">
         <v>23</v>
       </c>
-      <c r="E88" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F88" s="11">
-        <v>8700</v>
-      </c>
-      <c r="G88" t="s">
-        <v>167</v>
+      <c r="E88" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F88" s="2">
+        <v>30850</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H88" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -12503,19 +12488,22 @@
         <v>115</v>
       </c>
       <c r="C89" t="s">
-        <v>140</v>
+        <v>27</v>
       </c>
       <c r="D89" t="s">
         <v>23</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F89" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G89" t="s">
-        <v>167</v>
+      <c r="E89" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F89" s="2">
+        <v>19150</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H89" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -12526,19 +12514,22 @@
         <v>115</v>
       </c>
       <c r="C90" t="s">
-        <v>136</v>
+        <v>27</v>
       </c>
       <c r="D90" t="s">
         <v>23</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F90" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G90" t="s">
-        <v>167</v>
+      <c r="E90" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F90" s="2">
+        <v>12936</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H90" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -12549,19 +12540,22 @@
         <v>115</v>
       </c>
       <c r="C91" t="s">
-        <v>124</v>
+        <v>27</v>
       </c>
       <c r="D91" t="s">
-        <v>20</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F91" s="11">
-        <v>9600</v>
-      </c>
-      <c r="G91" t="s">
-        <v>167</v>
+        <v>23</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F91" s="2">
+        <v>31462</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H91" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -12572,19 +12566,19 @@
         <v>115</v>
       </c>
       <c r="C92" t="s">
-        <v>124</v>
-      </c>
-      <c r="D92" s="10" t="s">
-        <v>179</v>
+        <v>27</v>
+      </c>
+      <c r="D92" t="s">
+        <v>23</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F92">
-        <v>30000</v>
-      </c>
-      <c r="G92" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
+      </c>
+      <c r="F92" s="11">
+        <v>3700</v>
+      </c>
+      <c r="G92" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -12594,20 +12588,20 @@
       <c r="B93" s="1">
         <v>115</v>
       </c>
-      <c r="C93" t="s">
-        <v>137</v>
-      </c>
-      <c r="D93" t="s">
-        <v>23</v>
+      <c r="C93" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F93" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G93" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F93" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H93" s="13" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -12617,20 +12611,20 @@
       <c r="B94" s="1">
         <v>115</v>
       </c>
-      <c r="C94" t="s">
-        <v>138</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="C94" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F94" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G94" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F94" s="14">
+        <v>4600</v>
+      </c>
+      <c r="H94" s="13" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -12641,16 +12635,16 @@
         <v>115</v>
       </c>
       <c r="C95" t="s">
-        <v>161</v>
-      </c>
-      <c r="D95" s="10" t="s">
-        <v>179</v>
+        <v>135</v>
+      </c>
+      <c r="D95" t="s">
+        <v>23</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F95" s="11">
-        <v>400</v>
+        <v>3500</v>
       </c>
       <c r="G95" t="s">
         <v>167</v>
@@ -12663,20 +12657,20 @@
       <c r="B96" s="1">
         <v>115</v>
       </c>
-      <c r="C96" t="s">
-        <v>161</v>
-      </c>
-      <c r="D96" s="10" t="s">
-        <v>179</v>
+      <c r="C96" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F96">
-        <v>39613</v>
-      </c>
-      <c r="G96" s="10" t="s">
-        <v>184</v>
+        <v>223</v>
+      </c>
+      <c r="F96" s="14">
+        <v>2400</v>
+      </c>
+      <c r="H96" s="13" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -12686,20 +12680,20 @@
       <c r="B97" s="1">
         <v>115</v>
       </c>
-      <c r="C97" t="s">
-        <v>160</v>
-      </c>
-      <c r="D97" s="10" t="s">
-        <v>179</v>
+      <c r="C97" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F97" s="11">
-        <v>500</v>
-      </c>
-      <c r="G97" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F97" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H97" s="13" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -12709,23 +12703,23 @@
       <c r="B98" s="1">
         <v>115</v>
       </c>
-      <c r="C98" t="s">
-        <v>139</v>
-      </c>
-      <c r="D98" t="s">
-        <v>23</v>
+      <c r="C98" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F98" s="11">
-        <v>8700</v>
-      </c>
-      <c r="G98" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="F98" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="17.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -12733,19 +12727,19 @@
         <v>115</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F99" s="2">
-        <v>11185</v>
+        <v>150000</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -12756,19 +12750,22 @@
         <v>115</v>
       </c>
       <c r="C100" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="D100" t="s">
-        <v>20</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F100" s="11">
-        <v>2500</v>
-      </c>
-      <c r="G100" t="s">
-        <v>167</v>
+        <v>29</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F100" s="2">
+        <v>17789</v>
+      </c>
+      <c r="G100" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H100" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -12778,20 +12775,23 @@
       <c r="B101" s="1">
         <v>115</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>7</v>
+      <c r="C101" t="s">
+        <v>28</v>
+      </c>
+      <c r="D101" t="s">
+        <v>29</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="F101" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>8</v>
+        <v>8085</v>
+      </c>
+      <c r="G101" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H101" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -12801,20 +12801,20 @@
       <c r="B102" s="1">
         <v>115</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>23</v>
+      <c r="C102" t="s">
+        <v>28</v>
+      </c>
+      <c r="D102" t="s">
+        <v>29</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F102" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F102" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G102" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -12824,20 +12824,20 @@
       <c r="B103" s="1">
         <v>115</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>23</v>
+      <c r="C103" t="s">
+        <v>28</v>
+      </c>
+      <c r="D103" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F103" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>8</v>
+        <v>182</v>
+      </c>
+      <c r="F103">
+        <v>42500</v>
+      </c>
+      <c r="G103" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -12848,7 +12848,7 @@
         <v>115</v>
       </c>
       <c r="C104" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="D104" t="s">
         <v>23</v>
@@ -12857,7 +12857,7 @@
         <v>169</v>
       </c>
       <c r="F104" s="11">
-        <v>5000</v>
+        <v>8700</v>
       </c>
       <c r="G104" t="s">
         <v>167</v>
@@ -12870,20 +12870,20 @@
       <c r="B105" s="1">
         <v>115</v>
       </c>
-      <c r="C105" t="s">
-        <v>30</v>
-      </c>
-      <c r="D105" s="10" t="s">
-        <v>64</v>
+      <c r="C105" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F105">
-        <v>12000</v>
-      </c>
-      <c r="G105" s="10" t="s">
-        <v>184</v>
+        <v>223</v>
+      </c>
+      <c r="F105" s="14">
+        <v>4800</v>
+      </c>
+      <c r="H105" s="13" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -12893,20 +12893,20 @@
       <c r="B106" s="1">
         <v>115</v>
       </c>
-      <c r="C106" s="1" t="s">
-        <v>31</v>
+      <c r="C106" s="13" t="s">
+        <v>131</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F106" s="2">
-        <v>70000</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>8</v>
+        <v>223</v>
+      </c>
+      <c r="F106" s="14">
+        <v>2000</v>
+      </c>
+      <c r="H106" s="13" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -12916,20 +12916,20 @@
       <c r="B107" s="1">
         <v>115</v>
       </c>
-      <c r="C107" t="s">
-        <v>31</v>
-      </c>
-      <c r="D107" t="s">
+      <c r="C107" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E107" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F107" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G107" s="9" t="s">
-        <v>88</v>
+      <c r="E107" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F107" s="15">
+        <v>688</v>
+      </c>
+      <c r="H107" s="13" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -12939,20 +12939,20 @@
       <c r="B108" s="1">
         <v>115</v>
       </c>
-      <c r="C108" t="s">
-        <v>31</v>
-      </c>
-      <c r="D108" t="s">
+      <c r="C108" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F108" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G108" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F108" s="14">
+        <v>2000</v>
+      </c>
+      <c r="H108" s="13" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -12962,23 +12962,20 @@
       <c r="B109" s="1">
         <v>115</v>
       </c>
-      <c r="C109" t="s">
-        <v>96</v>
-      </c>
-      <c r="D109" t="s">
+      <c r="C109" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E109" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F109" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G109" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H109" t="s">
-        <v>110</v>
+      <c r="E109" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F109" s="14">
+        <v>2000</v>
+      </c>
+      <c r="H109" s="13" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -12989,22 +12986,19 @@
         <v>115</v>
       </c>
       <c r="C110" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="D110" t="s">
         <v>23</v>
       </c>
-      <c r="E110" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F110" s="2">
-        <v>38015</v>
-      </c>
-      <c r="G110" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H110" t="s">
-        <v>110</v>
+      <c r="E110" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F110" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G110" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -13015,10 +13009,10 @@
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>96</v>
-      </c>
-      <c r="D111" s="10" t="s">
-        <v>64</v>
+        <v>136</v>
+      </c>
+      <c r="D111" t="s">
+        <v>23</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>169</v>
@@ -13037,20 +13031,20 @@
       <c r="B112" s="1">
         <v>115</v>
       </c>
-      <c r="C112" t="s">
-        <v>127</v>
-      </c>
-      <c r="D112" t="s">
+      <c r="C112" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F112" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G112" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F112" s="14">
+        <v>7000</v>
+      </c>
+      <c r="H112" s="13" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -13060,20 +13054,20 @@
       <c r="B113" s="1">
         <v>115</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>13</v>
+      <c r="C113" t="s">
+        <v>124</v>
+      </c>
+      <c r="D113" t="s">
+        <v>20</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F113" s="2">
-        <v>56000</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F113" s="11">
+        <v>9600</v>
+      </c>
+      <c r="G113" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -13083,20 +13077,20 @@
       <c r="B114" s="1">
         <v>115</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>13</v>
+      <c r="C114" t="s">
+        <v>124</v>
+      </c>
+      <c r="D114" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F114" s="2">
-        <v>39355</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>84</v>
+        <v>182</v>
+      </c>
+      <c r="F114">
+        <v>30000</v>
+      </c>
+      <c r="G114" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -13107,16 +13101,16 @@
         <v>115</v>
       </c>
       <c r="C115" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="D115" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F115" s="11">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="G115" t="s">
         <v>167</v>
@@ -13129,20 +13123,20 @@
       <c r="B116" s="1">
         <v>115</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>10</v>
+      <c r="C116" t="s">
+        <v>138</v>
+      </c>
+      <c r="D116" t="s">
+        <v>23</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F116" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F116" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G116" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -13152,43 +13146,43 @@
       <c r="B117" s="1">
         <v>115</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>10</v>
+      <c r="C117" t="s">
+        <v>161</v>
+      </c>
+      <c r="D117" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F117" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" ht="17.25">
+        <v>169</v>
+      </c>
+      <c r="F117" s="11">
+        <v>400</v>
+      </c>
+      <c r="G117" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118" s="1">
         <v>115</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D118" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F118" s="2">
-        <v>106530</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>82</v>
+      <c r="C118" t="s">
+        <v>161</v>
+      </c>
+      <c r="D118" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F118">
+        <v>39613</v>
+      </c>
+      <c r="G118" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -13198,23 +13192,20 @@
       <c r="B119" s="1">
         <v>115</v>
       </c>
-      <c r="C119" t="s">
-        <v>33</v>
-      </c>
-      <c r="D119" t="s">
-        <v>10</v>
-      </c>
-      <c r="E119" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F119" s="2">
-        <v>19942</v>
-      </c>
-      <c r="G119" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H119" t="s">
-        <v>108</v>
+      <c r="C119" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F119" s="14">
+        <v>20000</v>
+      </c>
+      <c r="H119" s="13" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -13225,45 +13216,42 @@
         <v>115</v>
       </c>
       <c r="C120" t="s">
-        <v>33</v>
-      </c>
-      <c r="D120" t="s">
-        <v>10</v>
-      </c>
-      <c r="E120" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F120" s="2">
-        <v>16447</v>
-      </c>
-      <c r="G120" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H120" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" ht="17.25">
+        <v>160</v>
+      </c>
+      <c r="D120" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F120" s="11">
+        <v>500</v>
+      </c>
+      <c r="G120" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
       <c r="A121">
         <v>120</v>
       </c>
       <c r="B121" s="1">
         <v>115</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F121" s="2">
-        <v>117750</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>82</v>
+      <c r="C121" t="s">
+        <v>139</v>
+      </c>
+      <c r="D121" t="s">
+        <v>23</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F121" s="11">
+        <v>8700</v>
+      </c>
+      <c r="G121" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -13273,20 +13261,20 @@
       <c r="B122" s="1">
         <v>115</v>
       </c>
-      <c r="C122" t="s">
-        <v>74</v>
-      </c>
-      <c r="D122" s="10" t="s">
-        <v>77</v>
+      <c r="C122" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F122" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G122" t="s">
-        <v>167</v>
+        <v>83</v>
+      </c>
+      <c r="F122" s="2">
+        <v>11185</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -13296,20 +13284,20 @@
       <c r="B123" s="1">
         <v>115</v>
       </c>
-      <c r="C123" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>29</v>
+      <c r="C123" t="s">
+        <v>123</v>
+      </c>
+      <c r="D123" t="s">
+        <v>20</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F123" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F123" s="11">
+        <v>2500</v>
+      </c>
+      <c r="G123" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -13319,20 +13307,20 @@
       <c r="B124" s="1">
         <v>115</v>
       </c>
-      <c r="C124" t="s">
-        <v>34</v>
-      </c>
-      <c r="D124" t="s">
-        <v>29</v>
+      <c r="C124" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F124" s="11">
-        <v>6000</v>
-      </c>
-      <c r="G124" t="s">
-        <v>167</v>
+        <v>7</v>
+      </c>
+      <c r="F124" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -13342,20 +13330,20 @@
       <c r="B125" s="1">
         <v>115</v>
       </c>
-      <c r="C125" t="s">
-        <v>34</v>
-      </c>
-      <c r="D125" s="10" t="s">
-        <v>76</v>
+      <c r="C125" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F125">
-        <v>37500</v>
-      </c>
-      <c r="G125" s="10" t="s">
-        <v>184</v>
+        <v>11</v>
+      </c>
+      <c r="F125" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -13365,20 +13353,20 @@
       <c r="B126" s="1">
         <v>115</v>
       </c>
-      <c r="C126" t="s">
-        <v>146</v>
-      </c>
-      <c r="D126" t="s">
+      <c r="C126" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F126" s="11">
-        <v>6400</v>
-      </c>
-      <c r="G126" t="s">
-        <v>167</v>
+        <v>21</v>
+      </c>
+      <c r="F126" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -13388,20 +13376,20 @@
       <c r="B127" s="1">
         <v>115</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D127" s="1" t="s">
+      <c r="C127" t="s">
+        <v>30</v>
+      </c>
+      <c r="D127" t="s">
         <v>23</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F127" s="2">
-        <v>23014</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>84</v>
+        <v>169</v>
+      </c>
+      <c r="F127" s="11">
+        <v>5000</v>
+      </c>
+      <c r="G127" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -13412,160 +13400,163 @@
         <v>115</v>
       </c>
       <c r="C128" t="s">
-        <v>69</v>
-      </c>
-      <c r="D128" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="D128" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F128" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G128" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7">
+        <v>182</v>
+      </c>
+      <c r="F128">
+        <v>12000</v>
+      </c>
+      <c r="G128" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
       <c r="A129">
         <v>128</v>
       </c>
       <c r="B129" s="1">
         <v>115</v>
       </c>
-      <c r="C129" t="s">
-        <v>132</v>
-      </c>
-      <c r="D129" t="s">
+      <c r="C129" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F129" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G129" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" ht="17.25">
+        <v>223</v>
+      </c>
+      <c r="F129" s="14">
+        <v>6000</v>
+      </c>
+      <c r="H129" s="13" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
       <c r="A130">
         <v>129</v>
       </c>
       <c r="B130" s="1">
         <v>115</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>71</v>
+      <c r="C130" s="13" t="s">
+        <v>30</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E130" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F130" s="2">
-        <v>300000</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7">
+      <c r="E130" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F130" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H130" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
       <c r="A131">
         <v>130</v>
       </c>
       <c r="B131" s="1">
         <v>115</v>
       </c>
-      <c r="C131" t="s">
-        <v>71</v>
-      </c>
-      <c r="D131" s="10" t="s">
-        <v>64</v>
+      <c r="C131" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F131" s="11">
-        <v>3800</v>
-      </c>
-      <c r="G131" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7">
+        <v>7</v>
+      </c>
+      <c r="F131" s="2">
+        <v>70000</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
       <c r="A132">
         <v>131</v>
       </c>
       <c r="B132" s="1">
         <v>115</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>11</v>
+      <c r="C132" t="s">
+        <v>31</v>
+      </c>
+      <c r="D132" t="s">
+        <v>23</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="F132" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" ht="17.25">
+        <v>40000</v>
+      </c>
+      <c r="G132" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
       <c r="A133">
         <v>132</v>
       </c>
       <c r="B133" s="1">
         <v>115</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E133" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F133" s="2">
-        <v>255000</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7">
+      <c r="C133" t="s">
+        <v>31</v>
+      </c>
+      <c r="D133" t="s">
+        <v>23</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F133" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G133" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
       <c r="A134">
         <v>133</v>
       </c>
       <c r="B134" s="1">
         <v>115</v>
       </c>
-      <c r="C134" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>83</v>
+      <c r="C134" t="s">
+        <v>96</v>
+      </c>
+      <c r="D134" t="s">
+        <v>23</v>
+      </c>
+      <c r="E134" s="10" t="s">
+        <v>170</v>
       </c>
       <c r="F134" s="2">
-        <v>8285</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7">
+        <v>50000</v>
+      </c>
+      <c r="G134" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H134" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
       <c r="A135">
         <v>134</v>
       </c>
@@ -13573,68 +13564,71 @@
         <v>115</v>
       </c>
       <c r="C135" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D135" t="s">
-        <v>16</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F135" s="11">
-        <v>9400</v>
-      </c>
-      <c r="G135" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7">
+        <v>23</v>
+      </c>
+      <c r="E135" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F135" s="2">
+        <v>38015</v>
+      </c>
+      <c r="G135" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H135" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
       <c r="A136">
         <v>135</v>
       </c>
       <c r="B136" s="1">
         <v>115</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>23</v>
+      <c r="C136" t="s">
+        <v>96</v>
+      </c>
+      <c r="D136" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F136" s="2">
-        <v>51000</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" ht="17.25">
+        <v>169</v>
+      </c>
+      <c r="F136" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G136" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
       <c r="A137">
         <v>136</v>
       </c>
       <c r="B137" s="1">
         <v>115</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>36</v>
+      <c r="C137" s="13" t="s">
+        <v>96</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E137" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F137" s="2">
-        <v>250000</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
+      <c r="E137" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F137" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H137" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
       <c r="A138">
         <v>137</v>
       </c>
@@ -13642,10 +13636,10 @@
         <v>115</v>
       </c>
       <c r="C138" t="s">
-        <v>36</v>
-      </c>
-      <c r="D138" s="10" t="s">
-        <v>64</v>
+        <v>127</v>
+      </c>
+      <c r="D138" t="s">
+        <v>23</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>169</v>
@@ -13657,7 +13651,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:8">
       <c r="A139">
         <v>138</v>
       </c>
@@ -13665,45 +13659,45 @@
         <v>115</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F139" s="2">
-        <v>20368</v>
+        <v>56000</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:8">
       <c r="A140">
         <v>139</v>
       </c>
       <c r="B140" s="1">
         <v>115</v>
       </c>
-      <c r="C140" t="s">
-        <v>37</v>
-      </c>
-      <c r="D140" t="s">
-        <v>23</v>
+      <c r="C140" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F140" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G140" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7">
+        <v>83</v>
+      </c>
+      <c r="F140" s="2">
+        <v>39355</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
       <c r="A141">
         <v>140</v>
       </c>
@@ -13711,88 +13705,88 @@
         <v>115</v>
       </c>
       <c r="C141" t="s">
-        <v>37</v>
-      </c>
-      <c r="D141" s="10" t="s">
-        <v>64</v>
+        <v>32</v>
+      </c>
+      <c r="D141" t="s">
+        <v>13</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F141">
-        <v>29750</v>
-      </c>
-      <c r="G141" s="10" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7">
+        <v>169</v>
+      </c>
+      <c r="F141" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G141" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
       <c r="A142">
         <v>141</v>
       </c>
       <c r="B142" s="1">
         <v>115</v>
       </c>
-      <c r="C142" t="s">
-        <v>162</v>
-      </c>
-      <c r="D142" s="10" t="s">
-        <v>179</v>
+      <c r="C142" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F142" s="11">
-        <v>7200</v>
-      </c>
-      <c r="G142" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7">
+        <v>11</v>
+      </c>
+      <c r="F142" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
       <c r="A143">
         <v>142</v>
       </c>
       <c r="B143" s="1">
         <v>115</v>
       </c>
-      <c r="C143" t="s">
-        <v>149</v>
-      </c>
-      <c r="D143" t="s">
-        <v>23</v>
+      <c r="C143" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F143" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G143" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7">
+        <v>7</v>
+      </c>
+      <c r="F143" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="17.25">
       <c r="A144">
         <v>143</v>
       </c>
       <c r="B144" s="1">
         <v>115</v>
       </c>
-      <c r="C144" t="s">
-        <v>122</v>
-      </c>
-      <c r="D144" t="s">
-        <v>20</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F144" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G144" t="s">
-        <v>167</v>
+      <c r="C144" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F144" s="2">
+        <v>106530</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -13803,19 +13797,22 @@
         <v>115</v>
       </c>
       <c r="C145" t="s">
-        <v>122</v>
-      </c>
-      <c r="D145" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F145">
-        <v>45000</v>
+        <v>33</v>
+      </c>
+      <c r="D145" t="s">
+        <v>10</v>
+      </c>
+      <c r="E145" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F145" s="2">
+        <v>19942</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>184</v>
+        <v>116</v>
+      </c>
+      <c r="H145" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -13826,42 +13823,45 @@
         <v>115</v>
       </c>
       <c r="C146" t="s">
-        <v>155</v>
+        <v>33</v>
       </c>
       <c r="D146" t="s">
-        <v>23</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F146" s="11">
-        <v>5700</v>
-      </c>
-      <c r="G146" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8">
+        <v>10</v>
+      </c>
+      <c r="E146" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F146" s="2">
+        <v>16447</v>
+      </c>
+      <c r="G146" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H146" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="17.25">
       <c r="A147">
         <v>146</v>
       </c>
       <c r="B147" s="1">
         <v>115</v>
       </c>
-      <c r="C147" t="s">
-        <v>166</v>
-      </c>
-      <c r="D147" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F147" s="11">
-        <v>1400</v>
-      </c>
-      <c r="G147" t="s">
-        <v>167</v>
+      <c r="C147" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F147" s="2">
+        <v>117750</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -13871,20 +13871,20 @@
       <c r="B148" s="1">
         <v>115</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>20</v>
+      <c r="C148" t="s">
+        <v>74</v>
+      </c>
+      <c r="D148" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F148" s="2">
-        <v>45000</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F148" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G148" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -13894,20 +13894,20 @@
       <c r="B149" s="1">
         <v>115</v>
       </c>
-      <c r="C149" t="s">
-        <v>38</v>
-      </c>
-      <c r="D149" t="s">
-        <v>20</v>
+      <c r="C149" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F149" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G149" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F149" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H149" s="13" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -13917,20 +13917,20 @@
       <c r="B150" s="1">
         <v>115</v>
       </c>
-      <c r="C150" t="s">
-        <v>38</v>
-      </c>
-      <c r="D150" s="10" t="s">
-        <v>86</v>
+      <c r="C150" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F150">
-        <v>13500</v>
-      </c>
-      <c r="G150" s="10" t="s">
-        <v>184</v>
+        <v>7</v>
+      </c>
+      <c r="F150" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -13941,22 +13941,19 @@
         <v>115</v>
       </c>
       <c r="C151" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="D151" t="s">
-        <v>60</v>
-      </c>
-      <c r="E151" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="F151" s="2">
-        <v>3400</v>
-      </c>
-      <c r="G151" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H151" t="s">
-        <v>115</v>
+        <v>29</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F151" s="11">
+        <v>6000</v>
+      </c>
+      <c r="G151" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -13967,22 +13964,19 @@
         <v>115</v>
       </c>
       <c r="C152" t="s">
-        <v>99</v>
-      </c>
-      <c r="D152" t="s">
-        <v>60</v>
-      </c>
-      <c r="E152" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="F152" s="2">
-        <v>13120</v>
+        <v>34</v>
+      </c>
+      <c r="D152" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F152">
+        <v>37500</v>
       </c>
       <c r="G152" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H152" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -13993,16 +13987,16 @@
         <v>115</v>
       </c>
       <c r="C153" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="D153" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F153" s="11">
-        <v>10000</v>
+        <v>6400</v>
       </c>
       <c r="G153" t="s">
         <v>167</v>
@@ -14016,19 +14010,19 @@
         <v>115</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="F154" s="2">
-        <v>2682</v>
+        <v>23014</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -14038,20 +14032,20 @@
       <c r="B155" s="1">
         <v>115</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>40</v>
+      <c r="C155" t="s">
+        <v>69</v>
+      </c>
+      <c r="D155" t="s">
+        <v>23</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F155" s="2">
-        <v>51000</v>
-      </c>
-      <c r="G155" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F155" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G155" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -14062,42 +14056,42 @@
         <v>115</v>
       </c>
       <c r="C156" t="s">
-        <v>39</v>
+        <v>132</v>
       </c>
       <c r="D156" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F156" s="11">
-        <v>900</v>
+        <v>3500</v>
       </c>
       <c r="G156" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" ht="17.25">
       <c r="A157">
         <v>156</v>
       </c>
       <c r="B157" s="1">
         <v>115</v>
       </c>
-      <c r="C157" t="s">
-        <v>39</v>
-      </c>
-      <c r="D157" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F157">
-        <v>17850</v>
-      </c>
-      <c r="G157" s="10" t="s">
-        <v>184</v>
+      <c r="C157" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F157" s="2">
+        <v>300000</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -14108,16 +14102,16 @@
         <v>115</v>
       </c>
       <c r="C158" t="s">
-        <v>156</v>
-      </c>
-      <c r="D158" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="D158" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F158" s="11">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="G158" t="s">
         <v>167</v>
@@ -14130,20 +14124,20 @@
       <c r="B159" s="1">
         <v>115</v>
       </c>
-      <c r="C159" s="1" t="s">
-        <v>41</v>
+      <c r="C159" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F159" s="2">
-        <v>16788</v>
-      </c>
-      <c r="G159" s="1" t="s">
-        <v>8</v>
+        <v>223</v>
+      </c>
+      <c r="F159" s="15">
+        <v>999</v>
+      </c>
+      <c r="H159" s="13" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -14153,69 +14147,69 @@
       <c r="B160" s="1">
         <v>115</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>41</v>
+      <c r="C160" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F160" s="2">
-        <v>12800</v>
-      </c>
-      <c r="G160" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7">
+        <v>223</v>
+      </c>
+      <c r="F160" s="14">
+        <v>4090</v>
+      </c>
+      <c r="H160" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
       <c r="A161">
         <v>160</v>
       </c>
       <c r="B161" s="1">
         <v>115</v>
       </c>
-      <c r="C161" t="s">
-        <v>41</v>
-      </c>
-      <c r="D161" s="10" t="s">
-        <v>179</v>
+      <c r="C161" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F161">
-        <v>15800</v>
-      </c>
-      <c r="G161" s="10" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" ht="17.25">
+        <v>223</v>
+      </c>
+      <c r="F161" s="14">
+        <v>8900</v>
+      </c>
+      <c r="H161" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
       <c r="A162">
         <v>161</v>
       </c>
       <c r="B162" s="1">
         <v>115</v>
       </c>
-      <c r="C162" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D162" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E162" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F162" s="2">
-        <v>143300</v>
-      </c>
-      <c r="G162" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7">
+      <c r="C162" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F162" s="14">
+        <v>2490</v>
+      </c>
+      <c r="H162" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
       <c r="A163">
         <v>162</v>
       </c>
@@ -14223,45 +14217,45 @@
         <v>115</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="F163" s="2">
-        <v>34568</v>
+        <v>59500</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" ht="17.25">
       <c r="A164">
         <v>163</v>
       </c>
       <c r="B164" s="1">
         <v>115</v>
       </c>
-      <c r="C164" t="s">
-        <v>66</v>
-      </c>
-      <c r="D164" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F164" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G164" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" ht="17.25">
+      <c r="C164" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F164" s="2">
+        <v>255000</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8">
       <c r="A165">
         <v>164</v>
       </c>
@@ -14269,22 +14263,22 @@
         <v>115</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E165" s="3" t="s">
-        <v>81</v>
+        <v>16</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F165" s="2">
-        <v>300000</v>
+        <v>8285</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
       <c r="A166">
         <v>165</v>
       </c>
@@ -14292,68 +14286,68 @@
         <v>115</v>
       </c>
       <c r="C166" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="D166" t="s">
-        <v>23</v>
-      </c>
-      <c r="E166" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F166" s="2">
-        <v>47500</v>
-      </c>
-      <c r="G166" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7">
+        <v>16</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F166" s="11">
+        <v>9400</v>
+      </c>
+      <c r="G166" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
       <c r="A167">
         <v>166</v>
       </c>
       <c r="B167" s="1">
         <v>115</v>
       </c>
-      <c r="C167" t="s">
-        <v>73</v>
-      </c>
-      <c r="D167" t="s">
+      <c r="C167" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F167" s="11">
-        <v>3700</v>
-      </c>
-      <c r="G167" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7">
+        <v>7</v>
+      </c>
+      <c r="F167" s="2">
+        <v>51000</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" ht="17.25">
       <c r="A168">
         <v>167</v>
       </c>
       <c r="B168" s="1">
         <v>115</v>
       </c>
-      <c r="C168" t="s">
-        <v>154</v>
-      </c>
-      <c r="D168" t="s">
+      <c r="C168" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E168" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F168" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G168" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7">
+      <c r="E168" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F168" s="2">
+        <v>250000</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
       <c r="A169">
         <v>168</v>
       </c>
@@ -14361,10 +14355,10 @@
         <v>115</v>
       </c>
       <c r="C169" t="s">
-        <v>157</v>
-      </c>
-      <c r="D169" t="s">
-        <v>23</v>
+        <v>36</v>
+      </c>
+      <c r="D169" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>169</v>
@@ -14376,145 +14370,145 @@
         <v>167</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:8">
       <c r="A170">
         <v>169</v>
       </c>
       <c r="B170" s="1">
         <v>115</v>
       </c>
-      <c r="C170" t="s">
-        <v>153</v>
-      </c>
-      <c r="D170" t="s">
+      <c r="C170" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F170" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G170" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="F170" s="2">
+        <v>20368</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
       <c r="A171">
         <v>170</v>
       </c>
       <c r="B171" s="1">
         <v>115</v>
       </c>
-      <c r="C171" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>16</v>
+      <c r="C171" t="s">
+        <v>37</v>
+      </c>
+      <c r="D171" t="s">
+        <v>23</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F171" s="2">
-        <v>52000</v>
-      </c>
-      <c r="G171" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" ht="17.25">
+        <v>169</v>
+      </c>
+      <c r="F171" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G171" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
       <c r="A172">
         <v>171</v>
       </c>
       <c r="B172" s="1">
         <v>115</v>
       </c>
-      <c r="C172" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D172" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E172" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F172" s="2">
-        <v>210000</v>
-      </c>
-      <c r="G172" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7">
+      <c r="C172" t="s">
+        <v>37</v>
+      </c>
+      <c r="D172" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F172">
+        <v>29750</v>
+      </c>
+      <c r="G172" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
       <c r="A173">
         <v>172</v>
       </c>
       <c r="B173" s="1">
         <v>115</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>43</v>
+      <c r="C173" s="13" t="s">
+        <v>37</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F173" s="2">
-        <v>42500</v>
-      </c>
-      <c r="G173" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7">
+        <v>223</v>
+      </c>
+      <c r="F173" s="14">
+        <v>3000</v>
+      </c>
+      <c r="H173" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8">
       <c r="A174">
         <v>173</v>
       </c>
       <c r="B174" s="1">
         <v>115</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>20</v>
+      <c r="C174" t="s">
+        <v>162</v>
+      </c>
+      <c r="D174" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F174" s="2">
-        <v>70000</v>
-      </c>
-      <c r="G174" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7">
+        <v>169</v>
+      </c>
+      <c r="F174" s="11">
+        <v>7200</v>
+      </c>
+      <c r="G174" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
       <c r="A175">
         <v>174</v>
       </c>
       <c r="B175" s="1">
         <v>115</v>
       </c>
-      <c r="C175" t="s">
-        <v>43</v>
-      </c>
-      <c r="D175" t="s">
-        <v>20</v>
+      <c r="C175" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F175" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G175" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7">
+        <v>223</v>
+      </c>
+      <c r="F175" s="14">
+        <v>7800</v>
+      </c>
+      <c r="H175" s="13" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
       <c r="A176">
         <v>175</v>
       </c>
@@ -14522,19 +14516,19 @@
         <v>115</v>
       </c>
       <c r="C176" t="s">
-        <v>43</v>
-      </c>
-      <c r="D176" s="10" t="s">
-        <v>86</v>
+        <v>149</v>
+      </c>
+      <c r="D176" t="s">
+        <v>23</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F176">
-        <v>20250</v>
-      </c>
-      <c r="G176" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
+      </c>
+      <c r="F176" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G176" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -14544,20 +14538,20 @@
       <c r="B177" s="1">
         <v>115</v>
       </c>
-      <c r="C177" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>16</v>
+      <c r="C177" t="s">
+        <v>122</v>
+      </c>
+      <c r="D177" t="s">
+        <v>20</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F177" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G177" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F177" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G177" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -14567,43 +14561,43 @@
       <c r="B178" s="1">
         <v>115</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>16</v>
+      <c r="C178" t="s">
+        <v>122</v>
+      </c>
+      <c r="D178" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F178" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G178" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" ht="17.25">
+        <v>182</v>
+      </c>
+      <c r="F178">
+        <v>45000</v>
+      </c>
+      <c r="G178" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8">
       <c r="A179">
         <v>178</v>
       </c>
       <c r="B179" s="1">
         <v>115</v>
       </c>
-      <c r="C179" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D179" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E179" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F179" s="2">
-        <v>200000</v>
-      </c>
-      <c r="G179" s="1" t="s">
-        <v>82</v>
+      <c r="C179" t="s">
+        <v>155</v>
+      </c>
+      <c r="D179" t="s">
+        <v>23</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F179" s="11">
+        <v>5700</v>
+      </c>
+      <c r="G179" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -14614,22 +14608,19 @@
         <v>115</v>
       </c>
       <c r="C180" t="s">
-        <v>94</v>
-      </c>
-      <c r="D180" t="s">
-        <v>23</v>
-      </c>
-      <c r="E180" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F180" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G180" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H180" t="s">
-        <v>101</v>
+        <v>166</v>
+      </c>
+      <c r="D180" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F180" s="11">
+        <v>1400</v>
+      </c>
+      <c r="G180" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -14639,23 +14630,20 @@
       <c r="B181" s="1">
         <v>115</v>
       </c>
-      <c r="C181" t="s">
-        <v>94</v>
-      </c>
-      <c r="D181" t="s">
-        <v>23</v>
-      </c>
-      <c r="E181" s="10" t="s">
-        <v>171</v>
+      <c r="C181" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="F181" s="2">
-        <v>42393</v>
-      </c>
-      <c r="G181" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H181" t="s">
-        <v>101</v>
+        <v>45000</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -14666,16 +14654,16 @@
         <v>115</v>
       </c>
       <c r="C182" t="s">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="D182" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F182" s="11">
-        <v>3500</v>
+        <v>5600</v>
       </c>
       <c r="G182" t="s">
         <v>167</v>
@@ -14689,19 +14677,19 @@
         <v>115</v>
       </c>
       <c r="C183" t="s">
-        <v>158</v>
-      </c>
-      <c r="D183" t="s">
-        <v>23</v>
+        <v>38</v>
+      </c>
+      <c r="D183" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F183" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G183" t="s">
-        <v>167</v>
+        <v>182</v>
+      </c>
+      <c r="F183">
+        <v>13500</v>
+      </c>
+      <c r="G183" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -14712,19 +14700,22 @@
         <v>115</v>
       </c>
       <c r="C184" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="D184" t="s">
-        <v>29</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F184" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G184" t="s">
-        <v>167</v>
+        <v>60</v>
+      </c>
+      <c r="E184" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="F184" s="2">
+        <v>3400</v>
+      </c>
+      <c r="G184" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H184" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -14734,43 +14725,46 @@
       <c r="B185" s="1">
         <v>115</v>
       </c>
-      <c r="C185" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>21</v>
+      <c r="C185" t="s">
+        <v>99</v>
+      </c>
+      <c r="D185" t="s">
+        <v>60</v>
+      </c>
+      <c r="E185" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="F185" s="2">
-        <v>44118</v>
-      </c>
-      <c r="G185" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8" ht="17.25">
+        <v>13120</v>
+      </c>
+      <c r="G185" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H185" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8">
       <c r="A186">
         <v>185</v>
       </c>
       <c r="B186" s="1">
         <v>115</v>
       </c>
-      <c r="C186" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D186" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E186" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F186" s="2">
-        <v>217500</v>
-      </c>
-      <c r="G186" s="1" t="s">
-        <v>82</v>
+      <c r="C186" t="s">
+        <v>99</v>
+      </c>
+      <c r="D186" t="s">
+        <v>60</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F186" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G186" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -14780,20 +14774,20 @@
       <c r="B187" s="1">
         <v>115</v>
       </c>
-      <c r="C187" t="s">
-        <v>45</v>
-      </c>
-      <c r="D187" t="s">
-        <v>46</v>
+      <c r="C187" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F187" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G187" t="s">
-        <v>167</v>
+        <v>21</v>
+      </c>
+      <c r="F187" s="2">
+        <v>2682</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -14803,20 +14797,20 @@
       <c r="B188" s="1">
         <v>115</v>
       </c>
-      <c r="C188" t="s">
-        <v>165</v>
-      </c>
-      <c r="D188" s="10" t="s">
-        <v>63</v>
+      <c r="C188" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F188" s="11">
-        <v>6000</v>
-      </c>
-      <c r="G188" t="s">
-        <v>167</v>
+        <v>7</v>
+      </c>
+      <c r="F188" s="2">
+        <v>51000</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -14827,16 +14821,16 @@
         <v>115</v>
       </c>
       <c r="C189" t="s">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="D189" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F189" s="11">
-        <v>10000</v>
+        <v>900</v>
       </c>
       <c r="G189" t="s">
         <v>167</v>
@@ -14849,20 +14843,20 @@
       <c r="B190" s="1">
         <v>115</v>
       </c>
-      <c r="C190" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>46</v>
+      <c r="C190" t="s">
+        <v>39</v>
+      </c>
+      <c r="D190" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F190" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G190" s="1" t="s">
-        <v>8</v>
+        <v>182</v>
+      </c>
+      <c r="F190">
+        <v>17850</v>
+      </c>
+      <c r="G190" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -14872,20 +14866,20 @@
       <c r="B191" s="1">
         <v>115</v>
       </c>
-      <c r="C191" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E191" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F191" s="2">
-        <v>60000</v>
-      </c>
-      <c r="G191" s="1" t="s">
-        <v>91</v>
+      <c r="C191" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F191" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H191" s="13" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -14896,16 +14890,16 @@
         <v>115</v>
       </c>
       <c r="C192" t="s">
-        <v>47</v>
+        <v>156</v>
       </c>
       <c r="D192" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F192" s="11">
-        <v>1400</v>
+        <v>3500</v>
       </c>
       <c r="G192" t="s">
         <v>167</v>
@@ -14918,20 +14912,20 @@
       <c r="B193" s="1">
         <v>115</v>
       </c>
-      <c r="C193" s="1" t="s">
-        <v>48</v>
+      <c r="C193" s="13" t="s">
+        <v>156</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F193" s="2">
-        <v>52500</v>
-      </c>
-      <c r="G193" s="1" t="s">
-        <v>8</v>
+        <v>223</v>
+      </c>
+      <c r="F193" s="14">
+        <v>7200</v>
+      </c>
+      <c r="H193" s="13" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -14942,19 +14936,19 @@
         <v>115</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="F194" s="2">
-        <v>52776</v>
+        <v>16788</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>84</v>
+        <v>8</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -14964,20 +14958,20 @@
       <c r="B195" s="1">
         <v>115</v>
       </c>
-      <c r="C195" t="s">
-        <v>48</v>
-      </c>
-      <c r="D195" t="s">
-        <v>13</v>
+      <c r="C195" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F195" s="11">
-        <v>900</v>
-      </c>
-      <c r="G195" t="s">
-        <v>167</v>
+        <v>11</v>
+      </c>
+      <c r="F195" s="2">
+        <v>12800</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -14987,43 +14981,43 @@
       <c r="B196" s="1">
         <v>115</v>
       </c>
-      <c r="C196" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>23</v>
+      <c r="C196" t="s">
+        <v>41</v>
+      </c>
+      <c r="D196" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F196" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G196" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8">
+        <v>182</v>
+      </c>
+      <c r="F196">
+        <v>15800</v>
+      </c>
+      <c r="G196" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" ht="17.25">
       <c r="A197">
         <v>196</v>
       </c>
       <c r="B197" s="1">
         <v>115</v>
       </c>
-      <c r="C197" t="s">
-        <v>49</v>
-      </c>
-      <c r="D197" t="s">
-        <v>23</v>
-      </c>
-      <c r="E197" s="8" t="s">
-        <v>87</v>
+      <c r="C197" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F197" s="2">
-        <v>41616</v>
-      </c>
-      <c r="G197" s="9" t="s">
-        <v>88</v>
+        <v>143300</v>
+      </c>
+      <c r="G197" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -15033,23 +15027,20 @@
       <c r="B198" s="1">
         <v>115</v>
       </c>
-      <c r="C198" t="s">
-        <v>49</v>
-      </c>
-      <c r="D198" t="s">
-        <v>23</v>
-      </c>
-      <c r="E198" s="10" t="s">
-        <v>170</v>
+      <c r="C198" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F198" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G198" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H198" t="s">
-        <v>109</v>
+        <v>34568</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -15060,22 +15051,19 @@
         <v>115</v>
       </c>
       <c r="C199" t="s">
-        <v>49</v>
-      </c>
-      <c r="D199" t="s">
-        <v>23</v>
-      </c>
-      <c r="E199" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F199" s="2">
-        <v>38569</v>
-      </c>
-      <c r="G199" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H199" t="s">
-        <v>109</v>
+        <v>66</v>
+      </c>
+      <c r="D199" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F199" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G199" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -15085,20 +15073,20 @@
       <c r="B200" s="1">
         <v>115</v>
       </c>
-      <c r="C200" t="s">
-        <v>49</v>
-      </c>
-      <c r="D200" t="s">
-        <v>23</v>
+      <c r="C200" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F200" s="11">
-        <v>5000</v>
-      </c>
-      <c r="G200" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F200" s="14">
+        <v>3600</v>
+      </c>
+      <c r="H200" s="13" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -15108,20 +15096,20 @@
       <c r="B201" s="1">
         <v>115</v>
       </c>
-      <c r="C201" t="s">
-        <v>49</v>
-      </c>
-      <c r="D201" s="10" t="s">
-        <v>64</v>
+      <c r="C201" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F201">
-        <v>50000</v>
-      </c>
-      <c r="G201" s="10" t="s">
-        <v>184</v>
+        <v>223</v>
+      </c>
+      <c r="F201" s="14">
+        <v>2000</v>
+      </c>
+      <c r="H201" s="13" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -15131,23 +15119,23 @@
       <c r="B202" s="1">
         <v>115</v>
       </c>
-      <c r="C202" t="s">
-        <v>141</v>
-      </c>
-      <c r="D202" t="s">
-        <v>23</v>
+      <c r="C202" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F202" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G202" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8">
+        <v>223</v>
+      </c>
+      <c r="F202" s="14">
+        <v>3600</v>
+      </c>
+      <c r="H202" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" ht="17.25">
       <c r="A203">
         <v>202</v>
       </c>
@@ -15155,19 +15143,19 @@
         <v>115</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E203" s="1" t="s">
-        <v>21</v>
+      <c r="E203" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F203" s="2">
-        <v>31500</v>
+        <v>300000</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -15178,19 +15166,19 @@
         <v>115</v>
       </c>
       <c r="C204" t="s">
-        <v>50</v>
-      </c>
-      <c r="D204" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F204" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G204" t="s">
-        <v>167</v>
+        <v>73</v>
+      </c>
+      <c r="D204" t="s">
+        <v>23</v>
+      </c>
+      <c r="E204" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F204" s="2">
+        <v>47500</v>
+      </c>
+      <c r="G204" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -15201,19 +15189,19 @@
         <v>115</v>
       </c>
       <c r="C205" t="s">
-        <v>50</v>
-      </c>
-      <c r="D205" s="10" t="s">
-        <v>64</v>
+        <v>73</v>
+      </c>
+      <c r="D205" t="s">
+        <v>23</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F205">
-        <v>30150</v>
-      </c>
-      <c r="G205" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
+      </c>
+      <c r="F205" s="11">
+        <v>3700</v>
+      </c>
+      <c r="G205" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -15223,20 +15211,20 @@
       <c r="B206" s="1">
         <v>115</v>
       </c>
-      <c r="C206" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>20</v>
+      <c r="C206" t="s">
+        <v>154</v>
+      </c>
+      <c r="D206" t="s">
+        <v>23</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F206" s="2">
-        <v>42500</v>
-      </c>
-      <c r="G206" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F206" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G206" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -15247,16 +15235,16 @@
         <v>115</v>
       </c>
       <c r="C207" t="s">
-        <v>51</v>
+        <v>157</v>
       </c>
       <c r="D207" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F207" s="11">
-        <v>5600</v>
+        <v>3500</v>
       </c>
       <c r="G207" t="s">
         <v>167</v>
@@ -15270,22 +15258,22 @@
         <v>115</v>
       </c>
       <c r="C208" t="s">
-        <v>51</v>
-      </c>
-      <c r="D208" s="10" t="s">
-        <v>86</v>
+        <v>153</v>
+      </c>
+      <c r="D208" t="s">
+        <v>23</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F208">
-        <v>12750</v>
-      </c>
-      <c r="G208" s="10" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8" ht="17.25">
+        <v>169</v>
+      </c>
+      <c r="F208" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G208" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8">
       <c r="A209">
         <v>208</v>
       </c>
@@ -15293,42 +15281,42 @@
         <v>115</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E209" s="3" t="s">
-        <v>81</v>
+        <v>16</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="F209" s="2">
-        <v>95912</v>
+        <v>52000</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" ht="17.25">
       <c r="A210">
         <v>209</v>
       </c>
       <c r="B210" s="1">
         <v>115</v>
       </c>
-      <c r="C210" t="s">
-        <v>72</v>
-      </c>
-      <c r="D210" t="s">
-        <v>23</v>
-      </c>
-      <c r="E210" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F210" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G210" t="s">
-        <v>167</v>
+      <c r="C210" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D210" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F210" s="2">
+        <v>210000</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -15338,23 +15326,23 @@
       <c r="B211" s="1">
         <v>115</v>
       </c>
-      <c r="C211" t="s">
-        <v>129</v>
-      </c>
-      <c r="D211" t="s">
-        <v>23</v>
+      <c r="C211" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F211" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G211" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8" ht="17.25">
+        <v>21</v>
+      </c>
+      <c r="F211" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8">
       <c r="A212">
         <v>211</v>
       </c>
@@ -15362,19 +15350,19 @@
         <v>115</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E212" s="3" t="s">
-        <v>81</v>
+        <v>20</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F212" s="2">
-        <v>28500</v>
+        <v>70000</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -15385,16 +15373,16 @@
         <v>115</v>
       </c>
       <c r="C213" t="s">
-        <v>128</v>
+        <v>43</v>
       </c>
       <c r="D213" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F213" s="11">
-        <v>3500</v>
+        <v>5600</v>
       </c>
       <c r="G213" t="s">
         <v>167</v>
@@ -15408,19 +15396,19 @@
         <v>115</v>
       </c>
       <c r="C214" t="s">
-        <v>142</v>
-      </c>
-      <c r="D214" t="s">
-        <v>23</v>
+        <v>43</v>
+      </c>
+      <c r="D214" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F214" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G214" t="s">
-        <v>167</v>
+        <v>182</v>
+      </c>
+      <c r="F214">
+        <v>20250</v>
+      </c>
+      <c r="G214" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -15430,20 +15418,20 @@
       <c r="B215" s="1">
         <v>115</v>
       </c>
-      <c r="C215" t="s">
-        <v>147</v>
-      </c>
-      <c r="D215" t="s">
-        <v>23</v>
+      <c r="C215" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F215" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G215" t="s">
-        <v>167</v>
+        <v>11</v>
+      </c>
+      <c r="F215" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G215" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -15453,23 +15441,23 @@
       <c r="B216" s="1">
         <v>115</v>
       </c>
-      <c r="C216" t="s">
-        <v>148</v>
-      </c>
-      <c r="D216" t="s">
-        <v>23</v>
+      <c r="C216" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F216" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G216" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="F216" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G216" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" ht="17.25">
       <c r="A217">
         <v>216</v>
       </c>
@@ -15477,19 +15465,19 @@
         <v>115</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D217" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E217" s="1" t="s">
-        <v>21</v>
+        <v>44</v>
+      </c>
+      <c r="D217" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F217" s="2">
-        <v>29250</v>
+        <v>200000</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -15500,22 +15488,22 @@
         <v>115</v>
       </c>
       <c r="C218" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="D218" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E218" s="10" t="s">
         <v>170</v>
       </c>
       <c r="F218" s="2">
-        <v>8900</v>
+        <v>50000</v>
       </c>
       <c r="G218" s="10" t="s">
         <v>116</v>
       </c>
       <c r="H218" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -15526,22 +15514,22 @@
         <v>115</v>
       </c>
       <c r="C219" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="D219" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F219" s="2">
-        <v>0</v>
+        <v>42393</v>
       </c>
       <c r="G219" s="10" t="s">
         <v>116</v>
       </c>
       <c r="H219" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -15552,22 +15540,19 @@
         <v>115</v>
       </c>
       <c r="C220" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="D220" t="s">
-        <v>29</v>
-      </c>
-      <c r="E220" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F220" s="2">
-        <v>19190</v>
-      </c>
-      <c r="G220" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H220" t="s">
-        <v>104</v>
+        <v>23</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F220" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G220" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -15578,22 +15563,19 @@
         <v>115</v>
       </c>
       <c r="C221" t="s">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c r="D221" t="s">
-        <v>29</v>
-      </c>
-      <c r="E221" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F221" s="2">
-        <v>17728</v>
-      </c>
-      <c r="G221" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H221" t="s">
-        <v>111</v>
+        <v>23</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F221" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G221" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -15604,7 +15586,7 @@
         <v>115</v>
       </c>
       <c r="C222" t="s">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="D222" t="s">
         <v>29</v>
@@ -15613,7 +15595,7 @@
         <v>169</v>
       </c>
       <c r="F222" s="11">
-        <v>2200</v>
+        <v>10000</v>
       </c>
       <c r="G222" t="s">
         <v>167</v>
@@ -15626,43 +15608,43 @@
       <c r="B223" s="1">
         <v>115</v>
       </c>
-      <c r="C223" t="s">
-        <v>52</v>
-      </c>
-      <c r="D223" s="10" t="s">
-        <v>76</v>
+      <c r="C223" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F223">
-        <v>32175</v>
-      </c>
-      <c r="G223" s="10" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8">
+        <v>21</v>
+      </c>
+      <c r="F223" s="2">
+        <v>44118</v>
+      </c>
+      <c r="G223" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" ht="17.25">
       <c r="A224">
         <v>223</v>
       </c>
       <c r="B224" s="1">
         <v>115</v>
       </c>
-      <c r="C224" t="s">
-        <v>159</v>
-      </c>
-      <c r="D224" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E224" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F224" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G224" t="s">
-        <v>167</v>
+      <c r="C224" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D224" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F224" s="2">
+        <v>217500</v>
+      </c>
+      <c r="G224" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="225" spans="1:8">
@@ -15673,22 +15655,19 @@
         <v>115</v>
       </c>
       <c r="C225" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="D225" t="s">
-        <v>23</v>
-      </c>
-      <c r="E225" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F225" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G225" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H225" t="s">
-        <v>113</v>
+        <v>46</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F225" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G225" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="226" spans="1:8">
@@ -15698,23 +15677,20 @@
       <c r="B226" s="1">
         <v>115</v>
       </c>
-      <c r="C226" t="s">
-        <v>98</v>
-      </c>
-      <c r="D226" t="s">
-        <v>23</v>
-      </c>
-      <c r="E226" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F226" s="2">
-        <v>17600</v>
-      </c>
-      <c r="G226" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H226" t="s">
-        <v>113</v>
+      <c r="C226" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D226" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F226" s="14">
+        <v>3582</v>
+      </c>
+      <c r="H226" s="13" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -15725,16 +15701,16 @@
         <v>115</v>
       </c>
       <c r="C227" t="s">
-        <v>98</v>
-      </c>
-      <c r="D227" t="s">
-        <v>23</v>
+        <v>165</v>
+      </c>
+      <c r="D227" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F227" s="11">
-        <v>3500</v>
+        <v>6000</v>
       </c>
       <c r="G227" t="s">
         <v>167</v>
@@ -15748,16 +15724,16 @@
         <v>115</v>
       </c>
       <c r="C228" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="D228" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F228" s="11">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="G228" t="s">
         <v>167</v>
@@ -15770,20 +15746,20 @@
       <c r="B229" s="1">
         <v>115</v>
       </c>
-      <c r="C229" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D229" s="1" t="s">
-        <v>23</v>
+      <c r="C229" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="D229" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F229" s="2">
-        <v>41384</v>
-      </c>
-      <c r="G229" s="1" t="s">
-        <v>8</v>
+        <v>223</v>
+      </c>
+      <c r="F229" s="14">
+        <v>2400</v>
+      </c>
+      <c r="H229" s="13" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="230" spans="1:8">
@@ -15793,23 +15769,20 @@
       <c r="B230" s="1">
         <v>115</v>
       </c>
-      <c r="C230" t="s">
-        <v>53</v>
-      </c>
-      <c r="D230" t="s">
-        <v>23</v>
-      </c>
-      <c r="E230" s="10" t="s">
-        <v>170</v>
+      <c r="C230" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F230" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G230" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H230" t="s">
-        <v>114</v>
+        <v>59500</v>
+      </c>
+      <c r="G230" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="231" spans="1:8">
@@ -15819,23 +15792,20 @@
       <c r="B231" s="1">
         <v>115</v>
       </c>
-      <c r="C231" t="s">
-        <v>53</v>
-      </c>
-      <c r="D231" t="s">
-        <v>23</v>
-      </c>
-      <c r="E231" s="10" t="s">
-        <v>171</v>
+      <c r="C231" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E231" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="F231" s="2">
-        <v>19200</v>
-      </c>
-      <c r="G231" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H231" t="s">
-        <v>114</v>
+        <v>60000</v>
+      </c>
+      <c r="G231" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -15846,16 +15816,16 @@
         <v>115</v>
       </c>
       <c r="C232" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D232" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F232" s="11">
-        <v>3500</v>
+        <v>1400</v>
       </c>
       <c r="G232" t="s">
         <v>167</v>
@@ -15869,7 +15839,7 @@
         <v>115</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>13</v>
@@ -15878,7 +15848,7 @@
         <v>7</v>
       </c>
       <c r="F233" s="2">
-        <v>56000</v>
+        <v>52500</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>8</v>
@@ -15892,7 +15862,7 @@
         <v>115</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>13</v>
@@ -15901,7 +15871,7 @@
         <v>83</v>
       </c>
       <c r="F234" s="2">
-        <v>48284</v>
+        <v>52776</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>84</v>
@@ -15915,7 +15885,7 @@
         <v>115</v>
       </c>
       <c r="C235" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D235" t="s">
         <v>13</v>
@@ -15924,7 +15894,7 @@
         <v>169</v>
       </c>
       <c r="F235" s="11">
-        <v>6300</v>
+        <v>900</v>
       </c>
       <c r="G235" t="s">
         <v>167</v>
@@ -15938,16 +15908,16 @@
         <v>115</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F236" s="2">
-        <v>42500</v>
+        <v>63000</v>
       </c>
       <c r="G236" s="1" t="s">
         <v>8</v>
@@ -15961,19 +15931,19 @@
         <v>115</v>
       </c>
       <c r="C237" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D237" t="s">
-        <v>20</v>
-      </c>
-      <c r="E237" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F237" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G237" t="s">
-        <v>167</v>
+        <v>23</v>
+      </c>
+      <c r="E237" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F237" s="2">
+        <v>41616</v>
+      </c>
+      <c r="G237" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -15984,19 +15954,22 @@
         <v>115</v>
       </c>
       <c r="C238" t="s">
-        <v>55</v>
-      </c>
-      <c r="D238" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="E238" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F238">
-        <v>19125</v>
+        <v>49</v>
+      </c>
+      <c r="D238" t="s">
+        <v>23</v>
+      </c>
+      <c r="E238" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F238" s="2">
+        <v>50000</v>
       </c>
       <c r="G238" s="10" t="s">
-        <v>184</v>
+        <v>116</v>
+      </c>
+      <c r="H238" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -16006,20 +15979,23 @@
       <c r="B239" s="1">
         <v>115</v>
       </c>
-      <c r="C239" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D239" s="1" t="s">
+      <c r="C239" t="s">
+        <v>49</v>
+      </c>
+      <c r="D239" t="s">
         <v>23</v>
       </c>
-      <c r="E239" s="1" t="s">
-        <v>21</v>
+      <c r="E239" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="F239" s="2">
-        <v>41770</v>
-      </c>
-      <c r="G239" s="1" t="s">
-        <v>8</v>
+        <v>38569</v>
+      </c>
+      <c r="G239" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H239" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -16030,7 +16006,7 @@
         <v>115</v>
       </c>
       <c r="C240" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D240" t="s">
         <v>23</v>
@@ -16039,13 +16015,13 @@
         <v>169</v>
       </c>
       <c r="F240" s="11">
-        <v>4100</v>
+        <v>5000</v>
       </c>
       <c r="G240" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="241" spans="1:7">
+    <row r="241" spans="1:8">
       <c r="A241">
         <v>240</v>
       </c>
@@ -16053,7 +16029,7 @@
         <v>115</v>
       </c>
       <c r="C241" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D241" s="10" t="s">
         <v>64</v>
@@ -16062,105 +16038,105 @@
         <v>182</v>
       </c>
       <c r="F241">
-        <v>18584</v>
+        <v>50000</v>
       </c>
       <c r="G241" s="10" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="242" spans="1:7">
+    <row r="242" spans="1:8">
       <c r="A242">
         <v>241</v>
       </c>
       <c r="B242" s="1">
         <v>115</v>
       </c>
-      <c r="C242" s="1" t="s">
-        <v>57</v>
+      <c r="C242" s="13" t="s">
+        <v>49</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F242" s="2">
-        <v>45000</v>
-      </c>
-      <c r="G242" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7">
+        <v>223</v>
+      </c>
+      <c r="F242" s="14">
+        <v>3081</v>
+      </c>
+      <c r="H242" s="13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8">
       <c r="A243">
         <v>242</v>
       </c>
       <c r="B243" s="1">
         <v>115</v>
       </c>
-      <c r="C243" t="s">
-        <v>57</v>
-      </c>
-      <c r="D243" t="s">
-        <v>86</v>
-      </c>
-      <c r="E243" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F243" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G243" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7">
+      <c r="C243" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F243" s="14">
+        <v>4800</v>
+      </c>
+      <c r="H243" s="13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8">
       <c r="A244">
         <v>243</v>
       </c>
       <c r="B244" s="1">
         <v>115</v>
       </c>
-      <c r="C244" t="s">
-        <v>57</v>
-      </c>
-      <c r="D244" t="s">
-        <v>20</v>
+      <c r="C244" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F244" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G244" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7">
+        <v>223</v>
+      </c>
+      <c r="F244" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H244" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8">
       <c r="A245">
         <v>244</v>
       </c>
       <c r="B245" s="1">
         <v>115</v>
       </c>
-      <c r="C245" t="s">
-        <v>151</v>
-      </c>
-      <c r="D245" t="s">
+      <c r="C245" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D245" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F245" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G245" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7">
+        <v>223</v>
+      </c>
+      <c r="F245" s="15">
+        <v>500</v>
+      </c>
+      <c r="H245" s="13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8">
       <c r="A246">
         <v>245</v>
       </c>
@@ -16168,7 +16144,7 @@
         <v>115</v>
       </c>
       <c r="C246" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D246" t="s">
         <v>23</v>
@@ -16177,13 +16153,13 @@
         <v>169</v>
       </c>
       <c r="F246" s="11">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="G246" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="247" spans="1:7">
+    <row r="247" spans="1:8">
       <c r="A247">
         <v>246</v>
       </c>
@@ -16191,22 +16167,22 @@
         <v>115</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="F247" s="2">
-        <v>39125</v>
+        <v>31500</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8">
       <c r="A248">
         <v>247</v>
       </c>
@@ -16214,22 +16190,22 @@
         <v>115</v>
       </c>
       <c r="C248" t="s">
-        <v>65</v>
-      </c>
-      <c r="D248" t="s">
-        <v>23</v>
+        <v>50</v>
+      </c>
+      <c r="D248" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F248" s="11">
-        <v>7500</v>
+        <v>3500</v>
       </c>
       <c r="G248" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="249" spans="1:7">
+    <row r="249" spans="1:8">
       <c r="A249">
         <v>248</v>
       </c>
@@ -16237,45 +16213,45 @@
         <v>115</v>
       </c>
       <c r="C249" t="s">
-        <v>163</v>
+        <v>50</v>
       </c>
       <c r="D249" s="10" t="s">
-        <v>179</v>
+        <v>64</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F249" s="11">
-        <v>5200</v>
-      </c>
-      <c r="G249" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7">
+        <v>182</v>
+      </c>
+      <c r="F249">
+        <v>30150</v>
+      </c>
+      <c r="G249" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8">
       <c r="A250">
         <v>249</v>
       </c>
       <c r="B250" s="1">
         <v>115</v>
       </c>
-      <c r="C250" t="s">
-        <v>164</v>
-      </c>
-      <c r="D250" t="s">
-        <v>40</v>
+      <c r="C250" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F250" s="11">
-        <v>5200</v>
-      </c>
-      <c r="G250" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="F250" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G250" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8">
       <c r="A251">
         <v>250</v>
       </c>
@@ -16283,45 +16259,45 @@
         <v>115</v>
       </c>
       <c r="C251" t="s">
-        <v>164</v>
-      </c>
-      <c r="D251" s="10" t="s">
-        <v>179</v>
+        <v>51</v>
+      </c>
+      <c r="D251" t="s">
+        <v>20</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F251">
-        <v>13515</v>
-      </c>
-      <c r="G251" s="10" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7">
+        <v>169</v>
+      </c>
+      <c r="F251" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G251" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8">
       <c r="A252">
         <v>251</v>
       </c>
       <c r="B252" s="1">
         <v>115</v>
       </c>
-      <c r="C252" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D252" s="1" t="s">
-        <v>60</v>
+      <c r="C252" t="s">
+        <v>51</v>
+      </c>
+      <c r="D252" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F252" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G252" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" ht="17.25">
+        <v>182</v>
+      </c>
+      <c r="F252">
+        <v>12750</v>
+      </c>
+      <c r="G252" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" ht="17.25">
       <c r="A253">
         <v>252</v>
       </c>
@@ -16329,45 +16305,45 @@
         <v>115</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D253" s="4" t="s">
-        <v>80</v>
+        <v>72</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>81</v>
       </c>
       <c r="F253" s="2">
-        <v>221000</v>
+        <v>95912</v>
       </c>
       <c r="G253" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="254" spans="1:7">
+    <row r="254" spans="1:8">
       <c r="A254">
         <v>253</v>
       </c>
       <c r="B254" s="1">
         <v>115</v>
       </c>
-      <c r="C254" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D254" s="1" t="s">
-        <v>60</v>
+      <c r="C254" t="s">
+        <v>72</v>
+      </c>
+      <c r="D254" t="s">
+        <v>23</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F254" s="2">
-        <v>26283</v>
-      </c>
-      <c r="G254" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7">
+        <v>169</v>
+      </c>
+      <c r="F254" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G254" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8">
       <c r="A255">
         <v>254</v>
       </c>
@@ -16375,22 +16351,22 @@
         <v>115</v>
       </c>
       <c r="C255" t="s">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="D255" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F255" s="11">
-        <v>1100</v>
-      </c>
-      <c r="G255" s="12" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7">
+        <v>3500</v>
+      </c>
+      <c r="G255" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" ht="17.25">
       <c r="A256">
         <v>255</v>
       </c>
@@ -16398,19 +16374,19 @@
         <v>115</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E256" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
+      </c>
+      <c r="E256" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F256" s="2">
-        <v>63000</v>
+        <v>28500</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>183</v>
+        <v>82</v>
       </c>
     </row>
     <row r="257" spans="1:8">
@@ -16421,16 +16397,16 @@
         <v>115</v>
       </c>
       <c r="C257" t="s">
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="D257" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F257" s="11">
-        <v>2700</v>
+        <v>3500</v>
       </c>
       <c r="G257" t="s">
         <v>167</v>
@@ -16443,20 +16419,20 @@
       <c r="B258" s="1">
         <v>115</v>
       </c>
-      <c r="C258" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D258" s="4" t="s">
-        <v>64</v>
+      <c r="C258" t="s">
+        <v>142</v>
+      </c>
+      <c r="D258" t="s">
+        <v>23</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F258" s="14">
-        <v>1000</v>
-      </c>
-      <c r="H258" s="13" t="s">
-        <v>185</v>
+        <v>169</v>
+      </c>
+      <c r="F258" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G258" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -16466,20 +16442,20 @@
       <c r="B259" s="1">
         <v>115</v>
       </c>
-      <c r="C259" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D259" s="4" t="s">
-        <v>77</v>
+      <c r="C259" t="s">
+        <v>147</v>
+      </c>
+      <c r="D259" t="s">
+        <v>23</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F259" s="14">
-        <v>3600</v>
-      </c>
-      <c r="H259" s="13" t="s">
-        <v>186</v>
+        <v>169</v>
+      </c>
+      <c r="F259" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G259" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="260" spans="1:8">
@@ -16490,19 +16466,19 @@
         <v>115</v>
       </c>
       <c r="C260" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D260" s="4" t="s">
-        <v>78</v>
+        <v>147</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>223</v>
       </c>
       <c r="F260" s="14">
-        <v>4800</v>
+        <v>20000</v>
       </c>
       <c r="H260" s="13" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -16512,20 +16488,20 @@
       <c r="B261" s="1">
         <v>115</v>
       </c>
-      <c r="C261" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D261" s="1" t="s">
+      <c r="C261" t="s">
+        <v>148</v>
+      </c>
+      <c r="D261" t="s">
         <v>23</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F261" s="14">
-        <v>6000</v>
-      </c>
-      <c r="H261" s="13" t="s">
-        <v>188</v>
+        <v>169</v>
+      </c>
+      <c r="F261" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G261" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -16535,20 +16511,20 @@
       <c r="B262" s="1">
         <v>115</v>
       </c>
-      <c r="C262" s="13" t="s">
-        <v>95</v>
+      <c r="C262" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F262" s="14">
-        <v>4800</v>
-      </c>
-      <c r="H262" s="13" t="s">
-        <v>189</v>
+        <v>21</v>
+      </c>
+      <c r="F262" s="2">
+        <v>29250</v>
+      </c>
+      <c r="G262" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -16558,20 +16534,23 @@
       <c r="B263" s="1">
         <v>115</v>
       </c>
-      <c r="C263" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E263" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F263" s="14">
-        <v>4800</v>
-      </c>
-      <c r="H263" s="13" t="s">
-        <v>189</v>
+      <c r="C263" t="s">
+        <v>52</v>
+      </c>
+      <c r="D263" t="s">
+        <v>29</v>
+      </c>
+      <c r="E263" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F263" s="2">
+        <v>8900</v>
+      </c>
+      <c r="G263" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H263" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -16581,20 +16560,23 @@
       <c r="B264" s="1">
         <v>115</v>
       </c>
-      <c r="C264" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="D264" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E264" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F264" s="14">
-        <v>3000</v>
-      </c>
-      <c r="H264" s="13" t="s">
-        <v>190</v>
+      <c r="C264" t="s">
+        <v>52</v>
+      </c>
+      <c r="D264" t="s">
+        <v>29</v>
+      </c>
+      <c r="E264" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F264" s="2">
+        <v>0</v>
+      </c>
+      <c r="G264" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H264" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -16604,20 +16586,23 @@
       <c r="B265" s="1">
         <v>115</v>
       </c>
-      <c r="C265" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="D265" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E265" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F265" s="15">
-        <v>500</v>
-      </c>
-      <c r="H265" s="13" t="s">
-        <v>191</v>
+      <c r="C265" t="s">
+        <v>52</v>
+      </c>
+      <c r="D265" t="s">
+        <v>29</v>
+      </c>
+      <c r="E265" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F265" s="2">
+        <v>19190</v>
+      </c>
+      <c r="G265" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H265" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="266" spans="1:8">
@@ -16627,20 +16612,23 @@
       <c r="B266" s="1">
         <v>115</v>
       </c>
-      <c r="C266" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D266" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E266" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F266" s="14">
-        <v>3000</v>
-      </c>
-      <c r="H266" s="13" t="s">
-        <v>190</v>
+      <c r="C266" t="s">
+        <v>52</v>
+      </c>
+      <c r="D266" t="s">
+        <v>29</v>
+      </c>
+      <c r="E266" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F266" s="2">
+        <v>17728</v>
+      </c>
+      <c r="G266" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H266" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -16650,20 +16638,20 @@
       <c r="B267" s="1">
         <v>115</v>
       </c>
-      <c r="C267" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D267" s="1" t="s">
-        <v>23</v>
+      <c r="C267" t="s">
+        <v>52</v>
+      </c>
+      <c r="D267" t="s">
+        <v>29</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F267" s="14">
-        <v>3166</v>
-      </c>
-      <c r="H267" s="13" t="s">
-        <v>192</v>
+        <v>169</v>
+      </c>
+      <c r="F267" s="11">
+        <v>2200</v>
+      </c>
+      <c r="G267" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -16673,20 +16661,20 @@
       <c r="B268" s="1">
         <v>115</v>
       </c>
-      <c r="C268" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="D268" s="1" t="s">
-        <v>23</v>
+      <c r="C268" t="s">
+        <v>52</v>
+      </c>
+      <c r="D268" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F268" s="14">
-        <v>4500</v>
-      </c>
-      <c r="H268" s="13" t="s">
-        <v>193</v>
+        <v>182</v>
+      </c>
+      <c r="F268">
+        <v>32175</v>
+      </c>
+      <c r="G268" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -16697,19 +16685,19 @@
         <v>115</v>
       </c>
       <c r="C269" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>23</v>
+        <v>52</v>
+      </c>
+      <c r="D269" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>223</v>
       </c>
       <c r="F269" s="14">
-        <v>2000</v>
+        <v>8900</v>
       </c>
       <c r="H269" s="13" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -16719,20 +16707,20 @@
       <c r="B270" s="1">
         <v>115</v>
       </c>
-      <c r="C270" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D270" s="1" t="s">
-        <v>23</v>
+      <c r="C270" t="s">
+        <v>159</v>
+      </c>
+      <c r="D270" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F270" s="14">
-        <v>20000</v>
-      </c>
-      <c r="H270" s="13" t="s">
-        <v>195</v>
+        <v>169</v>
+      </c>
+      <c r="F270" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G270" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -16742,20 +16730,23 @@
       <c r="B271" s="1">
         <v>115</v>
       </c>
-      <c r="C271" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D271" s="1" t="s">
+      <c r="C271" t="s">
+        <v>98</v>
+      </c>
+      <c r="D271" t="s">
         <v>23</v>
       </c>
-      <c r="E271" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F271" s="14">
-        <v>3081</v>
-      </c>
-      <c r="H271" s="13" t="s">
-        <v>196</v>
+      <c r="E271" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F271" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G271" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H271" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -16765,20 +16756,23 @@
       <c r="B272" s="1">
         <v>115</v>
       </c>
-      <c r="C272" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="D272" s="1" t="s">
+      <c r="C272" t="s">
+        <v>98</v>
+      </c>
+      <c r="D272" t="s">
         <v>23</v>
       </c>
-      <c r="E272" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F272" s="14">
-        <v>2400</v>
-      </c>
-      <c r="H272" s="13" t="s">
-        <v>197</v>
+      <c r="E272" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F272" s="2">
+        <v>17600</v>
+      </c>
+      <c r="G272" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H272" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -16788,20 +16782,20 @@
       <c r="B273" s="1">
         <v>115</v>
       </c>
-      <c r="C273" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D273" s="4" t="s">
-        <v>77</v>
+      <c r="C273" t="s">
+        <v>98</v>
+      </c>
+      <c r="D273" t="s">
+        <v>23</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F273" s="14">
-        <v>2000</v>
-      </c>
-      <c r="H273" s="13" t="s">
-        <v>198</v>
+        <v>169</v>
+      </c>
+      <c r="F273" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G273" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -16811,20 +16805,20 @@
       <c r="B274" s="1">
         <v>115</v>
       </c>
-      <c r="C274" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="D274" s="1" t="s">
+      <c r="C274" t="s">
+        <v>150</v>
+      </c>
+      <c r="D274" t="s">
         <v>23</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F274" s="15">
-        <v>850</v>
-      </c>
-      <c r="H274" s="13" t="s">
-        <v>199</v>
+        <v>169</v>
+      </c>
+      <c r="F274" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G274" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -16834,20 +16828,20 @@
       <c r="B275" s="1">
         <v>115</v>
       </c>
-      <c r="C275" s="13" t="s">
-        <v>22</v>
+      <c r="C275" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F275" s="14">
-        <v>1000</v>
-      </c>
-      <c r="H275" s="13" t="s">
-        <v>200</v>
+        <v>21</v>
+      </c>
+      <c r="F275" s="2">
+        <v>41384</v>
+      </c>
+      <c r="G275" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -16857,20 +16851,23 @@
       <c r="B276" s="1">
         <v>115</v>
       </c>
-      <c r="C276" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="D276" s="1" t="s">
+      <c r="C276" t="s">
+        <v>53</v>
+      </c>
+      <c r="D276" t="s">
         <v>23</v>
       </c>
-      <c r="E276" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F276" s="14">
-        <v>1000</v>
-      </c>
-      <c r="H276" s="13" t="s">
-        <v>201</v>
+      <c r="E276" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F276" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G276" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H276" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -16880,20 +16877,23 @@
       <c r="B277" s="1">
         <v>115</v>
       </c>
-      <c r="C277" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D277" s="1" t="s">
+      <c r="C277" t="s">
+        <v>53</v>
+      </c>
+      <c r="D277" t="s">
         <v>23</v>
       </c>
-      <c r="E277" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F277" s="15">
-        <v>688</v>
-      </c>
-      <c r="H277" s="13" t="s">
-        <v>202</v>
+      <c r="E277" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F277" s="2">
+        <v>19200</v>
+      </c>
+      <c r="G277" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H277" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="278" spans="1:8">
@@ -16903,20 +16903,20 @@
       <c r="B278" s="1">
         <v>115</v>
       </c>
-      <c r="C278" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D278" s="4" t="s">
-        <v>77</v>
+      <c r="C278" t="s">
+        <v>53</v>
+      </c>
+      <c r="D278" t="s">
+        <v>23</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F278" s="14">
-        <v>1000</v>
-      </c>
-      <c r="H278" s="13" t="s">
-        <v>203</v>
+        <v>169</v>
+      </c>
+      <c r="F278" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G278" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -16926,20 +16926,20 @@
       <c r="B279" s="1">
         <v>115</v>
       </c>
-      <c r="C279" s="13" t="s">
-        <v>49</v>
+      <c r="C279" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F279" s="14">
-        <v>4800</v>
-      </c>
-      <c r="H279" s="13" t="s">
-        <v>187</v>
+        <v>7</v>
+      </c>
+      <c r="F279" s="2">
+        <v>56000</v>
+      </c>
+      <c r="G279" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -16949,20 +16949,20 @@
       <c r="B280" s="1">
         <v>115</v>
       </c>
-      <c r="C280" s="13" t="s">
-        <v>49</v>
+      <c r="C280" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F280" s="14">
-        <v>1000</v>
-      </c>
-      <c r="H280" s="13" t="s">
-        <v>200</v>
+        <v>83</v>
+      </c>
+      <c r="F280" s="2">
+        <v>48284</v>
+      </c>
+      <c r="G280" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -16972,20 +16972,20 @@
       <c r="B281" s="1">
         <v>115</v>
       </c>
-      <c r="C281" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>23</v>
+      <c r="C281" t="s">
+        <v>54</v>
+      </c>
+      <c r="D281" t="s">
+        <v>13</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F281" s="15">
-        <v>999</v>
-      </c>
-      <c r="H281" s="13" t="s">
-        <v>204</v>
+        <v>169</v>
+      </c>
+      <c r="F281" s="11">
+        <v>6300</v>
+      </c>
+      <c r="G281" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="282" spans="1:8">
@@ -16995,20 +16995,20 @@
       <c r="B282" s="1">
         <v>115</v>
       </c>
-      <c r="C282" s="13" t="s">
-        <v>71</v>
+      <c r="C282" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F282" s="14">
-        <v>4090</v>
-      </c>
-      <c r="H282" s="13" t="s">
-        <v>205</v>
+        <v>21</v>
+      </c>
+      <c r="F282" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G282" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="283" spans="1:8">
@@ -17018,20 +17018,20 @@
       <c r="B283" s="1">
         <v>115</v>
       </c>
-      <c r="C283" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>23</v>
+      <c r="C283" t="s">
+        <v>55</v>
+      </c>
+      <c r="D283" t="s">
+        <v>20</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F283" s="14">
-        <v>8900</v>
-      </c>
-      <c r="H283" s="13" t="s">
-        <v>206</v>
+        <v>169</v>
+      </c>
+      <c r="F283" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G283" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -17041,20 +17041,20 @@
       <c r="B284" s="1">
         <v>115</v>
       </c>
-      <c r="C284" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D284" s="1" t="s">
-        <v>23</v>
+      <c r="C284" t="s">
+        <v>55</v>
+      </c>
+      <c r="D284" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F284" s="14">
-        <v>2490</v>
-      </c>
-      <c r="H284" s="13" t="s">
-        <v>207</v>
+        <v>182</v>
+      </c>
+      <c r="F284">
+        <v>19125</v>
+      </c>
+      <c r="G284" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="285" spans="1:8">
@@ -17064,20 +17064,20 @@
       <c r="B285" s="1">
         <v>115</v>
       </c>
-      <c r="C285" s="13" t="s">
-        <v>96</v>
+      <c r="C285" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="D285" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F285" s="14">
-        <v>1000</v>
-      </c>
-      <c r="H285" s="13" t="s">
-        <v>200</v>
+        <v>21</v>
+      </c>
+      <c r="F285" s="2">
+        <v>41770</v>
+      </c>
+      <c r="G285" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="286" spans="1:8">
@@ -17087,20 +17087,20 @@
       <c r="B286" s="1">
         <v>115</v>
       </c>
-      <c r="C286" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D286" s="1" t="s">
+      <c r="C286" t="s">
+        <v>56</v>
+      </c>
+      <c r="D286" t="s">
         <v>23</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F286" s="14">
-        <v>1000</v>
-      </c>
-      <c r="H286" s="13" t="s">
-        <v>200</v>
+        <v>169</v>
+      </c>
+      <c r="F286" s="11">
+        <v>4100</v>
+      </c>
+      <c r="G286" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="287" spans="1:8">
@@ -17110,20 +17110,20 @@
       <c r="B287" s="1">
         <v>115</v>
       </c>
-      <c r="C287" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D287" s="1" t="s">
-        <v>23</v>
+      <c r="C287" t="s">
+        <v>56</v>
+      </c>
+      <c r="D287" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F287" s="14">
-        <v>4600</v>
-      </c>
-      <c r="H287" s="13" t="s">
-        <v>208</v>
+        <v>182</v>
+      </c>
+      <c r="F287">
+        <v>18584</v>
+      </c>
+      <c r="G287" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -17133,20 +17133,20 @@
       <c r="B288" s="1">
         <v>115</v>
       </c>
-      <c r="C288" s="13" t="s">
-        <v>144</v>
+      <c r="C288" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F288" s="14">
-        <v>4600</v>
-      </c>
-      <c r="H288" s="13" t="s">
-        <v>208</v>
+        <v>7</v>
+      </c>
+      <c r="F288" s="2">
+        <v>45000</v>
+      </c>
+      <c r="G288" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -17156,20 +17156,20 @@
       <c r="B289" s="1">
         <v>115</v>
       </c>
-      <c r="C289" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="D289" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E289" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F289" s="14">
-        <v>7000</v>
-      </c>
-      <c r="H289" s="13" t="s">
-        <v>209</v>
+      <c r="C289" t="s">
+        <v>57</v>
+      </c>
+      <c r="D289" t="s">
+        <v>86</v>
+      </c>
+      <c r="E289" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F289" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G289" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="290" spans="1:8">
@@ -17179,20 +17179,20 @@
       <c r="B290" s="1">
         <v>115</v>
       </c>
-      <c r="C290" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="D290" s="1" t="s">
-        <v>23</v>
+      <c r="C290" t="s">
+        <v>57</v>
+      </c>
+      <c r="D290" t="s">
+        <v>20</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F290" s="14">
-        <v>4600</v>
-      </c>
-      <c r="H290" s="13" t="s">
-        <v>208</v>
+        <v>169</v>
+      </c>
+      <c r="F290" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G290" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="291" spans="1:8">
@@ -17202,20 +17202,20 @@
       <c r="B291" s="1">
         <v>115</v>
       </c>
-      <c r="C291" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="D291" s="1" t="s">
+      <c r="C291" t="s">
+        <v>151</v>
+      </c>
+      <c r="D291" t="s">
         <v>23</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F291" s="14">
-        <v>7000</v>
-      </c>
-      <c r="H291" s="13" t="s">
-        <v>209</v>
+        <v>169</v>
+      </c>
+      <c r="F291" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G291" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -17226,19 +17226,19 @@
         <v>115</v>
       </c>
       <c r="C292" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D292" s="4" t="s">
-        <v>77</v>
+        <v>151</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>223</v>
       </c>
       <c r="F292" s="14">
-        <v>3600</v>
+        <v>4500</v>
       </c>
       <c r="H292" s="13" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -17249,19 +17249,19 @@
         <v>115</v>
       </c>
       <c r="C293" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D293" s="4" t="s">
-        <v>179</v>
+        <v>151</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F293" s="14">
-        <v>20000</v>
+      <c r="F293" s="15">
+        <v>850</v>
       </c>
       <c r="H293" s="13" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -17271,20 +17271,20 @@
       <c r="B294" s="1">
         <v>115</v>
       </c>
-      <c r="C294" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D294" s="4" t="s">
-        <v>63</v>
+      <c r="C294" t="s">
+        <v>152</v>
+      </c>
+      <c r="D294" t="s">
+        <v>23</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F294" s="14">
-        <v>3582</v>
-      </c>
-      <c r="H294" s="13" t="s">
-        <v>212</v>
+        <v>169</v>
+      </c>
+      <c r="F294" s="11">
+        <v>5000</v>
+      </c>
+      <c r="G294" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -17295,19 +17295,19 @@
         <v>115</v>
       </c>
       <c r="C295" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D295" s="4" t="s">
-        <v>179</v>
+        <v>152</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F295" s="14">
-        <v>1000</v>
+      <c r="F295" s="15">
+        <v>500</v>
       </c>
       <c r="H295" s="13" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -17317,20 +17317,20 @@
       <c r="B296" s="1">
         <v>115</v>
       </c>
-      <c r="C296" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D296" s="4" t="s">
-        <v>76</v>
+      <c r="C296" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F296" s="14">
-        <v>8900</v>
-      </c>
-      <c r="H296" s="13" t="s">
-        <v>213</v>
+        <v>83</v>
+      </c>
+      <c r="F296" s="2">
+        <v>39125</v>
+      </c>
+      <c r="G296" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -17340,20 +17340,20 @@
       <c r="B297" s="1">
         <v>115</v>
       </c>
-      <c r="C297" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="D297" s="1" t="s">
+      <c r="C297" t="s">
+        <v>65</v>
+      </c>
+      <c r="D297" t="s">
         <v>23</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F297" s="14">
-        <v>7200</v>
-      </c>
-      <c r="H297" s="13" t="s">
-        <v>214</v>
+        <v>169</v>
+      </c>
+      <c r="F297" s="11">
+        <v>7500</v>
+      </c>
+      <c r="G297" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -17363,20 +17363,20 @@
       <c r="B298" s="1">
         <v>115</v>
       </c>
-      <c r="C298" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>23</v>
+      <c r="C298" t="s">
+        <v>163</v>
+      </c>
+      <c r="D298" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F298" s="15">
-        <v>500</v>
-      </c>
-      <c r="H298" s="13" t="s">
-        <v>215</v>
+        <v>169</v>
+      </c>
+      <c r="F298" s="11">
+        <v>5200</v>
+      </c>
+      <c r="G298" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -17386,20 +17386,20 @@
       <c r="B299" s="1">
         <v>115</v>
       </c>
-      <c r="C299" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="D299" s="4" t="s">
-        <v>63</v>
+      <c r="C299" t="s">
+        <v>164</v>
+      </c>
+      <c r="D299" t="s">
+        <v>40</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F299" s="14">
-        <v>7800</v>
-      </c>
-      <c r="H299" s="13" t="s">
-        <v>217</v>
+        <v>169</v>
+      </c>
+      <c r="F299" s="11">
+        <v>5200</v>
+      </c>
+      <c r="G299" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -17409,20 +17409,20 @@
       <c r="B300" s="1">
         <v>115</v>
       </c>
-      <c r="C300" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="D300" s="4" t="s">
-        <v>79</v>
+      <c r="C300" t="s">
+        <v>164</v>
+      </c>
+      <c r="D300" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F300" s="14">
-        <v>2400</v>
-      </c>
-      <c r="H300" s="13" t="s">
-        <v>218</v>
+        <v>182</v>
+      </c>
+      <c r="F300">
+        <v>13515</v>
+      </c>
+      <c r="G300" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -17432,43 +17432,43 @@
       <c r="B301" s="1">
         <v>115</v>
       </c>
-      <c r="C301" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D301" s="4" t="s">
-        <v>86</v>
+      <c r="C301" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F301" s="14">
-        <v>12000</v>
-      </c>
-      <c r="H301" s="13" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="302" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="F301" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G301" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" ht="17.25">
       <c r="A302">
         <v>301</v>
       </c>
       <c r="B302" s="1">
         <v>115</v>
       </c>
-      <c r="C302" s="13" t="s">
-        <v>15</v>
+      <c r="C302" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E302" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F302" s="14">
-        <v>12000</v>
-      </c>
-      <c r="H302" s="13" t="s">
-        <v>219</v>
+        <v>80</v>
+      </c>
+      <c r="E302" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F302" s="2">
+        <v>221000</v>
+      </c>
+      <c r="G302" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -17478,20 +17478,20 @@
       <c r="B303" s="1">
         <v>115</v>
       </c>
-      <c r="C303" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D303" s="4" t="s">
-        <v>78</v>
+      <c r="C303" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F303" s="14">
-        <v>12000</v>
-      </c>
-      <c r="H303" s="13" t="s">
-        <v>219</v>
+        <v>83</v>
+      </c>
+      <c r="F303" s="2">
+        <v>26283</v>
+      </c>
+      <c r="G303" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -17501,71 +17501,71 @@
       <c r="B304" s="1">
         <v>115</v>
       </c>
-      <c r="C304" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D304" s="1" t="s">
-        <v>23</v>
+      <c r="C304" t="s">
+        <v>58</v>
+      </c>
+      <c r="D304" t="s">
+        <v>60</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F304" s="14">
-        <v>5960</v>
-      </c>
-      <c r="H304" s="13" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="305" spans="1:8">
+        <v>169</v>
+      </c>
+      <c r="F304" s="11">
+        <v>1100</v>
+      </c>
+      <c r="G304" s="12" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
       <c r="A305">
         <v>304</v>
       </c>
       <c r="B305" s="1">
         <v>115</v>
       </c>
-      <c r="C305" s="13" t="s">
-        <v>131</v>
+      <c r="C305" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F305" s="14">
-        <v>2000</v>
-      </c>
-      <c r="H305" s="13" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="306" spans="1:8">
+        <v>11</v>
+      </c>
+      <c r="F305" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G305" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7">
       <c r="A306">
         <v>305</v>
       </c>
       <c r="B306" s="1">
         <v>115</v>
       </c>
-      <c r="C306" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D306" s="1" t="s">
-        <v>23</v>
+      <c r="C306" t="s">
+        <v>59</v>
+      </c>
+      <c r="D306" t="s">
+        <v>60</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F306" s="14">
-        <v>2000</v>
-      </c>
-      <c r="H306" s="13" t="s">
-        <v>222</v>
+        <v>169</v>
+      </c>
+      <c r="F306" s="11">
+        <v>2700</v>
+      </c>
+      <c r="G306" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H257">
-    <sortCondition ref="C2:C257"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:H306">
+    <sortCondition ref="C2:C306"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2294B3F-7E5F-4A72-995B-22913B073146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDF8455-C3F9-41C4-8F4C-C229FDD4D9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料表!$A$1:$H$306</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料表!$A$1:$H$1</definedName>
     <definedName name="Barcode">OFFSET(#REF!,MATCH(#REF!,#REF!,0)-1,0)</definedName>
     <definedName name="重大活動行事曆">[1]重要活動行事曆!$C$2:$I$467</definedName>
     <definedName name="資料">#REF!</definedName>
@@ -30,7 +30,7 @@
     <definedName name="簽退時間">'[1]條碼_簽到表 (v2)'!$L$2:$L$452</definedName>
     <definedName name="簽退條碼">'[1]條碼_簽到表 (v2)'!$I$2:$I$452</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="230">
   <si>
     <t>序號</t>
   </si>
@@ -1142,6 +1142,27 @@
   </si>
   <si>
     <t>教師參加國內研習(討)會</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳家蓁</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔡政廷</t>
+  </si>
+  <si>
+    <t>黃文助</t>
+  </si>
+  <si>
+    <t>李士毅</t>
+  </si>
+  <si>
+    <t>升等獎勵金</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>升等審查費</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -10400,7 +10421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BAC909-8D45-4443-AECB-1592B366F0B1}">
-  <dimension ref="A1:H306"/>
+  <dimension ref="A1:H312"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="4.75" bestFit="1" customWidth="1"/>
@@ -11742,20 +11763,17 @@
       <c r="B57" s="1">
         <v>115</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>8</v>
+      <c r="C57" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F57" s="11">
+        <v>20000</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -11772,10 +11790,10 @@
         <v>23</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F58" s="2">
-        <v>20564</v>
+        <v>59500</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>8</v>
@@ -11788,20 +11806,20 @@
       <c r="B59" s="1">
         <v>115</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E59" s="8" t="s">
-        <v>87</v>
+      <c r="E59" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="F59" s="2">
-        <v>45000</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>88</v>
+        <v>20564</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -11817,14 +11835,14 @@
       <c r="D60" t="s">
         <v>23</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F60" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G60" t="s">
-        <v>167</v>
+      <c r="E60" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F60" s="2">
+        <v>45000</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -11837,17 +11855,17 @@
       <c r="C61" t="s">
         <v>22</v>
       </c>
-      <c r="D61" s="10" t="s">
-        <v>64</v>
+      <c r="D61" t="s">
+        <v>23</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F61">
-        <v>17479</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
+      </c>
+      <c r="F61" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G61" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -11857,20 +11875,20 @@
       <c r="B62" s="1">
         <v>115</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C62" t="s">
         <v>22</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>23</v>
+      <c r="D62" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F62" s="14">
-        <v>1000</v>
-      </c>
-      <c r="H62" s="13" t="s">
-        <v>200</v>
+        <v>182</v>
+      </c>
+      <c r="F62">
+        <v>17479</v>
+      </c>
+      <c r="G62" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -11880,20 +11898,20 @@
       <c r="B63" s="1">
         <v>115</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>24</v>
+      <c r="C63" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" s="2">
-        <v>51750</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>8</v>
+        <v>223</v>
+      </c>
+      <c r="F63" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H63" s="13" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -11910,13 +11928,13 @@
         <v>13</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F64" s="2">
-        <v>47687</v>
+        <v>51750</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>84</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -11926,20 +11944,20 @@
       <c r="B65" s="1">
         <v>115</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F65" s="11">
-        <v>7200</v>
-      </c>
-      <c r="G65" t="s">
-        <v>167</v>
+        <v>83</v>
+      </c>
+      <c r="F65" s="2">
+        <v>47687</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -11950,16 +11968,16 @@
         <v>115</v>
       </c>
       <c r="C66" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="D66" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F66" s="11">
-        <v>1500</v>
+        <v>7200</v>
       </c>
       <c r="G66" t="s">
         <v>167</v>
@@ -11972,20 +11990,20 @@
       <c r="B67" s="1">
         <v>115</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>16</v>
+      <c r="C67" t="s">
+        <v>133</v>
+      </c>
+      <c r="D67" t="s">
+        <v>23</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F67" s="2">
-        <v>42500</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F67" s="11">
+        <v>1500</v>
+      </c>
+      <c r="G67" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -12002,10 +12020,10 @@
         <v>16</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F68" s="2">
-        <v>63000</v>
+        <v>42500</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>8</v>
@@ -12018,20 +12036,20 @@
       <c r="B69" s="1">
         <v>115</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F69" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G69" t="s">
-        <v>167</v>
+        <v>11</v>
+      </c>
+      <c r="F69" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -12041,20 +12059,20 @@
       <c r="B70" s="1">
         <v>115</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C70" t="s">
         <v>25</v>
       </c>
-      <c r="D70" s="4" t="s">
-        <v>78</v>
+      <c r="D70" t="s">
+        <v>16</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F70" s="14">
-        <v>4800</v>
-      </c>
-      <c r="H70" s="13" t="s">
-        <v>187</v>
+        <v>169</v>
+      </c>
+      <c r="F70" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G70" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -12074,10 +12092,10 @@
         <v>223</v>
       </c>
       <c r="F71" s="14">
-        <v>12000</v>
+        <v>4800</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -12087,20 +12105,20 @@
       <c r="B72" s="1">
         <v>115</v>
       </c>
-      <c r="C72" t="s">
-        <v>134</v>
-      </c>
-      <c r="D72" t="s">
-        <v>23</v>
+      <c r="C72" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F72" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G72" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F72" s="14">
+        <v>12000</v>
+      </c>
+      <c r="H72" s="13" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -12110,20 +12128,20 @@
       <c r="B73" s="1">
         <v>115</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>20</v>
+      <c r="C73" t="s">
+        <v>134</v>
+      </c>
+      <c r="D73" t="s">
+        <v>23</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F73" s="2">
-        <v>17000</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F73" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G73" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -12140,10 +12158,10 @@
         <v>20</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F74" s="2">
-        <v>60000</v>
+        <v>17000</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>8</v>
@@ -12156,20 +12174,20 @@
       <c r="B75" s="1">
         <v>115</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D75" t="s">
-        <v>86</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>87</v>
+      <c r="D75" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="F75" s="2">
-        <v>47500</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>88</v>
+        <v>60000</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -12183,16 +12201,16 @@
         <v>26</v>
       </c>
       <c r="D76" t="s">
-        <v>20</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F76" s="11">
-        <v>8400</v>
-      </c>
-      <c r="G76" t="s">
-        <v>167</v>
+        <v>86</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F76" s="2">
+        <v>47500</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -12205,17 +12223,17 @@
       <c r="C77" t="s">
         <v>26</v>
       </c>
-      <c r="D77" s="10" t="s">
-        <v>86</v>
+      <c r="D77" t="s">
+        <v>20</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F77">
-        <v>43200</v>
-      </c>
-      <c r="G77" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
+      </c>
+      <c r="F77" s="11">
+        <v>8400</v>
+      </c>
+      <c r="G77" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -12225,20 +12243,20 @@
       <c r="B78" s="1">
         <v>115</v>
       </c>
-      <c r="C78" s="13" t="s">
+      <c r="C78" t="s">
         <v>26</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" s="10" t="s">
         <v>86</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F78" s="14">
-        <v>12000</v>
-      </c>
-      <c r="H78" s="13" t="s">
-        <v>219</v>
+        <v>182</v>
+      </c>
+      <c r="F78">
+        <v>43200</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -12248,20 +12266,20 @@
       <c r="B79" s="1">
         <v>115</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F79" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>88</v>
+      <c r="C79" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F79" s="14">
+        <v>12000</v>
+      </c>
+      <c r="H79" s="13" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -12271,23 +12289,20 @@
       <c r="B80" s="1">
         <v>115</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E80" s="10" t="s">
-        <v>170</v>
+      <c r="E80" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="F80" s="2">
-        <v>30850</v>
-      </c>
-      <c r="G80" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H80" t="s">
-        <v>107</v>
+        <v>50000</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -12304,10 +12319,10 @@
         <v>23</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F81" s="2">
-        <v>9696</v>
+        <v>30850</v>
       </c>
       <c r="G81" s="10" t="s">
         <v>116</v>
@@ -12329,14 +12344,17 @@
       <c r="D82" t="s">
         <v>23</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F82" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G82" t="s">
-        <v>167</v>
+      <c r="E82" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F82" s="2">
+        <v>9696</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H82" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -12346,20 +12364,20 @@
       <c r="B83" s="1">
         <v>115</v>
       </c>
-      <c r="C83" s="13" t="s">
+      <c r="C83" t="s">
         <v>85</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D83" t="s">
         <v>23</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F83" s="14">
-        <v>5960</v>
-      </c>
-      <c r="H83" s="13" t="s">
-        <v>220</v>
+        <v>169</v>
+      </c>
+      <c r="F83" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G83" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -12369,20 +12387,20 @@
       <c r="B84" s="1">
         <v>115</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>27</v>
+      <c r="C84" s="13" t="s">
+        <v>85</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F84" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>8</v>
+        <v>223</v>
+      </c>
+      <c r="F84" s="14">
+        <v>5960</v>
+      </c>
+      <c r="H84" s="13" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -12392,46 +12410,46 @@
       <c r="B85" s="1">
         <v>115</v>
       </c>
-      <c r="C85" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>93</v>
+      <c r="C85" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F85" s="2">
-        <v>32320</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="17.25">
+        <v>59500</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" s="1">
         <v>115</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>81</v>
+      <c r="C86" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="F86" s="2">
-        <v>140000</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
+        <v>32320</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="17.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -12444,14 +12462,14 @@
       <c r="D87" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>83</v>
+      <c r="E87" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F87" s="2">
-        <v>28884</v>
+        <v>140000</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -12461,23 +12479,20 @@
       <c r="B88" s="1">
         <v>115</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E88" s="10" t="s">
-        <v>170</v>
+      <c r="E88" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F88" s="2">
-        <v>30850</v>
-      </c>
-      <c r="G88" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H88" t="s">
-        <v>100</v>
+        <v>28884</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -12497,13 +12512,13 @@
         <v>170</v>
       </c>
       <c r="F89" s="2">
-        <v>19150</v>
+        <v>30850</v>
       </c>
       <c r="G89" s="10" t="s">
         <v>116</v>
       </c>
       <c r="H89" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -12520,16 +12535,16 @@
         <v>23</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F90" s="2">
-        <v>12936</v>
+        <v>19150</v>
       </c>
       <c r="G90" s="10" t="s">
         <v>116</v>
       </c>
       <c r="H90" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -12549,13 +12564,13 @@
         <v>171</v>
       </c>
       <c r="F91" s="2">
-        <v>31462</v>
+        <v>12936</v>
       </c>
       <c r="G91" s="10" t="s">
         <v>116</v>
       </c>
       <c r="H91" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -12571,14 +12586,17 @@
       <c r="D92" t="s">
         <v>23</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F92" s="11">
-        <v>3700</v>
-      </c>
-      <c r="G92" t="s">
-        <v>167</v>
+      <c r="E92" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F92" s="2">
+        <v>31462</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H92" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -12588,20 +12606,20 @@
       <c r="B93" s="1">
         <v>115</v>
       </c>
-      <c r="C93" s="13" t="s">
+      <c r="C93" t="s">
         <v>27</v>
       </c>
-      <c r="D93" s="4" t="s">
-        <v>64</v>
+      <c r="D93" t="s">
+        <v>23</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F93" s="14">
-        <v>1000</v>
-      </c>
-      <c r="H93" s="13" t="s">
-        <v>185</v>
+        <v>169</v>
+      </c>
+      <c r="F93" s="11">
+        <v>3700</v>
+      </c>
+      <c r="G93" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -12614,17 +12632,17 @@
       <c r="C94" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>23</v>
+      <c r="D94" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>223</v>
       </c>
       <c r="F94" s="14">
-        <v>4600</v>
+        <v>1000</v>
       </c>
       <c r="H94" s="13" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -12634,20 +12652,20 @@
       <c r="B95" s="1">
         <v>115</v>
       </c>
-      <c r="C95" t="s">
-        <v>135</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="C95" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F95" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G95" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F95" s="14">
+        <v>4600</v>
+      </c>
+      <c r="H95" s="13" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -12657,20 +12675,20 @@
       <c r="B96" s="1">
         <v>115</v>
       </c>
-      <c r="C96" s="13" t="s">
+      <c r="C96" t="s">
         <v>135</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="D96" t="s">
         <v>23</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F96" s="14">
-        <v>2400</v>
-      </c>
-      <c r="H96" s="13" t="s">
-        <v>197</v>
+        <v>169</v>
+      </c>
+      <c r="F96" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G96" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -12690,10 +12708,10 @@
         <v>223</v>
       </c>
       <c r="F97" s="14">
-        <v>1000</v>
+        <v>2400</v>
       </c>
       <c r="H97" s="13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -12703,23 +12721,23 @@
       <c r="B98" s="1">
         <v>115</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>28</v>
+      <c r="C98" s="13" t="s">
+        <v>135</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F98" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" ht="17.25">
+        <v>223</v>
+      </c>
+      <c r="F98" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H98" s="13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
       <c r="A99">
         <v>98</v>
       </c>
@@ -12730,42 +12748,39 @@
         <v>28</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>81</v>
+        <v>29</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F99" s="2">
-        <v>150000</v>
+        <v>63000</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="17.25">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100" s="1">
         <v>115</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D100" t="s">
-        <v>29</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>170</v>
+      <c r="D100" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F100" s="2">
-        <v>17789</v>
-      </c>
-      <c r="G100" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H100" t="s">
-        <v>106</v>
+        <v>150000</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -12782,10 +12797,10 @@
         <v>29</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F101" s="2">
-        <v>8085</v>
+        <v>17789</v>
       </c>
       <c r="G101" s="10" t="s">
         <v>116</v>
@@ -12807,14 +12822,17 @@
       <c r="D102" t="s">
         <v>29</v>
       </c>
-      <c r="E102" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F102" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G102" t="s">
-        <v>167</v>
+      <c r="E102" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F102" s="2">
+        <v>8085</v>
+      </c>
+      <c r="G102" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H102" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -12827,17 +12845,17 @@
       <c r="C103" t="s">
         <v>28</v>
       </c>
-      <c r="D103" s="10" t="s">
-        <v>76</v>
+      <c r="D103" t="s">
+        <v>29</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F103">
-        <v>42500</v>
-      </c>
-      <c r="G103" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
+      </c>
+      <c r="F103" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G103" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -12848,19 +12866,19 @@
         <v>115</v>
       </c>
       <c r="C104" t="s">
-        <v>131</v>
-      </c>
-      <c r="D104" t="s">
-        <v>23</v>
+        <v>28</v>
+      </c>
+      <c r="D104" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F104" s="11">
-        <v>8700</v>
-      </c>
-      <c r="G104" t="s">
-        <v>167</v>
+        <v>182</v>
+      </c>
+      <c r="F104">
+        <v>42500</v>
+      </c>
+      <c r="G104" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -12870,20 +12888,20 @@
       <c r="B105" s="1">
         <v>115</v>
       </c>
-      <c r="C105" s="13" t="s">
+      <c r="C105" t="s">
         <v>131</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D105" t="s">
         <v>23</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F105" s="14">
-        <v>4800</v>
-      </c>
-      <c r="H105" s="13" t="s">
-        <v>189</v>
+        <v>169</v>
+      </c>
+      <c r="F105" s="11">
+        <v>8700</v>
+      </c>
+      <c r="G105" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -12903,10 +12921,10 @@
         <v>223</v>
       </c>
       <c r="F106" s="14">
-        <v>2000</v>
+        <v>4800</v>
       </c>
       <c r="H106" s="13" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -12925,11 +12943,11 @@
       <c r="E107" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F107" s="15">
-        <v>688</v>
+      <c r="F107" s="14">
+        <v>2000</v>
       </c>
       <c r="H107" s="13" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -12948,11 +12966,11 @@
       <c r="E108" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F108" s="14">
-        <v>2000</v>
+      <c r="F108" s="15">
+        <v>688</v>
       </c>
       <c r="H108" s="13" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -12975,7 +12993,7 @@
         <v>2000</v>
       </c>
       <c r="H109" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -12985,20 +13003,20 @@
       <c r="B110" s="1">
         <v>115</v>
       </c>
-      <c r="C110" t="s">
-        <v>140</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="C110" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F110" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G110" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F110" s="14">
+        <v>2000</v>
+      </c>
+      <c r="H110" s="13" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -13009,7 +13027,7 @@
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D111" t="s">
         <v>23</v>
@@ -13031,20 +13049,20 @@
       <c r="B112" s="1">
         <v>115</v>
       </c>
-      <c r="C112" s="13" t="s">
+      <c r="C112" t="s">
         <v>136</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="D112" t="s">
         <v>23</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F112" s="14">
-        <v>7000</v>
-      </c>
-      <c r="H112" s="13" t="s">
-        <v>209</v>
+        <v>169</v>
+      </c>
+      <c r="F112" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G112" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -13054,20 +13072,20 @@
       <c r="B113" s="1">
         <v>115</v>
       </c>
-      <c r="C113" t="s">
-        <v>124</v>
-      </c>
-      <c r="D113" t="s">
-        <v>20</v>
+      <c r="C113" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F113" s="11">
-        <v>9600</v>
-      </c>
-      <c r="G113" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F113" s="14">
+        <v>7000</v>
+      </c>
+      <c r="H113" s="13" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -13080,17 +13098,17 @@
       <c r="C114" t="s">
         <v>124</v>
       </c>
-      <c r="D114" s="10" t="s">
-        <v>179</v>
+      <c r="D114" t="s">
+        <v>20</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F114">
-        <v>30000</v>
-      </c>
-      <c r="G114" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
+      </c>
+      <c r="F114" s="11">
+        <v>9600</v>
+      </c>
+      <c r="G114" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -13101,19 +13119,19 @@
         <v>115</v>
       </c>
       <c r="C115" t="s">
-        <v>137</v>
-      </c>
-      <c r="D115" t="s">
-        <v>23</v>
+        <v>124</v>
+      </c>
+      <c r="D115" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F115" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G115" t="s">
-        <v>167</v>
+        <v>182</v>
+      </c>
+      <c r="F115">
+        <v>30000</v>
+      </c>
+      <c r="G115" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -13124,7 +13142,7 @@
         <v>115</v>
       </c>
       <c r="C116" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D116" t="s">
         <v>23</v>
@@ -13133,7 +13151,7 @@
         <v>169</v>
       </c>
       <c r="F116" s="11">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="G116" t="s">
         <v>167</v>
@@ -13147,16 +13165,16 @@
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>161</v>
-      </c>
-      <c r="D117" s="10" t="s">
-        <v>179</v>
+        <v>138</v>
+      </c>
+      <c r="D117" t="s">
+        <v>23</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F117" s="11">
-        <v>400</v>
+        <v>10000</v>
       </c>
       <c r="G117" t="s">
         <v>167</v>
@@ -13176,13 +13194,13 @@
         <v>179</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F118">
-        <v>39613</v>
-      </c>
-      <c r="G118" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
+      </c>
+      <c r="F118" s="11">
+        <v>400</v>
+      </c>
+      <c r="G118" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -13192,20 +13210,20 @@
       <c r="B119" s="1">
         <v>115</v>
       </c>
-      <c r="C119" s="13" t="s">
+      <c r="C119" t="s">
         <v>161</v>
       </c>
-      <c r="D119" s="4" t="s">
+      <c r="D119" s="10" t="s">
         <v>179</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F119" s="14">
-        <v>20000</v>
-      </c>
-      <c r="H119" s="13" t="s">
-        <v>211</v>
+        <v>182</v>
+      </c>
+      <c r="F119">
+        <v>39613</v>
+      </c>
+      <c r="G119" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -13215,20 +13233,20 @@
       <c r="B120" s="1">
         <v>115</v>
       </c>
-      <c r="C120" t="s">
-        <v>160</v>
-      </c>
-      <c r="D120" s="10" t="s">
+      <c r="C120" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="D120" s="4" t="s">
         <v>179</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F120" s="11">
-        <v>500</v>
-      </c>
-      <c r="G120" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F120" s="14">
+        <v>20000</v>
+      </c>
+      <c r="H120" s="13" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -13239,16 +13257,16 @@
         <v>115</v>
       </c>
       <c r="C121" t="s">
-        <v>139</v>
-      </c>
-      <c r="D121" t="s">
-        <v>23</v>
+        <v>160</v>
+      </c>
+      <c r="D121" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F121" s="11">
-        <v>8700</v>
+        <v>500</v>
       </c>
       <c r="G121" t="s">
         <v>167</v>
@@ -13261,20 +13279,20 @@
       <c r="B122" s="1">
         <v>115</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>60</v>
+      <c r="C122" t="s">
+        <v>139</v>
+      </c>
+      <c r="D122" t="s">
+        <v>23</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F122" s="2">
-        <v>11185</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>84</v>
+        <v>169</v>
+      </c>
+      <c r="F122" s="11">
+        <v>8700</v>
+      </c>
+      <c r="G122" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -13284,20 +13302,20 @@
       <c r="B123" s="1">
         <v>115</v>
       </c>
-      <c r="C123" t="s">
-        <v>123</v>
-      </c>
-      <c r="D123" t="s">
-        <v>20</v>
+      <c r="C123" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F123" s="11">
-        <v>2500</v>
-      </c>
-      <c r="G123" t="s">
-        <v>167</v>
+        <v>83</v>
+      </c>
+      <c r="F123" s="2">
+        <v>11185</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -13307,20 +13325,20 @@
       <c r="B124" s="1">
         <v>115</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>23</v>
+      <c r="C124" t="s">
+        <v>123</v>
+      </c>
+      <c r="D124" t="s">
+        <v>20</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F124" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F124" s="11">
+        <v>2500</v>
+      </c>
+      <c r="G124" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -13337,10 +13355,10 @@
         <v>23</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F125" s="2">
-        <v>63000</v>
+        <v>59500</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>8</v>
@@ -13360,10 +13378,10 @@
         <v>23</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F126" s="2">
-        <v>40000</v>
+        <v>63000</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>8</v>
@@ -13376,20 +13394,20 @@
       <c r="B127" s="1">
         <v>115</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C127" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D127" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F127" s="11">
-        <v>5000</v>
-      </c>
-      <c r="G127" t="s">
-        <v>167</v>
+        <v>21</v>
+      </c>
+      <c r="F127" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -13402,17 +13420,17 @@
       <c r="C128" t="s">
         <v>30</v>
       </c>
-      <c r="D128" s="10" t="s">
-        <v>64</v>
+      <c r="D128" t="s">
+        <v>23</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F128">
-        <v>12000</v>
-      </c>
-      <c r="G128" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
+      </c>
+      <c r="F128" s="11">
+        <v>5000</v>
+      </c>
+      <c r="G128" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -13422,20 +13440,20 @@
       <c r="B129" s="1">
         <v>115</v>
       </c>
-      <c r="C129" s="13" t="s">
+      <c r="C129" t="s">
         <v>30</v>
       </c>
-      <c r="D129" s="1" t="s">
-        <v>23</v>
+      <c r="D129" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F129" s="14">
-        <v>6000</v>
-      </c>
-      <c r="H129" s="13" t="s">
-        <v>188</v>
+        <v>182</v>
+      </c>
+      <c r="F129">
+        <v>12000</v>
+      </c>
+      <c r="G129" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -13455,10 +13473,10 @@
         <v>223</v>
       </c>
       <c r="F130" s="14">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="H130" s="13" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -13468,20 +13486,20 @@
       <c r="B131" s="1">
         <v>115</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>31</v>
+      <c r="C131" s="13" t="s">
+        <v>30</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F131" s="2">
-        <v>70000</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>8</v>
+        <v>223</v>
+      </c>
+      <c r="F131" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H131" s="13" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -13491,20 +13509,20 @@
       <c r="B132" s="1">
         <v>115</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C132" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D132" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E132" s="8" t="s">
-        <v>87</v>
+      <c r="E132" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F132" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G132" s="9" t="s">
-        <v>88</v>
+        <v>70000</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -13520,14 +13538,14 @@
       <c r="D133" t="s">
         <v>23</v>
       </c>
-      <c r="E133" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F133" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G133" t="s">
-        <v>167</v>
+      <c r="E133" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F133" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G133" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -13538,22 +13556,19 @@
         <v>115</v>
       </c>
       <c r="C134" t="s">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="D134" t="s">
         <v>23</v>
       </c>
-      <c r="E134" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F134" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G134" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H134" t="s">
-        <v>110</v>
+      <c r="E134" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F134" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G134" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -13570,10 +13585,10 @@
         <v>23</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F135" s="2">
-        <v>38015</v>
+        <v>50000</v>
       </c>
       <c r="G135" s="10" t="s">
         <v>116</v>
@@ -13592,17 +13607,20 @@
       <c r="C136" t="s">
         <v>96</v>
       </c>
-      <c r="D136" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F136" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G136" t="s">
-        <v>167</v>
+      <c r="D136" t="s">
+        <v>23</v>
+      </c>
+      <c r="E136" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F136" s="2">
+        <v>38015</v>
+      </c>
+      <c r="G136" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H136" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -13612,20 +13630,20 @@
       <c r="B137" s="1">
         <v>115</v>
       </c>
-      <c r="C137" s="13" t="s">
+      <c r="C137" t="s">
         <v>96</v>
       </c>
-      <c r="D137" s="1" t="s">
-        <v>23</v>
+      <c r="D137" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F137" s="14">
-        <v>1000</v>
-      </c>
-      <c r="H137" s="13" t="s">
-        <v>200</v>
+        <v>169</v>
+      </c>
+      <c r="F137" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G137" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -13635,20 +13653,20 @@
       <c r="B138" s="1">
         <v>115</v>
       </c>
-      <c r="C138" t="s">
-        <v>127</v>
-      </c>
-      <c r="D138" t="s">
+      <c r="C138" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F138" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G138" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F138" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H138" s="13" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -13658,20 +13676,20 @@
       <c r="B139" s="1">
         <v>115</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>13</v>
+      <c r="C139" t="s">
+        <v>127</v>
+      </c>
+      <c r="D139" t="s">
+        <v>23</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F139" s="2">
-        <v>56000</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F139" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G139" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -13688,13 +13706,13 @@
         <v>13</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F140" s="2">
-        <v>39355</v>
+        <v>56000</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>84</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -13704,20 +13722,20 @@
       <c r="B141" s="1">
         <v>115</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C141" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D141" t="s">
+      <c r="D141" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F141" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G141" t="s">
-        <v>167</v>
+        <v>83</v>
+      </c>
+      <c r="F141" s="2">
+        <v>39355</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -13727,20 +13745,20 @@
       <c r="B142" s="1">
         <v>115</v>
       </c>
-      <c r="C142" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>10</v>
+      <c r="C142" t="s">
+        <v>32</v>
+      </c>
+      <c r="D142" t="s">
+        <v>13</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F142" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G142" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F142" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G142" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -13757,16 +13775,16 @@
         <v>10</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F143" s="2">
-        <v>63000</v>
+        <v>59500</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="17.25">
+    <row r="144" spans="1:8">
       <c r="A144">
         <v>143</v>
       </c>
@@ -13776,43 +13794,40 @@
       <c r="C144" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D144" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E144" s="3" t="s">
-        <v>81</v>
+      <c r="D144" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F144" s="2">
-        <v>106530</v>
+        <v>63000</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="17.25">
       <c r="A145">
         <v>144</v>
       </c>
       <c r="B145" s="1">
         <v>115</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C145" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D145" t="s">
-        <v>10</v>
-      </c>
-      <c r="E145" s="10" t="s">
-        <v>170</v>
+      <c r="D145" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F145" s="2">
-        <v>19942</v>
-      </c>
-      <c r="G145" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H145" t="s">
-        <v>108</v>
+        <v>106530</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -13829,10 +13844,10 @@
         <v>10</v>
       </c>
       <c r="E146" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F146" s="2">
-        <v>16447</v>
+        <v>19942</v>
       </c>
       <c r="G146" s="10" t="s">
         <v>116</v>
@@ -13841,50 +13856,53 @@
         <v>108</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="17.25">
+    <row r="147" spans="1:8">
       <c r="A147">
         <v>146</v>
       </c>
       <c r="B147" s="1">
         <v>115</v>
       </c>
-      <c r="C147" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D147" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E147" s="3" t="s">
-        <v>81</v>
+      <c r="C147" t="s">
+        <v>33</v>
+      </c>
+      <c r="D147" t="s">
+        <v>10</v>
+      </c>
+      <c r="E147" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="F147" s="2">
-        <v>117750</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8">
+        <v>16447</v>
+      </c>
+      <c r="G147" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H147" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="17.25">
       <c r="A148">
         <v>147</v>
       </c>
       <c r="B148" s="1">
         <v>115</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C148" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D148" s="10" t="s">
+      <c r="D148" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E148" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F148" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G148" t="s">
-        <v>167</v>
+      <c r="E148" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F148" s="2">
+        <v>117750</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -13894,20 +13912,20 @@
       <c r="B149" s="1">
         <v>115</v>
       </c>
-      <c r="C149" s="13" t="s">
+      <c r="C149" t="s">
         <v>74</v>
       </c>
-      <c r="D149" s="4" t="s">
+      <c r="D149" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F149" s="14">
-        <v>1000</v>
-      </c>
-      <c r="H149" s="13" t="s">
-        <v>203</v>
+        <v>169</v>
+      </c>
+      <c r="F149" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G149" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -13917,20 +13935,20 @@
       <c r="B150" s="1">
         <v>115</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>29</v>
+      <c r="C150" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F150" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G150" s="1" t="s">
-        <v>8</v>
+        <v>223</v>
+      </c>
+      <c r="F150" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H150" s="13" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -13940,20 +13958,20 @@
       <c r="B151" s="1">
         <v>115</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C151" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D151" t="s">
+      <c r="D151" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F151" s="11">
-        <v>6000</v>
-      </c>
-      <c r="G151" t="s">
-        <v>167</v>
+        <v>7</v>
+      </c>
+      <c r="F151" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -13966,17 +13984,17 @@
       <c r="C152" t="s">
         <v>34</v>
       </c>
-      <c r="D152" s="10" t="s">
-        <v>76</v>
+      <c r="D152" t="s">
+        <v>29</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F152">
-        <v>37500</v>
-      </c>
-      <c r="G152" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
+      </c>
+      <c r="F152" s="11">
+        <v>6000</v>
+      </c>
+      <c r="G152" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -13987,19 +14005,19 @@
         <v>115</v>
       </c>
       <c r="C153" t="s">
-        <v>146</v>
-      </c>
-      <c r="D153" t="s">
-        <v>23</v>
+        <v>34</v>
+      </c>
+      <c r="D153" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F153" s="11">
-        <v>6400</v>
-      </c>
-      <c r="G153" t="s">
-        <v>167</v>
+        <v>182</v>
+      </c>
+      <c r="F153">
+        <v>37500</v>
+      </c>
+      <c r="G153" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -14009,20 +14027,20 @@
       <c r="B154" s="1">
         <v>115</v>
       </c>
-      <c r="C154" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D154" s="1" t="s">
+      <c r="C154" t="s">
+        <v>146</v>
+      </c>
+      <c r="D154" t="s">
         <v>23</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F154" s="2">
-        <v>23014</v>
-      </c>
-      <c r="G154" s="1" t="s">
-        <v>84</v>
+        <v>169</v>
+      </c>
+      <c r="F154" s="11">
+        <v>6400</v>
+      </c>
+      <c r="G154" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -14032,20 +14050,20 @@
       <c r="B155" s="1">
         <v>115</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C155" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D155" t="s">
+      <c r="D155" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F155" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G155" t="s">
-        <v>167</v>
+        <v>83</v>
+      </c>
+      <c r="F155" s="2">
+        <v>23014</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -14056,7 +14074,7 @@
         <v>115</v>
       </c>
       <c r="C156" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="D156" t="s">
         <v>23</v>
@@ -14065,56 +14083,56 @@
         <v>169</v>
       </c>
       <c r="F156" s="11">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="G156" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="17.25">
+    <row r="157" spans="1:8">
       <c r="A157">
         <v>156</v>
       </c>
       <c r="B157" s="1">
         <v>115</v>
       </c>
-      <c r="C157" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D157" s="1" t="s">
+      <c r="C157" t="s">
+        <v>132</v>
+      </c>
+      <c r="D157" t="s">
         <v>23</v>
       </c>
-      <c r="E157" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F157" s="2">
-        <v>300000</v>
-      </c>
-      <c r="G157" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8">
+      <c r="E157" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F157" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G157" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="17.25">
       <c r="A158">
         <v>157</v>
       </c>
       <c r="B158" s="1">
         <v>115</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C158" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D158" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F158" s="11">
-        <v>3800</v>
-      </c>
-      <c r="G158" t="s">
-        <v>167</v>
+      <c r="D158" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F158" s="2">
+        <v>300000</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -14124,20 +14142,20 @@
       <c r="B159" s="1">
         <v>115</v>
       </c>
-      <c r="C159" s="13" t="s">
+      <c r="C159" t="s">
         <v>71</v>
       </c>
-      <c r="D159" s="1" t="s">
-        <v>23</v>
+      <c r="D159" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F159" s="15">
-        <v>999</v>
-      </c>
-      <c r="H159" s="13" t="s">
-        <v>204</v>
+        <v>169</v>
+      </c>
+      <c r="F159" s="11">
+        <v>3800</v>
+      </c>
+      <c r="G159" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -14156,11 +14174,11 @@
       <c r="E160" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F160" s="14">
-        <v>4090</v>
+      <c r="F160" s="15">
+        <v>999</v>
       </c>
       <c r="H160" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -14180,10 +14198,10 @@
         <v>223</v>
       </c>
       <c r="F161" s="14">
-        <v>8900</v>
+        <v>4090</v>
       </c>
       <c r="H161" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -14203,10 +14221,10 @@
         <v>223</v>
       </c>
       <c r="F162" s="14">
-        <v>2490</v>
+        <v>8900</v>
       </c>
       <c r="H162" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -14216,23 +14234,23 @@
       <c r="B163" s="1">
         <v>115</v>
       </c>
-      <c r="C163" s="1" t="s">
-        <v>35</v>
+      <c r="C163" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F163" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G163" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" ht="17.25">
+        <v>223</v>
+      </c>
+      <c r="F163" s="14">
+        <v>2490</v>
+      </c>
+      <c r="H163" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8">
       <c r="A164">
         <v>163</v>
       </c>
@@ -14242,20 +14260,20 @@
       <c r="C164" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D164" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E164" s="3" t="s">
-        <v>81</v>
+      <c r="D164" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="F164" s="2">
-        <v>255000</v>
+        <v>59500</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" ht="17.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -14265,17 +14283,17 @@
       <c r="C165" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D165" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>83</v>
+      <c r="D165" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F165" s="2">
-        <v>8285</v>
+        <v>255000</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -14285,20 +14303,20 @@
       <c r="B166" s="1">
         <v>115</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C166" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D166" t="s">
+      <c r="D166" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F166" s="11">
-        <v>9400</v>
-      </c>
-      <c r="G166" t="s">
-        <v>167</v>
+        <v>83</v>
+      </c>
+      <c r="F166" s="2">
+        <v>8285</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -14308,23 +14326,23 @@
       <c r="B167" s="1">
         <v>115</v>
       </c>
-      <c r="C167" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>23</v>
+      <c r="C167" t="s">
+        <v>35</v>
+      </c>
+      <c r="D167" t="s">
+        <v>16</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F167" s="2">
-        <v>51000</v>
-      </c>
-      <c r="G167" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" ht="17.25">
+        <v>169</v>
+      </c>
+      <c r="F167" s="11">
+        <v>9400</v>
+      </c>
+      <c r="G167" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
       <c r="A168">
         <v>167</v>
       </c>
@@ -14337,37 +14355,37 @@
       <c r="D168" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E168" s="3" t="s">
-        <v>81</v>
+      <c r="E168" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F168" s="2">
-        <v>250000</v>
+        <v>51000</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" ht="17.25">
       <c r="A169">
         <v>168</v>
       </c>
       <c r="B169" s="1">
         <v>115</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C169" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D169" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F169" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G169" t="s">
-        <v>167</v>
+      <c r="D169" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F169" s="2">
+        <v>250000</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -14377,20 +14395,20 @@
       <c r="B170" s="1">
         <v>115</v>
       </c>
-      <c r="C170" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>23</v>
+      <c r="C170" t="s">
+        <v>36</v>
+      </c>
+      <c r="D170" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F170" s="2">
-        <v>20368</v>
-      </c>
-      <c r="G170" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F170" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G170" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -14400,20 +14418,20 @@
       <c r="B171" s="1">
         <v>115</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C171" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D171" t="s">
+      <c r="D171" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F171" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G171" t="s">
-        <v>167</v>
+        <v>21</v>
+      </c>
+      <c r="F171" s="2">
+        <v>20368</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -14426,17 +14444,17 @@
       <c r="C172" t="s">
         <v>37</v>
       </c>
-      <c r="D172" s="10" t="s">
-        <v>64</v>
+      <c r="D172" t="s">
+        <v>23</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F172">
-        <v>29750</v>
-      </c>
-      <c r="G172" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
+      </c>
+      <c r="F172" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G172" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -14446,20 +14464,20 @@
       <c r="B173" s="1">
         <v>115</v>
       </c>
-      <c r="C173" s="13" t="s">
+      <c r="C173" t="s">
         <v>37</v>
       </c>
-      <c r="D173" s="1" t="s">
-        <v>23</v>
+      <c r="D173" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F173" s="14">
-        <v>3000</v>
-      </c>
-      <c r="H173" s="13" t="s">
-        <v>190</v>
+        <v>182</v>
+      </c>
+      <c r="F173">
+        <v>29750</v>
+      </c>
+      <c r="G173" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -14469,20 +14487,20 @@
       <c r="B174" s="1">
         <v>115</v>
       </c>
-      <c r="C174" t="s">
-        <v>162</v>
-      </c>
-      <c r="D174" s="10" t="s">
-        <v>179</v>
+      <c r="C174" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F174" s="11">
-        <v>7200</v>
-      </c>
-      <c r="G174" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F174" s="14">
+        <v>3000</v>
+      </c>
+      <c r="H174" s="13" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -14492,20 +14510,20 @@
       <c r="B175" s="1">
         <v>115</v>
       </c>
-      <c r="C175" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="D175" s="4" t="s">
-        <v>63</v>
+      <c r="C175" t="s">
+        <v>162</v>
+      </c>
+      <c r="D175" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F175" s="14">
-        <v>7800</v>
-      </c>
-      <c r="H175" s="13" t="s">
-        <v>217</v>
+        <v>169</v>
+      </c>
+      <c r="F175" s="11">
+        <v>7200</v>
+      </c>
+      <c r="G175" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -14515,20 +14533,20 @@
       <c r="B176" s="1">
         <v>115</v>
       </c>
-      <c r="C176" t="s">
-        <v>149</v>
-      </c>
-      <c r="D176" t="s">
-        <v>23</v>
+      <c r="C176" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F176" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G176" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F176" s="14">
+        <v>7800</v>
+      </c>
+      <c r="H176" s="13" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -14539,16 +14557,16 @@
         <v>115</v>
       </c>
       <c r="C177" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="D177" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F177" s="11">
-        <v>5600</v>
+        <v>3500</v>
       </c>
       <c r="G177" t="s">
         <v>167</v>
@@ -14564,17 +14582,17 @@
       <c r="C178" t="s">
         <v>122</v>
       </c>
-      <c r="D178" s="10" t="s">
-        <v>86</v>
+      <c r="D178" t="s">
+        <v>20</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F178">
-        <v>45000</v>
-      </c>
-      <c r="G178" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
+      </c>
+      <c r="F178" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G178" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -14585,19 +14603,19 @@
         <v>115</v>
       </c>
       <c r="C179" t="s">
-        <v>155</v>
-      </c>
-      <c r="D179" t="s">
-        <v>23</v>
+        <v>122</v>
+      </c>
+      <c r="D179" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F179" s="11">
-        <v>5700</v>
-      </c>
-      <c r="G179" t="s">
-        <v>167</v>
+        <v>182</v>
+      </c>
+      <c r="F179">
+        <v>45000</v>
+      </c>
+      <c r="G179" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -14608,16 +14626,16 @@
         <v>115</v>
       </c>
       <c r="C180" t="s">
-        <v>166</v>
-      </c>
-      <c r="D180" s="10" t="s">
-        <v>63</v>
+        <v>155</v>
+      </c>
+      <c r="D180" t="s">
+        <v>23</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F180" s="11">
-        <v>1400</v>
+        <v>5700</v>
       </c>
       <c r="G180" t="s">
         <v>167</v>
@@ -14630,20 +14648,20 @@
       <c r="B181" s="1">
         <v>115</v>
       </c>
-      <c r="C181" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>20</v>
+      <c r="C181" t="s">
+        <v>166</v>
+      </c>
+      <c r="D181" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F181" s="2">
-        <v>45000</v>
-      </c>
-      <c r="G181" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F181" s="11">
+        <v>1400</v>
+      </c>
+      <c r="G181" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -14653,20 +14671,20 @@
       <c r="B182" s="1">
         <v>115</v>
       </c>
-      <c r="C182" t="s">
+      <c r="C182" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D182" t="s">
+      <c r="D182" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F182" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G182" t="s">
-        <v>167</v>
+        <v>21</v>
+      </c>
+      <c r="F182" s="2">
+        <v>45000</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -14679,17 +14697,17 @@
       <c r="C183" t="s">
         <v>38</v>
       </c>
-      <c r="D183" s="10" t="s">
-        <v>86</v>
+      <c r="D183" t="s">
+        <v>20</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F183">
-        <v>13500</v>
-      </c>
-      <c r="G183" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
+      </c>
+      <c r="F183" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G183" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -14700,22 +14718,19 @@
         <v>115</v>
       </c>
       <c r="C184" t="s">
-        <v>99</v>
-      </c>
-      <c r="D184" t="s">
-        <v>60</v>
-      </c>
-      <c r="E184" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="F184" s="2">
-        <v>3400</v>
+        <v>38</v>
+      </c>
+      <c r="D184" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F184">
+        <v>13500</v>
       </c>
       <c r="G184" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H184" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -14732,10 +14747,10 @@
         <v>60</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F185" s="2">
-        <v>13120</v>
+        <v>3400</v>
       </c>
       <c r="G185" s="10" t="s">
         <v>116</v>
@@ -14757,14 +14772,17 @@
       <c r="D186" t="s">
         <v>60</v>
       </c>
-      <c r="E186" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F186" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G186" t="s">
-        <v>167</v>
+      <c r="E186" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F186" s="2">
+        <v>13120</v>
+      </c>
+      <c r="G186" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H186" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -14774,20 +14792,20 @@
       <c r="B187" s="1">
         <v>115</v>
       </c>
-      <c r="C187" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>40</v>
+      <c r="C187" t="s">
+        <v>99</v>
+      </c>
+      <c r="D187" t="s">
+        <v>60</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F187" s="2">
-        <v>2682</v>
-      </c>
-      <c r="G187" s="1" t="s">
-        <v>8</v>
+        <v>172</v>
+      </c>
+      <c r="F187" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G187" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -14804,10 +14822,10 @@
         <v>40</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F188" s="2">
-        <v>51000</v>
+        <v>2682</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>8</v>
@@ -14820,20 +14838,20 @@
       <c r="B189" s="1">
         <v>115</v>
       </c>
-      <c r="C189" t="s">
+      <c r="C189" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D189" t="s">
+      <c r="D189" s="1" t="s">
         <v>40</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F189" s="11">
-        <v>900</v>
-      </c>
-      <c r="G189" t="s">
-        <v>167</v>
+        <v>7</v>
+      </c>
+      <c r="F189" s="2">
+        <v>51000</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -14846,17 +14864,17 @@
       <c r="C190" t="s">
         <v>39</v>
       </c>
-      <c r="D190" s="10" t="s">
-        <v>179</v>
+      <c r="D190" t="s">
+        <v>40</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F190">
-        <v>17850</v>
-      </c>
-      <c r="G190" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
+      </c>
+      <c r="F190" s="11">
+        <v>900</v>
+      </c>
+      <c r="G190" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -14866,20 +14884,20 @@
       <c r="B191" s="1">
         <v>115</v>
       </c>
-      <c r="C191" s="13" t="s">
+      <c r="C191" t="s">
         <v>39</v>
       </c>
-      <c r="D191" s="4" t="s">
+      <c r="D191" s="10" t="s">
         <v>179</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F191" s="14">
-        <v>1000</v>
-      </c>
-      <c r="H191" s="13" t="s">
-        <v>200</v>
+        <v>182</v>
+      </c>
+      <c r="F191">
+        <v>17850</v>
+      </c>
+      <c r="G191" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -14889,20 +14907,20 @@
       <c r="B192" s="1">
         <v>115</v>
       </c>
-      <c r="C192" t="s">
-        <v>156</v>
-      </c>
-      <c r="D192" t="s">
-        <v>23</v>
+      <c r="C192" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>179</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F192" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G192" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F192" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H192" s="13" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -14912,20 +14930,20 @@
       <c r="B193" s="1">
         <v>115</v>
       </c>
-      <c r="C193" s="13" t="s">
+      <c r="C193" t="s">
         <v>156</v>
       </c>
-      <c r="D193" s="1" t="s">
+      <c r="D193" t="s">
         <v>23</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F193" s="14">
-        <v>7200</v>
-      </c>
-      <c r="H193" s="13" t="s">
-        <v>214</v>
+        <v>169</v>
+      </c>
+      <c r="F193" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G193" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -14935,20 +14953,20 @@
       <c r="B194" s="1">
         <v>115</v>
       </c>
-      <c r="C194" s="1" t="s">
-        <v>41</v>
+      <c r="C194" s="13" t="s">
+        <v>156</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F194" s="2">
-        <v>16788</v>
-      </c>
-      <c r="G194" s="1" t="s">
-        <v>8</v>
+        <v>223</v>
+      </c>
+      <c r="F194" s="14">
+        <v>7200</v>
+      </c>
+      <c r="H194" s="13" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -14965,10 +14983,10 @@
         <v>40</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F195" s="2">
-        <v>12800</v>
+        <v>16788</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>8</v>
@@ -14981,46 +14999,46 @@
       <c r="B196" s="1">
         <v>115</v>
       </c>
-      <c r="C196" t="s">
+      <c r="C196" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D196" s="10" t="s">
-        <v>179</v>
+      <c r="D196" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F196">
-        <v>15800</v>
-      </c>
-      <c r="G196" s="10" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" ht="17.25">
+        <v>11</v>
+      </c>
+      <c r="F196" s="2">
+        <v>12800</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8">
       <c r="A197">
         <v>196</v>
       </c>
       <c r="B197" s="1">
         <v>115</v>
       </c>
-      <c r="C197" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D197" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E197" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F197" s="2">
-        <v>143300</v>
-      </c>
-      <c r="G197" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8">
+      <c r="C197" t="s">
+        <v>41</v>
+      </c>
+      <c r="D197" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F197">
+        <v>15800</v>
+      </c>
+      <c r="G197" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" ht="17.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -15030,17 +15048,17 @@
       <c r="C198" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D198" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>83</v>
+      <c r="D198" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F198" s="2">
-        <v>34568</v>
+        <v>143300</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -15050,20 +15068,20 @@
       <c r="B199" s="1">
         <v>115</v>
       </c>
-      <c r="C199" t="s">
+      <c r="C199" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D199" s="10" t="s">
-        <v>77</v>
+      <c r="D199" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F199" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G199" t="s">
-        <v>167</v>
+        <v>83</v>
+      </c>
+      <c r="F199" s="2">
+        <v>34568</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -15073,20 +15091,20 @@
       <c r="B200" s="1">
         <v>115</v>
       </c>
-      <c r="C200" s="13" t="s">
+      <c r="C200" t="s">
         <v>66</v>
       </c>
-      <c r="D200" s="4" t="s">
+      <c r="D200" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F200" s="14">
-        <v>3600</v>
-      </c>
-      <c r="H200" s="13" t="s">
-        <v>186</v>
+        <v>169</v>
+      </c>
+      <c r="F200" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G200" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -15106,10 +15124,10 @@
         <v>223</v>
       </c>
       <c r="F201" s="14">
-        <v>2000</v>
+        <v>3600</v>
       </c>
       <c r="H201" s="13" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -15129,33 +15147,33 @@
         <v>223</v>
       </c>
       <c r="F202" s="14">
-        <v>3600</v>
+        <v>2000</v>
       </c>
       <c r="H202" s="13" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" ht="17.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8">
       <c r="A203">
         <v>202</v>
       </c>
       <c r="B203" s="1">
         <v>115</v>
       </c>
-      <c r="C203" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E203" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F203" s="2">
-        <v>300000</v>
-      </c>
-      <c r="G203" s="1" t="s">
-        <v>82</v>
+      <c r="C203" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D203" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F203" s="14">
+        <v>3600</v>
+      </c>
+      <c r="H203" s="13" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -15165,20 +15183,17 @@
       <c r="B204" s="1">
         <v>115</v>
       </c>
-      <c r="C204" t="s">
-        <v>73</v>
-      </c>
-      <c r="D204" t="s">
-        <v>23</v>
-      </c>
-      <c r="E204" s="7" t="s">
-        <v>87</v>
+      <c r="C204" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="D204" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E204" s="10" t="s">
+        <v>228</v>
       </c>
       <c r="F204" s="2">
-        <v>47500</v>
-      </c>
-      <c r="G204" s="9" t="s">
-        <v>88</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -15188,43 +15203,40 @@
       <c r="B205" s="1">
         <v>115</v>
       </c>
-      <c r="C205" t="s">
-        <v>73</v>
-      </c>
-      <c r="D205" t="s">
-        <v>23</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>169</v>
+      <c r="C205" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="D205" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E205" s="10" t="s">
+        <v>229</v>
       </c>
       <c r="F205" s="11">
-        <v>3700</v>
-      </c>
-      <c r="G205" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" ht="17.25">
       <c r="A206">
         <v>205</v>
       </c>
       <c r="B206" s="1">
         <v>115</v>
       </c>
-      <c r="C206" t="s">
-        <v>154</v>
-      </c>
-      <c r="D206" t="s">
+      <c r="C206" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E206" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F206" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G206" t="s">
-        <v>167</v>
+      <c r="E206" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F206" s="2">
+        <v>300000</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -15235,19 +15247,19 @@
         <v>115</v>
       </c>
       <c r="C207" t="s">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="D207" t="s">
         <v>23</v>
       </c>
-      <c r="E207" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F207" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G207" t="s">
-        <v>167</v>
+      <c r="E207" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F207" s="2">
+        <v>47500</v>
+      </c>
+      <c r="G207" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -15258,7 +15270,7 @@
         <v>115</v>
       </c>
       <c r="C208" t="s">
-        <v>153</v>
+        <v>73</v>
       </c>
       <c r="D208" t="s">
         <v>23</v>
@@ -15267,7 +15279,7 @@
         <v>169</v>
       </c>
       <c r="F208" s="11">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="G208" t="s">
         <v>167</v>
@@ -15280,43 +15292,43 @@
       <c r="B209" s="1">
         <v>115</v>
       </c>
-      <c r="C209" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>16</v>
+      <c r="C209" t="s">
+        <v>154</v>
+      </c>
+      <c r="D209" t="s">
+        <v>23</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F209" s="2">
-        <v>52000</v>
-      </c>
-      <c r="G209" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8" ht="17.25">
+        <v>169</v>
+      </c>
+      <c r="F209" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G209" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8">
       <c r="A210">
         <v>209</v>
       </c>
       <c r="B210" s="1">
         <v>115</v>
       </c>
-      <c r="C210" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D210" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E210" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F210" s="2">
-        <v>210000</v>
-      </c>
-      <c r="G210" s="1" t="s">
-        <v>82</v>
+      <c r="C210" t="s">
+        <v>157</v>
+      </c>
+      <c r="D210" t="s">
+        <v>23</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F210" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G210" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -15326,20 +15338,20 @@
       <c r="B211" s="1">
         <v>115</v>
       </c>
-      <c r="C211" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>20</v>
+      <c r="C211" t="s">
+        <v>153</v>
+      </c>
+      <c r="D211" t="s">
+        <v>23</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F211" s="2">
-        <v>42500</v>
-      </c>
-      <c r="G211" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F211" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G211" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -15350,42 +15362,42 @@
         <v>115</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F212" s="2">
-        <v>70000</v>
+        <v>52000</v>
       </c>
       <c r="G212" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:8" ht="17.25">
       <c r="A213">
         <v>212</v>
       </c>
       <c r="B213" s="1">
         <v>115</v>
       </c>
-      <c r="C213" t="s">
-        <v>43</v>
-      </c>
-      <c r="D213" t="s">
-        <v>20</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F213" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G213" t="s">
-        <v>167</v>
+      <c r="C213" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D213" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F213" s="2">
+        <v>210000</v>
+      </c>
+      <c r="G213" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -15395,20 +15407,20 @@
       <c r="B214" s="1">
         <v>115</v>
       </c>
-      <c r="C214" t="s">
+      <c r="C214" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D214" s="10" t="s">
-        <v>86</v>
+      <c r="D214" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F214">
-        <v>20250</v>
-      </c>
-      <c r="G214" s="10" t="s">
-        <v>184</v>
+        <v>21</v>
+      </c>
+      <c r="F214" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G214" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -15419,16 +15431,16 @@
         <v>115</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F215" s="2">
-        <v>59500</v>
+        <v>70000</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>8</v>
@@ -15441,43 +15453,43 @@
       <c r="B216" s="1">
         <v>115</v>
       </c>
-      <c r="C216" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>16</v>
+      <c r="C216" t="s">
+        <v>43</v>
+      </c>
+      <c r="D216" t="s">
+        <v>20</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F216" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G216" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" ht="17.25">
+        <v>169</v>
+      </c>
+      <c r="F216" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G216" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8">
       <c r="A217">
         <v>216</v>
       </c>
       <c r="B217" s="1">
         <v>115</v>
       </c>
-      <c r="C217" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D217" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E217" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F217" s="2">
-        <v>200000</v>
-      </c>
-      <c r="G217" s="1" t="s">
-        <v>82</v>
+      <c r="C217" t="s">
+        <v>43</v>
+      </c>
+      <c r="D217" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F217">
+        <v>20250</v>
+      </c>
+      <c r="G217" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -15487,23 +15499,20 @@
       <c r="B218" s="1">
         <v>115</v>
       </c>
-      <c r="C218" t="s">
-        <v>94</v>
-      </c>
-      <c r="D218" t="s">
-        <v>23</v>
-      </c>
-      <c r="E218" s="10" t="s">
-        <v>170</v>
+      <c r="C218" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="F218" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G218" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H218" t="s">
-        <v>101</v>
+        <v>59500</v>
+      </c>
+      <c r="G218" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -15513,46 +15522,43 @@
       <c r="B219" s="1">
         <v>115</v>
       </c>
-      <c r="C219" t="s">
-        <v>94</v>
-      </c>
-      <c r="D219" t="s">
-        <v>23</v>
-      </c>
-      <c r="E219" s="10" t="s">
-        <v>171</v>
+      <c r="C219" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F219" s="2">
-        <v>42393</v>
-      </c>
-      <c r="G219" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H219" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8">
+        <v>59500</v>
+      </c>
+      <c r="G219" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" ht="17.25">
       <c r="A220">
         <v>219</v>
       </c>
       <c r="B220" s="1">
         <v>115</v>
       </c>
-      <c r="C220" t="s">
-        <v>94</v>
-      </c>
-      <c r="D220" t="s">
-        <v>23</v>
-      </c>
-      <c r="E220" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F220" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G220" t="s">
-        <v>167</v>
+      <c r="C220" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D220" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F220" s="2">
+        <v>200000</v>
+      </c>
+      <c r="G220" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -15563,19 +15569,22 @@
         <v>115</v>
       </c>
       <c r="C221" t="s">
-        <v>158</v>
+        <v>94</v>
       </c>
       <c r="D221" t="s">
         <v>23</v>
       </c>
-      <c r="E221" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F221" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G221" t="s">
-        <v>167</v>
+      <c r="E221" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F221" s="2">
+        <v>50000</v>
+      </c>
+      <c r="G221" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H221" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -15586,19 +15595,22 @@
         <v>115</v>
       </c>
       <c r="C222" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="D222" t="s">
-        <v>29</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F222" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G222" t="s">
-        <v>167</v>
+        <v>23</v>
+      </c>
+      <c r="E222" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F222" s="2">
+        <v>42393</v>
+      </c>
+      <c r="G222" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H222" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="223" spans="1:8">
@@ -15608,43 +15620,40 @@
       <c r="B223" s="1">
         <v>115</v>
       </c>
-      <c r="C223" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>46</v>
+      <c r="C223" t="s">
+        <v>94</v>
+      </c>
+      <c r="D223" t="s">
+        <v>23</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F223" s="2">
-        <v>44118</v>
-      </c>
-      <c r="G223" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" ht="17.25">
+        <v>169</v>
+      </c>
+      <c r="F223" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G223" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8">
       <c r="A224">
         <v>223</v>
       </c>
       <c r="B224" s="1">
         <v>115</v>
       </c>
-      <c r="C224" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D224" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E224" s="3" t="s">
-        <v>81</v>
+      <c r="C224" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="D224" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E224" s="10" t="s">
+        <v>228</v>
       </c>
       <c r="F224" s="2">
-        <v>217500</v>
-      </c>
-      <c r="G224" s="1" t="s">
-        <v>82</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="225" spans="1:8">
@@ -15655,16 +15664,16 @@
         <v>115</v>
       </c>
       <c r="C225" t="s">
-        <v>45</v>
+        <v>158</v>
       </c>
       <c r="D225" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F225" s="11">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="G225" t="s">
         <v>167</v>
@@ -15677,20 +15686,20 @@
       <c r="B226" s="1">
         <v>115</v>
       </c>
-      <c r="C226" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D226" s="4" t="s">
-        <v>63</v>
+      <c r="C226" t="s">
+        <v>118</v>
+      </c>
+      <c r="D226" t="s">
+        <v>29</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F226" s="14">
-        <v>3582</v>
-      </c>
-      <c r="H226" s="13" t="s">
-        <v>212</v>
+        <v>169</v>
+      </c>
+      <c r="F226" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G226" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -15700,43 +15709,43 @@
       <c r="B227" s="1">
         <v>115</v>
       </c>
-      <c r="C227" t="s">
-        <v>165</v>
-      </c>
-      <c r="D227" s="10" t="s">
-        <v>63</v>
+      <c r="C227" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F227" s="11">
-        <v>6000</v>
-      </c>
-      <c r="G227" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8">
+        <v>21</v>
+      </c>
+      <c r="F227" s="2">
+        <v>44118</v>
+      </c>
+      <c r="G227" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" ht="17.25">
       <c r="A228">
         <v>227</v>
       </c>
       <c r="B228" s="1">
         <v>115</v>
       </c>
-      <c r="C228" t="s">
-        <v>119</v>
-      </c>
-      <c r="D228" t="s">
-        <v>10</v>
-      </c>
-      <c r="E228" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F228" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G228" t="s">
-        <v>167</v>
+      <c r="C228" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D228" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F228" s="2">
+        <v>217500</v>
+      </c>
+      <c r="G228" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="229" spans="1:8">
@@ -15746,20 +15755,20 @@
       <c r="B229" s="1">
         <v>115</v>
       </c>
-      <c r="C229" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="D229" s="4" t="s">
-        <v>79</v>
+      <c r="C229" t="s">
+        <v>45</v>
+      </c>
+      <c r="D229" t="s">
+        <v>46</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F229" s="14">
-        <v>2400</v>
-      </c>
-      <c r="H229" s="13" t="s">
-        <v>218</v>
+        <v>169</v>
+      </c>
+      <c r="F229" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G229" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="230" spans="1:8">
@@ -15769,20 +15778,20 @@
       <c r="B230" s="1">
         <v>115</v>
       </c>
-      <c r="C230" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D230" s="1" t="s">
-        <v>46</v>
+      <c r="C230" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D230" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F230" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G230" s="1" t="s">
-        <v>8</v>
+        <v>223</v>
+      </c>
+      <c r="F230" s="14">
+        <v>3582</v>
+      </c>
+      <c r="H230" s="13" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="231" spans="1:8">
@@ -15792,20 +15801,17 @@
       <c r="B231" s="1">
         <v>115</v>
       </c>
-      <c r="C231" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D231" s="1" t="s">
+      <c r="C231" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D231" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="E231" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F231" s="2">
-        <v>60000</v>
-      </c>
-      <c r="G231" s="1" t="s">
-        <v>91</v>
+      <c r="E231" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F231" s="11">
+        <v>20000</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -15816,16 +15822,16 @@
         <v>115</v>
       </c>
       <c r="C232" t="s">
-        <v>47</v>
-      </c>
-      <c r="D232" t="s">
-        <v>46</v>
+        <v>165</v>
+      </c>
+      <c r="D232" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F232" s="11">
-        <v>1400</v>
+        <v>6000</v>
       </c>
       <c r="G232" t="s">
         <v>167</v>
@@ -15838,20 +15844,20 @@
       <c r="B233" s="1">
         <v>115</v>
       </c>
-      <c r="C233" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D233" s="1" t="s">
-        <v>13</v>
+      <c r="C233" t="s">
+        <v>119</v>
+      </c>
+      <c r="D233" t="s">
+        <v>10</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F233" s="2">
-        <v>52500</v>
-      </c>
-      <c r="G233" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F233" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G233" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="234" spans="1:8">
@@ -15861,20 +15867,20 @@
       <c r="B234" s="1">
         <v>115</v>
       </c>
-      <c r="C234" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>13</v>
+      <c r="C234" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="D234" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F234" s="2">
-        <v>52776</v>
-      </c>
-      <c r="G234" s="1" t="s">
-        <v>84</v>
+        <v>223</v>
+      </c>
+      <c r="F234" s="14">
+        <v>2400</v>
+      </c>
+      <c r="H234" s="13" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -15884,20 +15890,20 @@
       <c r="B235" s="1">
         <v>115</v>
       </c>
-      <c r="C235" t="s">
-        <v>48</v>
-      </c>
-      <c r="D235" t="s">
-        <v>13</v>
+      <c r="C235" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F235" s="11">
-        <v>900</v>
-      </c>
-      <c r="G235" t="s">
-        <v>167</v>
+        <v>7</v>
+      </c>
+      <c r="F235" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G235" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -15908,19 +15914,19 @@
         <v>115</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E236" s="1" t="s">
-        <v>7</v>
+        <v>63</v>
+      </c>
+      <c r="E236" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="F236" s="2">
-        <v>63000</v>
+        <v>60000</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -15931,19 +15937,19 @@
         <v>115</v>
       </c>
       <c r="C237" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D237" t="s">
-        <v>23</v>
-      </c>
-      <c r="E237" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F237" s="2">
-        <v>41616</v>
-      </c>
-      <c r="G237" s="9" t="s">
-        <v>88</v>
+        <v>46</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F237" s="11">
+        <v>1400</v>
+      </c>
+      <c r="G237" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -15953,23 +15959,20 @@
       <c r="B238" s="1">
         <v>115</v>
       </c>
-      <c r="C238" t="s">
-        <v>49</v>
-      </c>
-      <c r="D238" t="s">
-        <v>23</v>
-      </c>
-      <c r="E238" s="10" t="s">
-        <v>170</v>
+      <c r="C238" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F238" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G238" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H238" t="s">
-        <v>109</v>
+        <v>52500</v>
+      </c>
+      <c r="G238" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -15979,23 +15982,20 @@
       <c r="B239" s="1">
         <v>115</v>
       </c>
-      <c r="C239" t="s">
-        <v>49</v>
-      </c>
-      <c r="D239" t="s">
-        <v>23</v>
-      </c>
-      <c r="E239" s="10" t="s">
-        <v>171</v>
+      <c r="C239" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F239" s="2">
-        <v>38569</v>
-      </c>
-      <c r="G239" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H239" t="s">
-        <v>109</v>
+        <v>52776</v>
+      </c>
+      <c r="G239" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -16006,16 +16006,16 @@
         <v>115</v>
       </c>
       <c r="C240" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D240" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F240" s="11">
-        <v>5000</v>
+        <v>900</v>
       </c>
       <c r="G240" t="s">
         <v>167</v>
@@ -16028,20 +16028,20 @@
       <c r="B241" s="1">
         <v>115</v>
       </c>
-      <c r="C241" t="s">
+      <c r="C241" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D241" s="10" t="s">
-        <v>64</v>
+      <c r="D241" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F241">
-        <v>50000</v>
-      </c>
-      <c r="G241" s="10" t="s">
-        <v>184</v>
+        <v>7</v>
+      </c>
+      <c r="F241" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G241" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -16051,20 +16051,20 @@
       <c r="B242" s="1">
         <v>115</v>
       </c>
-      <c r="C242" s="13" t="s">
+      <c r="C242" t="s">
         <v>49</v>
       </c>
-      <c r="D242" s="1" t="s">
+      <c r="D242" t="s">
         <v>23</v>
       </c>
-      <c r="E242" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F242" s="14">
-        <v>3081</v>
-      </c>
-      <c r="H242" s="13" t="s">
-        <v>196</v>
+      <c r="E242" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F242" s="2">
+        <v>41616</v>
+      </c>
+      <c r="G242" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -16074,20 +16074,23 @@
       <c r="B243" s="1">
         <v>115</v>
       </c>
-      <c r="C243" s="13" t="s">
+      <c r="C243" t="s">
         <v>49</v>
       </c>
-      <c r="D243" s="1" t="s">
+      <c r="D243" t="s">
         <v>23</v>
       </c>
-      <c r="E243" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F243" s="14">
-        <v>4800</v>
-      </c>
-      <c r="H243" s="13" t="s">
-        <v>187</v>
+      <c r="E243" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F243" s="2">
+        <v>50000</v>
+      </c>
+      <c r="G243" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H243" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="244" spans="1:8">
@@ -16097,20 +16100,23 @@
       <c r="B244" s="1">
         <v>115</v>
       </c>
-      <c r="C244" s="13" t="s">
+      <c r="C244" t="s">
         <v>49</v>
       </c>
-      <c r="D244" s="1" t="s">
+      <c r="D244" t="s">
         <v>23</v>
       </c>
-      <c r="E244" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F244" s="14">
-        <v>1000</v>
-      </c>
-      <c r="H244" s="13" t="s">
-        <v>200</v>
+      <c r="E244" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F244" s="2">
+        <v>38569</v>
+      </c>
+      <c r="G244" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H244" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -16120,20 +16126,20 @@
       <c r="B245" s="1">
         <v>115</v>
       </c>
-      <c r="C245" s="13" t="s">
+      <c r="C245" t="s">
         <v>49</v>
       </c>
-      <c r="D245" s="1" t="s">
+      <c r="D245" t="s">
         <v>23</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F245" s="15">
-        <v>500</v>
-      </c>
-      <c r="H245" s="13" t="s">
-        <v>215</v>
+        <v>169</v>
+      </c>
+      <c r="F245" s="11">
+        <v>5000</v>
+      </c>
+      <c r="G245" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -16144,19 +16150,19 @@
         <v>115</v>
       </c>
       <c r="C246" t="s">
-        <v>141</v>
-      </c>
-      <c r="D246" t="s">
-        <v>23</v>
+        <v>49</v>
+      </c>
+      <c r="D246" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F246" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G246" t="s">
-        <v>167</v>
+        <v>182</v>
+      </c>
+      <c r="F246">
+        <v>50000</v>
+      </c>
+      <c r="G246" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="247" spans="1:8">
@@ -16166,20 +16172,20 @@
       <c r="B247" s="1">
         <v>115</v>
       </c>
-      <c r="C247" s="1" t="s">
-        <v>50</v>
+      <c r="C247" s="13" t="s">
+        <v>49</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F247" s="2">
-        <v>31500</v>
-      </c>
-      <c r="G247" s="1" t="s">
-        <v>8</v>
+        <v>223</v>
+      </c>
+      <c r="F247" s="14">
+        <v>3081</v>
+      </c>
+      <c r="H247" s="13" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -16189,20 +16195,20 @@
       <c r="B248" s="1">
         <v>115</v>
       </c>
-      <c r="C248" t="s">
-        <v>50</v>
-      </c>
-      <c r="D248" s="10" t="s">
-        <v>64</v>
+      <c r="C248" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F248" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G248" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F248" s="14">
+        <v>4800</v>
+      </c>
+      <c r="H248" s="13" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="249" spans="1:8">
@@ -16212,20 +16218,20 @@
       <c r="B249" s="1">
         <v>115</v>
       </c>
-      <c r="C249" t="s">
-        <v>50</v>
-      </c>
-      <c r="D249" s="10" t="s">
-        <v>64</v>
+      <c r="C249" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F249">
-        <v>30150</v>
-      </c>
-      <c r="G249" s="10" t="s">
-        <v>184</v>
+        <v>223</v>
+      </c>
+      <c r="F249" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H249" s="13" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="250" spans="1:8">
@@ -16235,20 +16241,20 @@
       <c r="B250" s="1">
         <v>115</v>
       </c>
-      <c r="C250" s="1" t="s">
-        <v>51</v>
+      <c r="C250" s="13" t="s">
+        <v>49</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F250" s="2">
-        <v>42500</v>
-      </c>
-      <c r="G250" s="1" t="s">
-        <v>8</v>
+        <v>223</v>
+      </c>
+      <c r="F250" s="15">
+        <v>500</v>
+      </c>
+      <c r="H250" s="13" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="251" spans="1:8">
@@ -16259,16 +16265,16 @@
         <v>115</v>
       </c>
       <c r="C251" t="s">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="D251" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F251" s="11">
-        <v>5600</v>
+        <v>3500</v>
       </c>
       <c r="G251" t="s">
         <v>167</v>
@@ -16281,43 +16287,43 @@
       <c r="B252" s="1">
         <v>115</v>
       </c>
-      <c r="C252" t="s">
-        <v>51</v>
-      </c>
-      <c r="D252" s="10" t="s">
-        <v>86</v>
+      <c r="C252" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F252">
-        <v>12750</v>
-      </c>
-      <c r="G252" s="10" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="253" spans="1:8" ht="17.25">
+        <v>21</v>
+      </c>
+      <c r="F252" s="2">
+        <v>31500</v>
+      </c>
+      <c r="G252" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8">
       <c r="A253">
         <v>252</v>
       </c>
       <c r="B253" s="1">
         <v>115</v>
       </c>
-      <c r="C253" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D253" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E253" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F253" s="2">
-        <v>95912</v>
-      </c>
-      <c r="G253" s="1" t="s">
-        <v>82</v>
+      <c r="C253" t="s">
+        <v>50</v>
+      </c>
+      <c r="D253" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F253" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G253" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="254" spans="1:8">
@@ -16328,19 +16334,19 @@
         <v>115</v>
       </c>
       <c r="C254" t="s">
-        <v>72</v>
-      </c>
-      <c r="D254" t="s">
-        <v>23</v>
+        <v>50</v>
+      </c>
+      <c r="D254" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F254" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G254" t="s">
-        <v>167</v>
+        <v>182</v>
+      </c>
+      <c r="F254">
+        <v>30150</v>
+      </c>
+      <c r="G254" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -16350,43 +16356,43 @@
       <c r="B255" s="1">
         <v>115</v>
       </c>
-      <c r="C255" t="s">
-        <v>129</v>
-      </c>
-      <c r="D255" t="s">
-        <v>23</v>
+      <c r="C255" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F255" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G255" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="256" spans="1:8" ht="17.25">
+        <v>21</v>
+      </c>
+      <c r="F255" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G255" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8">
       <c r="A256">
         <v>255</v>
       </c>
       <c r="B256" s="1">
         <v>115</v>
       </c>
-      <c r="C256" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D256" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E256" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F256" s="2">
-        <v>28500</v>
-      </c>
-      <c r="G256" s="1" t="s">
-        <v>82</v>
+      <c r="C256" t="s">
+        <v>51</v>
+      </c>
+      <c r="D256" t="s">
+        <v>20</v>
+      </c>
+      <c r="E256" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F256" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G256" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="257" spans="1:8">
@@ -16397,42 +16403,42 @@
         <v>115</v>
       </c>
       <c r="C257" t="s">
-        <v>128</v>
-      </c>
-      <c r="D257" t="s">
-        <v>23</v>
+        <v>51</v>
+      </c>
+      <c r="D257" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F257" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G257" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="258" spans="1:8">
+        <v>182</v>
+      </c>
+      <c r="F257">
+        <v>12750</v>
+      </c>
+      <c r="G257" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" ht="17.25">
       <c r="A258">
         <v>257</v>
       </c>
       <c r="B258" s="1">
         <v>115</v>
       </c>
-      <c r="C258" t="s">
-        <v>142</v>
-      </c>
-      <c r="D258" t="s">
+      <c r="C258" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D258" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E258" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F258" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G258" t="s">
-        <v>167</v>
+      <c r="E258" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F258" s="2">
+        <v>95912</v>
+      </c>
+      <c r="G258" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -16443,7 +16449,7 @@
         <v>115</v>
       </c>
       <c r="C259" t="s">
-        <v>147</v>
+        <v>72</v>
       </c>
       <c r="D259" t="s">
         <v>23</v>
@@ -16465,43 +16471,43 @@
       <c r="B260" s="1">
         <v>115</v>
       </c>
-      <c r="C260" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D260" s="1" t="s">
+      <c r="C260" t="s">
+        <v>129</v>
+      </c>
+      <c r="D260" t="s">
         <v>23</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F260" s="14">
-        <v>20000</v>
-      </c>
-      <c r="H260" s="13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="261" spans="1:8">
+        <v>169</v>
+      </c>
+      <c r="F260" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G260" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" ht="17.25">
       <c r="A261">
         <v>260</v>
       </c>
       <c r="B261" s="1">
         <v>115</v>
       </c>
-      <c r="C261" t="s">
-        <v>148</v>
-      </c>
-      <c r="D261" t="s">
-        <v>23</v>
-      </c>
-      <c r="E261" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F261" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G261" t="s">
-        <v>167</v>
+      <c r="C261" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E261" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F261" s="2">
+        <v>28500</v>
+      </c>
+      <c r="G261" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -16511,20 +16517,20 @@
       <c r="B262" s="1">
         <v>115</v>
       </c>
-      <c r="C262" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D262" s="1" t="s">
-        <v>29</v>
+      <c r="C262" t="s">
+        <v>128</v>
+      </c>
+      <c r="D262" t="s">
+        <v>23</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F262" s="2">
-        <v>29250</v>
-      </c>
-      <c r="G262" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F262" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G262" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -16535,22 +16541,19 @@
         <v>115</v>
       </c>
       <c r="C263" t="s">
-        <v>52</v>
+        <v>142</v>
       </c>
       <c r="D263" t="s">
-        <v>29</v>
-      </c>
-      <c r="E263" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F263" s="2">
-        <v>8900</v>
-      </c>
-      <c r="G263" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H263" t="s">
-        <v>104</v>
+        <v>23</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F263" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G263" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -16561,22 +16564,19 @@
         <v>115</v>
       </c>
       <c r="C264" t="s">
-        <v>52</v>
+        <v>147</v>
       </c>
       <c r="D264" t="s">
-        <v>29</v>
-      </c>
-      <c r="E264" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F264" s="2">
-        <v>0</v>
-      </c>
-      <c r="G264" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H264" t="s">
-        <v>111</v>
+        <v>23</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F264" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G264" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -16586,23 +16586,20 @@
       <c r="B265" s="1">
         <v>115</v>
       </c>
-      <c r="C265" t="s">
-        <v>52</v>
-      </c>
-      <c r="D265" t="s">
-        <v>29</v>
-      </c>
-      <c r="E265" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F265" s="2">
-        <v>19190</v>
-      </c>
-      <c r="G265" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H265" t="s">
-        <v>104</v>
+      <c r="C265" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F265" s="14">
+        <v>20000</v>
+      </c>
+      <c r="H265" s="13" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="266" spans="1:8">
@@ -16613,22 +16610,19 @@
         <v>115</v>
       </c>
       <c r="C266" t="s">
-        <v>52</v>
+        <v>148</v>
       </c>
       <c r="D266" t="s">
-        <v>29</v>
-      </c>
-      <c r="E266" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F266" s="2">
-        <v>17728</v>
-      </c>
-      <c r="G266" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H266" t="s">
-        <v>111</v>
+        <v>23</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F266" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G266" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -16638,20 +16632,20 @@
       <c r="B267" s="1">
         <v>115</v>
       </c>
-      <c r="C267" t="s">
+      <c r="C267" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D267" t="s">
+      <c r="D267" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F267" s="11">
-        <v>2200</v>
-      </c>
-      <c r="G267" t="s">
-        <v>167</v>
+        <v>21</v>
+      </c>
+      <c r="F267" s="2">
+        <v>29250</v>
+      </c>
+      <c r="G267" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -16664,17 +16658,20 @@
       <c r="C268" t="s">
         <v>52</v>
       </c>
-      <c r="D268" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E268" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F268">
-        <v>32175</v>
+      <c r="D268" t="s">
+        <v>29</v>
+      </c>
+      <c r="E268" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F268" s="2">
+        <v>8900</v>
       </c>
       <c r="G268" s="10" t="s">
-        <v>184</v>
+        <v>116</v>
+      </c>
+      <c r="H268" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -16684,20 +16681,23 @@
       <c r="B269" s="1">
         <v>115</v>
       </c>
-      <c r="C269" s="13" t="s">
+      <c r="C269" t="s">
         <v>52</v>
       </c>
-      <c r="D269" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E269" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F269" s="14">
-        <v>8900</v>
-      </c>
-      <c r="H269" s="13" t="s">
-        <v>213</v>
+      <c r="D269" t="s">
+        <v>29</v>
+      </c>
+      <c r="E269" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F269" s="2">
+        <v>0</v>
+      </c>
+      <c r="G269" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H269" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -16708,19 +16708,22 @@
         <v>115</v>
       </c>
       <c r="C270" t="s">
-        <v>159</v>
-      </c>
-      <c r="D270" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E270" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F270" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G270" t="s">
-        <v>167</v>
+        <v>52</v>
+      </c>
+      <c r="D270" t="s">
+        <v>29</v>
+      </c>
+      <c r="E270" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F270" s="2">
+        <v>19190</v>
+      </c>
+      <c r="G270" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H270" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -16731,22 +16734,22 @@
         <v>115</v>
       </c>
       <c r="C271" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="D271" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E271" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F271" s="2">
-        <v>40000</v>
+        <v>17728</v>
       </c>
       <c r="G271" s="10" t="s">
         <v>116</v>
       </c>
       <c r="H271" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -16757,22 +16760,19 @@
         <v>115</v>
       </c>
       <c r="C272" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="D272" t="s">
-        <v>23</v>
-      </c>
-      <c r="E272" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F272" s="2">
-        <v>17600</v>
-      </c>
-      <c r="G272" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H272" t="s">
-        <v>113</v>
+        <v>29</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F272" s="11">
+        <v>2200</v>
+      </c>
+      <c r="G272" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -16783,19 +16783,19 @@
         <v>115</v>
       </c>
       <c r="C273" t="s">
-        <v>98</v>
-      </c>
-      <c r="D273" t="s">
-        <v>23</v>
+        <v>52</v>
+      </c>
+      <c r="D273" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F273" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G273" t="s">
-        <v>167</v>
+        <v>182</v>
+      </c>
+      <c r="F273">
+        <v>32175</v>
+      </c>
+      <c r="G273" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -16805,20 +16805,20 @@
       <c r="B274" s="1">
         <v>115</v>
       </c>
-      <c r="C274" t="s">
-        <v>150</v>
-      </c>
-      <c r="D274" t="s">
-        <v>23</v>
+      <c r="C274" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D274" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F274" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G274" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F274" s="14">
+        <v>8900</v>
+      </c>
+      <c r="H274" s="13" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -16828,20 +16828,17 @@
       <c r="B275" s="1">
         <v>115</v>
       </c>
-      <c r="C275" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D275" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E275" s="1" t="s">
-        <v>21</v>
+      <c r="C275" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D275" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E275" s="10" t="s">
+        <v>228</v>
       </c>
       <c r="F275" s="2">
-        <v>41384</v>
-      </c>
-      <c r="G275" s="1" t="s">
-        <v>8</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -16852,22 +16849,19 @@
         <v>115</v>
       </c>
       <c r="C276" t="s">
-        <v>53</v>
-      </c>
-      <c r="D276" t="s">
-        <v>23</v>
-      </c>
-      <c r="E276" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F276" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G276" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H276" t="s">
-        <v>114</v>
+        <v>159</v>
+      </c>
+      <c r="D276" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F276" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G276" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -16878,22 +16872,22 @@
         <v>115</v>
       </c>
       <c r="C277" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="D277" t="s">
         <v>23</v>
       </c>
       <c r="E277" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F277" s="2">
-        <v>19200</v>
+        <v>40000</v>
       </c>
       <c r="G277" s="10" t="s">
         <v>116</v>
       </c>
       <c r="H277" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="278" spans="1:8">
@@ -16904,19 +16898,22 @@
         <v>115</v>
       </c>
       <c r="C278" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="D278" t="s">
         <v>23</v>
       </c>
-      <c r="E278" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F278" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G278" t="s">
-        <v>167</v>
+      <c r="E278" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F278" s="2">
+        <v>17600</v>
+      </c>
+      <c r="G278" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H278" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -16926,20 +16923,20 @@
       <c r="B279" s="1">
         <v>115</v>
       </c>
-      <c r="C279" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D279" s="1" t="s">
-        <v>13</v>
+      <c r="C279" t="s">
+        <v>98</v>
+      </c>
+      <c r="D279" t="s">
+        <v>23</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F279" s="2">
-        <v>56000</v>
-      </c>
-      <c r="G279" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F279" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G279" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -16949,20 +16946,20 @@
       <c r="B280" s="1">
         <v>115</v>
       </c>
-      <c r="C280" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D280" s="1" t="s">
-        <v>13</v>
+      <c r="C280" t="s">
+        <v>150</v>
+      </c>
+      <c r="D280" t="s">
+        <v>23</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F280" s="2">
-        <v>48284</v>
-      </c>
-      <c r="G280" s="1" t="s">
-        <v>84</v>
+        <v>169</v>
+      </c>
+      <c r="F280" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G280" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -16972,20 +16969,20 @@
       <c r="B281" s="1">
         <v>115</v>
       </c>
-      <c r="C281" t="s">
-        <v>54</v>
-      </c>
-      <c r="D281" t="s">
-        <v>13</v>
+      <c r="C281" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F281" s="11">
-        <v>6300</v>
-      </c>
-      <c r="G281" t="s">
-        <v>167</v>
+        <v>21</v>
+      </c>
+      <c r="F281" s="2">
+        <v>41384</v>
+      </c>
+      <c r="G281" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="282" spans="1:8">
@@ -16995,20 +16992,23 @@
       <c r="B282" s="1">
         <v>115</v>
       </c>
-      <c r="C282" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E282" s="1" t="s">
-        <v>21</v>
+      <c r="C282" t="s">
+        <v>53</v>
+      </c>
+      <c r="D282" t="s">
+        <v>23</v>
+      </c>
+      <c r="E282" s="10" t="s">
+        <v>170</v>
       </c>
       <c r="F282" s="2">
-        <v>42500</v>
-      </c>
-      <c r="G282" s="1" t="s">
-        <v>8</v>
+        <v>40000</v>
+      </c>
+      <c r="G282" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H282" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="283" spans="1:8">
@@ -17019,19 +17019,22 @@
         <v>115</v>
       </c>
       <c r="C283" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D283" t="s">
-        <v>20</v>
-      </c>
-      <c r="E283" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F283" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G283" t="s">
-        <v>167</v>
+        <v>23</v>
+      </c>
+      <c r="E283" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F283" s="2">
+        <v>19200</v>
+      </c>
+      <c r="G283" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H283" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -17042,19 +17045,19 @@
         <v>115</v>
       </c>
       <c r="C284" t="s">
-        <v>55</v>
-      </c>
-      <c r="D284" s="10" t="s">
-        <v>86</v>
+        <v>53</v>
+      </c>
+      <c r="D284" t="s">
+        <v>23</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F284">
-        <v>19125</v>
-      </c>
-      <c r="G284" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
+      </c>
+      <c r="F284" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G284" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="285" spans="1:8">
@@ -17065,16 +17068,16 @@
         <v>115</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F285" s="2">
-        <v>41770</v>
+        <v>56000</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>8</v>
@@ -17087,20 +17090,20 @@
       <c r="B286" s="1">
         <v>115</v>
       </c>
-      <c r="C286" t="s">
-        <v>56</v>
-      </c>
-      <c r="D286" t="s">
-        <v>23</v>
+      <c r="C286" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F286" s="11">
-        <v>4100</v>
-      </c>
-      <c r="G286" t="s">
-        <v>167</v>
+        <v>83</v>
+      </c>
+      <c r="F286" s="2">
+        <v>48284</v>
+      </c>
+      <c r="G286" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="287" spans="1:8">
@@ -17111,19 +17114,19 @@
         <v>115</v>
       </c>
       <c r="C287" t="s">
-        <v>56</v>
-      </c>
-      <c r="D287" s="10" t="s">
-        <v>64</v>
+        <v>54</v>
+      </c>
+      <c r="D287" t="s">
+        <v>13</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F287">
-        <v>18584</v>
-      </c>
-      <c r="G287" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
+      </c>
+      <c r="F287" s="11">
+        <v>6300</v>
+      </c>
+      <c r="G287" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -17134,16 +17137,16 @@
         <v>115</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D288" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F288" s="2">
-        <v>45000</v>
+        <v>42500</v>
       </c>
       <c r="G288" s="1" t="s">
         <v>8</v>
@@ -17157,19 +17160,19 @@
         <v>115</v>
       </c>
       <c r="C289" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D289" t="s">
-        <v>86</v>
-      </c>
-      <c r="E289" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F289" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G289" s="9" t="s">
-        <v>88</v>
+        <v>20</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F289" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G289" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="290" spans="1:8">
@@ -17180,19 +17183,19 @@
         <v>115</v>
       </c>
       <c r="C290" t="s">
-        <v>57</v>
-      </c>
-      <c r="D290" t="s">
-        <v>20</v>
+        <v>55</v>
+      </c>
+      <c r="D290" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F290" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G290" t="s">
-        <v>167</v>
+        <v>182</v>
+      </c>
+      <c r="F290">
+        <v>19125</v>
+      </c>
+      <c r="G290" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="291" spans="1:8">
@@ -17202,20 +17205,20 @@
       <c r="B291" s="1">
         <v>115</v>
       </c>
-      <c r="C291" t="s">
-        <v>151</v>
-      </c>
-      <c r="D291" t="s">
+      <c r="C291" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D291" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F291" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G291" t="s">
-        <v>167</v>
+        <v>21</v>
+      </c>
+      <c r="F291" s="2">
+        <v>41770</v>
+      </c>
+      <c r="G291" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -17225,20 +17228,20 @@
       <c r="B292" s="1">
         <v>115</v>
       </c>
-      <c r="C292" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="D292" s="1" t="s">
+      <c r="C292" t="s">
+        <v>56</v>
+      </c>
+      <c r="D292" t="s">
         <v>23</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F292" s="14">
-        <v>4500</v>
-      </c>
-      <c r="H292" s="13" t="s">
-        <v>193</v>
+        <v>169</v>
+      </c>
+      <c r="F292" s="11">
+        <v>4100</v>
+      </c>
+      <c r="G292" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -17248,20 +17251,20 @@
       <c r="B293" s="1">
         <v>115</v>
       </c>
-      <c r="C293" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>23</v>
+      <c r="C293" t="s">
+        <v>56</v>
+      </c>
+      <c r="D293" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F293" s="15">
-        <v>850</v>
-      </c>
-      <c r="H293" s="13" t="s">
-        <v>199</v>
+        <v>182</v>
+      </c>
+      <c r="F293">
+        <v>18584</v>
+      </c>
+      <c r="G293" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -17271,20 +17274,20 @@
       <c r="B294" s="1">
         <v>115</v>
       </c>
-      <c r="C294" t="s">
-        <v>152</v>
-      </c>
-      <c r="D294" t="s">
-        <v>23</v>
+      <c r="C294" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F294" s="11">
-        <v>5000</v>
-      </c>
-      <c r="G294" t="s">
-        <v>167</v>
+        <v>7</v>
+      </c>
+      <c r="F294" s="2">
+        <v>45000</v>
+      </c>
+      <c r="G294" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -17294,20 +17297,20 @@
       <c r="B295" s="1">
         <v>115</v>
       </c>
-      <c r="C295" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="D295" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E295" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F295" s="15">
-        <v>500</v>
-      </c>
-      <c r="H295" s="13" t="s">
-        <v>191</v>
+      <c r="C295" t="s">
+        <v>57</v>
+      </c>
+      <c r="D295" t="s">
+        <v>86</v>
+      </c>
+      <c r="E295" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F295" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G295" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -17317,20 +17320,20 @@
       <c r="B296" s="1">
         <v>115</v>
       </c>
-      <c r="C296" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D296" s="1" t="s">
-        <v>23</v>
+      <c r="C296" t="s">
+        <v>57</v>
+      </c>
+      <c r="D296" t="s">
+        <v>20</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F296" s="2">
-        <v>39125</v>
-      </c>
-      <c r="G296" s="1" t="s">
-        <v>84</v>
+        <v>169</v>
+      </c>
+      <c r="F296" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G296" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -17341,7 +17344,7 @@
         <v>115</v>
       </c>
       <c r="C297" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="D297" t="s">
         <v>23</v>
@@ -17350,7 +17353,7 @@
         <v>169</v>
       </c>
       <c r="F297" s="11">
-        <v>7500</v>
+        <v>3500</v>
       </c>
       <c r="G297" t="s">
         <v>167</v>
@@ -17363,20 +17366,20 @@
       <c r="B298" s="1">
         <v>115</v>
       </c>
-      <c r="C298" t="s">
-        <v>163</v>
-      </c>
-      <c r="D298" s="10" t="s">
-        <v>179</v>
+      <c r="C298" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F298" s="11">
-        <v>5200</v>
-      </c>
-      <c r="G298" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F298" s="14">
+        <v>4500</v>
+      </c>
+      <c r="H298" s="13" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -17386,20 +17389,20 @@
       <c r="B299" s="1">
         <v>115</v>
       </c>
-      <c r="C299" t="s">
-        <v>164</v>
-      </c>
-      <c r="D299" t="s">
-        <v>40</v>
+      <c r="C299" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="D299" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F299" s="11">
-        <v>5200</v>
-      </c>
-      <c r="G299" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F299" s="15">
+        <v>850</v>
+      </c>
+      <c r="H299" s="13" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -17410,19 +17413,19 @@
         <v>115</v>
       </c>
       <c r="C300" t="s">
-        <v>164</v>
-      </c>
-      <c r="D300" s="10" t="s">
-        <v>179</v>
+        <v>152</v>
+      </c>
+      <c r="D300" t="s">
+        <v>23</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F300">
-        <v>13515</v>
-      </c>
-      <c r="G300" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
+      </c>
+      <c r="F300" s="11">
+        <v>5000</v>
+      </c>
+      <c r="G300" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -17432,23 +17435,23 @@
       <c r="B301" s="1">
         <v>115</v>
       </c>
-      <c r="C301" s="1" t="s">
-        <v>58</v>
+      <c r="C301" s="13" t="s">
+        <v>152</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F301" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G301" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="302" spans="1:8" ht="17.25">
+        <v>223</v>
+      </c>
+      <c r="F301" s="15">
+        <v>500</v>
+      </c>
+      <c r="H301" s="13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8">
       <c r="A302">
         <v>301</v>
       </c>
@@ -17456,19 +17459,19 @@
         <v>115</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D302" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E302" s="3" t="s">
-        <v>81</v>
+        <v>65</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E302" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F302" s="2">
-        <v>221000</v>
+        <v>39125</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -17478,20 +17481,20 @@
       <c r="B303" s="1">
         <v>115</v>
       </c>
-      <c r="C303" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D303" s="1" t="s">
-        <v>60</v>
+      <c r="C303" t="s">
+        <v>65</v>
+      </c>
+      <c r="D303" t="s">
+        <v>23</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F303" s="2">
-        <v>26283</v>
-      </c>
-      <c r="G303" s="1" t="s">
-        <v>84</v>
+        <v>169</v>
+      </c>
+      <c r="F303" s="11">
+        <v>7500</v>
+      </c>
+      <c r="G303" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -17502,19 +17505,19 @@
         <v>115</v>
       </c>
       <c r="C304" t="s">
-        <v>58</v>
-      </c>
-      <c r="D304" t="s">
-        <v>60</v>
+        <v>163</v>
+      </c>
+      <c r="D304" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F304" s="11">
-        <v>1100</v>
-      </c>
-      <c r="G304" s="12" t="s">
-        <v>168</v>
+        <v>5200</v>
+      </c>
+      <c r="G304" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="305" spans="1:7">
@@ -17524,20 +17527,20 @@
       <c r="B305" s="1">
         <v>115</v>
       </c>
-      <c r="C305" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D305" s="1" t="s">
-        <v>60</v>
+      <c r="C305" t="s">
+        <v>164</v>
+      </c>
+      <c r="D305" t="s">
+        <v>40</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F305" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G305" s="1" t="s">
-        <v>183</v>
+        <v>169</v>
+      </c>
+      <c r="F305" s="11">
+        <v>5200</v>
+      </c>
+      <c r="G305" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="306" spans="1:7">
@@ -17548,24 +17551,163 @@
         <v>115</v>
       </c>
       <c r="C306" t="s">
+        <v>164</v>
+      </c>
+      <c r="D306" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E306" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F306">
+        <v>13515</v>
+      </c>
+      <c r="G306" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7">
+      <c r="A307">
+        <v>306</v>
+      </c>
+      <c r="B307" s="1">
+        <v>115</v>
+      </c>
+      <c r="C307" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E307" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F307" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G307" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" ht="17.25">
+      <c r="A308">
+        <v>307</v>
+      </c>
+      <c r="B308" s="1">
+        <v>115</v>
+      </c>
+      <c r="C308" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D308" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E308" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F308" s="2">
+        <v>221000</v>
+      </c>
+      <c r="G308" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7">
+      <c r="A309">
+        <v>308</v>
+      </c>
+      <c r="B309" s="1">
+        <v>115</v>
+      </c>
+      <c r="C309" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E309" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F309" s="2">
+        <v>26283</v>
+      </c>
+      <c r="G309" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7">
+      <c r="A310">
+        <v>309</v>
+      </c>
+      <c r="B310" s="1">
+        <v>115</v>
+      </c>
+      <c r="C310" t="s">
+        <v>58</v>
+      </c>
+      <c r="D310" t="s">
+        <v>60</v>
+      </c>
+      <c r="E310" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F310" s="11">
+        <v>1100</v>
+      </c>
+      <c r="G310" s="12" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7">
+      <c r="A311">
+        <v>310</v>
+      </c>
+      <c r="B311" s="1">
+        <v>115</v>
+      </c>
+      <c r="C311" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D306" t="s">
+      <c r="D311" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E306" s="1" t="s">
+      <c r="E311" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F311" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G311" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7">
+      <c r="A312">
+        <v>311</v>
+      </c>
+      <c r="B312" s="1">
+        <v>115</v>
+      </c>
+      <c r="C312" t="s">
+        <v>59</v>
+      </c>
+      <c r="D312" t="s">
+        <v>60</v>
+      </c>
+      <c r="E312" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F306" s="11">
+      <c r="F312" s="11">
         <v>2700</v>
       </c>
-      <c r="G306" t="s">
+      <c r="G312" t="s">
         <v>167</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:H306">
-    <sortCondition ref="C2:C306"/>
+  <autoFilter ref="A1:H1" xr:uid="{75BAC909-8D45-4443-AECB-1592B366F0B1}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:H312">
+    <sortCondition ref="C2:C312"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDF8455-C3F9-41C4-8F4C-C229FDD4D9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F7CDF9-3BF1-488E-8F15-3A77946E1035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="229">
   <si>
     <t>序號</t>
   </si>
@@ -1159,10 +1159,6 @@
   </si>
   <si>
     <t>升等獎勵金</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>升等審查費</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -10421,7 +10417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BAC909-8D45-4443-AECB-1592B366F0B1}">
-  <dimension ref="A1:H312"/>
+  <dimension ref="A1:H311"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="4.75" bestFit="1" customWidth="1"/>
@@ -10460,6 +10456,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
+        <f>ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -10483,6 +10480,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3">
+        <f t="shared" ref="A3:A66" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" s="1">
@@ -10506,6 +10504,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" s="1">
@@ -10529,6 +10528,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="1">
@@ -10552,6 +10552,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="1">
@@ -10575,6 +10576,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="1">
@@ -10601,6 +10603,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="1">
@@ -10627,6 +10630,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="1">
@@ -10650,6 +10654,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" s="1">
@@ -10673,6 +10678,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" s="1">
@@ -10696,6 +10702,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="1">
@@ -10719,6 +10726,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" s="1">
@@ -10742,6 +10750,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" s="1">
@@ -10765,6 +10774,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" s="1">
@@ -10788,6 +10798,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" s="1">
@@ -10811,6 +10822,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" s="1">
@@ -10834,6 +10846,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" s="1">
@@ -10860,6 +10873,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19" s="1">
@@ -10886,6 +10900,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20" s="1">
@@ -10909,6 +10924,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21" s="1">
@@ -10932,6 +10948,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22" s="1">
@@ -10955,6 +10972,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B23" s="1">
@@ -10978,6 +10996,7 @@
     </row>
     <row r="24" spans="1:8" ht="17.25">
       <c r="A24">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B24" s="1">
@@ -11001,6 +11020,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B25" s="1">
@@ -11027,6 +11047,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B26" s="1">
@@ -11053,6 +11074,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B27" s="1">
@@ -11076,6 +11098,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B28" s="1">
@@ -11099,6 +11122,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B29" s="1">
@@ -11122,6 +11146,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B30" s="1">
@@ -11145,6 +11170,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B31" s="1">
@@ -11168,6 +11194,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B32" s="1">
@@ -11191,6 +11218,7 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B33" s="1">
@@ -11214,6 +11242,7 @@
     </row>
     <row r="34" spans="1:8" ht="17.25">
       <c r="A34">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B34" s="1">
@@ -11237,6 +11266,7 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B35" s="1">
@@ -11260,6 +11290,7 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B36" s="1">
@@ -11283,6 +11314,7 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B37" s="1">
@@ -11306,6 +11338,7 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B38" s="1">
@@ -11329,6 +11362,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="B39" s="1">
@@ -11352,6 +11386,7 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="B40" s="1">
@@ -11375,6 +11410,7 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="B41" s="1">
@@ -11398,6 +11434,7 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B42" s="1">
@@ -11421,6 +11458,7 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="B43" s="1">
@@ -11444,6 +11482,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="B44" s="1">
@@ -11467,6 +11506,7 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="B45" s="1">
@@ -11490,6 +11530,7 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46">
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="B46" s="1">
@@ -11513,6 +11554,7 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="B47" s="1">
@@ -11536,6 +11578,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="B48" s="1">
@@ -11559,6 +11602,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="B49" s="1">
@@ -11585,6 +11629,7 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="B50" s="1">
@@ -11611,6 +11656,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51">
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="B51" s="1">
@@ -11637,6 +11683,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52">
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="B52" s="1">
@@ -11663,6 +11710,7 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53">
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="B53" s="1">
@@ -11689,6 +11737,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54">
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="B54" s="1">
@@ -11712,6 +11761,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="B55" s="1">
@@ -11735,6 +11785,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="B56" s="1">
@@ -11758,6 +11809,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="B57" s="1">
@@ -11778,6 +11830,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="B58" s="1">
@@ -11801,6 +11854,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="B59" s="1">
@@ -11824,6 +11878,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="B60" s="1">
@@ -11847,6 +11902,7 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="B61" s="1">
@@ -11870,6 +11926,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
+        <f t="shared" si="0"/>
         <v>61</v>
       </c>
       <c r="B62" s="1">
@@ -11893,6 +11950,7 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="B63" s="1">
@@ -11916,6 +11974,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="B64" s="1">
@@ -11939,6 +11998,7 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65">
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="B65" s="1">
@@ -11962,6 +12022,7 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66">
+        <f t="shared" si="0"/>
         <v>65</v>
       </c>
       <c r="B66" s="1">
@@ -11985,6 +12046,7 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67">
+        <f t="shared" ref="A67:A130" si="1">ROW()-1</f>
         <v>66</v>
       </c>
       <c r="B67" s="1">
@@ -12008,6 +12070,7 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68">
+        <f t="shared" si="1"/>
         <v>67</v>
       </c>
       <c r="B68" s="1">
@@ -12031,6 +12094,7 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
+        <f t="shared" si="1"/>
         <v>68</v>
       </c>
       <c r="B69" s="1">
@@ -12054,6 +12118,7 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
+        <f t="shared" si="1"/>
         <v>69</v>
       </c>
       <c r="B70" s="1">
@@ -12077,6 +12142,7 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
+        <f t="shared" si="1"/>
         <v>70</v>
       </c>
       <c r="B71" s="1">
@@ -12100,6 +12166,7 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72">
+        <f t="shared" si="1"/>
         <v>71</v>
       </c>
       <c r="B72" s="1">
@@ -12123,6 +12190,7 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73">
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="B73" s="1">
@@ -12146,6 +12214,7 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74">
+        <f t="shared" si="1"/>
         <v>73</v>
       </c>
       <c r="B74" s="1">
@@ -12169,6 +12238,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75">
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="B75" s="1">
@@ -12192,6 +12262,7 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
+        <f t="shared" si="1"/>
         <v>75</v>
       </c>
       <c r="B76" s="1">
@@ -12215,6 +12286,7 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77">
+        <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="B77" s="1">
@@ -12238,6 +12310,7 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78">
+        <f t="shared" si="1"/>
         <v>77</v>
       </c>
       <c r="B78" s="1">
@@ -12261,6 +12334,7 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79">
+        <f t="shared" si="1"/>
         <v>78</v>
       </c>
       <c r="B79" s="1">
@@ -12284,6 +12358,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80">
+        <f t="shared" si="1"/>
         <v>79</v>
       </c>
       <c r="B80" s="1">
@@ -12307,6 +12382,7 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81">
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="B81" s="1">
@@ -12333,6 +12409,7 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82">
+        <f t="shared" si="1"/>
         <v>81</v>
       </c>
       <c r="B82" s="1">
@@ -12359,6 +12436,7 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83">
+        <f t="shared" si="1"/>
         <v>82</v>
       </c>
       <c r="B83" s="1">
@@ -12382,6 +12460,7 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84">
+        <f t="shared" si="1"/>
         <v>83</v>
       </c>
       <c r="B84" s="1">
@@ -12405,6 +12484,7 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85">
+        <f t="shared" si="1"/>
         <v>84</v>
       </c>
       <c r="B85" s="1">
@@ -12428,6 +12508,7 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86">
+        <f t="shared" si="1"/>
         <v>85</v>
       </c>
       <c r="B86" s="1">
@@ -12451,6 +12532,7 @@
     </row>
     <row r="87" spans="1:8" ht="17.25">
       <c r="A87">
+        <f t="shared" si="1"/>
         <v>86</v>
       </c>
       <c r="B87" s="1">
@@ -12474,6 +12556,7 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88">
+        <f t="shared" si="1"/>
         <v>87</v>
       </c>
       <c r="B88" s="1">
@@ -12497,6 +12580,7 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89">
+        <f t="shared" si="1"/>
         <v>88</v>
       </c>
       <c r="B89" s="1">
@@ -12523,6 +12607,7 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90">
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="B90" s="1">
@@ -12549,6 +12634,7 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91">
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="B91" s="1">
@@ -12575,6 +12661,7 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92">
+        <f t="shared" si="1"/>
         <v>91</v>
       </c>
       <c r="B92" s="1">
@@ -12601,6 +12688,7 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93">
+        <f t="shared" si="1"/>
         <v>92</v>
       </c>
       <c r="B93" s="1">
@@ -12624,6 +12712,7 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94">
+        <f t="shared" si="1"/>
         <v>93</v>
       </c>
       <c r="B94" s="1">
@@ -12647,6 +12736,7 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95">
+        <f t="shared" si="1"/>
         <v>94</v>
       </c>
       <c r="B95" s="1">
@@ -12670,6 +12760,7 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96">
+        <f t="shared" si="1"/>
         <v>95</v>
       </c>
       <c r="B96" s="1">
@@ -12693,6 +12784,7 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97">
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="B97" s="1">
@@ -12716,6 +12808,7 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98">
+        <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="B98" s="1">
@@ -12739,6 +12832,7 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99">
+        <f t="shared" si="1"/>
         <v>98</v>
       </c>
       <c r="B99" s="1">
@@ -12762,6 +12856,7 @@
     </row>
     <row r="100" spans="1:8" ht="17.25">
       <c r="A100">
+        <f t="shared" si="1"/>
         <v>99</v>
       </c>
       <c r="B100" s="1">
@@ -12785,6 +12880,7 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101">
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="B101" s="1">
@@ -12811,6 +12907,7 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102">
+        <f t="shared" si="1"/>
         <v>101</v>
       </c>
       <c r="B102" s="1">
@@ -12837,6 +12934,7 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103">
+        <f t="shared" si="1"/>
         <v>102</v>
       </c>
       <c r="B103" s="1">
@@ -12860,6 +12958,7 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104">
+        <f t="shared" si="1"/>
         <v>103</v>
       </c>
       <c r="B104" s="1">
@@ -12883,6 +12982,7 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105">
+        <f t="shared" si="1"/>
         <v>104</v>
       </c>
       <c r="B105" s="1">
@@ -12906,6 +13006,7 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106">
+        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="B106" s="1">
@@ -12929,6 +13030,7 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107">
+        <f t="shared" si="1"/>
         <v>106</v>
       </c>
       <c r="B107" s="1">
@@ -12952,6 +13054,7 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108">
+        <f t="shared" si="1"/>
         <v>107</v>
       </c>
       <c r="B108" s="1">
@@ -12975,6 +13078,7 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109">
+        <f t="shared" si="1"/>
         <v>108</v>
       </c>
       <c r="B109" s="1">
@@ -12998,6 +13102,7 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110">
+        <f t="shared" si="1"/>
         <v>109</v>
       </c>
       <c r="B110" s="1">
@@ -13021,6 +13126,7 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111">
+        <f t="shared" si="1"/>
         <v>110</v>
       </c>
       <c r="B111" s="1">
@@ -13044,6 +13150,7 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112">
+        <f t="shared" si="1"/>
         <v>111</v>
       </c>
       <c r="B112" s="1">
@@ -13067,6 +13174,7 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113">
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="B113" s="1">
@@ -13090,6 +13198,7 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114">
+        <f t="shared" si="1"/>
         <v>113</v>
       </c>
       <c r="B114" s="1">
@@ -13113,6 +13222,7 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115">
+        <f t="shared" si="1"/>
         <v>114</v>
       </c>
       <c r="B115" s="1">
@@ -13136,6 +13246,7 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116">
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="B116" s="1">
@@ -13159,6 +13270,7 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117">
+        <f t="shared" si="1"/>
         <v>116</v>
       </c>
       <c r="B117" s="1">
@@ -13182,6 +13294,7 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118">
+        <f t="shared" si="1"/>
         <v>117</v>
       </c>
       <c r="B118" s="1">
@@ -13205,6 +13318,7 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119">
+        <f t="shared" si="1"/>
         <v>118</v>
       </c>
       <c r="B119" s="1">
@@ -13228,6 +13342,7 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120">
+        <f t="shared" si="1"/>
         <v>119</v>
       </c>
       <c r="B120" s="1">
@@ -13251,6 +13366,7 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121">
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="B121" s="1">
@@ -13274,6 +13390,7 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122">
+        <f t="shared" si="1"/>
         <v>121</v>
       </c>
       <c r="B122" s="1">
@@ -13297,6 +13414,7 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123">
+        <f t="shared" si="1"/>
         <v>122</v>
       </c>
       <c r="B123" s="1">
@@ -13320,6 +13438,7 @@
     </row>
     <row r="124" spans="1:8">
       <c r="A124">
+        <f t="shared" si="1"/>
         <v>123</v>
       </c>
       <c r="B124" s="1">
@@ -13343,6 +13462,7 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125">
+        <f t="shared" si="1"/>
         <v>124</v>
       </c>
       <c r="B125" s="1">
@@ -13366,6 +13486,7 @@
     </row>
     <row r="126" spans="1:8">
       <c r="A126">
+        <f t="shared" si="1"/>
         <v>125</v>
       </c>
       <c r="B126" s="1">
@@ -13389,6 +13510,7 @@
     </row>
     <row r="127" spans="1:8">
       <c r="A127">
+        <f t="shared" si="1"/>
         <v>126</v>
       </c>
       <c r="B127" s="1">
@@ -13412,6 +13534,7 @@
     </row>
     <row r="128" spans="1:8">
       <c r="A128">
+        <f t="shared" si="1"/>
         <v>127</v>
       </c>
       <c r="B128" s="1">
@@ -13435,6 +13558,7 @@
     </row>
     <row r="129" spans="1:8">
       <c r="A129">
+        <f t="shared" si="1"/>
         <v>128</v>
       </c>
       <c r="B129" s="1">
@@ -13458,6 +13582,7 @@
     </row>
     <row r="130" spans="1:8">
       <c r="A130">
+        <f t="shared" si="1"/>
         <v>129</v>
       </c>
       <c r="B130" s="1">
@@ -13481,6 +13606,7 @@
     </row>
     <row r="131" spans="1:8">
       <c r="A131">
+        <f t="shared" ref="A131:A194" si="2">ROW()-1</f>
         <v>130</v>
       </c>
       <c r="B131" s="1">
@@ -13504,6 +13630,7 @@
     </row>
     <row r="132" spans="1:8">
       <c r="A132">
+        <f t="shared" si="2"/>
         <v>131</v>
       </c>
       <c r="B132" s="1">
@@ -13527,6 +13654,7 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133">
+        <f t="shared" si="2"/>
         <v>132</v>
       </c>
       <c r="B133" s="1">
@@ -13550,6 +13678,7 @@
     </row>
     <row r="134" spans="1:8">
       <c r="A134">
+        <f t="shared" si="2"/>
         <v>133</v>
       </c>
       <c r="B134" s="1">
@@ -13573,6 +13702,7 @@
     </row>
     <row r="135" spans="1:8">
       <c r="A135">
+        <f t="shared" si="2"/>
         <v>134</v>
       </c>
       <c r="B135" s="1">
@@ -13599,6 +13729,7 @@
     </row>
     <row r="136" spans="1:8">
       <c r="A136">
+        <f t="shared" si="2"/>
         <v>135</v>
       </c>
       <c r="B136" s="1">
@@ -13625,6 +13756,7 @@
     </row>
     <row r="137" spans="1:8">
       <c r="A137">
+        <f t="shared" si="2"/>
         <v>136</v>
       </c>
       <c r="B137" s="1">
@@ -13648,6 +13780,7 @@
     </row>
     <row r="138" spans="1:8">
       <c r="A138">
+        <f t="shared" si="2"/>
         <v>137</v>
       </c>
       <c r="B138" s="1">
@@ -13671,6 +13804,7 @@
     </row>
     <row r="139" spans="1:8">
       <c r="A139">
+        <f t="shared" si="2"/>
         <v>138</v>
       </c>
       <c r="B139" s="1">
@@ -13694,6 +13828,7 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140">
+        <f t="shared" si="2"/>
         <v>139</v>
       </c>
       <c r="B140" s="1">
@@ -13717,6 +13852,7 @@
     </row>
     <row r="141" spans="1:8">
       <c r="A141">
+        <f t="shared" si="2"/>
         <v>140</v>
       </c>
       <c r="B141" s="1">
@@ -13740,6 +13876,7 @@
     </row>
     <row r="142" spans="1:8">
       <c r="A142">
+        <f t="shared" si="2"/>
         <v>141</v>
       </c>
       <c r="B142" s="1">
@@ -13763,6 +13900,7 @@
     </row>
     <row r="143" spans="1:8">
       <c r="A143">
+        <f t="shared" si="2"/>
         <v>142</v>
       </c>
       <c r="B143" s="1">
@@ -13786,6 +13924,7 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144">
+        <f t="shared" si="2"/>
         <v>143</v>
       </c>
       <c r="B144" s="1">
@@ -13809,6 +13948,7 @@
     </row>
     <row r="145" spans="1:8" ht="17.25">
       <c r="A145">
+        <f t="shared" si="2"/>
         <v>144</v>
       </c>
       <c r="B145" s="1">
@@ -13832,6 +13972,7 @@
     </row>
     <row r="146" spans="1:8">
       <c r="A146">
+        <f t="shared" si="2"/>
         <v>145</v>
       </c>
       <c r="B146" s="1">
@@ -13858,6 +13999,7 @@
     </row>
     <row r="147" spans="1:8">
       <c r="A147">
+        <f t="shared" si="2"/>
         <v>146</v>
       </c>
       <c r="B147" s="1">
@@ -13884,6 +14026,7 @@
     </row>
     <row r="148" spans="1:8" ht="17.25">
       <c r="A148">
+        <f t="shared" si="2"/>
         <v>147</v>
       </c>
       <c r="B148" s="1">
@@ -13907,6 +14050,7 @@
     </row>
     <row r="149" spans="1:8">
       <c r="A149">
+        <f t="shared" si="2"/>
         <v>148</v>
       </c>
       <c r="B149" s="1">
@@ -13930,6 +14074,7 @@
     </row>
     <row r="150" spans="1:8">
       <c r="A150">
+        <f t="shared" si="2"/>
         <v>149</v>
       </c>
       <c r="B150" s="1">
@@ -13953,6 +14098,7 @@
     </row>
     <row r="151" spans="1:8">
       <c r="A151">
+        <f t="shared" si="2"/>
         <v>150</v>
       </c>
       <c r="B151" s="1">
@@ -13976,6 +14122,7 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152">
+        <f t="shared" si="2"/>
         <v>151</v>
       </c>
       <c r="B152" s="1">
@@ -13999,6 +14146,7 @@
     </row>
     <row r="153" spans="1:8">
       <c r="A153">
+        <f t="shared" si="2"/>
         <v>152</v>
       </c>
       <c r="B153" s="1">
@@ -14022,6 +14170,7 @@
     </row>
     <row r="154" spans="1:8">
       <c r="A154">
+        <f t="shared" si="2"/>
         <v>153</v>
       </c>
       <c r="B154" s="1">
@@ -14045,6 +14194,7 @@
     </row>
     <row r="155" spans="1:8">
       <c r="A155">
+        <f t="shared" si="2"/>
         <v>154</v>
       </c>
       <c r="B155" s="1">
@@ -14068,6 +14218,7 @@
     </row>
     <row r="156" spans="1:8">
       <c r="A156">
+        <f t="shared" si="2"/>
         <v>155</v>
       </c>
       <c r="B156" s="1">
@@ -14091,6 +14242,7 @@
     </row>
     <row r="157" spans="1:8">
       <c r="A157">
+        <f t="shared" si="2"/>
         <v>156</v>
       </c>
       <c r="B157" s="1">
@@ -14114,6 +14266,7 @@
     </row>
     <row r="158" spans="1:8" ht="17.25">
       <c r="A158">
+        <f t="shared" si="2"/>
         <v>157</v>
       </c>
       <c r="B158" s="1">
@@ -14137,6 +14290,7 @@
     </row>
     <row r="159" spans="1:8">
       <c r="A159">
+        <f t="shared" si="2"/>
         <v>158</v>
       </c>
       <c r="B159" s="1">
@@ -14160,6 +14314,7 @@
     </row>
     <row r="160" spans="1:8">
       <c r="A160">
+        <f t="shared" si="2"/>
         <v>159</v>
       </c>
       <c r="B160" s="1">
@@ -14183,6 +14338,7 @@
     </row>
     <row r="161" spans="1:8">
       <c r="A161">
+        <f t="shared" si="2"/>
         <v>160</v>
       </c>
       <c r="B161" s="1">
@@ -14206,6 +14362,7 @@
     </row>
     <row r="162" spans="1:8">
       <c r="A162">
+        <f t="shared" si="2"/>
         <v>161</v>
       </c>
       <c r="B162" s="1">
@@ -14229,6 +14386,7 @@
     </row>
     <row r="163" spans="1:8">
       <c r="A163">
+        <f t="shared" si="2"/>
         <v>162</v>
       </c>
       <c r="B163" s="1">
@@ -14252,6 +14410,7 @@
     </row>
     <row r="164" spans="1:8">
       <c r="A164">
+        <f t="shared" si="2"/>
         <v>163</v>
       </c>
       <c r="B164" s="1">
@@ -14275,6 +14434,7 @@
     </row>
     <row r="165" spans="1:8" ht="17.25">
       <c r="A165">
+        <f t="shared" si="2"/>
         <v>164</v>
       </c>
       <c r="B165" s="1">
@@ -14298,6 +14458,7 @@
     </row>
     <row r="166" spans="1:8">
       <c r="A166">
+        <f t="shared" si="2"/>
         <v>165</v>
       </c>
       <c r="B166" s="1">
@@ -14321,6 +14482,7 @@
     </row>
     <row r="167" spans="1:8">
       <c r="A167">
+        <f t="shared" si="2"/>
         <v>166</v>
       </c>
       <c r="B167" s="1">
@@ -14344,6 +14506,7 @@
     </row>
     <row r="168" spans="1:8">
       <c r="A168">
+        <f t="shared" si="2"/>
         <v>167</v>
       </c>
       <c r="B168" s="1">
@@ -14367,6 +14530,7 @@
     </row>
     <row r="169" spans="1:8" ht="17.25">
       <c r="A169">
+        <f t="shared" si="2"/>
         <v>168</v>
       </c>
       <c r="B169" s="1">
@@ -14390,6 +14554,7 @@
     </row>
     <row r="170" spans="1:8">
       <c r="A170">
+        <f t="shared" si="2"/>
         <v>169</v>
       </c>
       <c r="B170" s="1">
@@ -14413,6 +14578,7 @@
     </row>
     <row r="171" spans="1:8">
       <c r="A171">
+        <f t="shared" si="2"/>
         <v>170</v>
       </c>
       <c r="B171" s="1">
@@ -14436,6 +14602,7 @@
     </row>
     <row r="172" spans="1:8">
       <c r="A172">
+        <f t="shared" si="2"/>
         <v>171</v>
       </c>
       <c r="B172" s="1">
@@ -14459,6 +14626,7 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173">
+        <f t="shared" si="2"/>
         <v>172</v>
       </c>
       <c r="B173" s="1">
@@ -14482,6 +14650,7 @@
     </row>
     <row r="174" spans="1:8">
       <c r="A174">
+        <f t="shared" si="2"/>
         <v>173</v>
       </c>
       <c r="B174" s="1">
@@ -14505,6 +14674,7 @@
     </row>
     <row r="175" spans="1:8">
       <c r="A175">
+        <f t="shared" si="2"/>
         <v>174</v>
       </c>
       <c r="B175" s="1">
@@ -14528,6 +14698,7 @@
     </row>
     <row r="176" spans="1:8">
       <c r="A176">
+        <f t="shared" si="2"/>
         <v>175</v>
       </c>
       <c r="B176" s="1">
@@ -14551,6 +14722,7 @@
     </row>
     <row r="177" spans="1:8">
       <c r="A177">
+        <f t="shared" si="2"/>
         <v>176</v>
       </c>
       <c r="B177" s="1">
@@ -14574,6 +14746,7 @@
     </row>
     <row r="178" spans="1:8">
       <c r="A178">
+        <f t="shared" si="2"/>
         <v>177</v>
       </c>
       <c r="B178" s="1">
@@ -14597,6 +14770,7 @@
     </row>
     <row r="179" spans="1:8">
       <c r="A179">
+        <f t="shared" si="2"/>
         <v>178</v>
       </c>
       <c r="B179" s="1">
@@ -14620,6 +14794,7 @@
     </row>
     <row r="180" spans="1:8">
       <c r="A180">
+        <f t="shared" si="2"/>
         <v>179</v>
       </c>
       <c r="B180" s="1">
@@ -14643,6 +14818,7 @@
     </row>
     <row r="181" spans="1:8">
       <c r="A181">
+        <f t="shared" si="2"/>
         <v>180</v>
       </c>
       <c r="B181" s="1">
@@ -14666,6 +14842,7 @@
     </row>
     <row r="182" spans="1:8">
       <c r="A182">
+        <f t="shared" si="2"/>
         <v>181</v>
       </c>
       <c r="B182" s="1">
@@ -14689,6 +14866,7 @@
     </row>
     <row r="183" spans="1:8">
       <c r="A183">
+        <f t="shared" si="2"/>
         <v>182</v>
       </c>
       <c r="B183" s="1">
@@ -14712,6 +14890,7 @@
     </row>
     <row r="184" spans="1:8">
       <c r="A184">
+        <f t="shared" si="2"/>
         <v>183</v>
       </c>
       <c r="B184" s="1">
@@ -14735,6 +14914,7 @@
     </row>
     <row r="185" spans="1:8">
       <c r="A185">
+        <f t="shared" si="2"/>
         <v>184</v>
       </c>
       <c r="B185" s="1">
@@ -14761,6 +14941,7 @@
     </row>
     <row r="186" spans="1:8">
       <c r="A186">
+        <f t="shared" si="2"/>
         <v>185</v>
       </c>
       <c r="B186" s="1">
@@ -14787,6 +14968,7 @@
     </row>
     <row r="187" spans="1:8">
       <c r="A187">
+        <f t="shared" si="2"/>
         <v>186</v>
       </c>
       <c r="B187" s="1">
@@ -14810,6 +14992,7 @@
     </row>
     <row r="188" spans="1:8">
       <c r="A188">
+        <f t="shared" si="2"/>
         <v>187</v>
       </c>
       <c r="B188" s="1">
@@ -14833,6 +15016,7 @@
     </row>
     <row r="189" spans="1:8">
       <c r="A189">
+        <f t="shared" si="2"/>
         <v>188</v>
       </c>
       <c r="B189" s="1">
@@ -14856,6 +15040,7 @@
     </row>
     <row r="190" spans="1:8">
       <c r="A190">
+        <f t="shared" si="2"/>
         <v>189</v>
       </c>
       <c r="B190" s="1">
@@ -14879,6 +15064,7 @@
     </row>
     <row r="191" spans="1:8">
       <c r="A191">
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="B191" s="1">
@@ -14902,6 +15088,7 @@
     </row>
     <row r="192" spans="1:8">
       <c r="A192">
+        <f t="shared" si="2"/>
         <v>191</v>
       </c>
       <c r="B192" s="1">
@@ -14925,6 +15112,7 @@
     </row>
     <row r="193" spans="1:8">
       <c r="A193">
+        <f t="shared" si="2"/>
         <v>192</v>
       </c>
       <c r="B193" s="1">
@@ -14948,6 +15136,7 @@
     </row>
     <row r="194" spans="1:8">
       <c r="A194">
+        <f t="shared" si="2"/>
         <v>193</v>
       </c>
       <c r="B194" s="1">
@@ -14971,6 +15160,7 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195">
+        <f t="shared" ref="A195:A257" si="3">ROW()-1</f>
         <v>194</v>
       </c>
       <c r="B195" s="1">
@@ -14994,6 +15184,7 @@
     </row>
     <row r="196" spans="1:8">
       <c r="A196">
+        <f t="shared" si="3"/>
         <v>195</v>
       </c>
       <c r="B196" s="1">
@@ -15017,6 +15208,7 @@
     </row>
     <row r="197" spans="1:8">
       <c r="A197">
+        <f t="shared" si="3"/>
         <v>196</v>
       </c>
       <c r="B197" s="1">
@@ -15040,6 +15232,7 @@
     </row>
     <row r="198" spans="1:8" ht="17.25">
       <c r="A198">
+        <f t="shared" si="3"/>
         <v>197</v>
       </c>
       <c r="B198" s="1">
@@ -15063,6 +15256,7 @@
     </row>
     <row r="199" spans="1:8">
       <c r="A199">
+        <f t="shared" si="3"/>
         <v>198</v>
       </c>
       <c r="B199" s="1">
@@ -15086,6 +15280,7 @@
     </row>
     <row r="200" spans="1:8">
       <c r="A200">
+        <f t="shared" si="3"/>
         <v>199</v>
       </c>
       <c r="B200" s="1">
@@ -15109,6 +15304,7 @@
     </row>
     <row r="201" spans="1:8">
       <c r="A201">
+        <f t="shared" si="3"/>
         <v>200</v>
       </c>
       <c r="B201" s="1">
@@ -15132,6 +15328,7 @@
     </row>
     <row r="202" spans="1:8">
       <c r="A202">
+        <f t="shared" si="3"/>
         <v>201</v>
       </c>
       <c r="B202" s="1">
@@ -15155,6 +15352,7 @@
     </row>
     <row r="203" spans="1:8">
       <c r="A203">
+        <f t="shared" si="3"/>
         <v>202</v>
       </c>
       <c r="B203" s="1">
@@ -15178,6 +15376,7 @@
     </row>
     <row r="204" spans="1:8">
       <c r="A204">
+        <f t="shared" si="3"/>
         <v>203</v>
       </c>
       <c r="B204" s="1">
@@ -15196,51 +15395,57 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:8" ht="17.25">
       <c r="A205">
+        <f t="shared" si="3"/>
         <v>204</v>
       </c>
       <c r="B205" s="1">
         <v>115</v>
       </c>
-      <c r="C205" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="D205" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E205" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="F205" s="11">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8" ht="17.25">
+      <c r="C205" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F205" s="2">
+        <v>300000</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8">
       <c r="A206">
+        <f t="shared" si="3"/>
         <v>205</v>
       </c>
       <c r="B206" s="1">
         <v>115</v>
       </c>
-      <c r="C206" s="1" t="s">
+      <c r="C206" t="s">
         <v>73</v>
       </c>
-      <c r="D206" s="1" t="s">
+      <c r="D206" t="s">
         <v>23</v>
       </c>
-      <c r="E206" s="3" t="s">
-        <v>81</v>
+      <c r="E206" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="F206" s="2">
-        <v>300000</v>
-      </c>
-      <c r="G206" s="1" t="s">
-        <v>82</v>
+        <v>47500</v>
+      </c>
+      <c r="G206" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="207" spans="1:8">
       <c r="A207">
+        <f t="shared" si="3"/>
         <v>206</v>
       </c>
       <c r="B207" s="1">
@@ -15252,25 +15457,26 @@
       <c r="D207" t="s">
         <v>23</v>
       </c>
-      <c r="E207" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F207" s="2">
-        <v>47500</v>
-      </c>
-      <c r="G207" s="9" t="s">
-        <v>88</v>
+      <c r="E207" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F207" s="11">
+        <v>3700</v>
+      </c>
+      <c r="G207" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208">
+        <f t="shared" si="3"/>
         <v>207</v>
       </c>
       <c r="B208" s="1">
         <v>115</v>
       </c>
       <c r="C208" t="s">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="D208" t="s">
         <v>23</v>
@@ -15279,7 +15485,7 @@
         <v>169</v>
       </c>
       <c r="F208" s="11">
-        <v>3700</v>
+        <v>3500</v>
       </c>
       <c r="G208" t="s">
         <v>167</v>
@@ -15287,13 +15493,14 @@
     </row>
     <row r="209" spans="1:8">
       <c r="A209">
+        <f t="shared" si="3"/>
         <v>208</v>
       </c>
       <c r="B209" s="1">
         <v>115</v>
       </c>
       <c r="C209" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D209" t="s">
         <v>23</v>
@@ -15310,13 +15517,14 @@
     </row>
     <row r="210" spans="1:8">
       <c r="A210">
+        <f t="shared" si="3"/>
         <v>209</v>
       </c>
       <c r="B210" s="1">
         <v>115</v>
       </c>
       <c r="C210" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D210" t="s">
         <v>23</v>
@@ -15333,29 +15541,31 @@
     </row>
     <row r="211" spans="1:8">
       <c r="A211">
+        <f t="shared" si="3"/>
         <v>210</v>
       </c>
       <c r="B211" s="1">
         <v>115</v>
       </c>
-      <c r="C211" t="s">
-        <v>153</v>
-      </c>
-      <c r="D211" t="s">
-        <v>23</v>
+      <c r="C211" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F211" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G211" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8">
+        <v>11</v>
+      </c>
+      <c r="F211" s="2">
+        <v>52000</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" ht="17.25">
       <c r="A212">
+        <f t="shared" si="3"/>
         <v>211</v>
       </c>
       <c r="B212" s="1">
@@ -15364,44 +15574,46 @@
       <c r="C212" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D212" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>11</v>
+      <c r="D212" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F212" s="2">
-        <v>52000</v>
+        <v>210000</v>
       </c>
       <c r="G212" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8">
+      <c r="A213">
+        <f t="shared" si="3"/>
+        <v>212</v>
+      </c>
+      <c r="B213" s="1">
+        <v>115</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F213" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G213" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" ht="17.25">
-      <c r="A213">
-        <v>212</v>
-      </c>
-      <c r="B213" s="1">
-        <v>115</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D213" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E213" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F213" s="2">
-        <v>210000</v>
-      </c>
-      <c r="G213" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="214" spans="1:8">
       <c r="A214">
+        <f t="shared" si="3"/>
         <v>213</v>
       </c>
       <c r="B214" s="1">
@@ -15414,10 +15626,10 @@
         <v>20</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F214" s="2">
-        <v>42500</v>
+        <v>70000</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>8</v>
@@ -15425,29 +15637,31 @@
     </row>
     <row r="215" spans="1:8">
       <c r="A215">
+        <f t="shared" si="3"/>
         <v>214</v>
       </c>
       <c r="B215" s="1">
         <v>115</v>
       </c>
-      <c r="C215" s="1" t="s">
+      <c r="C215" t="s">
         <v>43</v>
       </c>
-      <c r="D215" s="1" t="s">
+      <c r="D215" t="s">
         <v>20</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F215" s="2">
-        <v>70000</v>
-      </c>
-      <c r="G215" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F215" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G215" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="216" spans="1:8">
       <c r="A216">
+        <f t="shared" si="3"/>
         <v>215</v>
       </c>
       <c r="B216" s="1">
@@ -15456,44 +15670,46 @@
       <c r="C216" t="s">
         <v>43</v>
       </c>
-      <c r="D216" t="s">
-        <v>20</v>
+      <c r="D216" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F216" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G216" t="s">
-        <v>167</v>
+        <v>182</v>
+      </c>
+      <c r="F216">
+        <v>20250</v>
+      </c>
+      <c r="G216" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="217" spans="1:8">
       <c r="A217">
+        <f t="shared" si="3"/>
         <v>216</v>
       </c>
       <c r="B217" s="1">
         <v>115</v>
       </c>
-      <c r="C217" t="s">
-        <v>43</v>
-      </c>
-      <c r="D217" s="10" t="s">
-        <v>86</v>
+      <c r="C217" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F217">
-        <v>20250</v>
-      </c>
-      <c r="G217" s="10" t="s">
-        <v>184</v>
+        <v>11</v>
+      </c>
+      <c r="F217" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G217" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="218" spans="1:8">
       <c r="A218">
+        <f t="shared" si="3"/>
         <v>217</v>
       </c>
       <c r="B218" s="1">
@@ -15506,7 +15722,7 @@
         <v>16</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F218" s="2">
         <v>59500</v>
@@ -15515,8 +15731,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" ht="17.25">
       <c r="A219">
+        <f t="shared" si="3"/>
         <v>218</v>
       </c>
       <c r="B219" s="1">
@@ -15525,44 +15742,49 @@
       <c r="C219" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D219" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E219" s="1" t="s">
-        <v>7</v>
+      <c r="D219" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F219" s="2">
-        <v>59500</v>
+        <v>200000</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8" ht="17.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8">
       <c r="A220">
+        <f t="shared" si="3"/>
         <v>219</v>
       </c>
       <c r="B220" s="1">
         <v>115</v>
       </c>
-      <c r="C220" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D220" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E220" s="3" t="s">
-        <v>81</v>
+      <c r="C220" t="s">
+        <v>94</v>
+      </c>
+      <c r="D220" t="s">
+        <v>23</v>
+      </c>
+      <c r="E220" s="10" t="s">
+        <v>170</v>
       </c>
       <c r="F220" s="2">
-        <v>200000</v>
-      </c>
-      <c r="G220" s="1" t="s">
-        <v>82</v>
+        <v>50000</v>
+      </c>
+      <c r="G220" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H220" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="221" spans="1:8">
       <c r="A221">
+        <f t="shared" si="3"/>
         <v>220</v>
       </c>
       <c r="B221" s="1">
@@ -15575,10 +15797,10 @@
         <v>23</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F221" s="2">
-        <v>50000</v>
+        <v>42393</v>
       </c>
       <c r="G221" s="10" t="s">
         <v>116</v>
@@ -15589,6 +15811,7 @@
     </row>
     <row r="222" spans="1:8">
       <c r="A222">
+        <f t="shared" si="3"/>
         <v>221</v>
       </c>
       <c r="B222" s="1">
@@ -15600,80 +15823,80 @@
       <c r="D222" t="s">
         <v>23</v>
       </c>
-      <c r="E222" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F222" s="2">
-        <v>42393</v>
-      </c>
-      <c r="G222" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H222" t="s">
-        <v>101</v>
+      <c r="E222" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F222" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G222" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="223" spans="1:8">
       <c r="A223">
+        <f t="shared" si="3"/>
         <v>222</v>
       </c>
       <c r="B223" s="1">
         <v>115</v>
       </c>
-      <c r="C223" t="s">
-        <v>94</v>
-      </c>
-      <c r="D223" t="s">
-        <v>23</v>
-      </c>
-      <c r="E223" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F223" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G223" t="s">
-        <v>167</v>
+      <c r="C223" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="D223" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E223" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F223" s="2">
+        <v>20000</v>
       </c>
     </row>
     <row r="224" spans="1:8">
       <c r="A224">
+        <f t="shared" si="3"/>
         <v>223</v>
       </c>
       <c r="B224" s="1">
         <v>115</v>
       </c>
-      <c r="C224" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="D224" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E224" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="F224" s="2">
-        <v>20000</v>
+      <c r="C224" t="s">
+        <v>158</v>
+      </c>
+      <c r="D224" t="s">
+        <v>23</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F224" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G224" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="225" spans="1:8">
       <c r="A225">
+        <f t="shared" si="3"/>
         <v>224</v>
       </c>
       <c r="B225" s="1">
         <v>115</v>
       </c>
       <c r="C225" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="D225" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F225" s="11">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="G225" t="s">
         <v>167</v>
@@ -15681,29 +15904,31 @@
     </row>
     <row r="226" spans="1:8">
       <c r="A226">
+        <f t="shared" si="3"/>
         <v>225</v>
       </c>
       <c r="B226" s="1">
         <v>115</v>
       </c>
-      <c r="C226" t="s">
-        <v>118</v>
-      </c>
-      <c r="D226" t="s">
-        <v>29</v>
+      <c r="C226" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F226" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G226" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8">
+        <v>21</v>
+      </c>
+      <c r="F226" s="2">
+        <v>44118</v>
+      </c>
+      <c r="G226" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" ht="17.25">
       <c r="A227">
+        <f t="shared" si="3"/>
         <v>226</v>
       </c>
       <c r="B227" s="1">
@@ -15712,126 +15937,131 @@
       <c r="C227" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D227" s="1" t="s">
+      <c r="D227" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F227" s="2">
+        <v>217500</v>
+      </c>
+      <c r="G227" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8">
+      <c r="A228">
+        <f t="shared" si="3"/>
+        <v>227</v>
+      </c>
+      <c r="B228" s="1">
+        <v>115</v>
+      </c>
+      <c r="C228" t="s">
+        <v>45</v>
+      </c>
+      <c r="D228" t="s">
         <v>46</v>
       </c>
-      <c r="E227" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F227" s="2">
-        <v>44118</v>
-      </c>
-      <c r="G227" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8" ht="17.25">
-      <c r="A228">
-        <v>227</v>
-      </c>
-      <c r="B228" s="1">
-        <v>115</v>
-      </c>
-      <c r="C228" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D228" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E228" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F228" s="2">
-        <v>217500</v>
-      </c>
-      <c r="G228" s="1" t="s">
-        <v>82</v>
+      <c r="E228" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F228" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G228" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="229" spans="1:8">
       <c r="A229">
+        <f t="shared" si="3"/>
         <v>228</v>
       </c>
       <c r="B229" s="1">
         <v>115</v>
       </c>
-      <c r="C229" t="s">
+      <c r="C229" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D229" t="s">
-        <v>46</v>
+      <c r="D229" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F229" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G229" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F229" s="14">
+        <v>3582</v>
+      </c>
+      <c r="H229" s="13" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="230" spans="1:8">
       <c r="A230">
+        <f t="shared" si="3"/>
         <v>229</v>
       </c>
       <c r="B230" s="1">
         <v>115</v>
       </c>
-      <c r="C230" s="13" t="s">
+      <c r="C230" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D230" s="4" t="s">
+      <c r="D230" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="E230" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F230" s="14">
-        <v>3582</v>
-      </c>
-      <c r="H230" s="13" t="s">
-        <v>212</v>
+      <c r="E230" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F230" s="11">
+        <v>20000</v>
       </c>
     </row>
     <row r="231" spans="1:8">
       <c r="A231">
+        <f t="shared" si="3"/>
         <v>230</v>
       </c>
       <c r="B231" s="1">
         <v>115</v>
       </c>
-      <c r="C231" s="10" t="s">
-        <v>45</v>
+      <c r="C231" t="s">
+        <v>165</v>
       </c>
       <c r="D231" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="E231" s="10" t="s">
-        <v>228</v>
+      <c r="E231" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="F231" s="11">
-        <v>20000</v>
+        <v>6000</v>
+      </c>
+      <c r="G231" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="232" spans="1:8">
       <c r="A232">
+        <f t="shared" si="3"/>
         <v>231</v>
       </c>
       <c r="B232" s="1">
         <v>115</v>
       </c>
       <c r="C232" t="s">
-        <v>165</v>
-      </c>
-      <c r="D232" s="10" t="s">
-        <v>63</v>
+        <v>119</v>
+      </c>
+      <c r="D232" t="s">
+        <v>10</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F232" s="11">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="G232" t="s">
         <v>167</v>
@@ -15839,121 +16069,127 @@
     </row>
     <row r="233" spans="1:8">
       <c r="A233">
+        <f t="shared" si="3"/>
         <v>232</v>
       </c>
       <c r="B233" s="1">
         <v>115</v>
       </c>
-      <c r="C233" t="s">
+      <c r="C233" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="D233" t="s">
-        <v>10</v>
+      <c r="D233" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F233" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G233" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F233" s="14">
+        <v>2400</v>
+      </c>
+      <c r="H233" s="13" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="234" spans="1:8">
       <c r="A234">
+        <f t="shared" si="3"/>
         <v>233</v>
       </c>
       <c r="B234" s="1">
         <v>115</v>
       </c>
-      <c r="C234" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="D234" s="4" t="s">
-        <v>79</v>
+      <c r="C234" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F234" s="14">
-        <v>2400</v>
-      </c>
-      <c r="H234" s="13" t="s">
-        <v>218</v>
+        <v>7</v>
+      </c>
+      <c r="F234" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G234" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="235" spans="1:8">
       <c r="A235">
+        <f t="shared" si="3"/>
         <v>234</v>
       </c>
       <c r="B235" s="1">
         <v>115</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E235" s="1" t="s">
-        <v>7</v>
+        <v>63</v>
+      </c>
+      <c r="E235" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="F235" s="2">
-        <v>59500</v>
+        <v>60000</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
     </row>
     <row r="236" spans="1:8">
       <c r="A236">
+        <f t="shared" si="3"/>
         <v>235</v>
       </c>
       <c r="B236" s="1">
         <v>115</v>
       </c>
-      <c r="C236" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D236" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E236" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F236" s="2">
-        <v>60000</v>
-      </c>
-      <c r="G236" s="1" t="s">
-        <v>91</v>
+      <c r="C236" t="s">
+        <v>47</v>
+      </c>
+      <c r="D236" t="s">
+        <v>46</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F236" s="11">
+        <v>1400</v>
+      </c>
+      <c r="G236" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="237" spans="1:8">
       <c r="A237">
+        <f t="shared" si="3"/>
         <v>236</v>
       </c>
       <c r="B237" s="1">
         <v>115</v>
       </c>
-      <c r="C237" t="s">
-        <v>47</v>
-      </c>
-      <c r="D237" t="s">
-        <v>46</v>
+      <c r="C237" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F237" s="11">
-        <v>1400</v>
-      </c>
-      <c r="G237" t="s">
-        <v>167</v>
+        <v>7</v>
+      </c>
+      <c r="F237" s="2">
+        <v>52500</v>
+      </c>
+      <c r="G237" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="238" spans="1:8">
       <c r="A238">
+        <f t="shared" si="3"/>
         <v>237</v>
       </c>
       <c r="B238" s="1">
@@ -15966,86 +16202,90 @@
         <v>13</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F238" s="2">
-        <v>52500</v>
+        <v>52776</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="239" spans="1:8">
       <c r="A239">
+        <f t="shared" si="3"/>
         <v>238</v>
       </c>
       <c r="B239" s="1">
         <v>115</v>
       </c>
-      <c r="C239" s="1" t="s">
+      <c r="C239" t="s">
         <v>48</v>
       </c>
-      <c r="D239" s="1" t="s">
+      <c r="D239" t="s">
         <v>13</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F239" s="2">
-        <v>52776</v>
-      </c>
-      <c r="G239" s="1" t="s">
-        <v>84</v>
+        <v>169</v>
+      </c>
+      <c r="F239" s="11">
+        <v>900</v>
+      </c>
+      <c r="G239" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="240" spans="1:8">
       <c r="A240">
+        <f t="shared" si="3"/>
         <v>239</v>
       </c>
       <c r="B240" s="1">
         <v>115</v>
       </c>
-      <c r="C240" t="s">
-        <v>48</v>
-      </c>
-      <c r="D240" t="s">
-        <v>13</v>
+      <c r="C240" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F240" s="11">
-        <v>900</v>
-      </c>
-      <c r="G240" t="s">
-        <v>167</v>
+        <v>7</v>
+      </c>
+      <c r="F240" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G240" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:8">
       <c r="A241">
+        <f t="shared" si="3"/>
         <v>240</v>
       </c>
       <c r="B241" s="1">
         <v>115</v>
       </c>
-      <c r="C241" s="1" t="s">
+      <c r="C241" t="s">
         <v>49</v>
       </c>
-      <c r="D241" s="1" t="s">
+      <c r="D241" t="s">
         <v>23</v>
       </c>
-      <c r="E241" s="1" t="s">
-        <v>7</v>
+      <c r="E241" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="F241" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G241" s="1" t="s">
-        <v>8</v>
+        <v>41616</v>
+      </c>
+      <c r="G241" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="242" spans="1:8">
       <c r="A242">
+        <f t="shared" si="3"/>
         <v>241</v>
       </c>
       <c r="B242" s="1">
@@ -16057,18 +16297,22 @@
       <c r="D242" t="s">
         <v>23</v>
       </c>
-      <c r="E242" s="8" t="s">
-        <v>87</v>
+      <c r="E242" s="10" t="s">
+        <v>170</v>
       </c>
       <c r="F242" s="2">
-        <v>41616</v>
-      </c>
-      <c r="G242" s="9" t="s">
-        <v>88</v>
+        <v>50000</v>
+      </c>
+      <c r="G242" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H242" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="243" spans="1:8">
       <c r="A243">
+        <f t="shared" si="3"/>
         <v>242</v>
       </c>
       <c r="B243" s="1">
@@ -16081,10 +16325,10 @@
         <v>23</v>
       </c>
       <c r="E243" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F243" s="2">
-        <v>50000</v>
+        <v>38569</v>
       </c>
       <c r="G243" s="10" t="s">
         <v>116</v>
@@ -16095,6 +16339,7 @@
     </row>
     <row r="244" spans="1:8">
       <c r="A244">
+        <f t="shared" si="3"/>
         <v>243</v>
       </c>
       <c r="B244" s="1">
@@ -16106,21 +16351,19 @@
       <c r="D244" t="s">
         <v>23</v>
       </c>
-      <c r="E244" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F244" s="2">
-        <v>38569</v>
-      </c>
-      <c r="G244" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H244" t="s">
-        <v>109</v>
+      <c r="E244" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F244" s="11">
+        <v>5000</v>
+      </c>
+      <c r="G244" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="245" spans="1:8">
       <c r="A245">
+        <f t="shared" si="3"/>
         <v>244</v>
       </c>
       <c r="B245" s="1">
@@ -16129,44 +16372,46 @@
       <c r="C245" t="s">
         <v>49</v>
       </c>
-      <c r="D245" t="s">
-        <v>23</v>
+      <c r="D245" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F245" s="11">
-        <v>5000</v>
-      </c>
-      <c r="G245" t="s">
-        <v>167</v>
+        <v>182</v>
+      </c>
+      <c r="F245">
+        <v>50000</v>
+      </c>
+      <c r="G245" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="246" spans="1:8">
       <c r="A246">
+        <f t="shared" si="3"/>
         <v>245</v>
       </c>
       <c r="B246" s="1">
         <v>115</v>
       </c>
-      <c r="C246" t="s">
+      <c r="C246" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D246" s="10" t="s">
-        <v>64</v>
+      <c r="D246" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F246">
-        <v>50000</v>
-      </c>
-      <c r="G246" s="10" t="s">
-        <v>184</v>
+        <v>223</v>
+      </c>
+      <c r="F246" s="14">
+        <v>3081</v>
+      </c>
+      <c r="H246" s="13" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="247" spans="1:8">
       <c r="A247">
+        <f t="shared" si="3"/>
         <v>246</v>
       </c>
       <c r="B247" s="1">
@@ -16182,14 +16427,15 @@
         <v>223</v>
       </c>
       <c r="F247" s="14">
-        <v>3081</v>
+        <v>4800</v>
       </c>
       <c r="H247" s="13" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
     </row>
     <row r="248" spans="1:8">
       <c r="A248">
+        <f t="shared" si="3"/>
         <v>247</v>
       </c>
       <c r="B248" s="1">
@@ -16205,14 +16451,15 @@
         <v>223</v>
       </c>
       <c r="F248" s="14">
-        <v>4800</v>
+        <v>1000</v>
       </c>
       <c r="H248" s="13" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
     </row>
     <row r="249" spans="1:8">
       <c r="A249">
+        <f t="shared" si="3"/>
         <v>248</v>
       </c>
       <c r="B249" s="1">
@@ -16227,84 +16474,88 @@
       <c r="E249" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F249" s="14">
-        <v>1000</v>
+      <c r="F249" s="15">
+        <v>500</v>
       </c>
       <c r="H249" s="13" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
     </row>
     <row r="250" spans="1:8">
       <c r="A250">
+        <f t="shared" si="3"/>
         <v>249</v>
       </c>
       <c r="B250" s="1">
         <v>115</v>
       </c>
-      <c r="C250" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D250" s="1" t="s">
+      <c r="C250" t="s">
+        <v>141</v>
+      </c>
+      <c r="D250" t="s">
         <v>23</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F250" s="15">
-        <v>500</v>
-      </c>
-      <c r="H250" s="13" t="s">
-        <v>215</v>
+        <v>169</v>
+      </c>
+      <c r="F250" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G250" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="251" spans="1:8">
       <c r="A251">
+        <f t="shared" si="3"/>
         <v>250</v>
       </c>
       <c r="B251" s="1">
         <v>115</v>
       </c>
-      <c r="C251" t="s">
-        <v>141</v>
-      </c>
-      <c r="D251" t="s">
+      <c r="C251" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D251" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F251" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G251" t="s">
-        <v>167</v>
+        <v>21</v>
+      </c>
+      <c r="F251" s="2">
+        <v>31500</v>
+      </c>
+      <c r="G251" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="252" spans="1:8">
       <c r="A252">
+        <f t="shared" si="3"/>
         <v>251</v>
       </c>
       <c r="B252" s="1">
         <v>115</v>
       </c>
-      <c r="C252" s="1" t="s">
+      <c r="C252" t="s">
         <v>50</v>
       </c>
-      <c r="D252" s="1" t="s">
-        <v>23</v>
+      <c r="D252" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F252" s="2">
-        <v>31500</v>
-      </c>
-      <c r="G252" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F252" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G252" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="253" spans="1:8">
       <c r="A253">
+        <f t="shared" si="3"/>
         <v>252</v>
       </c>
       <c r="B253" s="1">
@@ -16317,63 +16568,66 @@
         <v>64</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F253" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G253" t="s">
-        <v>167</v>
+        <v>182</v>
+      </c>
+      <c r="F253">
+        <v>30150</v>
+      </c>
+      <c r="G253" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="254" spans="1:8">
       <c r="A254">
+        <f t="shared" si="3"/>
         <v>253</v>
       </c>
       <c r="B254" s="1">
         <v>115</v>
       </c>
-      <c r="C254" t="s">
-        <v>50</v>
-      </c>
-      <c r="D254" s="10" t="s">
-        <v>64</v>
+      <c r="C254" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F254">
-        <v>30150</v>
-      </c>
-      <c r="G254" s="10" t="s">
-        <v>184</v>
+        <v>21</v>
+      </c>
+      <c r="F254" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G254" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="255" spans="1:8">
       <c r="A255">
+        <f t="shared" si="3"/>
         <v>254</v>
       </c>
       <c r="B255" s="1">
         <v>115</v>
       </c>
-      <c r="C255" s="1" t="s">
+      <c r="C255" t="s">
         <v>51</v>
       </c>
-      <c r="D255" s="1" t="s">
+      <c r="D255" t="s">
         <v>20</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F255" s="2">
-        <v>42500</v>
-      </c>
-      <c r="G255" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F255" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G255" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="256" spans="1:8">
       <c r="A256">
+        <f t="shared" si="3"/>
         <v>255</v>
       </c>
       <c r="B256" s="1">
@@ -16382,74 +16636,77 @@
       <c r="C256" t="s">
         <v>51</v>
       </c>
-      <c r="D256" t="s">
-        <v>20</v>
+      <c r="D256" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="E256" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F256">
+        <v>12750</v>
+      </c>
+      <c r="G256" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" ht="17.25">
+      <c r="A257">
+        <f t="shared" si="3"/>
+        <v>256</v>
+      </c>
+      <c r="B257" s="1">
+        <v>115</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F257" s="2">
+        <v>95912</v>
+      </c>
+      <c r="G257" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8">
+      <c r="A258">
+        <f t="shared" ref="A258:A311" si="4">ROW()-1</f>
+        <v>257</v>
+      </c>
+      <c r="B258" s="1">
+        <v>115</v>
+      </c>
+      <c r="C258" t="s">
+        <v>72</v>
+      </c>
+      <c r="D258" t="s">
+        <v>23</v>
+      </c>
+      <c r="E258" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F256" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G256" t="s">
+      <c r="F258" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G258" t="s">
         <v>167</v>
-      </c>
-    </row>
-    <row r="257" spans="1:8">
-      <c r="A257">
-        <v>256</v>
-      </c>
-      <c r="B257" s="1">
-        <v>115</v>
-      </c>
-      <c r="C257" t="s">
-        <v>51</v>
-      </c>
-      <c r="D257" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="E257" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F257">
-        <v>12750</v>
-      </c>
-      <c r="G257" s="10" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="258" spans="1:8" ht="17.25">
-      <c r="A258">
-        <v>257</v>
-      </c>
-      <c r="B258" s="1">
-        <v>115</v>
-      </c>
-      <c r="C258" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D258" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E258" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F258" s="2">
-        <v>95912</v>
-      </c>
-      <c r="G258" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="259" spans="1:8">
       <c r="A259">
+        <f t="shared" si="4"/>
         <v>258</v>
       </c>
       <c r="B259" s="1">
         <v>115</v>
       </c>
       <c r="C259" t="s">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="D259" t="s">
         <v>23</v>
@@ -16464,61 +16721,64 @@
         <v>167</v>
       </c>
     </row>
-    <row r="260" spans="1:8">
+    <row r="260" spans="1:8" ht="17.25">
       <c r="A260">
+        <f t="shared" si="4"/>
         <v>259</v>
       </c>
       <c r="B260" s="1">
         <v>115</v>
       </c>
-      <c r="C260" t="s">
-        <v>129</v>
-      </c>
-      <c r="D260" t="s">
+      <c r="C260" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F260" s="2">
+        <v>28500</v>
+      </c>
+      <c r="G260" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8">
+      <c r="A261">
+        <f t="shared" si="4"/>
+        <v>260</v>
+      </c>
+      <c r="B261" s="1">
+        <v>115</v>
+      </c>
+      <c r="C261" t="s">
+        <v>128</v>
+      </c>
+      <c r="D261" t="s">
         <v>23</v>
       </c>
-      <c r="E260" s="1" t="s">
+      <c r="E261" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F260" s="11">
+      <c r="F261" s="11">
         <v>3500</v>
       </c>
-      <c r="G260" t="s">
+      <c r="G261" t="s">
         <v>167</v>
-      </c>
-    </row>
-    <row r="261" spans="1:8" ht="17.25">
-      <c r="A261">
-        <v>260</v>
-      </c>
-      <c r="B261" s="1">
-        <v>115</v>
-      </c>
-      <c r="C261" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D261" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E261" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F261" s="2">
-        <v>28500</v>
-      </c>
-      <c r="G261" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="262" spans="1:8">
       <c r="A262">
+        <f t="shared" si="4"/>
         <v>261</v>
       </c>
       <c r="B262" s="1">
         <v>115</v>
       </c>
       <c r="C262" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D262" t="s">
         <v>23</v>
@@ -16535,13 +16795,14 @@
     </row>
     <row r="263" spans="1:8">
       <c r="A263">
+        <f t="shared" si="4"/>
         <v>262</v>
       </c>
       <c r="B263" s="1">
         <v>115</v>
       </c>
       <c r="C263" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D263" t="s">
         <v>23</v>
@@ -16558,98 +16819,106 @@
     </row>
     <row r="264" spans="1:8">
       <c r="A264">
+        <f t="shared" si="4"/>
         <v>263</v>
       </c>
       <c r="B264" s="1">
         <v>115</v>
       </c>
-      <c r="C264" t="s">
+      <c r="C264" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="D264" t="s">
+      <c r="D264" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F264" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G264" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F264" s="14">
+        <v>20000</v>
+      </c>
+      <c r="H264" s="13" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="265" spans="1:8">
       <c r="A265">
+        <f t="shared" si="4"/>
         <v>264</v>
       </c>
       <c r="B265" s="1">
         <v>115</v>
       </c>
-      <c r="C265" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D265" s="1" t="s">
+      <c r="C265" t="s">
+        <v>148</v>
+      </c>
+      <c r="D265" t="s">
         <v>23</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F265" s="14">
-        <v>20000</v>
-      </c>
-      <c r="H265" s="13" t="s">
-        <v>195</v>
+        <v>169</v>
+      </c>
+      <c r="F265" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G265" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="266" spans="1:8">
       <c r="A266">
+        <f t="shared" si="4"/>
         <v>265</v>
       </c>
       <c r="B266" s="1">
         <v>115</v>
       </c>
-      <c r="C266" t="s">
-        <v>148</v>
-      </c>
-      <c r="D266" t="s">
-        <v>23</v>
+      <c r="C266" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F266" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G266" t="s">
-        <v>167</v>
+        <v>21</v>
+      </c>
+      <c r="F266" s="2">
+        <v>29250</v>
+      </c>
+      <c r="G266" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="267" spans="1:8">
       <c r="A267">
+        <f t="shared" si="4"/>
         <v>266</v>
       </c>
       <c r="B267" s="1">
         <v>115</v>
       </c>
-      <c r="C267" s="1" t="s">
+      <c r="C267" t="s">
         <v>52</v>
       </c>
-      <c r="D267" s="1" t="s">
+      <c r="D267" t="s">
         <v>29</v>
       </c>
-      <c r="E267" s="1" t="s">
-        <v>21</v>
+      <c r="E267" s="10" t="s">
+        <v>170</v>
       </c>
       <c r="F267" s="2">
-        <v>29250</v>
-      </c>
-      <c r="G267" s="1" t="s">
-        <v>8</v>
+        <v>8900</v>
+      </c>
+      <c r="G267" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H267" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268">
+        <f t="shared" si="4"/>
         <v>267</v>
       </c>
       <c r="B268" s="1">
@@ -16665,17 +16934,18 @@
         <v>170</v>
       </c>
       <c r="F268" s="2">
-        <v>8900</v>
+        <v>0</v>
       </c>
       <c r="G268" s="10" t="s">
         <v>116</v>
       </c>
       <c r="H268" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="269" spans="1:8">
       <c r="A269">
+        <f t="shared" si="4"/>
         <v>268</v>
       </c>
       <c r="B269" s="1">
@@ -16688,20 +16958,21 @@
         <v>29</v>
       </c>
       <c r="E269" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F269" s="2">
-        <v>0</v>
+        <v>19190</v>
       </c>
       <c r="G269" s="10" t="s">
         <v>116</v>
       </c>
       <c r="H269" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="270" spans="1:8">
       <c r="A270">
+        <f t="shared" si="4"/>
         <v>269</v>
       </c>
       <c r="B270" s="1">
@@ -16717,17 +16988,18 @@
         <v>171</v>
       </c>
       <c r="F270" s="2">
-        <v>19190</v>
+        <v>17728</v>
       </c>
       <c r="G270" s="10" t="s">
         <v>116</v>
       </c>
       <c r="H270" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="271" spans="1:8">
       <c r="A271">
+        <f t="shared" si="4"/>
         <v>270</v>
       </c>
       <c r="B271" s="1">
@@ -16739,21 +17011,19 @@
       <c r="D271" t="s">
         <v>29</v>
       </c>
-      <c r="E271" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F271" s="2">
-        <v>17728</v>
-      </c>
-      <c r="G271" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H271" t="s">
-        <v>111</v>
+      <c r="E271" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F271" s="11">
+        <v>2200</v>
+      </c>
+      <c r="G271" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="272" spans="1:8">
       <c r="A272">
+        <f t="shared" si="4"/>
         <v>271</v>
       </c>
       <c r="B272" s="1">
@@ -16762,110 +17032,118 @@
       <c r="C272" t="s">
         <v>52</v>
       </c>
-      <c r="D272" t="s">
-        <v>29</v>
+      <c r="D272" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F272" s="11">
-        <v>2200</v>
-      </c>
-      <c r="G272" t="s">
-        <v>167</v>
+        <v>182</v>
+      </c>
+      <c r="F272">
+        <v>32175</v>
+      </c>
+      <c r="G272" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="273" spans="1:8">
       <c r="A273">
+        <f t="shared" si="4"/>
         <v>272</v>
       </c>
       <c r="B273" s="1">
         <v>115</v>
       </c>
-      <c r="C273" t="s">
+      <c r="C273" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D273" s="10" t="s">
+      <c r="D273" s="4" t="s">
         <v>76</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F273">
-        <v>32175</v>
-      </c>
-      <c r="G273" s="10" t="s">
-        <v>184</v>
+        <v>223</v>
+      </c>
+      <c r="F273" s="14">
+        <v>8900</v>
+      </c>
+      <c r="H273" s="13" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="274" spans="1:8">
       <c r="A274">
+        <f t="shared" si="4"/>
         <v>273</v>
       </c>
       <c r="B274" s="1">
         <v>115</v>
       </c>
-      <c r="C274" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D274" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E274" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F274" s="14">
-        <v>8900</v>
-      </c>
-      <c r="H274" s="13" t="s">
-        <v>213</v>
+      <c r="C274" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D274" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E274" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F274" s="2">
+        <v>10000</v>
       </c>
     </row>
     <row r="275" spans="1:8">
       <c r="A275">
+        <f t="shared" si="4"/>
         <v>274</v>
       </c>
       <c r="B275" s="1">
         <v>115</v>
       </c>
-      <c r="C275" s="10" t="s">
-        <v>225</v>
+      <c r="C275" t="s">
+        <v>159</v>
       </c>
       <c r="D275" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E275" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="F275" s="2">
-        <v>10000</v>
+        <v>64</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F275" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G275" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="276" spans="1:8">
       <c r="A276">
+        <f t="shared" si="4"/>
         <v>275</v>
       </c>
       <c r="B276" s="1">
         <v>115</v>
       </c>
       <c r="C276" t="s">
-        <v>159</v>
-      </c>
-      <c r="D276" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E276" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F276" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G276" t="s">
-        <v>167</v>
+        <v>98</v>
+      </c>
+      <c r="D276" t="s">
+        <v>23</v>
+      </c>
+      <c r="E276" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F276" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G276" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H276" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="277" spans="1:8">
       <c r="A277">
+        <f t="shared" si="4"/>
         <v>276</v>
       </c>
       <c r="B277" s="1">
@@ -16878,10 +17156,10 @@
         <v>23</v>
       </c>
       <c r="E277" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F277" s="2">
-        <v>40000</v>
+        <v>17600</v>
       </c>
       <c r="G277" s="10" t="s">
         <v>116</v>
@@ -16892,6 +17170,7 @@
     </row>
     <row r="278" spans="1:8">
       <c r="A278">
+        <f t="shared" si="4"/>
         <v>277</v>
       </c>
       <c r="B278" s="1">
@@ -16903,28 +17182,26 @@
       <c r="D278" t="s">
         <v>23</v>
       </c>
-      <c r="E278" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F278" s="2">
-        <v>17600</v>
-      </c>
-      <c r="G278" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H278" t="s">
-        <v>113</v>
+      <c r="E278" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F278" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G278" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="279" spans="1:8">
       <c r="A279">
+        <f t="shared" si="4"/>
         <v>278</v>
       </c>
       <c r="B279" s="1">
         <v>115</v>
       </c>
       <c r="C279" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="D279" t="s">
         <v>23</v>
@@ -16941,52 +17218,58 @@
     </row>
     <row r="280" spans="1:8">
       <c r="A280">
+        <f t="shared" si="4"/>
         <v>279</v>
       </c>
       <c r="B280" s="1">
         <v>115</v>
       </c>
-      <c r="C280" t="s">
-        <v>150</v>
-      </c>
-      <c r="D280" t="s">
+      <c r="C280" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D280" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F280" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G280" t="s">
-        <v>167</v>
+        <v>21</v>
+      </c>
+      <c r="F280" s="2">
+        <v>41384</v>
+      </c>
+      <c r="G280" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="281" spans="1:8">
       <c r="A281">
+        <f t="shared" si="4"/>
         <v>280</v>
       </c>
       <c r="B281" s="1">
         <v>115</v>
       </c>
-      <c r="C281" s="1" t="s">
+      <c r="C281" t="s">
         <v>53</v>
       </c>
-      <c r="D281" s="1" t="s">
+      <c r="D281" t="s">
         <v>23</v>
       </c>
-      <c r="E281" s="1" t="s">
-        <v>21</v>
+      <c r="E281" s="10" t="s">
+        <v>170</v>
       </c>
       <c r="F281" s="2">
-        <v>41384</v>
-      </c>
-      <c r="G281" s="1" t="s">
-        <v>8</v>
+        <v>40000</v>
+      </c>
+      <c r="G281" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H281" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="282" spans="1:8">
       <c r="A282">
+        <f t="shared" si="4"/>
         <v>281</v>
       </c>
       <c r="B282" s="1">
@@ -16999,10 +17282,10 @@
         <v>23</v>
       </c>
       <c r="E282" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F282" s="2">
-        <v>40000</v>
+        <v>19200</v>
       </c>
       <c r="G282" s="10" t="s">
         <v>116</v>
@@ -17013,6 +17296,7 @@
     </row>
     <row r="283" spans="1:8">
       <c r="A283">
+        <f t="shared" si="4"/>
         <v>282</v>
       </c>
       <c r="B283" s="1">
@@ -17024,44 +17308,43 @@
       <c r="D283" t="s">
         <v>23</v>
       </c>
-      <c r="E283" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F283" s="2">
-        <v>19200</v>
-      </c>
-      <c r="G283" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H283" t="s">
-        <v>114</v>
+      <c r="E283" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F283" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G283" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="284" spans="1:8">
       <c r="A284">
+        <f t="shared" si="4"/>
         <v>283</v>
       </c>
       <c r="B284" s="1">
         <v>115</v>
       </c>
-      <c r="C284" t="s">
-        <v>53</v>
-      </c>
-      <c r="D284" t="s">
-        <v>23</v>
+      <c r="C284" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F284" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G284" t="s">
-        <v>167</v>
+        <v>7</v>
+      </c>
+      <c r="F284" s="2">
+        <v>56000</v>
+      </c>
+      <c r="G284" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="285" spans="1:8">
       <c r="A285">
+        <f t="shared" si="4"/>
         <v>284</v>
       </c>
       <c r="B285" s="1">
@@ -17074,86 +17357,90 @@
         <v>13</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F285" s="2">
-        <v>56000</v>
+        <v>48284</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="286" spans="1:8">
       <c r="A286">
+        <f t="shared" si="4"/>
         <v>285</v>
       </c>
       <c r="B286" s="1">
         <v>115</v>
       </c>
-      <c r="C286" s="1" t="s">
+      <c r="C286" t="s">
         <v>54</v>
       </c>
-      <c r="D286" s="1" t="s">
+      <c r="D286" t="s">
         <v>13</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F286" s="2">
-        <v>48284</v>
-      </c>
-      <c r="G286" s="1" t="s">
-        <v>84</v>
+        <v>169</v>
+      </c>
+      <c r="F286" s="11">
+        <v>6300</v>
+      </c>
+      <c r="G286" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="287" spans="1:8">
       <c r="A287">
+        <f t="shared" si="4"/>
         <v>286</v>
       </c>
       <c r="B287" s="1">
         <v>115</v>
       </c>
-      <c r="C287" t="s">
-        <v>54</v>
-      </c>
-      <c r="D287" t="s">
-        <v>13</v>
+      <c r="C287" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F287" s="11">
-        <v>6300</v>
-      </c>
-      <c r="G287" t="s">
-        <v>167</v>
+        <v>21</v>
+      </c>
+      <c r="F287" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G287" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="288" spans="1:8">
       <c r="A288">
+        <f t="shared" si="4"/>
         <v>287</v>
       </c>
       <c r="B288" s="1">
         <v>115</v>
       </c>
-      <c r="C288" s="1" t="s">
+      <c r="C288" t="s">
         <v>55</v>
       </c>
-      <c r="D288" s="1" t="s">
+      <c r="D288" t="s">
         <v>20</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F288" s="2">
-        <v>42500</v>
-      </c>
-      <c r="G288" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F288" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G288" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="289" spans="1:8">
       <c r="A289">
+        <f t="shared" si="4"/>
         <v>288</v>
       </c>
       <c r="B289" s="1">
@@ -17162,67 +17449,70 @@
       <c r="C289" t="s">
         <v>55</v>
       </c>
-      <c r="D289" t="s">
-        <v>20</v>
+      <c r="D289" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F289" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G289" t="s">
-        <v>167</v>
+        <v>182</v>
+      </c>
+      <c r="F289">
+        <v>19125</v>
+      </c>
+      <c r="G289" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="290" spans="1:8">
       <c r="A290">
+        <f t="shared" si="4"/>
         <v>289</v>
       </c>
       <c r="B290" s="1">
         <v>115</v>
       </c>
-      <c r="C290" t="s">
-        <v>55</v>
-      </c>
-      <c r="D290" s="10" t="s">
-        <v>86</v>
+      <c r="C290" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F290">
-        <v>19125</v>
-      </c>
-      <c r="G290" s="10" t="s">
-        <v>184</v>
+        <v>21</v>
+      </c>
+      <c r="F290" s="2">
+        <v>41770</v>
+      </c>
+      <c r="G290" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="291" spans="1:8">
       <c r="A291">
+        <f t="shared" si="4"/>
         <v>290</v>
       </c>
       <c r="B291" s="1">
         <v>115</v>
       </c>
-      <c r="C291" s="1" t="s">
+      <c r="C291" t="s">
         <v>56</v>
       </c>
-      <c r="D291" s="1" t="s">
+      <c r="D291" t="s">
         <v>23</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F291" s="2">
-        <v>41770</v>
-      </c>
-      <c r="G291" s="1" t="s">
-        <v>8</v>
+        <v>169</v>
+      </c>
+      <c r="F291" s="11">
+        <v>4100</v>
+      </c>
+      <c r="G291" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="292" spans="1:8">
       <c r="A292">
+        <f t="shared" si="4"/>
         <v>291</v>
       </c>
       <c r="B292" s="1">
@@ -17231,67 +17521,70 @@
       <c r="C292" t="s">
         <v>56</v>
       </c>
-      <c r="D292" t="s">
-        <v>23</v>
+      <c r="D292" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F292" s="11">
-        <v>4100</v>
-      </c>
-      <c r="G292" t="s">
-        <v>167</v>
+        <v>182</v>
+      </c>
+      <c r="F292">
+        <v>18584</v>
+      </c>
+      <c r="G292" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="293" spans="1:8">
       <c r="A293">
+        <f t="shared" si="4"/>
         <v>292</v>
       </c>
       <c r="B293" s="1">
         <v>115</v>
       </c>
-      <c r="C293" t="s">
-        <v>56</v>
-      </c>
-      <c r="D293" s="10" t="s">
-        <v>64</v>
+      <c r="C293" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F293">
-        <v>18584</v>
-      </c>
-      <c r="G293" s="10" t="s">
-        <v>184</v>
+        <v>7</v>
+      </c>
+      <c r="F293" s="2">
+        <v>45000</v>
+      </c>
+      <c r="G293" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="294" spans="1:8">
       <c r="A294">
+        <f t="shared" si="4"/>
         <v>293</v>
       </c>
       <c r="B294" s="1">
         <v>115</v>
       </c>
-      <c r="C294" s="1" t="s">
+      <c r="C294" t="s">
         <v>57</v>
       </c>
-      <c r="D294" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E294" s="1" t="s">
-        <v>7</v>
+      <c r="D294" t="s">
+        <v>86</v>
+      </c>
+      <c r="E294" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="F294" s="2">
-        <v>45000</v>
-      </c>
-      <c r="G294" s="1" t="s">
-        <v>8</v>
+        <v>40000</v>
+      </c>
+      <c r="G294" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="295" spans="1:8">
       <c r="A295">
+        <f t="shared" si="4"/>
         <v>294</v>
       </c>
       <c r="B295" s="1">
@@ -17301,36 +17594,37 @@
         <v>57</v>
       </c>
       <c r="D295" t="s">
-        <v>86</v>
-      </c>
-      <c r="E295" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F295" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G295" s="9" t="s">
-        <v>88</v>
+        <v>20</v>
+      </c>
+      <c r="E295" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F295" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G295" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="296" spans="1:8">
       <c r="A296">
+        <f t="shared" si="4"/>
         <v>295</v>
       </c>
       <c r="B296" s="1">
         <v>115</v>
       </c>
       <c r="C296" t="s">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="D296" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F296" s="11">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="G296" t="s">
         <v>167</v>
@@ -17338,29 +17632,31 @@
     </row>
     <row r="297" spans="1:8">
       <c r="A297">
+        <f t="shared" si="4"/>
         <v>296</v>
       </c>
       <c r="B297" s="1">
         <v>115</v>
       </c>
-      <c r="C297" t="s">
+      <c r="C297" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="D297" t="s">
+      <c r="D297" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F297" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G297" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F297" s="14">
+        <v>4500</v>
+      </c>
+      <c r="H297" s="13" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="298" spans="1:8">
       <c r="A298">
+        <f t="shared" si="4"/>
         <v>297</v>
       </c>
       <c r="B298" s="1">
@@ -17375,123 +17671,128 @@
       <c r="E298" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F298" s="14">
-        <v>4500</v>
+      <c r="F298" s="15">
+        <v>850</v>
       </c>
       <c r="H298" s="13" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="299" spans="1:8">
       <c r="A299">
+        <f t="shared" si="4"/>
         <v>298</v>
       </c>
       <c r="B299" s="1">
         <v>115</v>
       </c>
-      <c r="C299" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="D299" s="1" t="s">
+      <c r="C299" t="s">
+        <v>152</v>
+      </c>
+      <c r="D299" t="s">
         <v>23</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F299" s="15">
-        <v>850</v>
-      </c>
-      <c r="H299" s="13" t="s">
-        <v>199</v>
+        <v>169</v>
+      </c>
+      <c r="F299" s="11">
+        <v>5000</v>
+      </c>
+      <c r="G299" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="300" spans="1:8">
       <c r="A300">
+        <f t="shared" si="4"/>
         <v>299</v>
       </c>
       <c r="B300" s="1">
         <v>115</v>
       </c>
-      <c r="C300" t="s">
+      <c r="C300" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="D300" t="s">
+      <c r="D300" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F300" s="11">
-        <v>5000</v>
-      </c>
-      <c r="G300" t="s">
-        <v>167</v>
+        <v>223</v>
+      </c>
+      <c r="F300" s="15">
+        <v>500</v>
+      </c>
+      <c r="H300" s="13" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="301" spans="1:8">
       <c r="A301">
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="B301" s="1">
         <v>115</v>
       </c>
-      <c r="C301" s="13" t="s">
-        <v>152</v>
+      <c r="C301" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F301" s="15">
-        <v>500</v>
-      </c>
-      <c r="H301" s="13" t="s">
-        <v>191</v>
+        <v>83</v>
+      </c>
+      <c r="F301" s="2">
+        <v>39125</v>
+      </c>
+      <c r="G301" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="302" spans="1:8">
       <c r="A302">
+        <f t="shared" si="4"/>
         <v>301</v>
       </c>
       <c r="B302" s="1">
         <v>115</v>
       </c>
-      <c r="C302" s="1" t="s">
+      <c r="C302" t="s">
         <v>65</v>
       </c>
-      <c r="D302" s="1" t="s">
+      <c r="D302" t="s">
         <v>23</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F302" s="2">
-        <v>39125</v>
-      </c>
-      <c r="G302" s="1" t="s">
-        <v>84</v>
+        <v>169</v>
+      </c>
+      <c r="F302" s="11">
+        <v>7500</v>
+      </c>
+      <c r="G302" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="303" spans="1:8">
       <c r="A303">
+        <f t="shared" si="4"/>
         <v>302</v>
       </c>
       <c r="B303" s="1">
         <v>115</v>
       </c>
       <c r="C303" t="s">
-        <v>65</v>
-      </c>
-      <c r="D303" t="s">
-        <v>23</v>
+        <v>163</v>
+      </c>
+      <c r="D303" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F303" s="11">
-        <v>7500</v>
+        <v>5200</v>
       </c>
       <c r="G303" t="s">
         <v>167</v>
@@ -17499,16 +17800,17 @@
     </row>
     <row r="304" spans="1:8">
       <c r="A304">
+        <f t="shared" si="4"/>
         <v>303</v>
       </c>
       <c r="B304" s="1">
         <v>115</v>
       </c>
       <c r="C304" t="s">
-        <v>163</v>
-      </c>
-      <c r="D304" s="10" t="s">
-        <v>179</v>
+        <v>164</v>
+      </c>
+      <c r="D304" t="s">
+        <v>40</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>169</v>
@@ -17522,6 +17824,7 @@
     </row>
     <row r="305" spans="1:7">
       <c r="A305">
+        <f t="shared" si="4"/>
         <v>304</v>
       </c>
       <c r="B305" s="1">
@@ -17530,44 +17833,46 @@
       <c r="C305" t="s">
         <v>164</v>
       </c>
-      <c r="D305" t="s">
-        <v>40</v>
+      <c r="D305" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F305" s="11">
-        <v>5200</v>
-      </c>
-      <c r="G305" t="s">
-        <v>167</v>
+        <v>182</v>
+      </c>
+      <c r="F305">
+        <v>13515</v>
+      </c>
+      <c r="G305" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="306" spans="1:7">
       <c r="A306">
+        <f t="shared" si="4"/>
         <v>305</v>
       </c>
       <c r="B306" s="1">
         <v>115</v>
       </c>
-      <c r="C306" t="s">
-        <v>164</v>
-      </c>
-      <c r="D306" s="10" t="s">
-        <v>179</v>
+      <c r="C306" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F306">
-        <v>13515</v>
-      </c>
-      <c r="G306" s="10" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="307" spans="1:7">
+        <v>7</v>
+      </c>
+      <c r="F306" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G306" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" ht="17.25">
       <c r="A307">
+        <f t="shared" si="4"/>
         <v>306</v>
       </c>
       <c r="B307" s="1">
@@ -17576,21 +17881,22 @@
       <c r="C307" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D307" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E307" s="1" t="s">
-        <v>7</v>
+      <c r="D307" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E307" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F307" s="2">
-        <v>59500</v>
+        <v>221000</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7" ht="17.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7">
       <c r="A308">
+        <f t="shared" si="4"/>
         <v>307</v>
       </c>
       <c r="B308" s="1">
@@ -17599,115 +17905,95 @@
       <c r="C308" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D308" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E308" s="3" t="s">
-        <v>81</v>
+      <c r="D308" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E308" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F308" s="2">
-        <v>221000</v>
+        <v>26283</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="309" spans="1:7">
       <c r="A309">
+        <f t="shared" si="4"/>
         <v>308</v>
       </c>
       <c r="B309" s="1">
         <v>115</v>
       </c>
-      <c r="C309" s="1" t="s">
+      <c r="C309" t="s">
         <v>58</v>
       </c>
-      <c r="D309" s="1" t="s">
+      <c r="D309" t="s">
         <v>60</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F309" s="2">
-        <v>26283</v>
-      </c>
-      <c r="G309" s="1" t="s">
-        <v>84</v>
+        <v>169</v>
+      </c>
+      <c r="F309" s="11">
+        <v>1100</v>
+      </c>
+      <c r="G309" s="12" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="310" spans="1:7">
       <c r="A310">
+        <f t="shared" si="4"/>
         <v>309</v>
       </c>
       <c r="B310" s="1">
         <v>115</v>
       </c>
-      <c r="C310" t="s">
-        <v>58</v>
-      </c>
-      <c r="D310" t="s">
+      <c r="C310" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D310" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F310" s="11">
-        <v>1100</v>
-      </c>
-      <c r="G310" s="12" t="s">
-        <v>168</v>
+        <v>11</v>
+      </c>
+      <c r="F310" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G310" s="1" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="311" spans="1:7">
       <c r="A311">
+        <f t="shared" si="4"/>
         <v>310</v>
       </c>
       <c r="B311" s="1">
         <v>115</v>
       </c>
-      <c r="C311" s="1" t="s">
+      <c r="C311" t="s">
         <v>59</v>
       </c>
-      <c r="D311" s="1" t="s">
+      <c r="D311" t="s">
         <v>60</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F311" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G311" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="312" spans="1:7">
-      <c r="A312">
-        <v>311</v>
-      </c>
-      <c r="B312" s="1">
-        <v>115</v>
-      </c>
-      <c r="C312" t="s">
-        <v>59</v>
-      </c>
-      <c r="D312" t="s">
-        <v>60</v>
-      </c>
-      <c r="E312" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F312" s="11">
+      <c r="F311" s="11">
         <v>2700</v>
       </c>
-      <c r="G312" t="s">
+      <c r="G311" t="s">
         <v>167</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{75BAC909-8D45-4443-AECB-1592B366F0B1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:H312">
-    <sortCondition ref="C2:C312"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:H311">
+    <sortCondition ref="C2:C311"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B8A5A6-7529-4E3B-BC82-64C8A211DEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F723A3BB-DA8A-4371-96FD-BE13D5FA7DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11179,9 +11179,9 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>383</v>
-      </c>
-      <c r="B28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
         <v>115</v>
       </c>
       <c r="C28" t="s">
@@ -11205,9 +11205,9 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>384</v>
-      </c>
-      <c r="B29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1">
         <v>115</v>
       </c>
       <c r="C29" t="s">
@@ -11231,9 +11231,9 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>398</v>
-      </c>
-      <c r="B30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1">
         <v>115</v>
       </c>
       <c r="C30" t="s">
@@ -11257,9 +11257,9 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>399</v>
-      </c>
-      <c r="B31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1">
         <v>115</v>
       </c>
       <c r="C31" t="s">
@@ -11283,7 +11283,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B32" s="1">
         <v>115</v>
@@ -11306,7 +11306,7 @@
     </row>
     <row r="33" spans="1:8" ht="17.25">
       <c r="A33">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B33" s="1">
         <v>115</v>
@@ -11329,7 +11329,7 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B34" s="1">
         <v>115</v>
@@ -11355,7 +11355,7 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B35" s="1">
         <v>115</v>
@@ -11381,7 +11381,7 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B36" s="1">
         <v>115</v>
@@ -11404,7 +11404,7 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B37" s="1">
         <v>115</v>
@@ -11427,7 +11427,7 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B38" s="1">
         <v>115</v>
@@ -11450,7 +11450,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B39" s="1">
         <v>115</v>
@@ -11473,7 +11473,7 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B40" s="1">
         <v>115</v>
@@ -11496,7 +11496,7 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B41" s="1">
         <v>115</v>
@@ -11519,7 +11519,7 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B42" s="1">
         <v>115</v>
@@ -11542,7 +11542,7 @@
     </row>
     <row r="43" spans="1:8" ht="17.25">
       <c r="A43">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B43" s="1">
         <v>115</v>
@@ -11565,7 +11565,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B44" s="1">
         <v>115</v>
@@ -11588,7 +11588,7 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B45" s="1">
         <v>115</v>
@@ -11611,7 +11611,7 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B46" s="1">
         <v>115</v>
@@ -11634,7 +11634,7 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B47" s="1">
         <v>115</v>
@@ -11660,7 +11660,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B48" s="1">
         <v>115</v>
@@ -11686,7 +11686,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B49" s="1">
         <v>115</v>
@@ -11712,7 +11712,7 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B50" s="1">
         <v>115</v>
@@ -11738,7 +11738,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B51" s="1">
         <v>115</v>
@@ -11761,7 +11761,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B52" s="1">
         <v>115</v>
@@ -11784,7 +11784,7 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B53" s="1">
         <v>115</v>
@@ -11807,7 +11807,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B54" s="1">
         <v>115</v>
@@ -11833,7 +11833,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B55" s="1">
         <v>115</v>
@@ -11859,7 +11859,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B56" s="1">
         <v>115</v>
@@ -11885,7 +11885,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B57" s="1">
         <v>115</v>
@@ -11911,7 +11911,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B58" s="1">
         <v>115</v>
@@ -11934,7 +11934,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B59" s="1">
         <v>115</v>
@@ -11957,7 +11957,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B60" s="1">
         <v>115</v>
@@ -11980,7 +11980,7 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B61" s="1">
         <v>115</v>
@@ -12003,7 +12003,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B62" s="1">
         <v>115</v>
@@ -12029,7 +12029,7 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B63" s="1">
         <v>115</v>
@@ -12055,7 +12055,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B64" s="1">
         <v>115</v>
@@ -12081,7 +12081,7 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B65" s="1">
         <v>115</v>
@@ -12107,7 +12107,7 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B66" s="1">
         <v>115</v>
@@ -12130,7 +12130,7 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B67" s="1">
         <v>115</v>
@@ -12153,7 +12153,7 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B68" s="1">
         <v>115</v>
@@ -12176,7 +12176,7 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B69" s="1">
         <v>115</v>
@@ -12199,7 +12199,7 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B70" s="1">
         <v>115</v>
@@ -12225,7 +12225,7 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B71" s="1">
         <v>115</v>
@@ -12251,7 +12251,7 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B72" s="1">
         <v>115</v>
@@ -12277,7 +12277,7 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B73" s="1">
         <v>115</v>
@@ -12303,7 +12303,7 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B74" s="1">
         <v>115</v>
@@ -12329,7 +12329,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B75" s="1">
         <v>115</v>
@@ -12352,7 +12352,7 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B76" s="1">
         <v>115</v>
@@ -12375,7 +12375,7 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B77" s="1">
         <v>115</v>
@@ -12398,7 +12398,7 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B78" s="1">
         <v>115</v>
@@ -12418,7 +12418,7 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B79" s="1">
         <v>115</v>
@@ -12441,7 +12441,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B80" s="1">
         <v>115</v>
@@ -12464,7 +12464,7 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B81" s="1">
         <v>115</v>
@@ -12487,7 +12487,7 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B82" s="1">
         <v>115</v>
@@ -12510,7 +12510,7 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B83" s="1">
         <v>115</v>
@@ -12533,7 +12533,7 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B84" s="1">
         <v>115</v>
@@ -12556,7 +12556,7 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B85" s="1">
         <v>115</v>
@@ -12579,7 +12579,7 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B86" s="1">
         <v>115</v>
@@ -12602,7 +12602,7 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B87" s="1">
         <v>115</v>
@@ -12625,7 +12625,7 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B88" s="1">
         <v>115</v>
@@ -12651,7 +12651,7 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B89" s="1">
         <v>115</v>
@@ -12677,7 +12677,7 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B90" s="1">
         <v>115</v>
@@ -12703,7 +12703,7 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B91" s="1">
         <v>115</v>
@@ -12729,7 +12729,7 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B92" s="1">
         <v>115</v>
@@ -12755,7 +12755,7 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B93" s="1">
         <v>115</v>
@@ -12778,7 +12778,7 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B94" s="1">
         <v>115</v>
@@ -12801,7 +12801,7 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B95" s="1">
         <v>115</v>
@@ -12824,7 +12824,7 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B96" s="1">
         <v>115</v>
@@ -12847,7 +12847,7 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B97" s="1">
         <v>115</v>
@@ -12870,7 +12870,7 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B98" s="1">
         <v>115</v>
@@ -12893,7 +12893,7 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B99" s="1">
         <v>115</v>
@@ -12919,7 +12919,7 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B100" s="1">
         <v>115</v>
@@ -12945,7 +12945,7 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B101" s="1">
         <v>115</v>
@@ -12971,7 +12971,7 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B102" s="1">
         <v>115</v>
@@ -12997,7 +12997,7 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B103" s="1">
         <v>115</v>
@@ -13023,7 +13023,7 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B104" s="1">
         <v>115</v>
@@ -13049,7 +13049,7 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B105" s="1">
         <v>115</v>
@@ -13072,7 +13072,7 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B106" s="1">
         <v>115</v>
@@ -13095,7 +13095,7 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B107" s="1">
         <v>115</v>
@@ -13118,7 +13118,7 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B108" s="1">
         <v>115</v>
@@ -13141,7 +13141,7 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B109" s="1">
         <v>115</v>
@@ -13164,7 +13164,7 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B110" s="1">
         <v>115</v>
@@ -13187,7 +13187,7 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B111" s="1">
         <v>115</v>
@@ -13210,7 +13210,7 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B112" s="1">
         <v>115</v>
@@ -13233,7 +13233,7 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B113" s="1">
         <v>115</v>
@@ -13259,7 +13259,7 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B114" s="1">
         <v>115</v>
@@ -13285,7 +13285,7 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B115" s="1">
         <v>115</v>
@@ -13308,7 +13308,7 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B116" s="1">
         <v>115</v>
@@ -13331,7 +13331,7 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B117" s="1">
         <v>115</v>
@@ -13354,7 +13354,7 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B118" s="1">
         <v>115</v>
@@ -13377,7 +13377,7 @@
     </row>
     <row r="119" spans="1:8" ht="17.25">
       <c r="A119">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B119" s="1">
         <v>115</v>
@@ -13400,7 +13400,7 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B120" s="1">
         <v>115</v>
@@ -13423,7 +13423,7 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B121" s="1">
         <v>115</v>
@@ -13449,7 +13449,7 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B122" s="1">
         <v>115</v>
@@ -13475,7 +13475,7 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B123" s="1">
         <v>115</v>
@@ -13501,7 +13501,7 @@
     </row>
     <row r="124" spans="1:8">
       <c r="A124">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B124" s="1">
         <v>115</v>
@@ -13527,7 +13527,7 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B125" s="1">
         <v>115</v>
@@ -13550,7 +13550,7 @@
     </row>
     <row r="126" spans="1:8">
       <c r="A126">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B126" s="1">
         <v>115</v>
@@ -13573,7 +13573,7 @@
     </row>
     <row r="127" spans="1:8">
       <c r="A127">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B127" s="1">
         <v>115</v>
@@ -13596,7 +13596,7 @@
     </row>
     <row r="128" spans="1:8">
       <c r="A128">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B128" s="1">
         <v>115</v>
@@ -13619,7 +13619,7 @@
     </row>
     <row r="129" spans="1:8">
       <c r="A129">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B129" s="1">
         <v>115</v>
@@ -13645,7 +13645,7 @@
     </row>
     <row r="130" spans="1:8">
       <c r="A130">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B130" s="1">
         <v>115</v>
@@ -13668,7 +13668,7 @@
     </row>
     <row r="131" spans="1:8">
       <c r="A131">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B131" s="1">
         <v>115</v>
@@ -13691,7 +13691,7 @@
     </row>
     <row r="132" spans="1:8">
       <c r="A132">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B132" s="1">
         <v>115</v>
@@ -13714,7 +13714,7 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B133" s="1">
         <v>115</v>
@@ -13737,7 +13737,7 @@
     </row>
     <row r="134" spans="1:8" ht="17.25">
       <c r="A134">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B134" s="1">
         <v>115</v>
@@ -13760,7 +13760,7 @@
     </row>
     <row r="135" spans="1:8">
       <c r="A135">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B135" s="1">
         <v>115</v>
@@ -13786,7 +13786,7 @@
     </row>
     <row r="136" spans="1:8">
       <c r="A136">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B136" s="1">
         <v>115</v>
@@ -13812,7 +13812,7 @@
     </row>
     <row r="137" spans="1:8">
       <c r="A137">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B137" s="1">
         <v>115</v>
@@ -13835,7 +13835,7 @@
     </row>
     <row r="138" spans="1:8">
       <c r="A138">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B138" s="1">
         <v>115</v>
@@ -13858,9 +13858,9 @@
     </row>
     <row r="139" spans="1:8">
       <c r="A139">
-        <v>387</v>
-      </c>
-      <c r="B139">
+        <v>138</v>
+      </c>
+      <c r="B139" s="1">
         <v>115</v>
       </c>
       <c r="C139" t="s">
@@ -13884,9 +13884,9 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140">
-        <v>402</v>
-      </c>
-      <c r="B140">
+        <v>139</v>
+      </c>
+      <c r="B140" s="1">
         <v>115</v>
       </c>
       <c r="C140" t="s">
@@ -13910,7 +13910,7 @@
     </row>
     <row r="141" spans="1:8">
       <c r="A141">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B141" s="1">
         <v>115</v>
@@ -13933,7 +13933,7 @@
     </row>
     <row r="142" spans="1:8">
       <c r="A142">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B142" s="1">
         <v>115</v>
@@ -13956,7 +13956,7 @@
     </row>
     <row r="143" spans="1:8">
       <c r="A143">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B143" s="1">
         <v>115</v>
@@ -13979,7 +13979,7 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B144" s="1">
         <v>115</v>
@@ -14002,7 +14002,7 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B145" s="1">
         <v>115</v>
@@ -14025,7 +14025,7 @@
     </row>
     <row r="146" spans="1:8">
       <c r="A146">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B146" s="1">
         <v>115</v>
@@ -14048,9 +14048,9 @@
     </row>
     <row r="147" spans="1:8">
       <c r="A147">
-        <v>390</v>
-      </c>
-      <c r="B147">
+        <v>146</v>
+      </c>
+      <c r="B147" s="1">
         <v>115</v>
       </c>
       <c r="C147" t="s">
@@ -14074,9 +14074,9 @@
     </row>
     <row r="148" spans="1:8">
       <c r="A148">
-        <v>405</v>
-      </c>
-      <c r="B148">
+        <v>147</v>
+      </c>
+      <c r="B148" s="1">
         <v>115</v>
       </c>
       <c r="C148" t="s">
@@ -14100,7 +14100,7 @@
     </row>
     <row r="149" spans="1:8">
       <c r="A149">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B149" s="1">
         <v>115</v>
@@ -14123,7 +14123,7 @@
     </row>
     <row r="150" spans="1:8">
       <c r="A150">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B150" s="1">
         <v>115</v>
@@ -14146,7 +14146,7 @@
     </row>
     <row r="151" spans="1:8">
       <c r="A151">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B151" s="1">
         <v>115</v>
@@ -14169,7 +14169,7 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B152" s="1">
         <v>115</v>
@@ -14192,7 +14192,7 @@
     </row>
     <row r="153" spans="1:8">
       <c r="A153">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B153" s="1">
         <v>115</v>
@@ -14215,7 +14215,7 @@
     </row>
     <row r="154" spans="1:8">
       <c r="A154">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B154" s="1">
         <v>115</v>
@@ -14238,7 +14238,7 @@
     </row>
     <row r="155" spans="1:8">
       <c r="A155">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B155" s="1">
         <v>115</v>
@@ -14261,9 +14261,9 @@
     </row>
     <row r="156" spans="1:8">
       <c r="A156">
-        <v>389</v>
-      </c>
-      <c r="B156">
+        <v>155</v>
+      </c>
+      <c r="B156" s="1">
         <v>115</v>
       </c>
       <c r="C156" t="s">
@@ -14287,9 +14287,9 @@
     </row>
     <row r="157" spans="1:8">
       <c r="A157">
-        <v>404</v>
-      </c>
-      <c r="B157">
+        <v>156</v>
+      </c>
+      <c r="B157" s="1">
         <v>115</v>
       </c>
       <c r="C157" t="s">
@@ -14313,7 +14313,7 @@
     </row>
     <row r="158" spans="1:8">
       <c r="A158">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B158" s="1">
         <v>115</v>
@@ -14336,7 +14336,7 @@
     </row>
     <row r="159" spans="1:8">
       <c r="A159">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B159" s="1">
         <v>115</v>
@@ -14359,7 +14359,7 @@
     </row>
     <row r="160" spans="1:8">
       <c r="A160">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="B160" s="1">
         <v>115</v>
@@ -14382,7 +14382,7 @@
     </row>
     <row r="161" spans="1:8">
       <c r="A161">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="B161" s="1">
         <v>115</v>
@@ -14405,7 +14405,7 @@
     </row>
     <row r="162" spans="1:8">
       <c r="A162">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B162" s="1">
         <v>115</v>
@@ -14431,7 +14431,7 @@
     </row>
     <row r="163" spans="1:8">
       <c r="A163">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="B163" s="1">
         <v>115</v>
@@ -14454,9 +14454,9 @@
     </row>
     <row r="164" spans="1:8">
       <c r="A164">
-        <v>388</v>
-      </c>
-      <c r="B164">
+        <v>163</v>
+      </c>
+      <c r="B164" s="1">
         <v>115</v>
       </c>
       <c r="C164" t="s">
@@ -14480,9 +14480,9 @@
     </row>
     <row r="165" spans="1:8">
       <c r="A165">
-        <v>403</v>
-      </c>
-      <c r="B165">
+        <v>164</v>
+      </c>
+      <c r="B165" s="1">
         <v>115</v>
       </c>
       <c r="C165" t="s">
@@ -14506,7 +14506,7 @@
     </row>
     <row r="166" spans="1:8">
       <c r="A166">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="B166" s="1">
         <v>115</v>
@@ -14529,7 +14529,7 @@
     </row>
     <row r="167" spans="1:8">
       <c r="A167">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="B167" s="1">
         <v>115</v>
@@ -14552,7 +14552,7 @@
     </row>
     <row r="168" spans="1:8">
       <c r="A168">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="B168" s="1">
         <v>115</v>
@@ -14575,7 +14575,7 @@
     </row>
     <row r="169" spans="1:8">
       <c r="A169">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="B169" s="1">
         <v>115</v>
@@ -14598,7 +14598,7 @@
     </row>
     <row r="170" spans="1:8">
       <c r="A170">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="B170" s="1">
         <v>115</v>
@@ -14621,7 +14621,7 @@
     </row>
     <row r="171" spans="1:8">
       <c r="A171">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="B171" s="1">
         <v>115</v>
@@ -14644,7 +14644,7 @@
     </row>
     <row r="172" spans="1:8">
       <c r="A172">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B172" s="1">
         <v>115</v>
@@ -14667,7 +14667,7 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="B173" s="1">
         <v>115</v>
@@ -14690,7 +14690,7 @@
     </row>
     <row r="174" spans="1:8">
       <c r="A174">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B174" s="1">
         <v>115</v>
@@ -14713,7 +14713,7 @@
     </row>
     <row r="175" spans="1:8">
       <c r="A175">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="B175" s="1">
         <v>115</v>
@@ -14736,9 +14736,9 @@
     </row>
     <row r="176" spans="1:8">
       <c r="A176">
-        <v>386</v>
-      </c>
-      <c r="B176">
+        <v>175</v>
+      </c>
+      <c r="B176" s="1">
         <v>115</v>
       </c>
       <c r="C176" t="s">
@@ -14762,9 +14762,9 @@
     </row>
     <row r="177" spans="1:8">
       <c r="A177">
-        <v>401</v>
-      </c>
-      <c r="B177">
+        <v>176</v>
+      </c>
+      <c r="B177" s="1">
         <v>115</v>
       </c>
       <c r="C177" t="s">
@@ -14788,7 +14788,7 @@
     </row>
     <row r="178" spans="1:8">
       <c r="A178">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="B178" s="1">
         <v>115</v>
@@ -14811,7 +14811,7 @@
     </row>
     <row r="179" spans="1:8">
       <c r="A179">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B179" s="1">
         <v>115</v>
@@ -14834,7 +14834,7 @@
     </row>
     <row r="180" spans="1:8">
       <c r="A180">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="B180" s="1">
         <v>115</v>
@@ -14857,7 +14857,7 @@
     </row>
     <row r="181" spans="1:8">
       <c r="A181">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="B181" s="1">
         <v>115</v>
@@ -14883,7 +14883,7 @@
     </row>
     <row r="182" spans="1:8">
       <c r="A182">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="B182" s="1">
         <v>115</v>
@@ -14909,7 +14909,7 @@
     </row>
     <row r="183" spans="1:8">
       <c r="A183">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="B183" s="1">
         <v>115</v>
@@ -14932,7 +14932,7 @@
     </row>
     <row r="184" spans="1:8">
       <c r="A184">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B184" s="1">
         <v>115</v>
@@ -14955,7 +14955,7 @@
     </row>
     <row r="185" spans="1:8">
       <c r="A185">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B185" s="1">
         <v>115</v>
@@ -14978,7 +14978,7 @@
     </row>
     <row r="186" spans="1:8">
       <c r="A186">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="B186" s="1">
         <v>115</v>
@@ -15001,7 +15001,7 @@
     </row>
     <row r="187" spans="1:8">
       <c r="A187">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="B187" s="1">
         <v>115</v>
@@ -15024,7 +15024,7 @@
     </row>
     <row r="188" spans="1:8">
       <c r="A188">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="B188" s="1">
         <v>115</v>
@@ -15047,7 +15047,7 @@
     </row>
     <row r="189" spans="1:8">
       <c r="A189">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="B189" s="1">
         <v>115</v>
@@ -15073,7 +15073,7 @@
     </row>
     <row r="190" spans="1:8">
       <c r="A190">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="B190" s="1">
         <v>115</v>
@@ -15096,7 +15096,7 @@
     </row>
     <row r="191" spans="1:8">
       <c r="A191">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="B191" s="1">
         <v>115</v>
@@ -15119,7 +15119,7 @@
     </row>
     <row r="192" spans="1:8" ht="17.25">
       <c r="A192">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="B192" s="1">
         <v>115</v>
@@ -15142,7 +15142,7 @@
     </row>
     <row r="193" spans="1:8">
       <c r="A193">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="B193" s="1">
         <v>115</v>
@@ -15168,7 +15168,7 @@
     </row>
     <row r="194" spans="1:8">
       <c r="A194">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="B194" s="1">
         <v>115</v>
@@ -15194,9 +15194,9 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195">
-        <v>377</v>
-      </c>
-      <c r="B195">
+        <v>194</v>
+      </c>
+      <c r="B195" s="1">
         <v>115</v>
       </c>
       <c r="C195" t="s">
@@ -15220,9 +15220,9 @@
     </row>
     <row r="196" spans="1:8">
       <c r="A196">
-        <v>392</v>
-      </c>
-      <c r="B196">
+        <v>195</v>
+      </c>
+      <c r="B196" s="1">
         <v>115</v>
       </c>
       <c r="C196" t="s">
@@ -15246,7 +15246,7 @@
     </row>
     <row r="197" spans="1:8" ht="17.25">
       <c r="A197">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="B197" s="1">
         <v>115</v>
@@ -15269,7 +15269,7 @@
     </row>
     <row r="198" spans="1:8">
       <c r="A198">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="B198" s="1">
         <v>115</v>
@@ -15292,7 +15292,7 @@
     </row>
     <row r="199" spans="1:8">
       <c r="A199">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="B199" s="1">
         <v>115</v>
@@ -15315,7 +15315,7 @@
     </row>
     <row r="200" spans="1:8">
       <c r="A200">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="B200" s="1">
         <v>115</v>
@@ -15341,9 +15341,9 @@
     </row>
     <row r="201" spans="1:8">
       <c r="A201">
-        <v>391</v>
-      </c>
-      <c r="B201">
+        <v>200</v>
+      </c>
+      <c r="B201" s="1">
         <v>115</v>
       </c>
       <c r="C201" t="s">
@@ -15367,9 +15367,9 @@
     </row>
     <row r="202" spans="1:8">
       <c r="A202">
-        <v>406</v>
-      </c>
-      <c r="B202">
+        <v>201</v>
+      </c>
+      <c r="B202" s="1">
         <v>115</v>
       </c>
       <c r="C202" t="s">
@@ -15393,7 +15393,7 @@
     </row>
     <row r="203" spans="1:8">
       <c r="A203">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="B203" s="1">
         <v>115</v>
@@ -15416,7 +15416,7 @@
     </row>
     <row r="204" spans="1:8">
       <c r="A204">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B204" s="1">
         <v>115</v>
@@ -15439,7 +15439,7 @@
     </row>
     <row r="205" spans="1:8">
       <c r="A205">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="B205" s="1">
         <v>115</v>
@@ -15462,7 +15462,7 @@
     </row>
     <row r="206" spans="1:8">
       <c r="A206">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="B206" s="1">
         <v>115</v>
@@ -15488,7 +15488,7 @@
     </row>
     <row r="207" spans="1:8">
       <c r="A207">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="B207" s="1">
         <v>115</v>
@@ -15511,7 +15511,7 @@
     </row>
     <row r="208" spans="1:8">
       <c r="A208">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="B208" s="1">
         <v>115</v>
@@ -15534,7 +15534,7 @@
     </row>
     <row r="209" spans="1:8">
       <c r="A209">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="B209" s="1">
         <v>115</v>
@@ -15557,7 +15557,7 @@
     </row>
     <row r="210" spans="1:8">
       <c r="A210">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="B210" s="1">
         <v>115</v>
@@ -15583,7 +15583,7 @@
     </row>
     <row r="211" spans="1:8">
       <c r="A211">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="B211" s="1">
         <v>115</v>
@@ -15609,7 +15609,7 @@
     </row>
     <row r="212" spans="1:8">
       <c r="A212">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="B212" s="1">
         <v>115</v>
@@ -15635,9 +15635,9 @@
     </row>
     <row r="213" spans="1:8">
       <c r="A213">
-        <v>378</v>
-      </c>
-      <c r="B213">
+        <v>212</v>
+      </c>
+      <c r="B213" s="1">
         <v>115</v>
       </c>
       <c r="C213" t="s">
@@ -15661,9 +15661,9 @@
     </row>
     <row r="214" spans="1:8">
       <c r="A214">
-        <v>393</v>
-      </c>
-      <c r="B214">
+        <v>213</v>
+      </c>
+      <c r="B214" s="1">
         <v>115</v>
       </c>
       <c r="C214" t="s">
@@ -15687,7 +15687,7 @@
     </row>
     <row r="215" spans="1:8">
       <c r="A215">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="B215" s="1">
         <v>115</v>
@@ -15710,7 +15710,7 @@
     </row>
     <row r="216" spans="1:8" ht="17.25">
       <c r="A216">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="B216" s="1">
         <v>115</v>
@@ -15733,7 +15733,7 @@
     </row>
     <row r="217" spans="1:8">
       <c r="A217">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="B217" s="1">
         <v>115</v>
@@ -15756,7 +15756,7 @@
     </row>
     <row r="218" spans="1:8">
       <c r="A218">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="B218" s="1">
         <v>115</v>
@@ -15779,7 +15779,7 @@
     </row>
     <row r="219" spans="1:8">
       <c r="A219">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B219" s="1">
         <v>115</v>
@@ -15802,7 +15802,7 @@
     </row>
     <row r="220" spans="1:8">
       <c r="A220">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="B220" s="1">
         <v>115</v>
@@ -15825,7 +15825,7 @@
     </row>
     <row r="221" spans="1:8">
       <c r="A221">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="B221" s="1">
         <v>115</v>
@@ -15848,7 +15848,7 @@
     </row>
     <row r="222" spans="1:8">
       <c r="A222">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="B222" s="1">
         <v>115</v>
@@ -15871,7 +15871,7 @@
     </row>
     <row r="223" spans="1:8" ht="17.25">
       <c r="A223">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="B223" s="1">
         <v>115</v>
@@ -15894,7 +15894,7 @@
     </row>
     <row r="224" spans="1:8">
       <c r="A224">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="B224" s="1">
         <v>115</v>
@@ -15917,7 +15917,7 @@
     </row>
     <row r="225" spans="1:8">
       <c r="A225">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="B225" s="1">
         <v>115</v>
@@ -15940,7 +15940,7 @@
     </row>
     <row r="226" spans="1:8">
       <c r="A226">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="B226" s="1">
         <v>115</v>
@@ -15966,7 +15966,7 @@
     </row>
     <row r="227" spans="1:8">
       <c r="A227">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="B227" s="1">
         <v>115</v>
@@ -15992,7 +15992,7 @@
     </row>
     <row r="228" spans="1:8">
       <c r="A228">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="B228" s="1">
         <v>115</v>
@@ -16018,7 +16018,7 @@
     </row>
     <row r="229" spans="1:8">
       <c r="A229">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="B229" s="1">
         <v>115</v>
@@ -16044,7 +16044,7 @@
     </row>
     <row r="230" spans="1:8">
       <c r="A230">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="B230" s="1">
         <v>115</v>
@@ -16070,7 +16070,7 @@
     </row>
     <row r="231" spans="1:8">
       <c r="A231">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="B231" s="1">
         <v>115</v>
@@ -16093,7 +16093,7 @@
     </row>
     <row r="232" spans="1:8" ht="17.25">
       <c r="A232">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B232" s="1">
         <v>115</v>
@@ -16116,7 +16116,7 @@
     </row>
     <row r="233" spans="1:8">
       <c r="A233">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="B233" s="1">
         <v>115</v>
@@ -16139,7 +16139,7 @@
     </row>
     <row r="234" spans="1:8">
       <c r="A234">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="B234" s="1">
         <v>115</v>
@@ -16162,7 +16162,7 @@
     </row>
     <row r="235" spans="1:8">
       <c r="A235">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="B235" s="1">
         <v>115</v>
@@ -16185,7 +16185,7 @@
     </row>
     <row r="236" spans="1:8">
       <c r="A236">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="B236" s="1">
         <v>115</v>
@@ -16208,7 +16208,7 @@
     </row>
     <row r="237" spans="1:8">
       <c r="A237">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="B237" s="1">
         <v>115</v>
@@ -16231,9 +16231,9 @@
     </row>
     <row r="238" spans="1:8">
       <c r="A238">
-        <v>379</v>
-      </c>
-      <c r="B238">
+        <v>237</v>
+      </c>
+      <c r="B238" s="1">
         <v>115</v>
       </c>
       <c r="C238" t="s">
@@ -16257,9 +16257,9 @@
     </row>
     <row r="239" spans="1:8">
       <c r="A239">
-        <v>380</v>
-      </c>
-      <c r="B239">
+        <v>238</v>
+      </c>
+      <c r="B239" s="1">
         <v>115</v>
       </c>
       <c r="C239" t="s">
@@ -16283,9 +16283,9 @@
     </row>
     <row r="240" spans="1:8">
       <c r="A240">
-        <v>394</v>
-      </c>
-      <c r="B240">
+        <v>239</v>
+      </c>
+      <c r="B240" s="1">
         <v>115</v>
       </c>
       <c r="C240" t="s">
@@ -16309,9 +16309,9 @@
     </row>
     <row r="241" spans="1:8">
       <c r="A241">
-        <v>395</v>
-      </c>
-      <c r="B241">
+        <v>240</v>
+      </c>
+      <c r="B241" s="1">
         <v>115</v>
       </c>
       <c r="C241" t="s">
@@ -16335,7 +16335,7 @@
     </row>
     <row r="242" spans="1:8">
       <c r="A242">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="B242" s="1">
         <v>115</v>
@@ -16358,7 +16358,7 @@
     </row>
     <row r="243" spans="1:8">
       <c r="A243">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="B243" s="1">
         <v>115</v>
@@ -16384,7 +16384,7 @@
     </row>
     <row r="244" spans="1:8">
       <c r="A244">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="B244" s="1">
         <v>115</v>
@@ -16407,7 +16407,7 @@
     </row>
     <row r="245" spans="1:8">
       <c r="A245">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="B245" s="1">
         <v>115</v>
@@ -16430,7 +16430,7 @@
     </row>
     <row r="246" spans="1:8">
       <c r="A246">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="B246" s="1">
         <v>115</v>
@@ -16453,7 +16453,7 @@
     </row>
     <row r="247" spans="1:8">
       <c r="A247">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="B247" s="1">
         <v>115</v>
@@ -16476,7 +16476,7 @@
     </row>
     <row r="248" spans="1:8">
       <c r="A248">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="B248" s="1">
         <v>115</v>
@@ -16499,7 +16499,7 @@
     </row>
     <row r="249" spans="1:8">
       <c r="A249">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="B249" s="1">
         <v>115</v>
@@ -16522,7 +16522,7 @@
     </row>
     <row r="250" spans="1:8">
       <c r="A250">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="B250" s="1">
         <v>115</v>
@@ -16545,7 +16545,7 @@
     </row>
     <row r="251" spans="1:8">
       <c r="A251">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="B251" s="1">
         <v>115</v>
@@ -16568,7 +16568,7 @@
     </row>
     <row r="252" spans="1:8">
       <c r="A252">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="B252" s="1">
         <v>115</v>
@@ -16591,7 +16591,7 @@
     </row>
     <row r="253" spans="1:8">
       <c r="A253">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="B253" s="1">
         <v>115</v>
@@ -16617,7 +16617,7 @@
     </row>
     <row r="254" spans="1:8">
       <c r="A254">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="B254" s="1">
         <v>115</v>
@@ -16643,7 +16643,7 @@
     </row>
     <row r="255" spans="1:8">
       <c r="A255">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="B255" s="1">
         <v>115</v>
@@ -16666,7 +16666,7 @@
     </row>
     <row r="256" spans="1:8">
       <c r="A256">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="B256" s="1">
         <v>115</v>
@@ -16689,7 +16689,7 @@
     </row>
     <row r="257" spans="1:8">
       <c r="A257">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="B257" s="1">
         <v>115</v>
@@ -16712,7 +16712,7 @@
     </row>
     <row r="258" spans="1:8">
       <c r="A258">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="B258" s="1">
         <v>115</v>
@@ -16735,7 +16735,7 @@
     </row>
     <row r="259" spans="1:8">
       <c r="A259">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="B259" s="1">
         <v>115</v>
@@ -16758,7 +16758,7 @@
     </row>
     <row r="260" spans="1:8">
       <c r="A260">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="B260" s="1">
         <v>115</v>
@@ -16781,7 +16781,7 @@
     </row>
     <row r="261" spans="1:8">
       <c r="A261">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="B261" s="1">
         <v>115</v>
@@ -16804,7 +16804,7 @@
     </row>
     <row r="262" spans="1:8">
       <c r="A262">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="B262" s="1">
         <v>115</v>
@@ -16827,7 +16827,7 @@
     </row>
     <row r="263" spans="1:8">
       <c r="A263">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="B263" s="1">
         <v>115</v>
@@ -16850,7 +16850,7 @@
     </row>
     <row r="264" spans="1:8">
       <c r="A264">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="B264" s="1">
         <v>115</v>
@@ -16873,7 +16873,7 @@
     </row>
     <row r="265" spans="1:8">
       <c r="A265">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="B265" s="1">
         <v>115</v>
@@ -16896,7 +16896,7 @@
     </row>
     <row r="266" spans="1:8" ht="17.25">
       <c r="A266">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="B266" s="1">
         <v>115</v>
@@ -16919,7 +16919,7 @@
     </row>
     <row r="267" spans="1:8">
       <c r="A267">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="B267" s="1">
         <v>115</v>
@@ -16942,7 +16942,7 @@
     </row>
     <row r="268" spans="1:8">
       <c r="A268">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="B268" s="1">
         <v>115</v>
@@ -16965,7 +16965,7 @@
     </row>
     <row r="269" spans="1:8">
       <c r="A269">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="B269" s="1">
         <v>115</v>
@@ -16988,7 +16988,7 @@
     </row>
     <row r="270" spans="1:8">
       <c r="A270">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="B270" s="1">
         <v>115</v>
@@ -17011,7 +17011,7 @@
     </row>
     <row r="271" spans="1:8">
       <c r="A271">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="B271" s="1">
         <v>115</v>
@@ -17034,7 +17034,7 @@
     </row>
     <row r="272" spans="1:8">
       <c r="A272">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="B272" s="1">
         <v>115</v>
@@ -17054,7 +17054,7 @@
     </row>
     <row r="273" spans="1:8">
       <c r="A273">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="B273" s="1">
         <v>115</v>
@@ -17080,7 +17080,7 @@
     </row>
     <row r="274" spans="1:8">
       <c r="A274">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="B274" s="1">
         <v>115</v>
@@ -17106,7 +17106,7 @@
     </row>
     <row r="275" spans="1:8" ht="17.25">
       <c r="A275">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="B275" s="1">
         <v>115</v>
@@ -17129,7 +17129,7 @@
     </row>
     <row r="276" spans="1:8">
       <c r="A276">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="B276" s="1">
         <v>115</v>
@@ -17152,7 +17152,7 @@
     </row>
     <row r="277" spans="1:8">
       <c r="A277">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="B277" s="1">
         <v>115</v>
@@ -17175,7 +17175,7 @@
     </row>
     <row r="278" spans="1:8">
       <c r="A278">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="B278" s="1">
         <v>115</v>
@@ -17198,7 +17198,7 @@
     </row>
     <row r="279" spans="1:8">
       <c r="A279">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="B279" s="1">
         <v>115</v>
@@ -17221,7 +17221,7 @@
     </row>
     <row r="280" spans="1:8">
       <c r="A280">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="B280" s="1">
         <v>115</v>
@@ -17244,7 +17244,7 @@
     </row>
     <row r="281" spans="1:8">
       <c r="A281">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="B281" s="1">
         <v>115</v>
@@ -17267,7 +17267,7 @@
     </row>
     <row r="282" spans="1:8" ht="17.25">
       <c r="A282">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="B282" s="1">
         <v>115</v>
@@ -17290,7 +17290,7 @@
     </row>
     <row r="283" spans="1:8">
       <c r="A283">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="B283" s="1">
         <v>115</v>
@@ -17313,7 +17313,7 @@
     </row>
     <row r="284" spans="1:8">
       <c r="A284">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="B284" s="1">
         <v>115</v>
@@ -17336,7 +17336,7 @@
     </row>
     <row r="285" spans="1:8">
       <c r="A285">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="B285" s="1">
         <v>115</v>
@@ -17359,7 +17359,7 @@
     </row>
     <row r="286" spans="1:8">
       <c r="A286">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="B286" s="1">
         <v>115</v>
@@ -17382,7 +17382,7 @@
     </row>
     <row r="287" spans="1:8">
       <c r="A287">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="B287" s="1">
         <v>115</v>
@@ -17408,7 +17408,7 @@
     </row>
     <row r="288" spans="1:8">
       <c r="A288">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="B288" s="1">
         <v>115</v>
@@ -17431,7 +17431,7 @@
     </row>
     <row r="289" spans="1:8">
       <c r="A289">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="B289" s="1">
         <v>115</v>
@@ -17454,7 +17454,7 @@
     </row>
     <row r="290" spans="1:8" ht="17.25">
       <c r="A290">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="B290" s="1">
         <v>115</v>
@@ -17477,7 +17477,7 @@
     </row>
     <row r="291" spans="1:8">
       <c r="A291">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="B291" s="1">
         <v>115</v>
@@ -17503,7 +17503,7 @@
     </row>
     <row r="292" spans="1:8">
       <c r="A292">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="B292" s="1">
         <v>115</v>
@@ -17529,7 +17529,7 @@
     </row>
     <row r="293" spans="1:8">
       <c r="A293">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="B293" s="1">
         <v>115</v>
@@ -17555,7 +17555,7 @@
     </row>
     <row r="294" spans="1:8">
       <c r="A294">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="B294" s="1">
         <v>115</v>
@@ -17581,7 +17581,7 @@
     </row>
     <row r="295" spans="1:8">
       <c r="A295">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="B295" s="1">
         <v>115</v>
@@ -17607,7 +17607,7 @@
     </row>
     <row r="296" spans="1:8">
       <c r="A296">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="B296" s="1">
         <v>115</v>
@@ -17633,7 +17633,7 @@
     </row>
     <row r="297" spans="1:8">
       <c r="A297">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="B297" s="1">
         <v>115</v>
@@ -17659,7 +17659,7 @@
     </row>
     <row r="298" spans="1:8">
       <c r="A298">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="B298" s="1">
         <v>115</v>
@@ -17682,7 +17682,7 @@
     </row>
     <row r="299" spans="1:8">
       <c r="A299">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="B299" s="1">
         <v>115</v>
@@ -17702,7 +17702,7 @@
     </row>
     <row r="300" spans="1:8">
       <c r="A300">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="B300" s="1">
         <v>115</v>
@@ -17725,7 +17725,7 @@
     </row>
     <row r="301" spans="1:8">
       <c r="A301">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="B301" s="1">
         <v>115</v>
@@ -17748,7 +17748,7 @@
     </row>
     <row r="302" spans="1:8">
       <c r="A302">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="B302" s="1">
         <v>115</v>
@@ -17771,7 +17771,7 @@
     </row>
     <row r="303" spans="1:8" ht="17.25">
       <c r="A303">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="B303" s="1">
         <v>115</v>
@@ -17794,7 +17794,7 @@
     </row>
     <row r="304" spans="1:8">
       <c r="A304">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="B304" s="1">
         <v>115</v>
@@ -17817,7 +17817,7 @@
     </row>
     <row r="305" spans="1:8">
       <c r="A305">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="B305" s="1">
         <v>115</v>
@@ -17840,7 +17840,7 @@
     </row>
     <row r="306" spans="1:8">
       <c r="A306">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="B306" s="1">
         <v>115</v>
@@ -17860,9 +17860,9 @@
     </row>
     <row r="307" spans="1:8">
       <c r="A307">
-        <v>385</v>
-      </c>
-      <c r="B307">
+        <v>306</v>
+      </c>
+      <c r="B307" s="1">
         <v>115</v>
       </c>
       <c r="C307" t="s">
@@ -17886,9 +17886,9 @@
     </row>
     <row r="308" spans="1:8">
       <c r="A308">
-        <v>400</v>
-      </c>
-      <c r="B308">
+        <v>307</v>
+      </c>
+      <c r="B308" s="1">
         <v>115</v>
       </c>
       <c r="C308" t="s">
@@ -17912,7 +17912,7 @@
     </row>
     <row r="309" spans="1:8">
       <c r="A309">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="B309" s="1">
         <v>115</v>
@@ -17935,7 +17935,7 @@
     </row>
     <row r="310" spans="1:8">
       <c r="A310">
-        <v>283</v>
+        <v>309</v>
       </c>
       <c r="B310" s="1">
         <v>115</v>
@@ -17958,7 +17958,7 @@
     </row>
     <row r="311" spans="1:8">
       <c r="A311">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="B311" s="1">
         <v>115</v>
@@ -17981,7 +17981,7 @@
     </row>
     <row r="312" spans="1:8">
       <c r="A312">
-        <v>285</v>
+        <v>311</v>
       </c>
       <c r="B312" s="1">
         <v>115</v>
@@ -18004,7 +18004,7 @@
     </row>
     <row r="313" spans="1:8">
       <c r="A313">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="B313" s="1">
         <v>115</v>
@@ -18027,7 +18027,7 @@
     </row>
     <row r="314" spans="1:8">
       <c r="A314">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="B314" s="1">
         <v>115</v>
@@ -18050,7 +18050,7 @@
     </row>
     <row r="315" spans="1:8">
       <c r="A315">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="B315" s="1">
         <v>115</v>
@@ -18073,7 +18073,7 @@
     </row>
     <row r="316" spans="1:8">
       <c r="A316">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="B316" s="1">
         <v>115</v>
@@ -18096,7 +18096,7 @@
     </row>
     <row r="317" spans="1:8">
       <c r="A317">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="B317" s="1">
         <v>115</v>
@@ -18119,7 +18119,7 @@
     </row>
     <row r="318" spans="1:8">
       <c r="A318">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="B318" s="1">
         <v>115</v>
@@ -18145,7 +18145,7 @@
     </row>
     <row r="319" spans="1:8">
       <c r="A319">
-        <v>292</v>
+        <v>318</v>
       </c>
       <c r="B319" s="1">
         <v>115</v>
@@ -18171,7 +18171,7 @@
     </row>
     <row r="320" spans="1:8">
       <c r="A320">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="B320" s="1">
         <v>115</v>
@@ -18197,7 +18197,7 @@
     </row>
     <row r="321" spans="1:8">
       <c r="A321">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="B321" s="1">
         <v>115</v>
@@ -18223,7 +18223,7 @@
     </row>
     <row r="322" spans="1:8">
       <c r="A322">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="B322" s="1">
         <v>115</v>
@@ -18249,7 +18249,7 @@
     </row>
     <row r="323" spans="1:8">
       <c r="A323">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="B323" s="1">
         <v>115</v>
@@ -18272,7 +18272,7 @@
     </row>
     <row r="324" spans="1:8">
       <c r="A324">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="B324" s="1">
         <v>115</v>
@@ -18295,7 +18295,7 @@
     </row>
     <row r="325" spans="1:8">
       <c r="A325">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="B325" s="1">
         <v>115</v>
@@ -18321,7 +18321,7 @@
     </row>
     <row r="326" spans="1:8">
       <c r="A326">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="B326" s="1">
         <v>115</v>
@@ -18347,7 +18347,7 @@
     </row>
     <row r="327" spans="1:8">
       <c r="A327">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="B327" s="1">
         <v>115</v>
@@ -18370,7 +18370,7 @@
     </row>
     <row r="328" spans="1:8">
       <c r="A328">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="B328" s="1">
         <v>115</v>
@@ -18393,7 +18393,7 @@
     </row>
     <row r="329" spans="1:8">
       <c r="A329">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="B329" s="1">
         <v>115</v>
@@ -18416,7 +18416,7 @@
     </row>
     <row r="330" spans="1:8">
       <c r="A330">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="B330" s="1">
         <v>115</v>
@@ -18439,7 +18439,7 @@
     </row>
     <row r="331" spans="1:8">
       <c r="A331">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="B331" s="1">
         <v>115</v>
@@ -18462,7 +18462,7 @@
     </row>
     <row r="332" spans="1:8">
       <c r="A332">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="B332" s="1">
         <v>115</v>
@@ -18485,7 +18485,7 @@
     </row>
     <row r="333" spans="1:8">
       <c r="A333">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="B333" s="1">
         <v>115</v>
@@ -18508,7 +18508,7 @@
     </row>
     <row r="334" spans="1:8">
       <c r="A334">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="B334" s="1">
         <v>115</v>
@@ -18531,7 +18531,7 @@
     </row>
     <row r="335" spans="1:8">
       <c r="A335">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="B335" s="1">
         <v>115</v>
@@ -18554,7 +18554,7 @@
     </row>
     <row r="336" spans="1:8">
       <c r="A336">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="B336" s="1">
         <v>115</v>
@@ -18577,7 +18577,7 @@
     </row>
     <row r="337" spans="1:8">
       <c r="A337">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="B337" s="1">
         <v>115</v>
@@ -18600,9 +18600,9 @@
     </row>
     <row r="338" spans="1:8">
       <c r="A338">
-        <v>311</v>
-      </c>
-      <c r="B338">
+        <v>337</v>
+      </c>
+      <c r="B338" s="1">
         <v>115</v>
       </c>
       <c r="C338" t="s">
@@ -18623,9 +18623,9 @@
     </row>
     <row r="339" spans="1:8">
       <c r="A339">
-        <v>312</v>
-      </c>
-      <c r="B339">
+        <v>338</v>
+      </c>
+      <c r="B339" s="1">
         <v>115</v>
       </c>
       <c r="C339" t="s">
@@ -18646,9 +18646,9 @@
     </row>
     <row r="340" spans="1:8" ht="17.25">
       <c r="A340">
-        <v>313</v>
-      </c>
-      <c r="B340">
+        <v>339</v>
+      </c>
+      <c r="B340" s="1">
         <v>115</v>
       </c>
       <c r="C340" s="1" t="s">
@@ -18669,9 +18669,9 @@
     </row>
     <row r="341" spans="1:8">
       <c r="A341">
-        <v>314</v>
-      </c>
-      <c r="B341">
+        <v>340</v>
+      </c>
+      <c r="B341" s="1">
         <v>115</v>
       </c>
       <c r="C341" t="s">
@@ -18692,9 +18692,9 @@
     </row>
     <row r="342" spans="1:8">
       <c r="A342">
-        <v>315</v>
-      </c>
-      <c r="B342">
+        <v>341</v>
+      </c>
+      <c r="B342" s="1">
         <v>115</v>
       </c>
       <c r="C342" t="s">
@@ -18715,9 +18715,9 @@
     </row>
     <row r="343" spans="1:8" ht="17.25">
       <c r="A343">
-        <v>316</v>
-      </c>
-      <c r="B343">
+        <v>342</v>
+      </c>
+      <c r="B343" s="1">
         <v>115</v>
       </c>
       <c r="C343" s="1" t="s">
@@ -18738,9 +18738,9 @@
     </row>
     <row r="344" spans="1:8">
       <c r="A344">
-        <v>317</v>
-      </c>
-      <c r="B344">
+        <v>343</v>
+      </c>
+      <c r="B344" s="1">
         <v>115</v>
       </c>
       <c r="C344" t="s">
@@ -18761,9 +18761,9 @@
     </row>
     <row r="345" spans="1:8">
       <c r="A345">
-        <v>318</v>
-      </c>
-      <c r="B345">
+        <v>344</v>
+      </c>
+      <c r="B345" s="1">
         <v>115</v>
       </c>
       <c r="C345" t="s">
@@ -18784,9 +18784,9 @@
     </row>
     <row r="346" spans="1:8">
       <c r="A346">
-        <v>319</v>
-      </c>
-      <c r="B346">
+        <v>345</v>
+      </c>
+      <c r="B346" s="1">
         <v>115</v>
       </c>
       <c r="C346" t="s">
@@ -18807,9 +18807,9 @@
     </row>
     <row r="347" spans="1:8">
       <c r="A347">
-        <v>320</v>
-      </c>
-      <c r="B347">
+        <v>346</v>
+      </c>
+      <c r="B347" s="1">
         <v>115</v>
       </c>
       <c r="C347" s="13" t="s">
@@ -18830,9 +18830,9 @@
     </row>
     <row r="348" spans="1:8">
       <c r="A348">
-        <v>321</v>
-      </c>
-      <c r="B348">
+        <v>347</v>
+      </c>
+      <c r="B348" s="1">
         <v>115</v>
       </c>
       <c r="C348" t="s">
@@ -18853,9 +18853,9 @@
     </row>
     <row r="349" spans="1:8">
       <c r="A349">
-        <v>322</v>
-      </c>
-      <c r="B349">
+        <v>348</v>
+      </c>
+      <c r="B349" s="1">
         <v>115</v>
       </c>
       <c r="C349" s="1" t="s">
@@ -18876,9 +18876,9 @@
     </row>
     <row r="350" spans="1:8">
       <c r="A350">
-        <v>323</v>
-      </c>
-      <c r="B350">
+        <v>349</v>
+      </c>
+      <c r="B350" s="1">
         <v>115</v>
       </c>
       <c r="C350" t="s">
@@ -18902,9 +18902,9 @@
     </row>
     <row r="351" spans="1:8">
       <c r="A351">
-        <v>324</v>
-      </c>
-      <c r="B351">
+        <v>350</v>
+      </c>
+      <c r="B351" s="1">
         <v>115</v>
       </c>
       <c r="C351" t="s">
@@ -18928,9 +18928,9 @@
     </row>
     <row r="352" spans="1:8">
       <c r="A352">
-        <v>325</v>
-      </c>
-      <c r="B352">
+        <v>351</v>
+      </c>
+      <c r="B352" s="1">
         <v>115</v>
       </c>
       <c r="C352" t="s">
@@ -18954,9 +18954,9 @@
     </row>
     <row r="353" spans="1:8">
       <c r="A353">
-        <v>326</v>
-      </c>
-      <c r="B353">
+        <v>352</v>
+      </c>
+      <c r="B353" s="1">
         <v>115</v>
       </c>
       <c r="C353" t="s">
@@ -18980,9 +18980,9 @@
     </row>
     <row r="354" spans="1:8">
       <c r="A354">
-        <v>327</v>
-      </c>
-      <c r="B354">
+        <v>353</v>
+      </c>
+      <c r="B354" s="1">
         <v>115</v>
       </c>
       <c r="C354" t="s">
@@ -19003,9 +19003,9 @@
     </row>
     <row r="355" spans="1:8">
       <c r="A355">
-        <v>328</v>
-      </c>
-      <c r="B355">
+        <v>354</v>
+      </c>
+      <c r="B355" s="1">
         <v>115</v>
       </c>
       <c r="C355" t="s">
@@ -19026,9 +19026,9 @@
     </row>
     <row r="356" spans="1:8">
       <c r="A356">
-        <v>329</v>
-      </c>
-      <c r="B356">
+        <v>355</v>
+      </c>
+      <c r="B356" s="1">
         <v>115</v>
       </c>
       <c r="C356" s="13" t="s">
@@ -19049,9 +19049,9 @@
     </row>
     <row r="357" spans="1:8">
       <c r="A357">
-        <v>330</v>
-      </c>
-      <c r="B357">
+        <v>356</v>
+      </c>
+      <c r="B357" s="1">
         <v>115</v>
       </c>
       <c r="C357" s="10" t="s">
@@ -19069,9 +19069,9 @@
     </row>
     <row r="358" spans="1:8">
       <c r="A358">
-        <v>331</v>
-      </c>
-      <c r="B358">
+        <v>357</v>
+      </c>
+      <c r="B358" s="1">
         <v>115</v>
       </c>
       <c r="C358" t="s">
@@ -19092,9 +19092,9 @@
     </row>
     <row r="359" spans="1:8">
       <c r="A359">
-        <v>332</v>
-      </c>
-      <c r="B359">
+        <v>358</v>
+      </c>
+      <c r="B359" s="1">
         <v>115</v>
       </c>
       <c r="C359" t="s">
@@ -19118,9 +19118,9 @@
     </row>
     <row r="360" spans="1:8">
       <c r="A360">
-        <v>333</v>
-      </c>
-      <c r="B360">
+        <v>359</v>
+      </c>
+      <c r="B360" s="1">
         <v>115</v>
       </c>
       <c r="C360" t="s">
@@ -19144,9 +19144,9 @@
     </row>
     <row r="361" spans="1:8">
       <c r="A361">
-        <v>334</v>
-      </c>
-      <c r="B361">
+        <v>360</v>
+      </c>
+      <c r="B361" s="1">
         <v>115</v>
       </c>
       <c r="C361" t="s">
@@ -19167,9 +19167,9 @@
     </row>
     <row r="362" spans="1:8">
       <c r="A362">
-        <v>335</v>
-      </c>
-      <c r="B362">
+        <v>361</v>
+      </c>
+      <c r="B362" s="1">
         <v>115</v>
       </c>
       <c r="C362" t="s">
@@ -19190,9 +19190,9 @@
     </row>
     <row r="363" spans="1:8">
       <c r="A363">
-        <v>336</v>
-      </c>
-      <c r="B363">
+        <v>362</v>
+      </c>
+      <c r="B363" s="1">
         <v>115</v>
       </c>
       <c r="C363" s="1" t="s">
@@ -19213,9 +19213,9 @@
     </row>
     <row r="364" spans="1:8">
       <c r="A364">
-        <v>337</v>
-      </c>
-      <c r="B364">
+        <v>363</v>
+      </c>
+      <c r="B364" s="1">
         <v>115</v>
       </c>
       <c r="C364" t="s">
@@ -19239,9 +19239,9 @@
     </row>
     <row r="365" spans="1:8">
       <c r="A365">
-        <v>338</v>
-      </c>
-      <c r="B365">
+        <v>364</v>
+      </c>
+      <c r="B365" s="1">
         <v>115</v>
       </c>
       <c r="C365" t="s">
@@ -19265,9 +19265,9 @@
     </row>
     <row r="366" spans="1:8">
       <c r="A366">
-        <v>339</v>
-      </c>
-      <c r="B366">
+        <v>365</v>
+      </c>
+      <c r="B366" s="1">
         <v>115</v>
       </c>
       <c r="C366" t="s">
@@ -19288,9 +19288,9 @@
     </row>
     <row r="367" spans="1:8">
       <c r="A367">
-        <v>340</v>
-      </c>
-      <c r="B367">
+        <v>366</v>
+      </c>
+      <c r="B367" s="1">
         <v>115</v>
       </c>
       <c r="C367" s="1" t="s">
@@ -19311,9 +19311,9 @@
     </row>
     <row r="368" spans="1:8">
       <c r="A368">
-        <v>341</v>
-      </c>
-      <c r="B368">
+        <v>367</v>
+      </c>
+      <c r="B368" s="1">
         <v>115</v>
       </c>
       <c r="C368" s="1" t="s">
@@ -19334,9 +19334,9 @@
     </row>
     <row r="369" spans="1:8">
       <c r="A369">
-        <v>342</v>
-      </c>
-      <c r="B369">
+        <v>368</v>
+      </c>
+      <c r="B369" s="1">
         <v>115</v>
       </c>
       <c r="C369" t="s">
@@ -19357,9 +19357,9 @@
     </row>
     <row r="370" spans="1:8">
       <c r="A370">
-        <v>343</v>
-      </c>
-      <c r="B370">
+        <v>369</v>
+      </c>
+      <c r="B370" s="1">
         <v>115</v>
       </c>
       <c r="C370" t="s">
@@ -19383,9 +19383,9 @@
     </row>
     <row r="371" spans="1:8">
       <c r="A371">
-        <v>344</v>
-      </c>
-      <c r="B371">
+        <v>370</v>
+      </c>
+      <c r="B371" s="1">
         <v>115</v>
       </c>
       <c r="C371" t="s">
@@ -19409,9 +19409,9 @@
     </row>
     <row r="372" spans="1:8">
       <c r="A372">
-        <v>345</v>
-      </c>
-      <c r="B372">
+        <v>371</v>
+      </c>
+      <c r="B372" s="1">
         <v>115</v>
       </c>
       <c r="C372" t="s">
@@ -19435,9 +19435,9 @@
     </row>
     <row r="373" spans="1:8">
       <c r="A373">
-        <v>346</v>
-      </c>
-      <c r="B373">
+        <v>372</v>
+      </c>
+      <c r="B373" s="1">
         <v>115</v>
       </c>
       <c r="C373" t="s">
@@ -19461,9 +19461,9 @@
     </row>
     <row r="374" spans="1:8">
       <c r="A374">
-        <v>347</v>
-      </c>
-      <c r="B374">
+        <v>373</v>
+      </c>
+      <c r="B374" s="1">
         <v>115</v>
       </c>
       <c r="C374" s="1" t="s">
@@ -19484,9 +19484,9 @@
     </row>
     <row r="375" spans="1:8">
       <c r="A375">
-        <v>348</v>
-      </c>
-      <c r="B375">
+        <v>374</v>
+      </c>
+      <c r="B375" s="1">
         <v>115</v>
       </c>
       <c r="C375" t="s">
@@ -19507,9 +19507,9 @@
     </row>
     <row r="376" spans="1:8">
       <c r="A376">
-        <v>349</v>
-      </c>
-      <c r="B376">
+        <v>375</v>
+      </c>
+      <c r="B376" s="1">
         <v>115</v>
       </c>
       <c r="C376" t="s">
@@ -19530,9 +19530,9 @@
     </row>
     <row r="377" spans="1:8">
       <c r="A377">
-        <v>350</v>
-      </c>
-      <c r="B377">
+        <v>376</v>
+      </c>
+      <c r="B377" s="1">
         <v>115</v>
       </c>
       <c r="C377" s="1" t="s">
@@ -19553,9 +19553,9 @@
     </row>
     <row r="378" spans="1:8">
       <c r="A378">
-        <v>351</v>
-      </c>
-      <c r="B378">
+        <v>377</v>
+      </c>
+      <c r="B378" s="1">
         <v>115</v>
       </c>
       <c r="C378" t="s">
@@ -19576,9 +19576,9 @@
     </row>
     <row r="379" spans="1:8">
       <c r="A379">
-        <v>352</v>
-      </c>
-      <c r="B379">
+        <v>378</v>
+      </c>
+      <c r="B379" s="1">
         <v>115</v>
       </c>
       <c r="C379" t="s">
@@ -19599,9 +19599,9 @@
     </row>
     <row r="380" spans="1:8">
       <c r="A380">
-        <v>381</v>
-      </c>
-      <c r="B380">
+        <v>379</v>
+      </c>
+      <c r="B380" s="1">
         <v>115</v>
       </c>
       <c r="C380" t="s">
@@ -19625,9 +19625,9 @@
     </row>
     <row r="381" spans="1:8">
       <c r="A381">
-        <v>382</v>
-      </c>
-      <c r="B381">
+        <v>380</v>
+      </c>
+      <c r="B381" s="1">
         <v>115</v>
       </c>
       <c r="C381" t="s">
@@ -19651,9 +19651,9 @@
     </row>
     <row r="382" spans="1:8">
       <c r="A382">
-        <v>396</v>
-      </c>
-      <c r="B382">
+        <v>381</v>
+      </c>
+      <c r="B382" s="1">
         <v>115</v>
       </c>
       <c r="C382" t="s">
@@ -19677,9 +19677,9 @@
     </row>
     <row r="383" spans="1:8">
       <c r="A383">
-        <v>397</v>
-      </c>
-      <c r="B383">
+        <v>382</v>
+      </c>
+      <c r="B383" s="1">
         <v>115</v>
       </c>
       <c r="C383" t="s">
@@ -19703,9 +19703,9 @@
     </row>
     <row r="384" spans="1:8">
       <c r="A384">
-        <v>353</v>
-      </c>
-      <c r="B384">
+        <v>383</v>
+      </c>
+      <c r="B384" s="1">
         <v>115</v>
       </c>
       <c r="C384" s="1" t="s">
@@ -19726,9 +19726,9 @@
     </row>
     <row r="385" spans="1:8">
       <c r="A385">
-        <v>354</v>
-      </c>
-      <c r="B385">
+        <v>384</v>
+      </c>
+      <c r="B385" s="1">
         <v>115</v>
       </c>
       <c r="C385" t="s">
@@ -19749,9 +19749,9 @@
     </row>
     <row r="386" spans="1:8">
       <c r="A386">
-        <v>355</v>
-      </c>
-      <c r="B386">
+        <v>385</v>
+      </c>
+      <c r="B386" s="1">
         <v>115</v>
       </c>
       <c r="C386" t="s">
@@ -19772,9 +19772,9 @@
     </row>
     <row r="387" spans="1:8">
       <c r="A387">
-        <v>356</v>
-      </c>
-      <c r="B387">
+        <v>386</v>
+      </c>
+      <c r="B387" s="1">
         <v>115</v>
       </c>
       <c r="C387" t="s">
@@ -19798,9 +19798,9 @@
     </row>
     <row r="388" spans="1:8">
       <c r="A388">
-        <v>357</v>
-      </c>
-      <c r="B388">
+        <v>387</v>
+      </c>
+      <c r="B388" s="1">
         <v>115</v>
       </c>
       <c r="C388" t="s">
@@ -19821,9 +19821,9 @@
     </row>
     <row r="389" spans="1:8">
       <c r="A389">
-        <v>358</v>
-      </c>
-      <c r="B389">
+        <v>388</v>
+      </c>
+      <c r="B389" s="1">
         <v>115</v>
       </c>
       <c r="C389" s="13" t="s">
@@ -19844,9 +19844,9 @@
     </row>
     <row r="390" spans="1:8">
       <c r="A390">
-        <v>359</v>
-      </c>
-      <c r="B390">
+        <v>389</v>
+      </c>
+      <c r="B390" s="1">
         <v>115</v>
       </c>
       <c r="C390" s="13" t="s">
@@ -19867,9 +19867,9 @@
     </row>
     <row r="391" spans="1:8">
       <c r="A391">
-        <v>360</v>
-      </c>
-      <c r="B391">
+        <v>390</v>
+      </c>
+      <c r="B391" s="1">
         <v>115</v>
       </c>
       <c r="C391" t="s">
@@ -19890,9 +19890,9 @@
     </row>
     <row r="392" spans="1:8">
       <c r="A392">
-        <v>361</v>
-      </c>
-      <c r="B392">
+        <v>391</v>
+      </c>
+      <c r="B392" s="1">
         <v>115</v>
       </c>
       <c r="C392" s="13" t="s">
@@ -19913,9 +19913,9 @@
     </row>
     <row r="393" spans="1:8">
       <c r="A393">
-        <v>362</v>
-      </c>
-      <c r="B393">
+        <v>392</v>
+      </c>
+      <c r="B393" s="1">
         <v>115</v>
       </c>
       <c r="C393" s="1" t="s">
@@ -19936,9 +19936,9 @@
     </row>
     <row r="394" spans="1:8">
       <c r="A394">
-        <v>363</v>
-      </c>
-      <c r="B394">
+        <v>393</v>
+      </c>
+      <c r="B394" s="1">
         <v>115</v>
       </c>
       <c r="C394" t="s">
@@ -19959,9 +19959,9 @@
     </row>
     <row r="395" spans="1:8">
       <c r="A395">
-        <v>364</v>
-      </c>
-      <c r="B395">
+        <v>394</v>
+      </c>
+      <c r="B395" s="1">
         <v>115</v>
       </c>
       <c r="C395" t="s">
@@ -19985,9 +19985,9 @@
     </row>
     <row r="396" spans="1:8">
       <c r="A396">
-        <v>365</v>
-      </c>
-      <c r="B396">
+        <v>395</v>
+      </c>
+      <c r="B396" s="1">
         <v>115</v>
       </c>
       <c r="C396" t="s">
@@ -20011,9 +20011,9 @@
     </row>
     <row r="397" spans="1:8">
       <c r="A397">
-        <v>366</v>
-      </c>
-      <c r="B397">
+        <v>396</v>
+      </c>
+      <c r="B397" s="1">
         <v>115</v>
       </c>
       <c r="C397" t="s">
@@ -20034,9 +20034,9 @@
     </row>
     <row r="398" spans="1:8">
       <c r="A398">
-        <v>367</v>
-      </c>
-      <c r="B398">
+        <v>397</v>
+      </c>
+      <c r="B398" s="1">
         <v>115</v>
       </c>
       <c r="C398" t="s">
@@ -20057,9 +20057,9 @@
     </row>
     <row r="399" spans="1:8">
       <c r="A399">
-        <v>368</v>
-      </c>
-      <c r="B399">
+        <v>398</v>
+      </c>
+      <c r="B399" s="1">
         <v>115</v>
       </c>
       <c r="C399" t="s">
@@ -20080,9 +20080,9 @@
     </row>
     <row r="400" spans="1:8">
       <c r="A400">
-        <v>369</v>
-      </c>
-      <c r="B400">
+        <v>399</v>
+      </c>
+      <c r="B400" s="1">
         <v>115</v>
       </c>
       <c r="C400" s="1" t="s">
@@ -20103,9 +20103,9 @@
     </row>
     <row r="401" spans="1:8" ht="17.25">
       <c r="A401">
-        <v>370</v>
-      </c>
-      <c r="B401">
+        <v>400</v>
+      </c>
+      <c r="B401" s="1">
         <v>115</v>
       </c>
       <c r="C401" s="1" t="s">
@@ -20126,9 +20126,9 @@
     </row>
     <row r="402" spans="1:8">
       <c r="A402">
-        <v>371</v>
-      </c>
-      <c r="B402">
+        <v>401</v>
+      </c>
+      <c r="B402" s="1">
         <v>115</v>
       </c>
       <c r="C402" s="1" t="s">
@@ -20149,9 +20149,9 @@
     </row>
     <row r="403" spans="1:8">
       <c r="A403">
-        <v>372</v>
-      </c>
-      <c r="B403">
+        <v>402</v>
+      </c>
+      <c r="B403" s="1">
         <v>115</v>
       </c>
       <c r="C403" t="s">
@@ -20172,9 +20172,9 @@
     </row>
     <row r="404" spans="1:8">
       <c r="A404">
-        <v>373</v>
-      </c>
-      <c r="B404">
+        <v>403</v>
+      </c>
+      <c r="B404" s="1">
         <v>115</v>
       </c>
       <c r="C404" t="s">
@@ -20198,9 +20198,9 @@
     </row>
     <row r="405" spans="1:8">
       <c r="A405">
-        <v>374</v>
-      </c>
-      <c r="B405">
+        <v>404</v>
+      </c>
+      <c r="B405" s="1">
         <v>115</v>
       </c>
       <c r="C405" s="1" t="s">
@@ -20221,9 +20221,9 @@
     </row>
     <row r="406" spans="1:8">
       <c r="A406">
-        <v>375</v>
-      </c>
-      <c r="B406">
+        <v>405</v>
+      </c>
+      <c r="B406" s="1">
         <v>115</v>
       </c>
       <c r="C406" t="s">
@@ -20244,9 +20244,9 @@
     </row>
     <row r="407" spans="1:8">
       <c r="A407">
-        <v>376</v>
-      </c>
-      <c r="B407">
+        <v>406</v>
+      </c>
+      <c r="B407" s="1">
         <v>115</v>
       </c>
       <c r="C407" t="s">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F723A3BB-DA8A-4371-96FD-BE13D5FA7DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F842D7-7443-4934-A39C-EB4D8BA0F9C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料表!$A$1:$H$312</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料表!$A$1:$H$407</definedName>
     <definedName name="Barcode">OFFSET(#REF!,MATCH(#REF!,#REF!,0)-1,0)</definedName>
     <definedName name="重大活動行事曆">[1]重要活動行事曆!$C$2:$I$467</definedName>
     <definedName name="資料">#REF!</definedName>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="255">
   <si>
     <t>序號</t>
   </si>
@@ -427,51 +427,6 @@
   </si>
   <si>
     <t>陳秀玲</t>
-  </si>
-  <si>
-    <t>新加坡/Effects of Generative AI Virtual Humans on Nursing Students Communication Skills, Self-Directed Learning, and Self-Efficacy: A Quasi-Experimental Study</t>
-  </si>
-  <si>
-    <t>加拿大/Effectiveness of a nursing simulation course in promoting preoperative care skills</t>
-  </si>
-  <si>
-    <t>新加坡/Stroke Symptom Recognition and Anticipated Coping Behaviors Among Senior Five-Year Nursing Students</t>
-  </si>
-  <si>
-    <t>新加坡/Adolescent Sexual Risk Control and Sexual Health Self-Care: A Mediation Model</t>
-  </si>
-  <si>
-    <t>韓國/Home and school contexts as mechanisms and buffers of socioeconomic gaps in executive function</t>
-  </si>
-  <si>
-    <t>Canada/Mastery Learning Using Past Exam Questions to Enhance Achievement and Self-Directed Learning</t>
-  </si>
-  <si>
-    <t>日本/Developing a Multicultural Story Corner to Foster Cultural Awareness in Early Childhood Education</t>
-  </si>
-  <si>
-    <t>新加坡/Exploring the Learning Effectiveness of Applying NotebookLM in a Nursing Professional Issues Seminar</t>
-  </si>
-  <si>
-    <t>日本/An Analysis of Criminal Disputes in Funeral and Burial Administration through Case Law: A Study of High Court Judgments</t>
-  </si>
-  <si>
-    <t>Austria/Integrating Gamification and Micro-Flipped Teaching into End-of-Life Care Nursing Education</t>
-  </si>
-  <si>
-    <t>奧地利/Embracing the Inner Child: Generative AI–Enabled Visualization and Scenario Simulation for Enhancing Affective Learning in Nursing Human Development</t>
-  </si>
-  <si>
-    <t>Singapore/The mediating role of teacher-child interaction in the association between parent-teacher relationship and preschoolers&amp;#039; executive function</t>
-  </si>
-  <si>
-    <t>日本/Self-Perceived Health Status and Health Behaviors Among Junior Nursing College Students</t>
-  </si>
-  <si>
-    <t>印尼/A Study of Nurses’ Experiences Caring for End-of-Life Residents in Nursing Homes</t>
-  </si>
-  <si>
-    <t>印尼/Enhancing Medical Terminology Instruction through the Use of H5P  Digital Learning Tools</t>
   </si>
   <si>
     <t>中華民國/AI-Supported Wound Care Decision Support for HomeBased and Long-Term Care Services</t>
@@ -1247,6 +1202,45 @@
   </si>
   <si>
     <t>日本/2026 10th International Conference on Education and E-Learning</t>
+  </si>
+  <si>
+    <t>日本/The third UTokyo Nursing International Conference (UTNIC 2026)</t>
+  </si>
+  <si>
+    <t>新加坡/The 29th EAFONS 2026</t>
+  </si>
+  <si>
+    <t>新加坡/29th East Asian Forum of Nursing Scholars (EAFONS) 2026</t>
+  </si>
+  <si>
+    <t>新加坡/EAFONS 2026</t>
+  </si>
+  <si>
+    <t>Canada/2026 Sigma 37th International Nursing Research Congress, 16-18 July in Toronto.</t>
+  </si>
+  <si>
+    <t>日本/The 16th Asian Conference on Cultural Studies</t>
+  </si>
+  <si>
+    <t>奧地利/The AMEE Conference 2026  (An International Association for Health Professions Education, AMEE )</t>
+  </si>
+  <si>
+    <t>日本/International Symposium on Education, Psychology and Social Sciences (8th ISEPSS)</t>
+  </si>
+  <si>
+    <t>加拿大/2026 Sigma 37th International Nursing Research Congress</t>
+  </si>
+  <si>
+    <t>Austria/The AMEE Conference 2026  (An International Association for Health Professions Education, AMEE ) Conference on / Vienna, Austria</t>
+  </si>
+  <si>
+    <t>Singapore/Pacific Early Childhood Education Research Association (PECERA) Annual Conference 2026</t>
+  </si>
+  <si>
+    <t>韓國/ISSBD (International Society for the Study of Behavioural Development) 雙年會</t>
+  </si>
+  <si>
+    <t>印尼/ASIA PACIFIC INTENSIVE CARE SYMPOSIUM (APICS) 2026</t>
   </si>
 </sst>
 </file>
@@ -10560,19 +10554,19 @@
         <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F2" s="11">
         <v>3500</v>
       </c>
       <c r="G2" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -10583,19 +10577,19 @@
         <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F3" s="11">
         <v>3500</v>
       </c>
       <c r="G3" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -10606,19 +10600,19 @@
         <v>115</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F4" s="14">
         <v>3000</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -10629,19 +10623,19 @@
         <v>115</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>86</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F5" s="11">
         <v>5100</v>
       </c>
       <c r="G5" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -10652,19 +10646,19 @@
         <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F6" s="11">
         <v>3500</v>
       </c>
       <c r="G6" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -10681,16 +10675,16 @@
         <v>23</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F7" s="2">
         <v>29000</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H7" t="s">
-        <v>112</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -10707,16 +10701,16 @@
         <v>23</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F8" s="2">
         <v>2000</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H8" t="s">
-        <v>112</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -10733,13 +10727,13 @@
         <v>23</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F9" s="11">
         <v>5000</v>
       </c>
       <c r="G9" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -10779,13 +10773,13 @@
         <v>23</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F11" s="11">
         <v>3500</v>
       </c>
       <c r="G11" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -10848,13 +10842,13 @@
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F14" s="11">
         <v>3700</v>
       </c>
       <c r="G14" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -10917,13 +10911,13 @@
         <v>13</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F17" s="11">
         <v>500</v>
       </c>
       <c r="G17" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -10940,16 +10934,16 @@
         <v>13</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F18">
         <v>9000</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H18" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -10966,16 +10960,16 @@
         <v>13</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F19">
         <v>15000</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H19" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -10992,16 +10986,16 @@
         <v>13</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F20">
         <v>10000</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H20" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -11018,16 +11012,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F21">
         <v>6000</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H21" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -11044,16 +11038,16 @@
         <v>13</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F22">
         <v>10000</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H22" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -11070,16 +11064,16 @@
         <v>23</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F23" s="2">
         <v>29636</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H23" t="s">
-        <v>103</v>
+        <v>243</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -11096,16 +11090,16 @@
         <v>23</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F24" s="2">
         <v>11068</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H24" t="s">
-        <v>103</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -11122,13 +11116,13 @@
         <v>23</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F25" s="11">
         <v>3900</v>
       </c>
       <c r="G25" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -11145,13 +11139,13 @@
         <v>23</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F26" s="14">
         <v>4800</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -11168,13 +11162,13 @@
         <v>23</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F27" s="14">
         <v>3166</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -11191,16 +11185,16 @@
         <v>23</v>
       </c>
       <c r="E28" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H28" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -11217,16 +11211,16 @@
         <v>23</v>
       </c>
       <c r="E29" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F29">
         <v>20364</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H29" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -11243,16 +11237,16 @@
         <v>23</v>
       </c>
       <c r="E30" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F30">
         <v>11850</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H30" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -11269,16 +11263,16 @@
         <v>23</v>
       </c>
       <c r="E31" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F31">
         <v>9468</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H31" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -11341,16 +11335,16 @@
         <v>23</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F34" s="2">
         <v>30850</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H34" t="s">
-        <v>102</v>
+        <v>243</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -11367,16 +11361,16 @@
         <v>23</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F35" s="2">
         <v>12726</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H35" t="s">
-        <v>102</v>
+        <v>243</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -11393,13 +11387,13 @@
         <v>23</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F36" s="11">
         <v>7600</v>
       </c>
       <c r="G36" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -11410,19 +11404,19 @@
         <v>115</v>
       </c>
       <c r="C37" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D37" t="s">
         <v>23</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F37" s="11">
         <v>3500</v>
       </c>
       <c r="G37" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -11433,19 +11427,19 @@
         <v>115</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F38" s="14">
         <v>4600</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -11456,19 +11450,19 @@
         <v>115</v>
       </c>
       <c r="C39" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D39" t="s">
         <v>23</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F39" s="11">
         <v>3500</v>
       </c>
       <c r="G39" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -11479,19 +11473,19 @@
         <v>115</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F40" s="14">
         <v>4600</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -11502,19 +11496,19 @@
         <v>115</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F41" s="14">
         <v>7000</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -11600,13 +11594,13 @@
         <v>16</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F45" s="11">
         <v>10000</v>
       </c>
       <c r="G45" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -11623,13 +11617,13 @@
         <v>78</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F46" s="14">
         <v>12000</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -11646,16 +11640,16 @@
         <v>16</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F47">
         <v>10000</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H47" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -11672,16 +11666,16 @@
         <v>16</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F48">
         <v>9000</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H48" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -11698,16 +11692,16 @@
         <v>16</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F49">
         <v>10000</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H49" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -11724,16 +11718,16 @@
         <v>16</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F50">
         <v>10000</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H50" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -11796,13 +11790,13 @@
         <v>13</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F53" s="11">
         <v>10000</v>
       </c>
       <c r="G53" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -11819,16 +11813,16 @@
         <v>13</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F54">
         <v>10000</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H54" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -11845,16 +11839,16 @@
         <v>13</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F55">
         <v>9000</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H55" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -11871,16 +11865,16 @@
         <v>13</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F56">
         <v>6000</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H56" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -11897,16 +11891,16 @@
         <v>13</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F57">
         <v>25000</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H57" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -11969,13 +11963,13 @@
         <v>16</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F60" s="11">
         <v>10000</v>
       </c>
       <c r="G60" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -11992,13 +11986,13 @@
         <v>78</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F61">
         <v>45000</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -12015,16 +12009,16 @@
         <v>16</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F62">
         <v>10000</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H62" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -12041,16 +12035,16 @@
         <v>16</v>
       </c>
       <c r="E63" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F63">
         <v>5000</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H63" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -12067,16 +12061,16 @@
         <v>16</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F64">
         <v>25000</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H64" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -12093,16 +12087,16 @@
         <v>16</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F65">
         <v>10000</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H65" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -12113,19 +12107,19 @@
         <v>115</v>
       </c>
       <c r="C66" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D66" t="s">
         <v>20</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F66" s="11">
         <v>10000</v>
       </c>
       <c r="G66" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -12136,19 +12130,19 @@
         <v>115</v>
       </c>
       <c r="C67" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D67" t="s">
         <v>23</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F67" s="11">
         <v>3900</v>
       </c>
       <c r="G67" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -12188,13 +12182,13 @@
         <v>16</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="F69" s="11">
         <v>10000</v>
       </c>
       <c r="G69" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -12211,16 +12205,16 @@
         <v>16</v>
       </c>
       <c r="E70" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F70" s="11">
         <v>10000</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H70" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -12237,16 +12231,16 @@
         <v>16</v>
       </c>
       <c r="E71" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F71" s="11">
         <v>10000</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H71" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -12263,16 +12257,16 @@
         <v>16</v>
       </c>
       <c r="E72" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F72" s="11">
         <v>10000</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H72" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -12289,16 +12283,16 @@
         <v>16</v>
       </c>
       <c r="E73" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F73" s="11">
         <v>10000</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H73" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -12315,16 +12309,16 @@
         <v>16</v>
       </c>
       <c r="E74" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F74" s="11">
         <v>10000</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H74" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -12364,13 +12358,13 @@
         <v>86</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F76">
         <v>25500</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -12381,19 +12375,19 @@
         <v>115</v>
       </c>
       <c r="C77" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="D77" t="s">
         <v>29</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F77" s="11">
         <v>10000</v>
       </c>
       <c r="G77" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -12404,13 +12398,13 @@
         <v>115</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>86</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="F78" s="11">
         <v>20000</v>
@@ -12499,13 +12493,13 @@
         <v>23</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F82" s="11">
         <v>3500</v>
       </c>
       <c r="G82" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -12522,13 +12516,13 @@
         <v>64</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F83">
         <v>17479</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -12545,13 +12539,13 @@
         <v>23</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F84" s="14">
         <v>1000</v>
       </c>
       <c r="H84" s="13" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -12614,13 +12608,13 @@
         <v>13</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F87" s="11">
         <v>7200</v>
       </c>
       <c r="G87" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -12637,16 +12631,16 @@
         <v>13</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F88">
         <v>8000</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H88" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -12663,16 +12657,16 @@
         <v>13</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F89">
         <v>15000</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H89" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -12689,16 +12683,16 @@
         <v>13</v>
       </c>
       <c r="E90" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F90">
         <v>10000</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H90" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -12715,16 +12709,16 @@
         <v>13</v>
       </c>
       <c r="E91" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F91">
         <v>10000</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H91" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -12741,16 +12735,16 @@
         <v>13</v>
       </c>
       <c r="E92" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F92">
         <v>7000</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H92" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -12761,19 +12755,19 @@
         <v>115</v>
       </c>
       <c r="C93" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D93" t="s">
         <v>23</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F93" s="11">
         <v>1500</v>
       </c>
       <c r="G93" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -12836,13 +12830,13 @@
         <v>16</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F96" s="11">
         <v>5600</v>
       </c>
       <c r="G96" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -12859,13 +12853,13 @@
         <v>78</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F97" s="14">
         <v>4800</v>
       </c>
       <c r="H97" s="13" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -12882,13 +12876,13 @@
         <v>78</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F98" s="14">
         <v>12000</v>
       </c>
       <c r="H98" s="13" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -12905,16 +12899,16 @@
         <v>16</v>
       </c>
       <c r="E99" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F99">
         <v>10000</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H99" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -12931,16 +12925,16 @@
         <v>16</v>
       </c>
       <c r="E100" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F100">
         <v>10000</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H100" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -12957,16 +12951,16 @@
         <v>16</v>
       </c>
       <c r="E101" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F101">
         <v>9000</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H101" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -12983,16 +12977,16 @@
         <v>16</v>
       </c>
       <c r="E102" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F102">
         <v>9000</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H102" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -13009,16 +13003,16 @@
         <v>16</v>
       </c>
       <c r="E103" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F103">
         <v>10000</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H103" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -13035,16 +13029,16 @@
         <v>16</v>
       </c>
       <c r="E104" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F104">
         <v>2000</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H104" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -13055,19 +13049,19 @@
         <v>115</v>
       </c>
       <c r="C105" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="D105" t="s">
         <v>23</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F105" s="11">
         <v>3500</v>
       </c>
       <c r="G105" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -13153,13 +13147,13 @@
         <v>20</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F109" s="11">
         <v>8400</v>
       </c>
       <c r="G109" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -13176,13 +13170,13 @@
         <v>86</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F110">
         <v>43200</v>
       </c>
       <c r="G110" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -13199,13 +13193,13 @@
         <v>86</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F111" s="14">
         <v>12000</v>
       </c>
       <c r="H111" s="13" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -13245,16 +13239,16 @@
         <v>23</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F113" s="2">
         <v>30850</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H113" t="s">
-        <v>107</v>
+        <v>244</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -13271,16 +13265,16 @@
         <v>23</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F114" s="2">
         <v>9696</v>
       </c>
       <c r="G114" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H114" t="s">
-        <v>107</v>
+        <v>244</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -13297,13 +13291,13 @@
         <v>23</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F115" s="11">
         <v>3500</v>
       </c>
       <c r="G115" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -13320,13 +13314,13 @@
         <v>23</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F116" s="14">
         <v>5960</v>
       </c>
       <c r="H116" s="13" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -13435,16 +13429,16 @@
         <v>23</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F121" s="2">
         <v>30850</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H121" t="s">
-        <v>100</v>
+        <v>245</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -13461,16 +13455,16 @@
         <v>23</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F122" s="2">
         <v>19150</v>
       </c>
       <c r="G122" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H122" t="s">
-        <v>105</v>
+        <v>246</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -13487,16 +13481,16 @@
         <v>23</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F123" s="2">
         <v>12936</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H123" t="s">
-        <v>100</v>
+        <v>245</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -13513,16 +13507,16 @@
         <v>23</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F124" s="2">
         <v>31462</v>
       </c>
       <c r="G124" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H124" t="s">
-        <v>105</v>
+        <v>246</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -13539,13 +13533,13 @@
         <v>23</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F125" s="11">
         <v>3700</v>
       </c>
       <c r="G125" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -13562,13 +13556,13 @@
         <v>64</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F126" s="14">
         <v>1000</v>
       </c>
       <c r="H126" s="13" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -13585,13 +13579,13 @@
         <v>23</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F127" s="14">
         <v>4600</v>
       </c>
       <c r="H127" s="13" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -13608,7 +13602,7 @@
         <v>64</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="F128">
         <v>32310</v>
@@ -13631,16 +13625,16 @@
         <v>23</v>
       </c>
       <c r="E129" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F129">
         <v>1488</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H129" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -13651,19 +13645,19 @@
         <v>115</v>
       </c>
       <c r="C130" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="D130" t="s">
         <v>23</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F130" s="11">
         <v>3500</v>
       </c>
       <c r="G130" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -13674,19 +13668,19 @@
         <v>115</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F131" s="14">
         <v>2400</v>
       </c>
       <c r="H131" s="13" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -13697,19 +13691,19 @@
         <v>115</v>
       </c>
       <c r="C132" s="13" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F132" s="14">
         <v>1000</v>
       </c>
       <c r="H132" s="13" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -13772,16 +13766,16 @@
         <v>29</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F135" s="2">
         <v>17789</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H135" t="s">
-        <v>106</v>
+        <v>247</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -13798,16 +13792,16 @@
         <v>29</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F136" s="2">
         <v>8085</v>
       </c>
       <c r="G136" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H136" t="s">
-        <v>106</v>
+        <v>247</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -13824,13 +13818,13 @@
         <v>29</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F137" s="11">
         <v>10000</v>
       </c>
       <c r="G137" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -13847,13 +13841,13 @@
         <v>76</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F138">
         <v>42500</v>
       </c>
       <c r="G138" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -13870,16 +13864,16 @@
         <v>29</v>
       </c>
       <c r="E139" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F139">
         <v>13600</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H139" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -13896,16 +13890,16 @@
         <v>29</v>
       </c>
       <c r="E140" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F140">
         <v>9507</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H140" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -13916,19 +13910,19 @@
         <v>115</v>
       </c>
       <c r="C141" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D141" t="s">
         <v>23</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F141" s="11">
         <v>8700</v>
       </c>
       <c r="G141" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -13939,19 +13933,19 @@
         <v>115</v>
       </c>
       <c r="C142" s="13" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F142" s="14">
         <v>4800</v>
       </c>
       <c r="H142" s="13" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -13962,19 +13956,19 @@
         <v>115</v>
       </c>
       <c r="C143" s="13" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F143" s="14">
         <v>2000</v>
       </c>
       <c r="H143" s="13" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -13985,19 +13979,19 @@
         <v>115</v>
       </c>
       <c r="C144" s="13" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F144" s="15">
         <v>688</v>
       </c>
       <c r="H144" s="13" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -14008,19 +14002,19 @@
         <v>115</v>
       </c>
       <c r="C145" s="13" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F145" s="14">
         <v>2000</v>
       </c>
       <c r="H145" s="13" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -14031,19 +14025,19 @@
         <v>115</v>
       </c>
       <c r="C146" s="13" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F146" s="14">
         <v>2000</v>
       </c>
       <c r="H146" s="13" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -14054,22 +14048,22 @@
         <v>115</v>
       </c>
       <c r="C147" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D147" t="s">
         <v>23</v>
       </c>
       <c r="E147" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F147">
         <v>35000</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H147" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -14080,22 +14074,22 @@
         <v>115</v>
       </c>
       <c r="C148" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D148" t="s">
         <v>23</v>
       </c>
       <c r="E148" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F148">
         <v>10880</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H148" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -14106,19 +14100,19 @@
         <v>115</v>
       </c>
       <c r="C149" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D149" t="s">
         <v>23</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F149" s="11">
         <v>3500</v>
       </c>
       <c r="G149" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -14129,19 +14123,19 @@
         <v>115</v>
       </c>
       <c r="C150" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="D150" t="s">
         <v>23</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F150" s="11">
         <v>3500</v>
       </c>
       <c r="G150" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -14152,19 +14146,19 @@
         <v>115</v>
       </c>
       <c r="C151" s="13" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F151" s="14">
         <v>7000</v>
       </c>
       <c r="H151" s="13" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -14175,19 +14169,19 @@
         <v>115</v>
       </c>
       <c r="C152" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="D152" t="s">
         <v>20</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F152" s="11">
         <v>9600</v>
       </c>
       <c r="G152" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -14198,19 +14192,19 @@
         <v>115</v>
       </c>
       <c r="C153" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="D153" s="10" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F153">
         <v>30000</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -14221,19 +14215,19 @@
         <v>115</v>
       </c>
       <c r="C154" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="D154" t="s">
         <v>23</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F154" s="11">
         <v>3500</v>
       </c>
       <c r="G154" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -14244,19 +14238,19 @@
         <v>115</v>
       </c>
       <c r="C155" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D155" t="s">
         <v>23</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F155" s="11">
         <v>10000</v>
       </c>
       <c r="G155" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -14267,22 +14261,22 @@
         <v>115</v>
       </c>
       <c r="C156" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D156" t="s">
         <v>23</v>
       </c>
       <c r="E156" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F156">
         <v>35000</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H156" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -14293,22 +14287,22 @@
         <v>115</v>
       </c>
       <c r="C157" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D157" t="s">
         <v>23</v>
       </c>
       <c r="E157" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F157">
         <v>7800</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H157" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -14319,19 +14313,19 @@
         <v>115</v>
       </c>
       <c r="C158" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F158" s="11">
         <v>400</v>
       </c>
       <c r="G158" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -14342,19 +14336,19 @@
         <v>115</v>
       </c>
       <c r="C159" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D159" s="10" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F159">
         <v>39613</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -14365,19 +14359,19 @@
         <v>115</v>
       </c>
       <c r="C160" s="13" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F160" s="14">
         <v>20000</v>
       </c>
       <c r="H160" s="13" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -14388,19 +14382,19 @@
         <v>115</v>
       </c>
       <c r="C161" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="D161" s="10" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F161" s="11">
         <v>500</v>
       </c>
       <c r="G161" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -14411,22 +14405,22 @@
         <v>115</v>
       </c>
       <c r="C162" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="D162" t="s">
         <v>40</v>
       </c>
       <c r="E162" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F162">
         <v>10000</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H162" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -14437,19 +14431,19 @@
         <v>115</v>
       </c>
       <c r="C163" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="D163" t="s">
         <v>23</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F163" s="11">
         <v>8700</v>
       </c>
       <c r="G163" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -14460,22 +14454,22 @@
         <v>115</v>
       </c>
       <c r="C164" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="D164" t="s">
         <v>23</v>
       </c>
       <c r="E164" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F164">
         <v>29000</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H164" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -14486,22 +14480,22 @@
         <v>115</v>
       </c>
       <c r="C165" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="D165" t="s">
         <v>23</v>
       </c>
       <c r="E165" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F165">
         <v>2000</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H165" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -14535,19 +14529,19 @@
         <v>115</v>
       </c>
       <c r="C167" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="D167" t="s">
         <v>20</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F167" s="11">
         <v>2500</v>
       </c>
       <c r="G167" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -14633,13 +14627,13 @@
         <v>23</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F171" s="11">
         <v>5000</v>
       </c>
       <c r="G171" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -14656,13 +14650,13 @@
         <v>64</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F172">
         <v>12000</v>
       </c>
       <c r="G172" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -14679,13 +14673,13 @@
         <v>23</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F173" s="14">
         <v>6000</v>
       </c>
       <c r="H173" s="13" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -14702,13 +14696,13 @@
         <v>23</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F174" s="14">
         <v>1000</v>
       </c>
       <c r="H174" s="13" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -14719,19 +14713,19 @@
         <v>115</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="D175" s="4" t="s">
         <v>64</v>
       </c>
       <c r="E175" s="6" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="F175">
         <v>32310</v>
       </c>
       <c r="G175" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -14748,16 +14742,16 @@
         <v>23</v>
       </c>
       <c r="E176" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F176">
         <v>29500</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H176" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -14774,16 +14768,16 @@
         <v>23</v>
       </c>
       <c r="E177" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F177">
         <v>0</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H177" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -14846,13 +14840,13 @@
         <v>23</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F180" s="11">
         <v>3500</v>
       </c>
       <c r="G180" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -14869,16 +14863,16 @@
         <v>23</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F181" s="2">
         <v>50000</v>
       </c>
       <c r="G181" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H181" t="s">
-        <v>110</v>
+        <v>248</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -14895,16 +14889,16 @@
         <v>23</v>
       </c>
       <c r="E182" s="10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F182" s="2">
         <v>38015</v>
       </c>
       <c r="G182" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H182" t="s">
-        <v>110</v>
+        <v>248</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -14921,13 +14915,13 @@
         <v>64</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F183" s="11">
         <v>3500</v>
       </c>
       <c r="G183" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -14944,13 +14938,13 @@
         <v>23</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F184" s="14">
         <v>1000</v>
       </c>
       <c r="H184" s="13" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -14961,19 +14955,19 @@
         <v>115</v>
       </c>
       <c r="C185" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D185" t="s">
         <v>23</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F185" s="11">
         <v>3500</v>
       </c>
       <c r="G185" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -15036,13 +15030,13 @@
         <v>13</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F188" s="11">
         <v>10000</v>
       </c>
       <c r="G188" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -15059,16 +15053,16 @@
         <v>13</v>
       </c>
       <c r="E189" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F189">
         <v>8000</v>
       </c>
       <c r="G189" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H189" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -15154,16 +15148,16 @@
         <v>10</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F193" s="2">
         <v>19942</v>
       </c>
       <c r="G193" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H193" t="s">
-        <v>108</v>
+        <v>249</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -15180,16 +15174,16 @@
         <v>10</v>
       </c>
       <c r="E194" s="10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F194" s="2">
         <v>16447</v>
       </c>
       <c r="G194" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H194" t="s">
-        <v>108</v>
+        <v>249</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -15206,16 +15200,16 @@
         <v>10</v>
       </c>
       <c r="E195" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F195">
         <v>21996</v>
       </c>
       <c r="G195" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H195" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -15232,16 +15226,16 @@
         <v>10</v>
       </c>
       <c r="E196" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F196">
         <v>16421</v>
       </c>
       <c r="G196" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H196" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="17.25">
@@ -15281,13 +15275,13 @@
         <v>77</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F198" s="11">
         <v>10000</v>
       </c>
       <c r="G198" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -15304,13 +15298,13 @@
         <v>77</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F199" s="14">
         <v>1000</v>
       </c>
       <c r="H199" s="13" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -15327,16 +15321,16 @@
         <v>13</v>
       </c>
       <c r="E200" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F200">
         <v>5000</v>
       </c>
       <c r="G200" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H200" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -15353,16 +15347,16 @@
         <v>13</v>
       </c>
       <c r="E201" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F201">
         <v>50000</v>
       </c>
       <c r="G201" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H201" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -15379,16 +15373,16 @@
         <v>13</v>
       </c>
       <c r="E202" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F202">
         <v>13949</v>
       </c>
       <c r="G202" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H202" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -15428,13 +15422,13 @@
         <v>29</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F204" s="11">
         <v>6000</v>
       </c>
       <c r="G204" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -15451,13 +15445,13 @@
         <v>76</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F205">
         <v>37500</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -15474,16 +15468,16 @@
         <v>29</v>
       </c>
       <c r="E206" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F206">
         <v>8000</v>
       </c>
       <c r="G206" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H206" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -15494,19 +15488,19 @@
         <v>115</v>
       </c>
       <c r="C207" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="D207" t="s">
         <v>23</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F207" s="11">
         <v>6400</v>
       </c>
       <c r="G207" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -15546,13 +15540,13 @@
         <v>23</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F209" s="11">
         <v>10000</v>
       </c>
       <c r="G209" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -15569,16 +15563,16 @@
         <v>23</v>
       </c>
       <c r="E210" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F210">
         <v>3000</v>
       </c>
       <c r="G210" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H210" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -15595,16 +15589,16 @@
         <v>23</v>
       </c>
       <c r="E211" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F211">
         <v>10000</v>
       </c>
       <c r="G211" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H211" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -15621,16 +15615,16 @@
         <v>23</v>
       </c>
       <c r="E212" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F212">
         <v>8000</v>
       </c>
       <c r="G212" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H212" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -15647,16 +15641,16 @@
         <v>23</v>
       </c>
       <c r="E213" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F213">
         <v>35000</v>
       </c>
       <c r="G213" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H213" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -15673,16 +15667,16 @@
         <v>23</v>
       </c>
       <c r="E214" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F214">
         <v>9610</v>
       </c>
       <c r="G214" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H214" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -15693,19 +15687,19 @@
         <v>115</v>
       </c>
       <c r="C215" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="D215" t="s">
         <v>23</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F215" s="11">
         <v>3500</v>
       </c>
       <c r="G215" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="17.25">
@@ -15745,13 +15739,13 @@
         <v>64</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F217" s="11">
         <v>3800</v>
       </c>
       <c r="G217" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -15768,13 +15762,13 @@
         <v>23</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F218" s="15">
         <v>999</v>
       </c>
       <c r="H218" s="13" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -15791,13 +15785,13 @@
         <v>23</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F219" s="14">
         <v>4090</v>
       </c>
       <c r="H219" s="13" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -15814,13 +15808,13 @@
         <v>23</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F220" s="14">
         <v>8900</v>
       </c>
       <c r="H220" s="13" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -15837,13 +15831,13 @@
         <v>23</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F221" s="14">
         <v>2490</v>
       </c>
       <c r="H221" s="13" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -15929,13 +15923,13 @@
         <v>16</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F225" s="11">
         <v>9400</v>
       </c>
       <c r="G225" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="226" spans="1:8">
@@ -15952,16 +15946,16 @@
         <v>16</v>
       </c>
       <c r="E226" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F226">
         <v>10000</v>
       </c>
       <c r="G226" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H226" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -15978,16 +15972,16 @@
         <v>16</v>
       </c>
       <c r="E227" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F227">
         <v>10000</v>
       </c>
       <c r="G227" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H227" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="228" spans="1:8">
@@ -16004,16 +15998,16 @@
         <v>16</v>
       </c>
       <c r="E228" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F228">
         <v>9000</v>
       </c>
       <c r="G228" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H228" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
     </row>
     <row r="229" spans="1:8">
@@ -16030,16 +16024,16 @@
         <v>16</v>
       </c>
       <c r="E229" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F229">
         <v>10000</v>
       </c>
       <c r="G229" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H229" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="230" spans="1:8">
@@ -16056,16 +16050,16 @@
         <v>16</v>
       </c>
       <c r="E230" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F230">
         <v>10000</v>
       </c>
       <c r="G230" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H230" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="231" spans="1:8">
@@ -16128,13 +16122,13 @@
         <v>64</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F233" s="11">
         <v>3500</v>
       </c>
       <c r="G233" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="234" spans="1:8">
@@ -16174,13 +16168,13 @@
         <v>23</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F235" s="11">
         <v>3500</v>
       </c>
       <c r="G235" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -16197,13 +16191,13 @@
         <v>64</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F236">
         <v>29750</v>
       </c>
       <c r="G236" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -16220,13 +16214,13 @@
         <v>23</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F237" s="14">
         <v>3000</v>
       </c>
       <c r="H237" s="13" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -16243,16 +16237,16 @@
         <v>23</v>
       </c>
       <c r="E238" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F238">
         <v>18500</v>
       </c>
       <c r="G238" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H238" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -16269,16 +16263,16 @@
         <v>23</v>
       </c>
       <c r="E239" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F239">
         <v>31500</v>
       </c>
       <c r="G239" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H239" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -16295,16 +16289,16 @@
         <v>23</v>
       </c>
       <c r="E240" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F240">
         <v>9838</v>
       </c>
       <c r="G240" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H240" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -16321,16 +16315,16 @@
         <v>23</v>
       </c>
       <c r="E241" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F241">
         <v>11872</v>
       </c>
       <c r="G241" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H241" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -16341,19 +16335,19 @@
         <v>115</v>
       </c>
       <c r="C242" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="D242" s="10" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F242" s="11">
         <v>7200</v>
       </c>
       <c r="G242" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -16364,22 +16358,22 @@
         <v>115</v>
       </c>
       <c r="C243" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="D243" t="s">
         <v>40</v>
       </c>
       <c r="E243" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F243">
         <v>10000</v>
       </c>
       <c r="G243" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H243" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="244" spans="1:8">
@@ -16390,19 +16384,19 @@
         <v>115</v>
       </c>
       <c r="C244" s="13" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="D244" s="4" t="s">
         <v>63</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F244" s="14">
         <v>7800</v>
       </c>
       <c r="H244" s="13" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -16413,19 +16407,19 @@
         <v>115</v>
       </c>
       <c r="C245" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="D245" t="s">
         <v>23</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F245" s="11">
         <v>3500</v>
       </c>
       <c r="G245" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -16436,19 +16430,19 @@
         <v>115</v>
       </c>
       <c r="C246" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="D246" t="s">
         <v>20</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F246" s="11">
         <v>5600</v>
       </c>
       <c r="G246" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="247" spans="1:8">
@@ -16459,19 +16453,19 @@
         <v>115</v>
       </c>
       <c r="C247" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="D247" s="10" t="s">
         <v>86</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F247">
         <v>45000</v>
       </c>
       <c r="G247" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -16482,19 +16476,19 @@
         <v>115</v>
       </c>
       <c r="C248" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="D248" t="s">
         <v>23</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F248" s="11">
         <v>5700</v>
       </c>
       <c r="G248" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="249" spans="1:8">
@@ -16505,19 +16499,19 @@
         <v>115</v>
       </c>
       <c r="C249" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="D249" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F249" s="11">
         <v>1400</v>
       </c>
       <c r="G249" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="250" spans="1:8">
@@ -16557,13 +16551,13 @@
         <v>20</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F251" s="11">
         <v>5600</v>
       </c>
       <c r="G251" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="252" spans="1:8">
@@ -16580,13 +16574,13 @@
         <v>86</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F252">
         <v>13500</v>
       </c>
       <c r="G252" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -16603,16 +16597,16 @@
         <v>60</v>
       </c>
       <c r="E253" s="10" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="F253" s="2">
         <v>3400</v>
       </c>
       <c r="G253" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H253" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="254" spans="1:8">
@@ -16629,16 +16623,16 @@
         <v>60</v>
       </c>
       <c r="E254" s="10" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="F254" s="2">
         <v>13120</v>
       </c>
       <c r="G254" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H254" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -16655,13 +16649,13 @@
         <v>60</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="F255" s="11">
         <v>10000</v>
       </c>
       <c r="G255" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="256" spans="1:8">
@@ -16724,13 +16718,13 @@
         <v>40</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F258" s="11">
         <v>900</v>
       </c>
       <c r="G258" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -16744,16 +16738,16 @@
         <v>39</v>
       </c>
       <c r="D259" s="10" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F259">
         <v>17850</v>
       </c>
       <c r="G259" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="260" spans="1:8">
@@ -16767,16 +16761,16 @@
         <v>39</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F260" s="14">
         <v>1000</v>
       </c>
       <c r="H260" s="13" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -16787,19 +16781,19 @@
         <v>115</v>
       </c>
       <c r="C261" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="D261" t="s">
         <v>23</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F261" s="11">
         <v>3500</v>
       </c>
       <c r="G261" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -16810,19 +16804,19 @@
         <v>115</v>
       </c>
       <c r="C262" s="13" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="D262" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F262" s="14">
         <v>7200</v>
       </c>
       <c r="H262" s="13" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -16882,16 +16876,16 @@
         <v>41</v>
       </c>
       <c r="D265" s="10" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F265">
         <v>15800</v>
       </c>
       <c r="G265" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="266" spans="1:8" ht="17.25">
@@ -16954,13 +16948,13 @@
         <v>77</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F268" s="11">
         <v>10000</v>
       </c>
       <c r="G268" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -16977,13 +16971,13 @@
         <v>77</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F269" s="14">
         <v>3600</v>
       </c>
       <c r="H269" s="13" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -17000,13 +16994,13 @@
         <v>77</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F270" s="14">
         <v>2000</v>
       </c>
       <c r="H270" s="13" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -17023,13 +17017,13 @@
         <v>77</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F271" s="14">
         <v>3600</v>
       </c>
       <c r="H271" s="13" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -17040,13 +17034,13 @@
         <v>115</v>
       </c>
       <c r="C272" s="10" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="D272" s="10" t="s">
         <v>77</v>
       </c>
       <c r="E272" s="10" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="F272" s="2">
         <v>10000</v>
@@ -17066,16 +17060,16 @@
         <v>13</v>
       </c>
       <c r="E273" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F273">
         <v>8000</v>
       </c>
       <c r="G273" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H273" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -17092,16 +17086,16 @@
         <v>13</v>
       </c>
       <c r="E274" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F274">
         <v>10000</v>
       </c>
       <c r="G274" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H274" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="275" spans="1:8" ht="17.25">
@@ -17164,13 +17158,13 @@
         <v>23</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F277" s="11">
         <v>3700</v>
       </c>
       <c r="G277" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="278" spans="1:8">
@@ -17181,19 +17175,19 @@
         <v>115</v>
       </c>
       <c r="C278" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="D278" t="s">
         <v>23</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F278" s="11">
         <v>3500</v>
       </c>
       <c r="G278" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -17204,19 +17198,19 @@
         <v>115</v>
       </c>
       <c r="C279" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D279" t="s">
         <v>23</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F279" s="11">
         <v>3500</v>
       </c>
       <c r="G279" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -17227,19 +17221,19 @@
         <v>115</v>
       </c>
       <c r="C280" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="D280" t="s">
         <v>23</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F280" s="11">
         <v>3500</v>
       </c>
       <c r="G280" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -17348,13 +17342,13 @@
         <v>20</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F285" s="11">
         <v>5600</v>
       </c>
       <c r="G285" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="286" spans="1:8">
@@ -17371,13 +17365,13 @@
         <v>86</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F286">
         <v>20250</v>
       </c>
       <c r="G286" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="287" spans="1:8">
@@ -17394,16 +17388,16 @@
         <v>20</v>
       </c>
       <c r="E287" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F287">
         <v>5000</v>
       </c>
       <c r="G287" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H287" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -17489,16 +17483,16 @@
         <v>16</v>
       </c>
       <c r="E291" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F291">
         <v>8000</v>
       </c>
       <c r="G291" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H291" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -17515,16 +17509,16 @@
         <v>16</v>
       </c>
       <c r="E292" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F292">
         <v>10000</v>
       </c>
       <c r="G292" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H292" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -17541,16 +17535,16 @@
         <v>16</v>
       </c>
       <c r="E293" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F293">
         <v>10000</v>
       </c>
       <c r="G293" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H293" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -17567,16 +17561,16 @@
         <v>16</v>
       </c>
       <c r="E294" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F294">
         <v>10000</v>
       </c>
       <c r="G294" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H294" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -17593,16 +17587,16 @@
         <v>16</v>
       </c>
       <c r="E295" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F295">
         <v>10000</v>
       </c>
       <c r="G295" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H295" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -17619,16 +17613,16 @@
         <v>23</v>
       </c>
       <c r="E296" s="10" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F296" s="2">
         <v>50000</v>
       </c>
       <c r="G296" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H296" t="s">
-        <v>101</v>
+        <v>250</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -17645,16 +17639,16 @@
         <v>23</v>
       </c>
       <c r="E297" s="10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F297" s="2">
         <v>42393</v>
       </c>
       <c r="G297" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H297" t="s">
-        <v>101</v>
+        <v>250</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -17671,13 +17665,13 @@
         <v>23</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F298" s="11">
         <v>3500</v>
       </c>
       <c r="G298" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -17688,13 +17682,13 @@
         <v>115</v>
       </c>
       <c r="C299" s="10" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="D299" s="10" t="s">
         <v>64</v>
       </c>
       <c r="E299" s="10" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="F299" s="2">
         <v>20000</v>
@@ -17708,19 +17702,19 @@
         <v>115</v>
       </c>
       <c r="C300" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="D300" t="s">
         <v>23</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F300" s="11">
         <v>3500</v>
       </c>
       <c r="G300" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -17731,19 +17725,19 @@
         <v>115</v>
       </c>
       <c r="C301" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D301" t="s">
         <v>29</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F301" s="11">
         <v>10000</v>
       </c>
       <c r="G301" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -17806,13 +17800,13 @@
         <v>46</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F304" s="11">
         <v>10000</v>
       </c>
       <c r="G304" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -17829,13 +17823,13 @@
         <v>63</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F305" s="14">
         <v>3582</v>
       </c>
       <c r="H305" s="13" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -17852,7 +17846,7 @@
         <v>63</v>
       </c>
       <c r="E306" s="10" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="F306" s="11">
         <v>20000</v>
@@ -17872,16 +17866,16 @@
         <v>46</v>
       </c>
       <c r="E307" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F307">
         <v>31430</v>
       </c>
       <c r="G307" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H307" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -17898,16 +17892,16 @@
         <v>46</v>
       </c>
       <c r="E308" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F308">
         <v>16000</v>
       </c>
       <c r="G308" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H308" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
     </row>
     <row r="309" spans="1:8">
@@ -17918,19 +17912,19 @@
         <v>115</v>
       </c>
       <c r="C309" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="D309" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F309" s="11">
         <v>6000</v>
       </c>
       <c r="G309" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="310" spans="1:8">
@@ -17941,19 +17935,19 @@
         <v>115</v>
       </c>
       <c r="C310" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D310" t="s">
         <v>10</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F310" s="11">
         <v>10000</v>
       </c>
       <c r="G310" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="311" spans="1:8">
@@ -17964,19 +17958,19 @@
         <v>115</v>
       </c>
       <c r="C311" s="13" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>79</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F311" s="14">
         <v>2400</v>
       </c>
       <c r="H311" s="13" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
     </row>
     <row r="312" spans="1:8">
@@ -18039,13 +18033,13 @@
         <v>46</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F314" s="11">
         <v>1400</v>
       </c>
       <c r="G314" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="315" spans="1:8">
@@ -18108,13 +18102,13 @@
         <v>13</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F317" s="11">
         <v>900</v>
       </c>
       <c r="G317" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="318" spans="1:8">
@@ -18131,16 +18125,16 @@
         <v>13</v>
       </c>
       <c r="E318" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F318">
         <v>9000</v>
       </c>
       <c r="G318" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H318" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
     </row>
     <row r="319" spans="1:8">
@@ -18157,16 +18151,16 @@
         <v>13</v>
       </c>
       <c r="E319" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F319">
         <v>20000</v>
       </c>
       <c r="G319" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H319" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
     </row>
     <row r="320" spans="1:8">
@@ -18183,16 +18177,16 @@
         <v>13</v>
       </c>
       <c r="E320" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F320">
         <v>10000</v>
       </c>
       <c r="G320" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H320" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="321" spans="1:8">
@@ -18209,16 +18203,16 @@
         <v>13</v>
       </c>
       <c r="E321" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F321">
         <v>6000</v>
       </c>
       <c r="G321" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H321" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -18235,16 +18229,16 @@
         <v>13</v>
       </c>
       <c r="E322" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F322">
         <v>5000</v>
       </c>
       <c r="G322" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H322" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -18307,16 +18301,16 @@
         <v>23</v>
       </c>
       <c r="E325" s="10" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F325" s="2">
         <v>50000</v>
       </c>
       <c r="G325" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H325" t="s">
-        <v>109</v>
+        <v>251</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -18333,16 +18327,16 @@
         <v>23</v>
       </c>
       <c r="E326" s="10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F326" s="2">
         <v>38569</v>
       </c>
       <c r="G326" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H326" t="s">
-        <v>109</v>
+        <v>251</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -18359,13 +18353,13 @@
         <v>23</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F327" s="11">
         <v>5000</v>
       </c>
       <c r="G327" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -18382,13 +18376,13 @@
         <v>64</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F328">
         <v>50000</v>
       </c>
       <c r="G328" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -18405,13 +18399,13 @@
         <v>23</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F329" s="14">
         <v>3081</v>
       </c>
       <c r="H329" s="13" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
     </row>
     <row r="330" spans="1:8">
@@ -18428,13 +18422,13 @@
         <v>23</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F330" s="14">
         <v>4800</v>
       </c>
       <c r="H330" s="13" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
     </row>
     <row r="331" spans="1:8">
@@ -18451,13 +18445,13 @@
         <v>23</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F331" s="14">
         <v>1000</v>
       </c>
       <c r="H331" s="13" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
     </row>
     <row r="332" spans="1:8">
@@ -18474,13 +18468,13 @@
         <v>23</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F332" s="15">
         <v>500</v>
       </c>
       <c r="H332" s="13" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -18491,19 +18485,19 @@
         <v>115</v>
       </c>
       <c r="C333" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="D333" t="s">
         <v>23</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F333" s="11">
         <v>3500</v>
       </c>
       <c r="G333" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -18543,13 +18537,13 @@
         <v>64</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F335" s="11">
         <v>3500</v>
       </c>
       <c r="G335" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="336" spans="1:8">
@@ -18566,13 +18560,13 @@
         <v>64</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F336">
         <v>30150</v>
       </c>
       <c r="G336" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="337" spans="1:8">
@@ -18612,13 +18606,13 @@
         <v>20</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F338" s="11">
         <v>5600</v>
       </c>
       <c r="G338" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="339" spans="1:8">
@@ -18635,13 +18629,13 @@
         <v>86</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F339">
         <v>12750</v>
       </c>
       <c r="G339" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="340" spans="1:8" ht="17.25">
@@ -18681,13 +18675,13 @@
         <v>23</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F341" s="11">
         <v>3500</v>
       </c>
       <c r="G341" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="342" spans="1:8">
@@ -18698,19 +18692,19 @@
         <v>115</v>
       </c>
       <c r="C342" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D342" t="s">
         <v>23</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F342" s="11">
         <v>3500</v>
       </c>
       <c r="G342" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="343" spans="1:8" ht="17.25">
@@ -18744,19 +18738,19 @@
         <v>115</v>
       </c>
       <c r="C344" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="D344" t="s">
         <v>23</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F344" s="11">
         <v>3500</v>
       </c>
       <c r="G344" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="345" spans="1:8">
@@ -18767,19 +18761,19 @@
         <v>115</v>
       </c>
       <c r="C345" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="D345" t="s">
         <v>23</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F345" s="11">
         <v>3500</v>
       </c>
       <c r="G345" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="346" spans="1:8">
@@ -18790,19 +18784,19 @@
         <v>115</v>
       </c>
       <c r="C346" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D346" t="s">
         <v>23</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F346" s="11">
         <v>3500</v>
       </c>
       <c r="G346" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="347" spans="1:8">
@@ -18813,19 +18807,19 @@
         <v>115</v>
       </c>
       <c r="C347" s="13" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D347" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F347" s="14">
         <v>20000</v>
       </c>
       <c r="H347" s="13" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
     </row>
     <row r="348" spans="1:8">
@@ -18836,19 +18830,19 @@
         <v>115</v>
       </c>
       <c r="C348" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="D348" t="s">
         <v>23</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F348" s="11">
         <v>3500</v>
       </c>
       <c r="G348" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="349" spans="1:8">
@@ -18888,16 +18882,16 @@
         <v>29</v>
       </c>
       <c r="E350" s="10" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F350" s="2">
         <v>8900</v>
       </c>
       <c r="G350" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H350" t="s">
-        <v>104</v>
+        <v>253</v>
       </c>
     </row>
     <row r="351" spans="1:8">
@@ -18914,16 +18908,16 @@
         <v>29</v>
       </c>
       <c r="E351" s="10" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F351" s="2">
         <v>0</v>
       </c>
       <c r="G351" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H351" t="s">
-        <v>111</v>
+        <v>252</v>
       </c>
     </row>
     <row r="352" spans="1:8">
@@ -18940,16 +18934,16 @@
         <v>29</v>
       </c>
       <c r="E352" s="10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F352" s="2">
         <v>19190</v>
       </c>
       <c r="G352" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H352" t="s">
-        <v>104</v>
+        <v>253</v>
       </c>
     </row>
     <row r="353" spans="1:8">
@@ -18966,16 +18960,16 @@
         <v>29</v>
       </c>
       <c r="E353" s="10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F353" s="2">
         <v>17728</v>
       </c>
       <c r="G353" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H353" t="s">
-        <v>111</v>
+        <v>252</v>
       </c>
     </row>
     <row r="354" spans="1:8">
@@ -18992,13 +18986,13 @@
         <v>29</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F354" s="11">
         <v>2200</v>
       </c>
       <c r="G354" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -19015,13 +19009,13 @@
         <v>76</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F355">
         <v>32175</v>
       </c>
       <c r="G355" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="356" spans="1:8">
@@ -19038,13 +19032,13 @@
         <v>76</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F356" s="14">
         <v>8900</v>
       </c>
       <c r="H356" s="13" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -19055,13 +19049,13 @@
         <v>115</v>
       </c>
       <c r="C357" s="10" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="D357" s="10" t="s">
         <v>78</v>
       </c>
       <c r="E357" s="10" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="F357" s="2">
         <v>10000</v>
@@ -19075,19 +19069,19 @@
         <v>115</v>
       </c>
       <c r="C358" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="D358" s="10" t="s">
         <v>64</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F358" s="11">
         <v>3500</v>
       </c>
       <c r="G358" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -19104,16 +19098,16 @@
         <v>23</v>
       </c>
       <c r="E359" s="10" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F359" s="2">
         <v>40000</v>
       </c>
       <c r="G359" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H359" t="s">
-        <v>113</v>
+        <v>254</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -19130,16 +19124,16 @@
         <v>23</v>
       </c>
       <c r="E360" s="10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F360" s="2">
         <v>17600</v>
       </c>
       <c r="G360" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H360" t="s">
-        <v>113</v>
+        <v>254</v>
       </c>
     </row>
     <row r="361" spans="1:8">
@@ -19156,13 +19150,13 @@
         <v>23</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F361" s="11">
         <v>3500</v>
       </c>
       <c r="G361" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -19173,19 +19167,19 @@
         <v>115</v>
       </c>
       <c r="C362" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D362" t="s">
         <v>23</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F362" s="11">
         <v>3500</v>
       </c>
       <c r="G362" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="363" spans="1:8">
@@ -19225,16 +19219,16 @@
         <v>23</v>
       </c>
       <c r="E364" s="10" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F364" s="2">
         <v>40000</v>
       </c>
       <c r="G364" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H364" t="s">
-        <v>114</v>
+        <v>254</v>
       </c>
     </row>
     <row r="365" spans="1:8">
@@ -19251,16 +19245,16 @@
         <v>23</v>
       </c>
       <c r="E365" s="10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F365" s="2">
         <v>19200</v>
       </c>
       <c r="G365" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H365" t="s">
-        <v>114</v>
+        <v>254</v>
       </c>
     </row>
     <row r="366" spans="1:8">
@@ -19277,13 +19271,13 @@
         <v>23</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F366" s="11">
         <v>3500</v>
       </c>
       <c r="G366" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="367" spans="1:8">
@@ -19346,13 +19340,13 @@
         <v>13</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F369" s="11">
         <v>6300</v>
       </c>
       <c r="G369" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="370" spans="1:8">
@@ -19369,16 +19363,16 @@
         <v>13</v>
       </c>
       <c r="E370" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F370">
         <v>10000</v>
       </c>
       <c r="G370" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H370" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="371" spans="1:8">
@@ -19395,16 +19389,16 @@
         <v>13</v>
       </c>
       <c r="E371" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F371">
         <v>8000</v>
       </c>
       <c r="G371" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H371" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
     </row>
     <row r="372" spans="1:8">
@@ -19421,16 +19415,16 @@
         <v>13</v>
       </c>
       <c r="E372" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F372">
         <v>5000</v>
       </c>
       <c r="G372" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H372" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
     </row>
     <row r="373" spans="1:8">
@@ -19447,16 +19441,16 @@
         <v>13</v>
       </c>
       <c r="E373" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F373">
         <v>25000</v>
       </c>
       <c r="G373" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H373" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
     </row>
     <row r="374" spans="1:8">
@@ -19496,13 +19490,13 @@
         <v>20</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F375" s="11">
         <v>5600</v>
       </c>
       <c r="G375" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="376" spans="1:8">
@@ -19519,13 +19513,13 @@
         <v>86</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F376">
         <v>19125</v>
       </c>
       <c r="G376" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="377" spans="1:8">
@@ -19565,13 +19559,13 @@
         <v>23</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F378" s="11">
         <v>4100</v>
       </c>
       <c r="G378" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="379" spans="1:8">
@@ -19588,13 +19582,13 @@
         <v>64</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F379">
         <v>18584</v>
       </c>
       <c r="G379" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -19611,16 +19605,16 @@
         <v>23</v>
       </c>
       <c r="E380" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F380">
         <v>18500</v>
       </c>
       <c r="G380" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H380" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
     </row>
     <row r="381" spans="1:8">
@@ -19637,16 +19631,16 @@
         <v>23</v>
       </c>
       <c r="E381" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F381">
         <v>31500</v>
       </c>
       <c r="G381" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H381" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="382" spans="1:8">
@@ -19663,16 +19657,16 @@
         <v>23</v>
       </c>
       <c r="E382" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F382">
         <v>8147</v>
       </c>
       <c r="G382" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H382" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
     </row>
     <row r="383" spans="1:8">
@@ -19689,16 +19683,16 @@
         <v>23</v>
       </c>
       <c r="E383" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="F383">
         <v>11915</v>
       </c>
       <c r="G383" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H383" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="384" spans="1:8">
@@ -19761,13 +19755,13 @@
         <v>20</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F386" s="11">
         <v>10000</v>
       </c>
       <c r="G386" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="387" spans="1:8">
@@ -19784,16 +19778,16 @@
         <v>20</v>
       </c>
       <c r="E387" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F387">
         <v>5000</v>
       </c>
       <c r="G387" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H387" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
     </row>
     <row r="388" spans="1:8">
@@ -19804,19 +19798,19 @@
         <v>115</v>
       </c>
       <c r="C388" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="D388" t="s">
         <v>23</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F388" s="11">
         <v>3500</v>
       </c>
       <c r="G388" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="389" spans="1:8">
@@ -19827,19 +19821,19 @@
         <v>115</v>
       </c>
       <c r="C389" s="13" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="D389" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F389" s="14">
         <v>4500</v>
       </c>
       <c r="H389" s="13" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
     </row>
     <row r="390" spans="1:8">
@@ -19850,19 +19844,19 @@
         <v>115</v>
       </c>
       <c r="C390" s="13" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="D390" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F390" s="15">
         <v>850</v>
       </c>
       <c r="H390" s="13" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
     </row>
     <row r="391" spans="1:8">
@@ -19873,19 +19867,19 @@
         <v>115</v>
       </c>
       <c r="C391" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="D391" t="s">
         <v>23</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F391" s="11">
         <v>5000</v>
       </c>
       <c r="G391" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="392" spans="1:8">
@@ -19896,19 +19890,19 @@
         <v>115</v>
       </c>
       <c r="C392" s="13" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="D392" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F392" s="15">
         <v>500</v>
       </c>
       <c r="H392" s="13" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
     </row>
     <row r="393" spans="1:8">
@@ -19948,13 +19942,13 @@
         <v>23</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F394" s="11">
         <v>7500</v>
       </c>
       <c r="G394" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="395" spans="1:8">
@@ -19971,16 +19965,16 @@
         <v>23</v>
       </c>
       <c r="E395" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F395">
         <v>25000</v>
       </c>
       <c r="G395" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H395" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
     </row>
     <row r="396" spans="1:8">
@@ -19997,16 +19991,16 @@
         <v>23</v>
       </c>
       <c r="E396" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F396">
         <v>20000</v>
       </c>
       <c r="G396" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H396" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
     </row>
     <row r="397" spans="1:8">
@@ -20017,19 +20011,19 @@
         <v>115</v>
       </c>
       <c r="C397" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D397" s="10" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F397" s="11">
         <v>5200</v>
       </c>
       <c r="G397" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="398" spans="1:8">
@@ -20040,19 +20034,19 @@
         <v>115</v>
       </c>
       <c r="C398" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="D398" t="s">
         <v>40</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F398" s="11">
         <v>5200</v>
       </c>
       <c r="G398" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="399" spans="1:8">
@@ -20063,19 +20057,19 @@
         <v>115</v>
       </c>
       <c r="C399" t="s">
+        <v>149</v>
+      </c>
+      <c r="D399" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="D399" s="10" t="s">
-        <v>179</v>
-      </c>
       <c r="E399" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F399">
         <v>13515</v>
       </c>
       <c r="G399" s="10" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="400" spans="1:8">
@@ -20161,13 +20155,13 @@
         <v>60</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F403" s="11">
         <v>1100</v>
       </c>
       <c r="G403" s="12" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
     </row>
     <row r="404" spans="1:8">
@@ -20184,16 +20178,16 @@
         <v>60</v>
       </c>
       <c r="E404" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F404">
         <v>8000</v>
       </c>
       <c r="G404" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H404" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
     </row>
     <row r="405" spans="1:8">
@@ -20216,7 +20210,7 @@
         <v>63000</v>
       </c>
       <c r="G405" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
     </row>
     <row r="406" spans="1:8">
@@ -20233,13 +20227,13 @@
         <v>60</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F406" s="11">
         <v>2700</v>
       </c>
       <c r="G406" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="407" spans="1:8">
@@ -20256,16 +20250,16 @@
         <v>60</v>
       </c>
       <c r="E407" s="16" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F407">
         <v>10000</v>
       </c>
       <c r="G407" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H407" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
